--- a/templates/R80302書式/支給申請/03_定額制サービスによる訓練に関する経費助成の内訳(様式第6-3号)※定額制.xlsx
+++ b/templates/R80302書式/支給申請/03_定額制サービスによる訓練に関する経費助成の内訳(様式第6-3号)※定額制.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="68" documentId="13_ncr:1_{97D5BD46-7B48-4514-A0B8-0C020D6B3C7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A39B408-E183-464A-A4F1-F43111DBC59A}"/>
   <bookViews>
-    <workbookView xWindow="44040" yWindow="11220" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22276" windowHeight="13276" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="様式第6-3号 " sheetId="58" r:id="rId1"/>
@@ -2594,7 +2594,7 @@
     <numFmt numFmtId="177" formatCode="yyyy/m/d;@"/>
     <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -4140,6 +4140,529 @@
     <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="2" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="5" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="24" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="5" borderId="58" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="5" borderId="59" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="5" borderId="60" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="19" fillId="0" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="19" fillId="4" borderId="13" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="19" fillId="4" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="19" fillId="4" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="38" fontId="5" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="9" borderId="37" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="9" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="9" borderId="38" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="9" borderId="36" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="9" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="5" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="5" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="5" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="5" borderId="8" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="9" borderId="13" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="9" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="36" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="5" borderId="37" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="5" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="5" borderId="38" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="5" borderId="36" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="5" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="5" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="19" fillId="9" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="19" fillId="9" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="57" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="19" fillId="4" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="19" fillId="4" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="57" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="57" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="38" fontId="19" fillId="4" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -4191,529 +4714,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="19" fillId="4" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="57" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="19" fillId="4" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="19" fillId="4" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="57" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="57" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="10" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="19" fillId="9" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="19" fillId="9" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="36" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="9" borderId="37" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="9" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="9" borderId="38" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="9" borderId="36" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="9" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="5" borderId="37" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="5" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="5" borderId="38" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="5" borderId="36" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="5" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="5" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="9" borderId="13" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="9" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="5" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="5" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="5" borderId="8" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="38" fontId="5" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="10" fillId="5" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="19" fillId="0" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="19" fillId="4" borderId="13" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="19" fillId="4" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="19" fillId="4" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="5" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="24" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="5" borderId="58" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="5" borderId="59" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="5" borderId="60" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="2" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -4960,6 +4960,10 @@
     <mc:Fallback/>
   </mc:AlternateContent>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5310,7 +5314,7 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:JB88"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="46" width="3.1328125" style="1" customWidth="1"/>
     <col min="47" max="47" width="1.3984375" style="1" customWidth="1"/>
@@ -5320,173 +5324,173 @@
     <col min="60" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:67" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:67" ht="17.25" customHeight="1">
       <c r="A1" s="44" t="s">
         <v>164</v>
       </c>
-      <c r="AO1" s="151"/>
-      <c r="AP1" s="151"/>
-      <c r="AQ1" s="151"/>
-      <c r="AR1" s="151"/>
-      <c r="AS1" s="151"/>
-      <c r="AT1" s="151"/>
+      <c r="AO1" s="319"/>
+      <c r="AP1" s="319"/>
+      <c r="AQ1" s="319"/>
+      <c r="AR1" s="319"/>
+      <c r="AS1" s="319"/>
+      <c r="AT1" s="319"/>
     </row>
-    <row r="2" spans="1:67" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="152"/>
-      <c r="B2" s="152"/>
-      <c r="C2" s="152"/>
-      <c r="D2" s="152"/>
-      <c r="E2" s="152"/>
-      <c r="F2" s="152"/>
-      <c r="G2" s="152"/>
-      <c r="H2" s="152"/>
-      <c r="I2" s="152"/>
-      <c r="J2" s="152"/>
-      <c r="K2" s="152"/>
-      <c r="L2" s="152"/>
-      <c r="M2" s="152"/>
-      <c r="AO2" s="151"/>
-      <c r="AP2" s="151"/>
-      <c r="AQ2" s="151"/>
-      <c r="AR2" s="151"/>
-      <c r="AS2" s="151"/>
-      <c r="AT2" s="151"/>
+    <row r="2" spans="1:67" ht="16.5">
+      <c r="A2" s="320"/>
+      <c r="B2" s="320"/>
+      <c r="C2" s="320"/>
+      <c r="D2" s="320"/>
+      <c r="E2" s="320"/>
+      <c r="F2" s="320"/>
+      <c r="G2" s="320"/>
+      <c r="H2" s="320"/>
+      <c r="I2" s="320"/>
+      <c r="J2" s="320"/>
+      <c r="K2" s="320"/>
+      <c r="L2" s="320"/>
+      <c r="M2" s="320"/>
+      <c r="AO2" s="319"/>
+      <c r="AP2" s="319"/>
+      <c r="AQ2" s="319"/>
+      <c r="AR2" s="319"/>
+      <c r="AS2" s="319"/>
+      <c r="AT2" s="319"/>
     </row>
-    <row r="3" spans="1:67" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="153" t="s">
+    <row r="3" spans="1:67" ht="50.25" customHeight="1">
+      <c r="A3" s="321" t="s">
         <v>114</v>
       </c>
-      <c r="B3" s="154"/>
-      <c r="C3" s="154"/>
-      <c r="D3" s="154"/>
-      <c r="E3" s="154"/>
-      <c r="F3" s="154"/>
-      <c r="G3" s="154"/>
-      <c r="H3" s="154"/>
-      <c r="I3" s="154"/>
-      <c r="J3" s="154"/>
-      <c r="K3" s="154"/>
-      <c r="L3" s="154"/>
-      <c r="M3" s="154"/>
-      <c r="N3" s="154"/>
-      <c r="O3" s="154"/>
-      <c r="P3" s="154"/>
-      <c r="Q3" s="154"/>
-      <c r="R3" s="154"/>
-      <c r="S3" s="154"/>
-      <c r="T3" s="154"/>
-      <c r="U3" s="154"/>
-      <c r="V3" s="154"/>
-      <c r="W3" s="154"/>
-      <c r="X3" s="154"/>
-      <c r="Y3" s="154"/>
-      <c r="Z3" s="154"/>
-      <c r="AA3" s="154"/>
-      <c r="AB3" s="154"/>
-      <c r="AC3" s="154"/>
-      <c r="AD3" s="154"/>
-      <c r="AE3" s="154"/>
-      <c r="AF3" s="154"/>
-      <c r="AG3" s="154"/>
-      <c r="AH3" s="154"/>
-      <c r="AI3" s="154"/>
-      <c r="AJ3" s="154"/>
-      <c r="AK3" s="154"/>
-      <c r="AL3" s="154"/>
-      <c r="AM3" s="154"/>
-      <c r="AN3" s="154"/>
-      <c r="AO3" s="154"/>
-      <c r="AP3" s="154"/>
-      <c r="AQ3" s="154"/>
-      <c r="AR3" s="154"/>
-      <c r="AS3" s="154"/>
-      <c r="AT3" s="154"/>
+      <c r="B3" s="322"/>
+      <c r="C3" s="322"/>
+      <c r="D3" s="322"/>
+      <c r="E3" s="322"/>
+      <c r="F3" s="322"/>
+      <c r="G3" s="322"/>
+      <c r="H3" s="322"/>
+      <c r="I3" s="322"/>
+      <c r="J3" s="322"/>
+      <c r="K3" s="322"/>
+      <c r="L3" s="322"/>
+      <c r="M3" s="322"/>
+      <c r="N3" s="322"/>
+      <c r="O3" s="322"/>
+      <c r="P3" s="322"/>
+      <c r="Q3" s="322"/>
+      <c r="R3" s="322"/>
+      <c r="S3" s="322"/>
+      <c r="T3" s="322"/>
+      <c r="U3" s="322"/>
+      <c r="V3" s="322"/>
+      <c r="W3" s="322"/>
+      <c r="X3" s="322"/>
+      <c r="Y3" s="322"/>
+      <c r="Z3" s="322"/>
+      <c r="AA3" s="322"/>
+      <c r="AB3" s="322"/>
+      <c r="AC3" s="322"/>
+      <c r="AD3" s="322"/>
+      <c r="AE3" s="322"/>
+      <c r="AF3" s="322"/>
+      <c r="AG3" s="322"/>
+      <c r="AH3" s="322"/>
+      <c r="AI3" s="322"/>
+      <c r="AJ3" s="322"/>
+      <c r="AK3" s="322"/>
+      <c r="AL3" s="322"/>
+      <c r="AM3" s="322"/>
+      <c r="AN3" s="322"/>
+      <c r="AO3" s="322"/>
+      <c r="AP3" s="322"/>
+      <c r="AQ3" s="322"/>
+      <c r="AR3" s="322"/>
+      <c r="AS3" s="322"/>
+      <c r="AT3" s="322"/>
     </row>
-    <row r="4" spans="1:67" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:67" ht="18.75" customHeight="1" thickBot="1">
       <c r="A4" s="1" t="s">
         <v>137</v>
       </c>
       <c r="AT4" s="45"/>
-      <c r="BE4" s="155" t="s">
+      <c r="BE4" s="323" t="s">
         <v>123</v>
       </c>
-      <c r="BF4" s="156"/>
-      <c r="BG4" s="157"/>
+      <c r="BF4" s="324"/>
+      <c r="BG4" s="325"/>
     </row>
-    <row r="5" spans="1:67" s="5" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:67" s="5" customFormat="1" ht="56.25" customHeight="1">
       <c r="A5" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="158" t="s">
+      <c r="B5" s="326" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="158"/>
-      <c r="D5" s="158"/>
-      <c r="E5" s="158"/>
-      <c r="F5" s="158"/>
-      <c r="G5" s="158"/>
-      <c r="H5" s="158"/>
-      <c r="I5" s="159"/>
-      <c r="J5" s="160"/>
-      <c r="K5" s="161"/>
+      <c r="C5" s="326"/>
+      <c r="D5" s="326"/>
+      <c r="E5" s="326"/>
+      <c r="F5" s="326"/>
+      <c r="G5" s="326"/>
+      <c r="H5" s="326"/>
+      <c r="I5" s="327"/>
+      <c r="J5" s="328"/>
+      <c r="K5" s="329"/>
       <c r="L5" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="M5" s="162" t="s">
+      <c r="M5" s="330" t="s">
         <v>115</v>
       </c>
-      <c r="N5" s="162"/>
-      <c r="O5" s="162"/>
-      <c r="P5" s="162"/>
-      <c r="Q5" s="162"/>
-      <c r="R5" s="162"/>
-      <c r="S5" s="162"/>
-      <c r="T5" s="162"/>
-      <c r="U5" s="162"/>
-      <c r="V5" s="163"/>
-      <c r="W5" s="164"/>
+      <c r="N5" s="330"/>
+      <c r="O5" s="330"/>
+      <c r="P5" s="330"/>
+      <c r="Q5" s="330"/>
+      <c r="R5" s="330"/>
+      <c r="S5" s="330"/>
+      <c r="T5" s="330"/>
+      <c r="U5" s="330"/>
+      <c r="V5" s="331"/>
+      <c r="W5" s="332"/>
       <c r="X5" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="Y5" s="165" t="s">
+      <c r="Y5" s="333" t="s">
         <v>5</v>
       </c>
-      <c r="Z5" s="165"/>
-      <c r="AA5" s="165"/>
-      <c r="AB5" s="165"/>
-      <c r="AC5" s="165"/>
-      <c r="AD5" s="165"/>
-      <c r="AE5" s="165"/>
-      <c r="AF5" s="165"/>
-      <c r="AG5" s="166"/>
-      <c r="AH5" s="172"/>
-      <c r="AI5" s="173"/>
+      <c r="Z5" s="333"/>
+      <c r="AA5" s="333"/>
+      <c r="AB5" s="333"/>
+      <c r="AC5" s="333"/>
+      <c r="AD5" s="333"/>
+      <c r="AE5" s="333"/>
+      <c r="AF5" s="333"/>
+      <c r="AG5" s="334"/>
+      <c r="AH5" s="308"/>
+      <c r="AI5" s="309"/>
       <c r="AJ5" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="AK5" s="174" t="s">
+      <c r="AK5" s="310" t="s">
         <v>163</v>
       </c>
-      <c r="AL5" s="174"/>
-      <c r="AM5" s="174"/>
-      <c r="AN5" s="174"/>
-      <c r="AO5" s="174"/>
-      <c r="AP5" s="174"/>
-      <c r="AQ5" s="174"/>
-      <c r="AR5" s="174"/>
-      <c r="AS5" s="174"/>
-      <c r="AT5" s="175"/>
+      <c r="AL5" s="310"/>
+      <c r="AM5" s="310"/>
+      <c r="AN5" s="310"/>
+      <c r="AO5" s="310"/>
+      <c r="AP5" s="310"/>
+      <c r="AQ5" s="310"/>
+      <c r="AR5" s="310"/>
+      <c r="AS5" s="310"/>
+      <c r="AT5" s="311"/>
       <c r="AU5" s="15"/>
-      <c r="AV5" s="176" t="s">
+      <c r="AV5" s="312" t="s">
         <v>133</v>
       </c>
-      <c r="AW5" s="176"/>
-      <c r="AX5" s="176"/>
-      <c r="AY5" s="176"/>
-      <c r="AZ5" s="176"/>
-      <c r="BA5" s="176"/>
-      <c r="BB5" s="176"/>
-      <c r="BC5" s="176"/>
+      <c r="AW5" s="312"/>
+      <c r="AX5" s="312"/>
+      <c r="AY5" s="312"/>
+      <c r="AZ5" s="312"/>
+      <c r="BA5" s="312"/>
+      <c r="BB5" s="312"/>
+      <c r="BC5" s="312"/>
       <c r="BD5" s="1"/>
       <c r="BE5" s="32"/>
       <c r="BF5" s="32"/>
@@ -5500,76 +5504,76 @@
       <c r="BN5" s="15"/>
       <c r="BO5" s="15"/>
     </row>
-    <row r="6" spans="1:67" s="5" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:67" s="5" customFormat="1" ht="36.75" customHeight="1">
       <c r="A6" s="50">
         <v>2</v>
       </c>
-      <c r="B6" s="177" t="s">
+      <c r="B6" s="313" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="167"/>
-      <c r="D6" s="167"/>
-      <c r="E6" s="167"/>
-      <c r="F6" s="167"/>
-      <c r="G6" s="167"/>
-      <c r="H6" s="167"/>
-      <c r="I6" s="168"/>
-      <c r="J6" s="178"/>
-      <c r="K6" s="178"/>
-      <c r="L6" s="178"/>
-      <c r="M6" s="178"/>
-      <c r="N6" s="178"/>
-      <c r="O6" s="178"/>
-      <c r="P6" s="178"/>
-      <c r="Q6" s="178"/>
-      <c r="R6" s="178"/>
-      <c r="S6" s="178"/>
-      <c r="T6" s="178"/>
-      <c r="U6" s="178"/>
-      <c r="V6" s="178"/>
-      <c r="W6" s="178"/>
+      <c r="C6" s="280"/>
+      <c r="D6" s="280"/>
+      <c r="E6" s="280"/>
+      <c r="F6" s="280"/>
+      <c r="G6" s="280"/>
+      <c r="H6" s="280"/>
+      <c r="I6" s="281"/>
+      <c r="J6" s="314"/>
+      <c r="K6" s="314"/>
+      <c r="L6" s="314"/>
+      <c r="M6" s="314"/>
+      <c r="N6" s="314"/>
+      <c r="O6" s="314"/>
+      <c r="P6" s="314"/>
+      <c r="Q6" s="314"/>
+      <c r="R6" s="314"/>
+      <c r="S6" s="314"/>
+      <c r="T6" s="314"/>
+      <c r="U6" s="314"/>
+      <c r="V6" s="314"/>
+      <c r="W6" s="314"/>
       <c r="X6" s="51">
         <v>3</v>
       </c>
-      <c r="Y6" s="167" t="s">
+      <c r="Y6" s="280" t="s">
         <v>139</v>
       </c>
-      <c r="Z6" s="167"/>
-      <c r="AA6" s="167"/>
-      <c r="AB6" s="167"/>
-      <c r="AC6" s="167"/>
-      <c r="AD6" s="167"/>
-      <c r="AE6" s="167"/>
-      <c r="AF6" s="168"/>
-      <c r="AG6" s="178"/>
-      <c r="AH6" s="178"/>
-      <c r="AI6" s="178"/>
-      <c r="AJ6" s="178"/>
-      <c r="AK6" s="178"/>
-      <c r="AL6" s="178"/>
-      <c r="AM6" s="178"/>
-      <c r="AN6" s="178"/>
-      <c r="AO6" s="178"/>
-      <c r="AP6" s="178"/>
-      <c r="AQ6" s="178"/>
-      <c r="AR6" s="178"/>
-      <c r="AS6" s="178"/>
-      <c r="AT6" s="179"/>
+      <c r="Z6" s="280"/>
+      <c r="AA6" s="280"/>
+      <c r="AB6" s="280"/>
+      <c r="AC6" s="280"/>
+      <c r="AD6" s="280"/>
+      <c r="AE6" s="280"/>
+      <c r="AF6" s="281"/>
+      <c r="AG6" s="314"/>
+      <c r="AH6" s="314"/>
+      <c r="AI6" s="314"/>
+      <c r="AJ6" s="314"/>
+      <c r="AK6" s="314"/>
+      <c r="AL6" s="314"/>
+      <c r="AM6" s="314"/>
+      <c r="AN6" s="314"/>
+      <c r="AO6" s="314"/>
+      <c r="AP6" s="314"/>
+      <c r="AQ6" s="314"/>
+      <c r="AR6" s="314"/>
+      <c r="AS6" s="314"/>
+      <c r="AT6" s="315"/>
       <c r="AU6" s="9"/>
       <c r="AV6" s="31"/>
-      <c r="AW6" s="180" t="s">
+      <c r="AW6" s="316" t="s">
         <v>140</v>
       </c>
-      <c r="AX6" s="181"/>
+      <c r="AX6" s="317"/>
       <c r="AY6" s="34" t="s">
         <v>134</v>
       </c>
-      <c r="AZ6" s="180" t="s">
+      <c r="AZ6" s="316" t="s">
         <v>135</v>
       </c>
-      <c r="BA6" s="181"/>
-      <c r="BB6" s="181"/>
-      <c r="BC6" s="182"/>
+      <c r="BA6" s="317"/>
+      <c r="BB6" s="317"/>
+      <c r="BC6" s="318"/>
       <c r="BD6" s="1"/>
       <c r="BE6" s="1">
         <v>2023</v>
@@ -5582,65 +5586,65 @@
       </c>
       <c r="BH6" s="19"/>
     </row>
-    <row r="7" spans="1:67" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:67" ht="36.75" customHeight="1">
       <c r="A7" s="52">
         <v>4</v>
       </c>
-      <c r="B7" s="167" t="s">
+      <c r="B7" s="280" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="167"/>
-      <c r="D7" s="167"/>
-      <c r="E7" s="167"/>
-      <c r="F7" s="167"/>
-      <c r="G7" s="167"/>
-      <c r="H7" s="167"/>
-      <c r="I7" s="168"/>
-      <c r="J7" s="169"/>
-      <c r="K7" s="169"/>
-      <c r="L7" s="169"/>
-      <c r="M7" s="169"/>
-      <c r="N7" s="169"/>
-      <c r="O7" s="169"/>
-      <c r="P7" s="169"/>
-      <c r="Q7" s="169"/>
-      <c r="R7" s="169"/>
-      <c r="S7" s="169"/>
-      <c r="T7" s="169"/>
-      <c r="U7" s="169"/>
-      <c r="V7" s="170" t="s">
+      <c r="C7" s="280"/>
+      <c r="D7" s="280"/>
+      <c r="E7" s="280"/>
+      <c r="F7" s="280"/>
+      <c r="G7" s="280"/>
+      <c r="H7" s="280"/>
+      <c r="I7" s="281"/>
+      <c r="J7" s="305"/>
+      <c r="K7" s="305"/>
+      <c r="L7" s="305"/>
+      <c r="M7" s="305"/>
+      <c r="N7" s="305"/>
+      <c r="O7" s="305"/>
+      <c r="P7" s="305"/>
+      <c r="Q7" s="305"/>
+      <c r="R7" s="305"/>
+      <c r="S7" s="305"/>
+      <c r="T7" s="305"/>
+      <c r="U7" s="305"/>
+      <c r="V7" s="306" t="s">
         <v>10</v>
       </c>
-      <c r="W7" s="170"/>
+      <c r="W7" s="306"/>
       <c r="X7" s="51">
         <v>5</v>
       </c>
-      <c r="Y7" s="167" t="s">
+      <c r="Y7" s="280" t="s">
         <v>122</v>
       </c>
-      <c r="Z7" s="167"/>
-      <c r="AA7" s="167"/>
-      <c r="AB7" s="167"/>
-      <c r="AC7" s="167"/>
-      <c r="AD7" s="167"/>
-      <c r="AE7" s="167"/>
-      <c r="AF7" s="168"/>
-      <c r="AG7" s="169"/>
-      <c r="AH7" s="169"/>
-      <c r="AI7" s="169"/>
-      <c r="AJ7" s="169"/>
-      <c r="AK7" s="169"/>
-      <c r="AL7" s="169"/>
-      <c r="AM7" s="169"/>
-      <c r="AN7" s="169"/>
-      <c r="AO7" s="169"/>
-      <c r="AP7" s="169"/>
-      <c r="AQ7" s="169"/>
-      <c r="AR7" s="169"/>
-      <c r="AS7" s="170" t="s">
+      <c r="Z7" s="280"/>
+      <c r="AA7" s="280"/>
+      <c r="AB7" s="280"/>
+      <c r="AC7" s="280"/>
+      <c r="AD7" s="280"/>
+      <c r="AE7" s="280"/>
+      <c r="AF7" s="281"/>
+      <c r="AG7" s="305"/>
+      <c r="AH7" s="305"/>
+      <c r="AI7" s="305"/>
+      <c r="AJ7" s="305"/>
+      <c r="AK7" s="305"/>
+      <c r="AL7" s="305"/>
+      <c r="AM7" s="305"/>
+      <c r="AN7" s="305"/>
+      <c r="AO7" s="305"/>
+      <c r="AP7" s="305"/>
+      <c r="AQ7" s="305"/>
+      <c r="AR7" s="305"/>
+      <c r="AS7" s="306" t="s">
         <v>10</v>
       </c>
-      <c r="AT7" s="171"/>
+      <c r="AT7" s="307"/>
       <c r="AV7" s="17"/>
       <c r="AW7" s="33" t="s">
         <v>13</v>
@@ -5675,70 +5679,70 @@
       </c>
       <c r="BH7" s="20"/>
     </row>
-    <row r="8" spans="1:67" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:67" ht="36.75" customHeight="1">
       <c r="A8" s="52">
         <v>6</v>
       </c>
-      <c r="B8" s="167" t="s">
+      <c r="B8" s="280" t="s">
         <v>121</v>
       </c>
-      <c r="C8" s="167"/>
-      <c r="D8" s="167"/>
-      <c r="E8" s="167"/>
-      <c r="F8" s="167"/>
-      <c r="G8" s="167"/>
-      <c r="H8" s="167"/>
-      <c r="I8" s="168"/>
-      <c r="J8" s="197" t="s">
+      <c r="C8" s="280"/>
+      <c r="D8" s="280"/>
+      <c r="E8" s="280"/>
+      <c r="F8" s="280"/>
+      <c r="G8" s="280"/>
+      <c r="H8" s="280"/>
+      <c r="I8" s="281"/>
+      <c r="J8" s="302" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="198"/>
-      <c r="L8" s="199"/>
-      <c r="M8" s="193"/>
-      <c r="N8" s="183"/>
-      <c r="O8" s="183"/>
-      <c r="P8" s="183"/>
+      <c r="K8" s="303"/>
+      <c r="L8" s="304"/>
+      <c r="M8" s="298"/>
+      <c r="N8" s="292"/>
+      <c r="O8" s="292"/>
+      <c r="P8" s="292"/>
       <c r="Q8" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="R8" s="183"/>
-      <c r="S8" s="183"/>
-      <c r="T8" s="183"/>
-      <c r="U8" s="183"/>
+      <c r="R8" s="292"/>
+      <c r="S8" s="292"/>
+      <c r="T8" s="292"/>
+      <c r="U8" s="292"/>
       <c r="V8" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="W8" s="183"/>
-      <c r="X8" s="183"/>
-      <c r="Y8" s="183"/>
-      <c r="Z8" s="183"/>
+      <c r="W8" s="292"/>
+      <c r="X8" s="292"/>
+      <c r="Y8" s="292"/>
+      <c r="Z8" s="292"/>
       <c r="AA8" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="AB8" s="197" t="s">
+      <c r="AB8" s="302" t="s">
         <v>17</v>
       </c>
-      <c r="AC8" s="198"/>
-      <c r="AD8" s="198"/>
-      <c r="AE8" s="199"/>
-      <c r="AF8" s="193"/>
-      <c r="AG8" s="183"/>
-      <c r="AH8" s="183"/>
-      <c r="AI8" s="183"/>
+      <c r="AC8" s="303"/>
+      <c r="AD8" s="303"/>
+      <c r="AE8" s="304"/>
+      <c r="AF8" s="298"/>
+      <c r="AG8" s="292"/>
+      <c r="AH8" s="292"/>
+      <c r="AI8" s="292"/>
       <c r="AJ8" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="AK8" s="183"/>
-      <c r="AL8" s="183"/>
-      <c r="AM8" s="183"/>
-      <c r="AN8" s="183"/>
+      <c r="AK8" s="292"/>
+      <c r="AL8" s="292"/>
+      <c r="AM8" s="292"/>
+      <c r="AN8" s="292"/>
       <c r="AO8" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="AP8" s="183"/>
-      <c r="AQ8" s="183"/>
-      <c r="AR8" s="183"/>
-      <c r="AS8" s="183"/>
+      <c r="AP8" s="292"/>
+      <c r="AQ8" s="292"/>
+      <c r="AR8" s="292"/>
+      <c r="AS8" s="292"/>
       <c r="AT8" s="54" t="s">
         <v>16</v>
       </c>
@@ -5783,70 +5787,70 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:67" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:67" ht="36.75" customHeight="1">
       <c r="A9" s="50">
         <v>7</v>
       </c>
-      <c r="B9" s="167" t="s">
+      <c r="B9" s="280" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="167"/>
-      <c r="D9" s="167"/>
-      <c r="E9" s="167"/>
-      <c r="F9" s="167"/>
-      <c r="G9" s="167"/>
-      <c r="H9" s="167"/>
-      <c r="I9" s="168"/>
-      <c r="J9" s="194" t="s">
+      <c r="C9" s="280"/>
+      <c r="D9" s="280"/>
+      <c r="E9" s="280"/>
+      <c r="F9" s="280"/>
+      <c r="G9" s="280"/>
+      <c r="H9" s="280"/>
+      <c r="I9" s="281"/>
+      <c r="J9" s="299" t="s">
         <v>13</v>
       </c>
-      <c r="K9" s="195"/>
-      <c r="L9" s="196"/>
-      <c r="M9" s="193"/>
-      <c r="N9" s="183"/>
-      <c r="O9" s="183"/>
-      <c r="P9" s="183"/>
+      <c r="K9" s="300"/>
+      <c r="L9" s="301"/>
+      <c r="M9" s="298"/>
+      <c r="N9" s="292"/>
+      <c r="O9" s="292"/>
+      <c r="P9" s="292"/>
       <c r="Q9" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="R9" s="183"/>
-      <c r="S9" s="183"/>
-      <c r="T9" s="183"/>
-      <c r="U9" s="183"/>
+      <c r="R9" s="292"/>
+      <c r="S9" s="292"/>
+      <c r="T9" s="292"/>
+      <c r="U9" s="292"/>
       <c r="V9" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="W9" s="183"/>
-      <c r="X9" s="183"/>
-      <c r="Y9" s="183"/>
-      <c r="Z9" s="183"/>
+      <c r="W9" s="292"/>
+      <c r="X9" s="292"/>
+      <c r="Y9" s="292"/>
+      <c r="Z9" s="292"/>
       <c r="AA9" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="AB9" s="197" t="s">
+      <c r="AB9" s="302" t="s">
         <v>17</v>
       </c>
-      <c r="AC9" s="198"/>
-      <c r="AD9" s="198"/>
-      <c r="AE9" s="199"/>
-      <c r="AF9" s="193"/>
-      <c r="AG9" s="183"/>
-      <c r="AH9" s="183"/>
-      <c r="AI9" s="183"/>
+      <c r="AC9" s="303"/>
+      <c r="AD9" s="303"/>
+      <c r="AE9" s="304"/>
+      <c r="AF9" s="298"/>
+      <c r="AG9" s="292"/>
+      <c r="AH9" s="292"/>
+      <c r="AI9" s="292"/>
       <c r="AJ9" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="AK9" s="183"/>
-      <c r="AL9" s="183"/>
-      <c r="AM9" s="183"/>
-      <c r="AN9" s="183"/>
+      <c r="AK9" s="292"/>
+      <c r="AL9" s="292"/>
+      <c r="AM9" s="292"/>
+      <c r="AN9" s="292"/>
       <c r="AO9" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="AP9" s="183"/>
-      <c r="AQ9" s="183"/>
-      <c r="AR9" s="183"/>
-      <c r="AS9" s="183"/>
+      <c r="AP9" s="292"/>
+      <c r="AQ9" s="292"/>
+      <c r="AR9" s="292"/>
+      <c r="AS9" s="292"/>
       <c r="AT9" s="54" t="s">
         <v>16</v>
       </c>
@@ -5880,20 +5884,20 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:67" ht="33" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:67" ht="33" customHeight="1">
       <c r="A10" s="55">
         <v>8</v>
       </c>
-      <c r="B10" s="184" t="s">
+      <c r="B10" s="293" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="184"/>
-      <c r="D10" s="184"/>
-      <c r="E10" s="184"/>
-      <c r="F10" s="184"/>
-      <c r="G10" s="184"/>
-      <c r="H10" s="184"/>
-      <c r="I10" s="184"/>
+      <c r="C10" s="293"/>
+      <c r="D10" s="293"/>
+      <c r="E10" s="293"/>
+      <c r="F10" s="293"/>
+      <c r="G10" s="293"/>
+      <c r="H10" s="293"/>
+      <c r="I10" s="293"/>
       <c r="J10" s="56"/>
       <c r="K10" s="57"/>
       <c r="L10" s="57"/>
@@ -5941,7 +5945,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:67" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:67" ht="9.75" customHeight="1">
       <c r="A11" s="62"/>
       <c r="B11" s="63"/>
       <c r="C11" s="63"/>
@@ -6006,55 +6010,55 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:67" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="185" t="s">
+    <row r="12" spans="1:67" ht="18.75" customHeight="1">
+      <c r="A12" s="294" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="186"/>
-      <c r="C12" s="186"/>
-      <c r="D12" s="186"/>
-      <c r="E12" s="186"/>
-      <c r="F12" s="186"/>
-      <c r="G12" s="186"/>
-      <c r="H12" s="186"/>
-      <c r="I12" s="186"/>
-      <c r="J12" s="186"/>
-      <c r="K12" s="186"/>
-      <c r="L12" s="186"/>
-      <c r="M12" s="186"/>
-      <c r="N12" s="186"/>
-      <c r="O12" s="186"/>
-      <c r="P12" s="186"/>
-      <c r="Q12" s="186"/>
-      <c r="R12" s="186"/>
-      <c r="S12" s="186"/>
-      <c r="T12" s="186"/>
-      <c r="U12" s="186"/>
-      <c r="V12" s="186"/>
-      <c r="W12" s="186"/>
-      <c r="X12" s="186"/>
-      <c r="Y12" s="186"/>
-      <c r="Z12" s="186"/>
-      <c r="AA12" s="186"/>
-      <c r="AB12" s="186"/>
-      <c r="AC12" s="186"/>
-      <c r="AD12" s="186"/>
-      <c r="AE12" s="186"/>
-      <c r="AF12" s="186"/>
-      <c r="AG12" s="186"/>
-      <c r="AH12" s="186"/>
-      <c r="AI12" s="186"/>
-      <c r="AJ12" s="186"/>
-      <c r="AK12" s="186"/>
-      <c r="AL12" s="186"/>
-      <c r="AM12" s="186"/>
-      <c r="AN12" s="186"/>
-      <c r="AO12" s="186"/>
-      <c r="AP12" s="186"/>
-      <c r="AQ12" s="186"/>
-      <c r="AR12" s="186"/>
-      <c r="AS12" s="186"/>
-      <c r="AT12" s="187"/>
+      <c r="B12" s="295"/>
+      <c r="C12" s="295"/>
+      <c r="D12" s="295"/>
+      <c r="E12" s="295"/>
+      <c r="F12" s="295"/>
+      <c r="G12" s="295"/>
+      <c r="H12" s="295"/>
+      <c r="I12" s="295"/>
+      <c r="J12" s="295"/>
+      <c r="K12" s="295"/>
+      <c r="L12" s="295"/>
+      <c r="M12" s="295"/>
+      <c r="N12" s="295"/>
+      <c r="O12" s="295"/>
+      <c r="P12" s="295"/>
+      <c r="Q12" s="295"/>
+      <c r="R12" s="295"/>
+      <c r="S12" s="295"/>
+      <c r="T12" s="295"/>
+      <c r="U12" s="295"/>
+      <c r="V12" s="295"/>
+      <c r="W12" s="295"/>
+      <c r="X12" s="295"/>
+      <c r="Y12" s="295"/>
+      <c r="Z12" s="295"/>
+      <c r="AA12" s="295"/>
+      <c r="AB12" s="295"/>
+      <c r="AC12" s="295"/>
+      <c r="AD12" s="295"/>
+      <c r="AE12" s="295"/>
+      <c r="AF12" s="295"/>
+      <c r="AG12" s="295"/>
+      <c r="AH12" s="295"/>
+      <c r="AI12" s="295"/>
+      <c r="AJ12" s="295"/>
+      <c r="AK12" s="295"/>
+      <c r="AL12" s="295"/>
+      <c r="AM12" s="295"/>
+      <c r="AN12" s="295"/>
+      <c r="AO12" s="295"/>
+      <c r="AP12" s="295"/>
+      <c r="AQ12" s="295"/>
+      <c r="AR12" s="295"/>
+      <c r="AS12" s="295"/>
+      <c r="AT12" s="296"/>
       <c r="AW12" s="16"/>
       <c r="AX12" s="16"/>
       <c r="AY12" s="16"/>
@@ -6073,58 +6077,58 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:67" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:67" ht="39.75" customHeight="1">
       <c r="A13" s="70"/>
       <c r="B13" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="168" t="s">
+      <c r="C13" s="281" t="s">
         <v>125</v>
       </c>
-      <c r="D13" s="188"/>
-      <c r="E13" s="188"/>
-      <c r="F13" s="188"/>
-      <c r="G13" s="188"/>
-      <c r="H13" s="188"/>
-      <c r="I13" s="188"/>
-      <c r="J13" s="188"/>
-      <c r="K13" s="188"/>
-      <c r="L13" s="188"/>
-      <c r="M13" s="188"/>
-      <c r="N13" s="188"/>
-      <c r="O13" s="188"/>
-      <c r="P13" s="188"/>
-      <c r="Q13" s="188"/>
-      <c r="R13" s="188"/>
-      <c r="S13" s="188"/>
-      <c r="T13" s="188"/>
-      <c r="U13" s="188"/>
-      <c r="V13" s="188"/>
-      <c r="W13" s="188"/>
-      <c r="X13" s="188"/>
-      <c r="Y13" s="188"/>
-      <c r="Z13" s="188"/>
-      <c r="AA13" s="188"/>
-      <c r="AB13" s="189"/>
-      <c r="AC13" s="189"/>
-      <c r="AD13" s="189"/>
-      <c r="AE13" s="189"/>
-      <c r="AF13" s="189"/>
-      <c r="AG13" s="189"/>
-      <c r="AH13" s="189"/>
-      <c r="AI13" s="189"/>
-      <c r="AJ13" s="189"/>
-      <c r="AK13" s="189"/>
-      <c r="AL13" s="189"/>
-      <c r="AM13" s="189"/>
-      <c r="AN13" s="189"/>
-      <c r="AO13" s="189"/>
-      <c r="AP13" s="189"/>
-      <c r="AQ13" s="190"/>
-      <c r="AR13" s="191" t="s">
+      <c r="D13" s="297"/>
+      <c r="E13" s="297"/>
+      <c r="F13" s="297"/>
+      <c r="G13" s="297"/>
+      <c r="H13" s="297"/>
+      <c r="I13" s="297"/>
+      <c r="J13" s="297"/>
+      <c r="K13" s="297"/>
+      <c r="L13" s="297"/>
+      <c r="M13" s="297"/>
+      <c r="N13" s="297"/>
+      <c r="O13" s="297"/>
+      <c r="P13" s="297"/>
+      <c r="Q13" s="297"/>
+      <c r="R13" s="297"/>
+      <c r="S13" s="297"/>
+      <c r="T13" s="297"/>
+      <c r="U13" s="297"/>
+      <c r="V13" s="297"/>
+      <c r="W13" s="297"/>
+      <c r="X13" s="297"/>
+      <c r="Y13" s="297"/>
+      <c r="Z13" s="297"/>
+      <c r="AA13" s="297"/>
+      <c r="AB13" s="278"/>
+      <c r="AC13" s="278"/>
+      <c r="AD13" s="278"/>
+      <c r="AE13" s="278"/>
+      <c r="AF13" s="278"/>
+      <c r="AG13" s="278"/>
+      <c r="AH13" s="278"/>
+      <c r="AI13" s="278"/>
+      <c r="AJ13" s="278"/>
+      <c r="AK13" s="278"/>
+      <c r="AL13" s="278"/>
+      <c r="AM13" s="278"/>
+      <c r="AN13" s="278"/>
+      <c r="AO13" s="278"/>
+      <c r="AP13" s="278"/>
+      <c r="AQ13" s="279"/>
+      <c r="AR13" s="273" t="s">
         <v>28</v>
       </c>
-      <c r="AS13" s="192"/>
+      <c r="AS13" s="274"/>
       <c r="AT13" s="72"/>
       <c r="AW13" s="16"/>
       <c r="AX13" s="16"/>
@@ -6138,60 +6142,60 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:67" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:67" ht="21" customHeight="1">
       <c r="A14" s="70"/>
-      <c r="B14" s="201" t="s">
+      <c r="B14" s="282" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="204" t="s">
+      <c r="C14" s="285" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="204"/>
-      <c r="E14" s="204"/>
-      <c r="F14" s="204"/>
-      <c r="G14" s="204"/>
-      <c r="H14" s="204"/>
-      <c r="I14" s="205"/>
-      <c r="J14" s="210" t="s">
+      <c r="D14" s="285"/>
+      <c r="E14" s="285"/>
+      <c r="F14" s="285"/>
+      <c r="G14" s="285"/>
+      <c r="H14" s="285"/>
+      <c r="I14" s="286"/>
+      <c r="J14" s="291" t="s">
         <v>31</v>
       </c>
-      <c r="K14" s="210"/>
-      <c r="L14" s="210"/>
-      <c r="M14" s="210"/>
-      <c r="N14" s="210"/>
-      <c r="O14" s="210"/>
-      <c r="P14" s="210"/>
-      <c r="Q14" s="210"/>
-      <c r="R14" s="210"/>
-      <c r="S14" s="210"/>
-      <c r="T14" s="210"/>
-      <c r="U14" s="210"/>
-      <c r="V14" s="210"/>
-      <c r="W14" s="210"/>
-      <c r="X14" s="210"/>
-      <c r="Y14" s="210"/>
-      <c r="Z14" s="210"/>
-      <c r="AA14" s="210"/>
-      <c r="AB14" s="210" t="s">
+      <c r="K14" s="291"/>
+      <c r="L14" s="291"/>
+      <c r="M14" s="291"/>
+      <c r="N14" s="291"/>
+      <c r="O14" s="291"/>
+      <c r="P14" s="291"/>
+      <c r="Q14" s="291"/>
+      <c r="R14" s="291"/>
+      <c r="S14" s="291"/>
+      <c r="T14" s="291"/>
+      <c r="U14" s="291"/>
+      <c r="V14" s="291"/>
+      <c r="W14" s="291"/>
+      <c r="X14" s="291"/>
+      <c r="Y14" s="291"/>
+      <c r="Z14" s="291"/>
+      <c r="AA14" s="291"/>
+      <c r="AB14" s="291" t="s">
         <v>30</v>
       </c>
-      <c r="AC14" s="210"/>
-      <c r="AD14" s="210"/>
-      <c r="AE14" s="210"/>
-      <c r="AF14" s="210"/>
-      <c r="AG14" s="210"/>
-      <c r="AH14" s="210"/>
-      <c r="AI14" s="210"/>
-      <c r="AJ14" s="210"/>
-      <c r="AK14" s="210"/>
-      <c r="AL14" s="210"/>
-      <c r="AM14" s="210"/>
-      <c r="AN14" s="210"/>
-      <c r="AO14" s="210"/>
-      <c r="AP14" s="210"/>
-      <c r="AQ14" s="210"/>
-      <c r="AR14" s="210"/>
-      <c r="AS14" s="210"/>
+      <c r="AC14" s="291"/>
+      <c r="AD14" s="291"/>
+      <c r="AE14" s="291"/>
+      <c r="AF14" s="291"/>
+      <c r="AG14" s="291"/>
+      <c r="AH14" s="291"/>
+      <c r="AI14" s="291"/>
+      <c r="AJ14" s="291"/>
+      <c r="AK14" s="291"/>
+      <c r="AL14" s="291"/>
+      <c r="AM14" s="291"/>
+      <c r="AN14" s="291"/>
+      <c r="AO14" s="291"/>
+      <c r="AP14" s="291"/>
+      <c r="AQ14" s="291"/>
+      <c r="AR14" s="291"/>
+      <c r="AS14" s="291"/>
       <c r="AT14" s="72"/>
       <c r="AW14" s="24"/>
       <c r="AX14" s="16"/>
@@ -6211,54 +6215,54 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:67" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:67" ht="39.75" customHeight="1">
       <c r="A15" s="70"/>
-      <c r="B15" s="202"/>
-      <c r="C15" s="206"/>
-      <c r="D15" s="206"/>
-      <c r="E15" s="206"/>
-      <c r="F15" s="206"/>
-      <c r="G15" s="206"/>
-      <c r="H15" s="206"/>
-      <c r="I15" s="207"/>
-      <c r="J15" s="200"/>
-      <c r="K15" s="200"/>
-      <c r="L15" s="200"/>
-      <c r="M15" s="200"/>
-      <c r="N15" s="200"/>
-      <c r="O15" s="200"/>
-      <c r="P15" s="200"/>
-      <c r="Q15" s="200"/>
-      <c r="R15" s="200"/>
-      <c r="S15" s="200"/>
-      <c r="T15" s="200"/>
-      <c r="U15" s="200"/>
-      <c r="V15" s="200"/>
-      <c r="W15" s="200"/>
-      <c r="X15" s="200"/>
-      <c r="Y15" s="200"/>
-      <c r="Z15" s="200"/>
-      <c r="AA15" s="200"/>
-      <c r="AB15" s="189"/>
-      <c r="AC15" s="189"/>
-      <c r="AD15" s="189"/>
-      <c r="AE15" s="189"/>
-      <c r="AF15" s="189"/>
-      <c r="AG15" s="189"/>
-      <c r="AH15" s="189"/>
-      <c r="AI15" s="189"/>
-      <c r="AJ15" s="189"/>
-      <c r="AK15" s="189"/>
-      <c r="AL15" s="189"/>
-      <c r="AM15" s="189"/>
-      <c r="AN15" s="189"/>
-      <c r="AO15" s="189"/>
-      <c r="AP15" s="189"/>
-      <c r="AQ15" s="190"/>
-      <c r="AR15" s="191" t="s">
+      <c r="B15" s="283"/>
+      <c r="C15" s="287"/>
+      <c r="D15" s="287"/>
+      <c r="E15" s="287"/>
+      <c r="F15" s="287"/>
+      <c r="G15" s="287"/>
+      <c r="H15" s="287"/>
+      <c r="I15" s="288"/>
+      <c r="J15" s="277"/>
+      <c r="K15" s="277"/>
+      <c r="L15" s="277"/>
+      <c r="M15" s="277"/>
+      <c r="N15" s="277"/>
+      <c r="O15" s="277"/>
+      <c r="P15" s="277"/>
+      <c r="Q15" s="277"/>
+      <c r="R15" s="277"/>
+      <c r="S15" s="277"/>
+      <c r="T15" s="277"/>
+      <c r="U15" s="277"/>
+      <c r="V15" s="277"/>
+      <c r="W15" s="277"/>
+      <c r="X15" s="277"/>
+      <c r="Y15" s="277"/>
+      <c r="Z15" s="277"/>
+      <c r="AA15" s="277"/>
+      <c r="AB15" s="278"/>
+      <c r="AC15" s="278"/>
+      <c r="AD15" s="278"/>
+      <c r="AE15" s="278"/>
+      <c r="AF15" s="278"/>
+      <c r="AG15" s="278"/>
+      <c r="AH15" s="278"/>
+      <c r="AI15" s="278"/>
+      <c r="AJ15" s="278"/>
+      <c r="AK15" s="278"/>
+      <c r="AL15" s="278"/>
+      <c r="AM15" s="278"/>
+      <c r="AN15" s="278"/>
+      <c r="AO15" s="278"/>
+      <c r="AP15" s="278"/>
+      <c r="AQ15" s="279"/>
+      <c r="AR15" s="273" t="s">
         <v>28</v>
       </c>
-      <c r="AS15" s="192"/>
+      <c r="AS15" s="274"/>
       <c r="AT15" s="72"/>
       <c r="AW15" s="16"/>
       <c r="AY15" s="16"/>
@@ -6277,54 +6281,54 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:67" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:67" ht="39.75" customHeight="1">
       <c r="A16" s="70"/>
-      <c r="B16" s="202"/>
-      <c r="C16" s="206"/>
-      <c r="D16" s="206"/>
-      <c r="E16" s="206"/>
-      <c r="F16" s="206"/>
-      <c r="G16" s="206"/>
-      <c r="H16" s="206"/>
-      <c r="I16" s="207"/>
-      <c r="J16" s="200"/>
-      <c r="K16" s="200"/>
-      <c r="L16" s="200"/>
-      <c r="M16" s="200"/>
-      <c r="N16" s="200"/>
-      <c r="O16" s="200"/>
-      <c r="P16" s="200"/>
-      <c r="Q16" s="200"/>
-      <c r="R16" s="200"/>
-      <c r="S16" s="200"/>
-      <c r="T16" s="200"/>
-      <c r="U16" s="200"/>
-      <c r="V16" s="200"/>
-      <c r="W16" s="200"/>
-      <c r="X16" s="200"/>
-      <c r="Y16" s="200"/>
-      <c r="Z16" s="200"/>
-      <c r="AA16" s="200"/>
-      <c r="AB16" s="189"/>
-      <c r="AC16" s="189"/>
-      <c r="AD16" s="189"/>
-      <c r="AE16" s="189"/>
-      <c r="AF16" s="189"/>
-      <c r="AG16" s="189"/>
-      <c r="AH16" s="189"/>
-      <c r="AI16" s="189"/>
-      <c r="AJ16" s="189"/>
-      <c r="AK16" s="189"/>
-      <c r="AL16" s="189"/>
-      <c r="AM16" s="189"/>
-      <c r="AN16" s="189"/>
-      <c r="AO16" s="189"/>
-      <c r="AP16" s="189"/>
-      <c r="AQ16" s="190"/>
-      <c r="AR16" s="191" t="s">
+      <c r="B16" s="283"/>
+      <c r="C16" s="287"/>
+      <c r="D16" s="287"/>
+      <c r="E16" s="287"/>
+      <c r="F16" s="287"/>
+      <c r="G16" s="287"/>
+      <c r="H16" s="287"/>
+      <c r="I16" s="288"/>
+      <c r="J16" s="277"/>
+      <c r="K16" s="277"/>
+      <c r="L16" s="277"/>
+      <c r="M16" s="277"/>
+      <c r="N16" s="277"/>
+      <c r="O16" s="277"/>
+      <c r="P16" s="277"/>
+      <c r="Q16" s="277"/>
+      <c r="R16" s="277"/>
+      <c r="S16" s="277"/>
+      <c r="T16" s="277"/>
+      <c r="U16" s="277"/>
+      <c r="V16" s="277"/>
+      <c r="W16" s="277"/>
+      <c r="X16" s="277"/>
+      <c r="Y16" s="277"/>
+      <c r="Z16" s="277"/>
+      <c r="AA16" s="277"/>
+      <c r="AB16" s="278"/>
+      <c r="AC16" s="278"/>
+      <c r="AD16" s="278"/>
+      <c r="AE16" s="278"/>
+      <c r="AF16" s="278"/>
+      <c r="AG16" s="278"/>
+      <c r="AH16" s="278"/>
+      <c r="AI16" s="278"/>
+      <c r="AJ16" s="278"/>
+      <c r="AK16" s="278"/>
+      <c r="AL16" s="278"/>
+      <c r="AM16" s="278"/>
+      <c r="AN16" s="278"/>
+      <c r="AO16" s="278"/>
+      <c r="AP16" s="278"/>
+      <c r="AQ16" s="279"/>
+      <c r="AR16" s="273" t="s">
         <v>28</v>
       </c>
-      <c r="AS16" s="192"/>
+      <c r="AS16" s="274"/>
       <c r="AT16" s="72"/>
       <c r="AW16" s="16"/>
       <c r="AX16" s="16"/>
@@ -6335,54 +6339,54 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:59" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:59" ht="39.75" customHeight="1">
       <c r="A17" s="70"/>
-      <c r="B17" s="203"/>
-      <c r="C17" s="208"/>
-      <c r="D17" s="208"/>
-      <c r="E17" s="208"/>
-      <c r="F17" s="208"/>
-      <c r="G17" s="208"/>
-      <c r="H17" s="208"/>
-      <c r="I17" s="209"/>
-      <c r="J17" s="200"/>
-      <c r="K17" s="200"/>
-      <c r="L17" s="200"/>
-      <c r="M17" s="200"/>
-      <c r="N17" s="200"/>
-      <c r="O17" s="200"/>
-      <c r="P17" s="200"/>
-      <c r="Q17" s="200"/>
-      <c r="R17" s="200"/>
-      <c r="S17" s="200"/>
-      <c r="T17" s="200"/>
-      <c r="U17" s="200"/>
-      <c r="V17" s="200"/>
-      <c r="W17" s="200"/>
-      <c r="X17" s="200"/>
-      <c r="Y17" s="200"/>
-      <c r="Z17" s="200"/>
-      <c r="AA17" s="200"/>
-      <c r="AB17" s="189"/>
-      <c r="AC17" s="189"/>
-      <c r="AD17" s="189"/>
-      <c r="AE17" s="189"/>
-      <c r="AF17" s="189"/>
-      <c r="AG17" s="189"/>
-      <c r="AH17" s="189"/>
-      <c r="AI17" s="189"/>
-      <c r="AJ17" s="189"/>
-      <c r="AK17" s="189"/>
-      <c r="AL17" s="189"/>
-      <c r="AM17" s="189"/>
-      <c r="AN17" s="189"/>
-      <c r="AO17" s="189"/>
-      <c r="AP17" s="189"/>
-      <c r="AQ17" s="190"/>
-      <c r="AR17" s="191" t="s">
+      <c r="B17" s="284"/>
+      <c r="C17" s="289"/>
+      <c r="D17" s="289"/>
+      <c r="E17" s="289"/>
+      <c r="F17" s="289"/>
+      <c r="G17" s="289"/>
+      <c r="H17" s="289"/>
+      <c r="I17" s="290"/>
+      <c r="J17" s="277"/>
+      <c r="K17" s="277"/>
+      <c r="L17" s="277"/>
+      <c r="M17" s="277"/>
+      <c r="N17" s="277"/>
+      <c r="O17" s="277"/>
+      <c r="P17" s="277"/>
+      <c r="Q17" s="277"/>
+      <c r="R17" s="277"/>
+      <c r="S17" s="277"/>
+      <c r="T17" s="277"/>
+      <c r="U17" s="277"/>
+      <c r="V17" s="277"/>
+      <c r="W17" s="277"/>
+      <c r="X17" s="277"/>
+      <c r="Y17" s="277"/>
+      <c r="Z17" s="277"/>
+      <c r="AA17" s="277"/>
+      <c r="AB17" s="278"/>
+      <c r="AC17" s="278"/>
+      <c r="AD17" s="278"/>
+      <c r="AE17" s="278"/>
+      <c r="AF17" s="278"/>
+      <c r="AG17" s="278"/>
+      <c r="AH17" s="278"/>
+      <c r="AI17" s="278"/>
+      <c r="AJ17" s="278"/>
+      <c r="AK17" s="278"/>
+      <c r="AL17" s="278"/>
+      <c r="AM17" s="278"/>
+      <c r="AN17" s="278"/>
+      <c r="AO17" s="278"/>
+      <c r="AP17" s="278"/>
+      <c r="AQ17" s="279"/>
+      <c r="AR17" s="273" t="s">
         <v>28</v>
       </c>
-      <c r="AS17" s="192"/>
+      <c r="AS17" s="274"/>
       <c r="AT17" s="73"/>
       <c r="AW17" s="13"/>
       <c r="AX17" s="16"/>
@@ -6393,58 +6397,58 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:59" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:59" ht="39.75" customHeight="1">
       <c r="A18" s="70"/>
       <c r="B18" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="167" t="s">
+      <c r="C18" s="280" t="s">
         <v>130</v>
       </c>
-      <c r="D18" s="167"/>
-      <c r="E18" s="167"/>
-      <c r="F18" s="167"/>
-      <c r="G18" s="167"/>
-      <c r="H18" s="167"/>
-      <c r="I18" s="168"/>
-      <c r="J18" s="200"/>
-      <c r="K18" s="200"/>
-      <c r="L18" s="200"/>
-      <c r="M18" s="200"/>
-      <c r="N18" s="200"/>
-      <c r="O18" s="200"/>
-      <c r="P18" s="200"/>
-      <c r="Q18" s="200"/>
-      <c r="R18" s="200"/>
-      <c r="S18" s="200"/>
-      <c r="T18" s="200"/>
-      <c r="U18" s="200"/>
-      <c r="V18" s="200"/>
-      <c r="W18" s="200"/>
-      <c r="X18" s="200"/>
-      <c r="Y18" s="200"/>
-      <c r="Z18" s="200"/>
-      <c r="AA18" s="200"/>
-      <c r="AB18" s="189"/>
-      <c r="AC18" s="189"/>
-      <c r="AD18" s="189"/>
-      <c r="AE18" s="189"/>
-      <c r="AF18" s="189"/>
-      <c r="AG18" s="189"/>
-      <c r="AH18" s="189"/>
-      <c r="AI18" s="189"/>
-      <c r="AJ18" s="189"/>
-      <c r="AK18" s="189"/>
-      <c r="AL18" s="189"/>
-      <c r="AM18" s="189"/>
-      <c r="AN18" s="189"/>
-      <c r="AO18" s="189"/>
-      <c r="AP18" s="189"/>
-      <c r="AQ18" s="190"/>
-      <c r="AR18" s="191" t="s">
+      <c r="D18" s="280"/>
+      <c r="E18" s="280"/>
+      <c r="F18" s="280"/>
+      <c r="G18" s="280"/>
+      <c r="H18" s="280"/>
+      <c r="I18" s="281"/>
+      <c r="J18" s="277"/>
+      <c r="K18" s="277"/>
+      <c r="L18" s="277"/>
+      <c r="M18" s="277"/>
+      <c r="N18" s="277"/>
+      <c r="O18" s="277"/>
+      <c r="P18" s="277"/>
+      <c r="Q18" s="277"/>
+      <c r="R18" s="277"/>
+      <c r="S18" s="277"/>
+      <c r="T18" s="277"/>
+      <c r="U18" s="277"/>
+      <c r="V18" s="277"/>
+      <c r="W18" s="277"/>
+      <c r="X18" s="277"/>
+      <c r="Y18" s="277"/>
+      <c r="Z18" s="277"/>
+      <c r="AA18" s="277"/>
+      <c r="AB18" s="278"/>
+      <c r="AC18" s="278"/>
+      <c r="AD18" s="278"/>
+      <c r="AE18" s="278"/>
+      <c r="AF18" s="278"/>
+      <c r="AG18" s="278"/>
+      <c r="AH18" s="278"/>
+      <c r="AI18" s="278"/>
+      <c r="AJ18" s="278"/>
+      <c r="AK18" s="278"/>
+      <c r="AL18" s="278"/>
+      <c r="AM18" s="278"/>
+      <c r="AN18" s="278"/>
+      <c r="AO18" s="278"/>
+      <c r="AP18" s="278"/>
+      <c r="AQ18" s="279"/>
+      <c r="AR18" s="273" t="s">
         <v>28</v>
       </c>
-      <c r="AS18" s="192"/>
+      <c r="AS18" s="274"/>
       <c r="AT18" s="73"/>
       <c r="AW18" s="13"/>
       <c r="AX18" s="16"/>
@@ -6452,65 +6456,65 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:59" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:59" ht="39.75" customHeight="1">
       <c r="A19" s="75"/>
-      <c r="B19" s="221" t="s">
+      <c r="B19" s="270" t="s">
         <v>136</v>
       </c>
-      <c r="C19" s="221"/>
-      <c r="D19" s="221"/>
-      <c r="E19" s="221"/>
-      <c r="F19" s="221"/>
-      <c r="G19" s="221"/>
-      <c r="H19" s="221"/>
-      <c r="I19" s="221"/>
-      <c r="J19" s="221"/>
-      <c r="K19" s="221"/>
-      <c r="L19" s="221"/>
-      <c r="M19" s="221"/>
-      <c r="N19" s="221"/>
-      <c r="O19" s="221"/>
-      <c r="P19" s="221"/>
-      <c r="Q19" s="221"/>
-      <c r="R19" s="221"/>
-      <c r="S19" s="221"/>
-      <c r="T19" s="221"/>
-      <c r="U19" s="221"/>
-      <c r="V19" s="221"/>
-      <c r="W19" s="221"/>
-      <c r="X19" s="221"/>
-      <c r="Y19" s="221"/>
-      <c r="Z19" s="221"/>
-      <c r="AA19" s="221"/>
-      <c r="AB19" s="222" t="str">
+      <c r="C19" s="270"/>
+      <c r="D19" s="270"/>
+      <c r="E19" s="270"/>
+      <c r="F19" s="270"/>
+      <c r="G19" s="270"/>
+      <c r="H19" s="270"/>
+      <c r="I19" s="270"/>
+      <c r="J19" s="270"/>
+      <c r="K19" s="270"/>
+      <c r="L19" s="270"/>
+      <c r="M19" s="270"/>
+      <c r="N19" s="270"/>
+      <c r="O19" s="270"/>
+      <c r="P19" s="270"/>
+      <c r="Q19" s="270"/>
+      <c r="R19" s="270"/>
+      <c r="S19" s="270"/>
+      <c r="T19" s="270"/>
+      <c r="U19" s="270"/>
+      <c r="V19" s="270"/>
+      <c r="W19" s="270"/>
+      <c r="X19" s="270"/>
+      <c r="Y19" s="270"/>
+      <c r="Z19" s="270"/>
+      <c r="AA19" s="270"/>
+      <c r="AB19" s="271" t="str">
         <f>IF(SUM(AB13,AB15:AQ17,-AB18)&gt;0,SUM(AB13,AB15:AQ17,-AB18), "" )</f>
         <v/>
       </c>
-      <c r="AC19" s="222"/>
-      <c r="AD19" s="222"/>
-      <c r="AE19" s="222"/>
-      <c r="AF19" s="222"/>
-      <c r="AG19" s="222"/>
-      <c r="AH19" s="222"/>
-      <c r="AI19" s="222"/>
-      <c r="AJ19" s="222"/>
-      <c r="AK19" s="222"/>
-      <c r="AL19" s="222"/>
-      <c r="AM19" s="222"/>
-      <c r="AN19" s="222"/>
-      <c r="AO19" s="222"/>
-      <c r="AP19" s="222"/>
-      <c r="AQ19" s="223"/>
-      <c r="AR19" s="191" t="s">
+      <c r="AC19" s="271"/>
+      <c r="AD19" s="271"/>
+      <c r="AE19" s="271"/>
+      <c r="AF19" s="271"/>
+      <c r="AG19" s="271"/>
+      <c r="AH19" s="271"/>
+      <c r="AI19" s="271"/>
+      <c r="AJ19" s="271"/>
+      <c r="AK19" s="271"/>
+      <c r="AL19" s="271"/>
+      <c r="AM19" s="271"/>
+      <c r="AN19" s="271"/>
+      <c r="AO19" s="271"/>
+      <c r="AP19" s="271"/>
+      <c r="AQ19" s="272"/>
+      <c r="AR19" s="273" t="s">
         <v>28</v>
       </c>
-      <c r="AS19" s="192"/>
+      <c r="AS19" s="274"/>
       <c r="AT19" s="73"/>
       <c r="BG19" s="14" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:59" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:59" ht="17.25" customHeight="1">
       <c r="A20" s="76"/>
       <c r="B20" s="77"/>
       <c r="C20" s="78"/>
@@ -6562,7 +6566,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:59" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:59" ht="18.75" customHeight="1">
       <c r="A21" s="83" t="s">
         <v>38</v>
       </c>
@@ -6615,7 +6619,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:59" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:59" ht="18.75" customHeight="1">
       <c r="A22" s="86"/>
       <c r="B22" s="66"/>
       <c r="C22" s="66"/>
@@ -6628,76 +6632,76 @@
       <c r="J22" s="87"/>
       <c r="K22" s="87"/>
       <c r="L22" s="87"/>
-      <c r="M22" s="224" t="s">
+      <c r="M22" s="275" t="s">
         <v>40</v>
       </c>
-      <c r="N22" s="224"/>
-      <c r="O22" s="224"/>
-      <c r="P22" s="224"/>
-      <c r="Q22" s="224"/>
-      <c r="R22" s="224"/>
-      <c r="S22" s="224"/>
-      <c r="T22" s="224"/>
+      <c r="N22" s="275"/>
+      <c r="O22" s="275"/>
+      <c r="P22" s="275"/>
+      <c r="Q22" s="275"/>
+      <c r="R22" s="275"/>
+      <c r="S22" s="275"/>
+      <c r="T22" s="275"/>
       <c r="U22" s="66"/>
       <c r="V22" s="66"/>
       <c r="W22" s="66"/>
       <c r="X22" s="66"/>
-      <c r="Y22" s="225" t="s">
+      <c r="Y22" s="260" t="s">
         <v>41</v>
       </c>
-      <c r="Z22" s="225"/>
-      <c r="AA22" s="225"/>
-      <c r="AB22" s="225"/>
-      <c r="AC22" s="225"/>
-      <c r="AD22" s="225"/>
-      <c r="AE22" s="225"/>
-      <c r="AF22" s="225"/>
+      <c r="Z22" s="260"/>
+      <c r="AA22" s="260"/>
+      <c r="AB22" s="260"/>
+      <c r="AC22" s="260"/>
+      <c r="AD22" s="260"/>
+      <c r="AE22" s="260"/>
+      <c r="AF22" s="260"/>
       <c r="AG22" s="87"/>
       <c r="AH22" s="87"/>
       <c r="AI22" s="87"/>
       <c r="AJ22" s="87"/>
-      <c r="AK22" s="226"/>
-      <c r="AL22" s="226"/>
-      <c r="AM22" s="226"/>
-      <c r="AN22" s="226"/>
-      <c r="AO22" s="226"/>
-      <c r="AP22" s="226"/>
-      <c r="AQ22" s="226"/>
-      <c r="AR22" s="226"/>
+      <c r="AK22" s="276"/>
+      <c r="AL22" s="276"/>
+      <c r="AM22" s="276"/>
+      <c r="AN22" s="276"/>
+      <c r="AO22" s="276"/>
+      <c r="AP22" s="276"/>
+      <c r="AQ22" s="276"/>
+      <c r="AR22" s="276"/>
       <c r="AS22" s="82"/>
       <c r="AT22" s="73"/>
       <c r="BG22" s="14" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:59" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:59" ht="39.75" customHeight="1">
       <c r="A23" s="86"/>
-      <c r="B23" s="211" t="s">
+      <c r="B23" s="240" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="211"/>
-      <c r="D23" s="211"/>
-      <c r="E23" s="211"/>
-      <c r="F23" s="211"/>
-      <c r="G23" s="211"/>
-      <c r="H23" s="211"/>
+      <c r="C23" s="240"/>
+      <c r="D23" s="240"/>
+      <c r="E23" s="240"/>
+      <c r="F23" s="240"/>
+      <c r="G23" s="240"/>
+      <c r="H23" s="240"/>
       <c r="J23" s="88"/>
       <c r="L23" s="88"/>
-      <c r="M23" s="212" t="str">
+      <c r="M23" s="261" t="str">
         <f>IF(J7=0,"",J7)</f>
         <v/>
       </c>
-      <c r="N23" s="213"/>
-      <c r="O23" s="213"/>
-      <c r="P23" s="213"/>
-      <c r="Q23" s="213"/>
-      <c r="R23" s="213"/>
-      <c r="S23" s="213"/>
-      <c r="T23" s="214"/>
-      <c r="U23" s="215" t="s">
+      <c r="N23" s="262"/>
+      <c r="O23" s="262"/>
+      <c r="P23" s="262"/>
+      <c r="Q23" s="262"/>
+      <c r="R23" s="262"/>
+      <c r="S23" s="262"/>
+      <c r="T23" s="263"/>
+      <c r="U23" s="220" t="s">
         <v>45</v>
       </c>
-      <c r="V23" s="216"/>
+      <c r="V23" s="211"/>
       <c r="X23" s="88"/>
       <c r="Y23" s="217" t="str">
         <f>IF(AP8="","",AY8)</f>
@@ -6710,21 +6714,21 @@
       <c r="AD23" s="218"/>
       <c r="AE23" s="218"/>
       <c r="AF23" s="219"/>
-      <c r="AG23" s="215" t="s">
+      <c r="AG23" s="220" t="s">
         <v>16</v>
       </c>
-      <c r="AH23" s="216"/>
+      <c r="AH23" s="211"/>
       <c r="AJ23" s="88"/>
-      <c r="AK23" s="220" t="s">
+      <c r="AK23" s="202" t="s">
         <v>47</v>
       </c>
-      <c r="AL23" s="220"/>
-      <c r="AM23" s="220"/>
-      <c r="AN23" s="220"/>
-      <c r="AO23" s="220"/>
-      <c r="AP23" s="220"/>
-      <c r="AQ23" s="220"/>
-      <c r="AR23" s="220"/>
+      <c r="AL23" s="202"/>
+      <c r="AM23" s="202"/>
+      <c r="AN23" s="202"/>
+      <c r="AO23" s="202"/>
+      <c r="AP23" s="202"/>
+      <c r="AQ23" s="202"/>
+      <c r="AR23" s="202"/>
       <c r="AS23" s="82"/>
       <c r="AT23" s="73"/>
       <c r="AX23" s="11"/>
@@ -6732,26 +6736,26 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:59" ht="19.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:59" ht="19.5" customHeight="1">
       <c r="A24" s="89"/>
-      <c r="B24" s="229" t="str">
+      <c r="B24" s="221" t="str">
         <f>AB19</f>
         <v/>
       </c>
-      <c r="C24" s="230"/>
-      <c r="D24" s="230"/>
-      <c r="E24" s="230"/>
-      <c r="F24" s="230"/>
-      <c r="G24" s="230"/>
-      <c r="H24" s="231"/>
-      <c r="I24" s="215" t="s">
+      <c r="C24" s="222"/>
+      <c r="D24" s="222"/>
+      <c r="E24" s="222"/>
+      <c r="F24" s="222"/>
+      <c r="G24" s="222"/>
+      <c r="H24" s="223"/>
+      <c r="I24" s="220" t="s">
         <v>28</v>
       </c>
-      <c r="J24" s="216"/>
-      <c r="K24" s="216" t="s">
+      <c r="J24" s="211"/>
+      <c r="K24" s="211" t="s">
         <v>44</v>
       </c>
-      <c r="L24" s="216"/>
+      <c r="L24" s="211"/>
       <c r="M24" s="90"/>
       <c r="N24" s="90"/>
       <c r="O24" s="90"/>
@@ -6762,10 +6766,10 @@
       <c r="T24" s="90"/>
       <c r="U24" s="88"/>
       <c r="V24" s="88"/>
-      <c r="W24" s="216" t="s">
+      <c r="W24" s="211" t="s">
         <v>44</v>
       </c>
-      <c r="X24" s="216"/>
+      <c r="X24" s="211"/>
       <c r="Y24" s="90"/>
       <c r="Z24" s="90"/>
       <c r="AA24" s="90"/>
@@ -6776,42 +6780,42 @@
       <c r="AF24" s="90"/>
       <c r="AG24" s="91"/>
       <c r="AH24" s="91"/>
-      <c r="AI24" s="216" t="s">
+      <c r="AI24" s="211" t="s">
         <v>46</v>
       </c>
-      <c r="AJ24" s="235"/>
-      <c r="AK24" s="236" t="str">
+      <c r="AJ24" s="227"/>
+      <c r="AK24" s="264" t="str">
         <f>IF(B24="","",B24*M23/M27*Y23/Y27)</f>
         <v/>
       </c>
-      <c r="AL24" s="237"/>
-      <c r="AM24" s="237"/>
-      <c r="AN24" s="237"/>
-      <c r="AO24" s="237"/>
-      <c r="AP24" s="237"/>
-      <c r="AQ24" s="237"/>
-      <c r="AR24" s="238"/>
-      <c r="AS24" s="227" t="s">
+      <c r="AL24" s="265"/>
+      <c r="AM24" s="265"/>
+      <c r="AN24" s="265"/>
+      <c r="AO24" s="265"/>
+      <c r="AP24" s="265"/>
+      <c r="AQ24" s="265"/>
+      <c r="AR24" s="266"/>
+      <c r="AS24" s="259" t="s">
         <v>28</v>
       </c>
-      <c r="AT24" s="228"/>
+      <c r="AT24" s="215"/>
       <c r="BG24" s="14" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:59" ht="19.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:59" ht="19.5" customHeight="1">
       <c r="A25" s="89"/>
-      <c r="B25" s="232"/>
-      <c r="C25" s="233"/>
-      <c r="D25" s="233"/>
-      <c r="E25" s="233"/>
-      <c r="F25" s="233"/>
-      <c r="G25" s="233"/>
-      <c r="H25" s="234"/>
-      <c r="I25" s="215"/>
-      <c r="J25" s="216"/>
-      <c r="K25" s="216"/>
-      <c r="L25" s="216"/>
+      <c r="B25" s="224"/>
+      <c r="C25" s="225"/>
+      <c r="D25" s="225"/>
+      <c r="E25" s="225"/>
+      <c r="F25" s="225"/>
+      <c r="G25" s="225"/>
+      <c r="H25" s="226"/>
+      <c r="I25" s="220"/>
+      <c r="J25" s="211"/>
+      <c r="K25" s="211"/>
+      <c r="L25" s="211"/>
       <c r="M25" s="87"/>
       <c r="N25" s="87"/>
       <c r="O25" s="87"/>
@@ -6822,8 +6826,8 @@
       <c r="T25" s="87"/>
       <c r="U25" s="88"/>
       <c r="V25" s="88"/>
-      <c r="W25" s="216"/>
-      <c r="X25" s="216"/>
+      <c r="W25" s="211"/>
+      <c r="X25" s="211"/>
       <c r="Y25" s="87"/>
       <c r="Z25" s="87"/>
       <c r="AA25" s="87"/>
@@ -6834,23 +6838,23 @@
       <c r="AF25" s="87"/>
       <c r="AG25" s="91"/>
       <c r="AH25" s="91"/>
-      <c r="AI25" s="216"/>
-      <c r="AJ25" s="235"/>
-      <c r="AK25" s="239"/>
-      <c r="AL25" s="240"/>
-      <c r="AM25" s="240"/>
-      <c r="AN25" s="240"/>
-      <c r="AO25" s="240"/>
-      <c r="AP25" s="240"/>
-      <c r="AQ25" s="240"/>
-      <c r="AR25" s="241"/>
-      <c r="AS25" s="227"/>
-      <c r="AT25" s="228"/>
+      <c r="AI25" s="211"/>
+      <c r="AJ25" s="227"/>
+      <c r="AK25" s="267"/>
+      <c r="AL25" s="268"/>
+      <c r="AM25" s="268"/>
+      <c r="AN25" s="268"/>
+      <c r="AO25" s="268"/>
+      <c r="AP25" s="268"/>
+      <c r="AQ25" s="268"/>
+      <c r="AR25" s="269"/>
+      <c r="AS25" s="259"/>
+      <c r="AT25" s="215"/>
       <c r="BG25" s="14" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:59" ht="18.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:59" ht="18.75" customHeight="1">
       <c r="A26" s="89"/>
       <c r="B26" s="93"/>
       <c r="C26" s="93"/>
@@ -6863,30 +6867,30 @@
       <c r="J26" s="88"/>
       <c r="K26" s="88"/>
       <c r="L26" s="88"/>
-      <c r="M26" s="225" t="s">
+      <c r="M26" s="260" t="s">
         <v>51</v>
       </c>
-      <c r="N26" s="225"/>
-      <c r="O26" s="225"/>
-      <c r="P26" s="225"/>
-      <c r="Q26" s="225"/>
-      <c r="R26" s="225"/>
-      <c r="S26" s="225"/>
-      <c r="T26" s="225"/>
+      <c r="N26" s="260"/>
+      <c r="O26" s="260"/>
+      <c r="P26" s="260"/>
+      <c r="Q26" s="260"/>
+      <c r="R26" s="260"/>
+      <c r="S26" s="260"/>
+      <c r="T26" s="260"/>
       <c r="U26" s="88"/>
       <c r="V26" s="88"/>
       <c r="W26" s="88"/>
       <c r="X26" s="88"/>
-      <c r="Y26" s="225" t="s">
+      <c r="Y26" s="260" t="s">
         <v>52</v>
       </c>
-      <c r="Z26" s="225"/>
-      <c r="AA26" s="225"/>
-      <c r="AB26" s="225"/>
-      <c r="AC26" s="225"/>
-      <c r="AD26" s="225"/>
-      <c r="AE26" s="225"/>
-      <c r="AF26" s="225"/>
+      <c r="Z26" s="260"/>
+      <c r="AA26" s="260"/>
+      <c r="AB26" s="260"/>
+      <c r="AC26" s="260"/>
+      <c r="AD26" s="260"/>
+      <c r="AE26" s="260"/>
+      <c r="AF26" s="260"/>
       <c r="AG26" s="91"/>
       <c r="AH26" s="91"/>
       <c r="AI26" s="88"/>
@@ -6905,7 +6909,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:59" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:59" ht="39.75" customHeight="1">
       <c r="A27" s="95"/>
       <c r="B27" s="87"/>
       <c r="C27" s="87"/>
@@ -6918,21 +6922,21 @@
       <c r="J27" s="88"/>
       <c r="K27" s="88"/>
       <c r="L27" s="88"/>
-      <c r="M27" s="212" t="str">
+      <c r="M27" s="261" t="str">
         <f>IF(AG7=0,"",IF(M23&gt;AG7,"エラー",AG7))</f>
         <v/>
       </c>
-      <c r="N27" s="213"/>
-      <c r="O27" s="213"/>
-      <c r="P27" s="213"/>
-      <c r="Q27" s="213"/>
-      <c r="R27" s="213"/>
-      <c r="S27" s="213"/>
-      <c r="T27" s="214"/>
-      <c r="U27" s="215" t="s">
+      <c r="N27" s="262"/>
+      <c r="O27" s="262"/>
+      <c r="P27" s="262"/>
+      <c r="Q27" s="262"/>
+      <c r="R27" s="262"/>
+      <c r="S27" s="262"/>
+      <c r="T27" s="263"/>
+      <c r="U27" s="220" t="s">
         <v>45</v>
       </c>
-      <c r="V27" s="216"/>
+      <c r="V27" s="211"/>
       <c r="W27" s="88"/>
       <c r="X27" s="88"/>
       <c r="Y27" s="217" t="str">
@@ -6946,10 +6950,10 @@
       <c r="AD27" s="218"/>
       <c r="AE27" s="218"/>
       <c r="AF27" s="219"/>
-      <c r="AG27" s="215" t="s">
+      <c r="AG27" s="220" t="s">
         <v>16</v>
       </c>
-      <c r="AH27" s="216"/>
+      <c r="AH27" s="211"/>
       <c r="AI27" s="88"/>
       <c r="AJ27" s="88"/>
       <c r="AS27" s="82"/>
@@ -6958,7 +6962,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:59" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:59" ht="18.75" customHeight="1">
       <c r="A28" s="83" t="s">
         <v>55</v>
       </c>
@@ -7006,53 +7010,53 @@
       <c r="AR28" s="81"/>
       <c r="AS28" s="82"/>
       <c r="AT28" s="73"/>
-      <c r="AW28" s="251" t="s">
+      <c r="AW28" s="253" t="s">
         <v>129</v>
       </c>
-      <c r="AX28" s="251"/>
+      <c r="AX28" s="253"/>
       <c r="BG28" s="14" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="29" spans="1:59" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:59" ht="39.75" customHeight="1">
       <c r="A29" s="86"/>
-      <c r="M29" s="249" t="s">
+      <c r="M29" s="251" t="s">
         <v>57</v>
       </c>
-      <c r="N29" s="249"/>
-      <c r="O29" s="249"/>
-      <c r="P29" s="249"/>
-      <c r="Q29" s="249"/>
-      <c r="R29" s="249"/>
-      <c r="S29" s="249"/>
-      <c r="T29" s="249"/>
+      <c r="N29" s="251"/>
+      <c r="O29" s="251"/>
+      <c r="P29" s="251"/>
+      <c r="Q29" s="251"/>
+      <c r="R29" s="251"/>
+      <c r="S29" s="251"/>
+      <c r="T29" s="251"/>
       <c r="U29" s="96"/>
       <c r="W29" s="96"/>
-      <c r="X29" s="252" t="s">
+      <c r="X29" s="254" t="s">
         <v>144</v>
       </c>
-      <c r="Y29" s="252"/>
-      <c r="Z29" s="252"/>
-      <c r="AA29" s="252"/>
-      <c r="AB29" s="252"/>
-      <c r="AC29" s="252"/>
-      <c r="AD29" s="252"/>
-      <c r="AE29" s="252"/>
-      <c r="AF29" s="252"/>
-      <c r="AG29" s="252"/>
-      <c r="AH29" s="252"/>
+      <c r="Y29" s="254"/>
+      <c r="Z29" s="254"/>
+      <c r="AA29" s="254"/>
+      <c r="AB29" s="254"/>
+      <c r="AC29" s="254"/>
+      <c r="AD29" s="254"/>
+      <c r="AE29" s="254"/>
+      <c r="AF29" s="254"/>
+      <c r="AG29" s="254"/>
+      <c r="AH29" s="254"/>
       <c r="AI29" s="96"/>
       <c r="AJ29" s="96"/>
-      <c r="AK29" s="253" t="s">
+      <c r="AK29" s="255" t="s">
         <v>58</v>
       </c>
-      <c r="AL29" s="253"/>
-      <c r="AM29" s="253"/>
-      <c r="AN29" s="253"/>
-      <c r="AO29" s="253"/>
-      <c r="AP29" s="253"/>
-      <c r="AQ29" s="253"/>
-      <c r="AR29" s="253"/>
+      <c r="AL29" s="255"/>
+      <c r="AM29" s="255"/>
+      <c r="AN29" s="255"/>
+      <c r="AO29" s="255"/>
+      <c r="AP29" s="255"/>
+      <c r="AQ29" s="255"/>
+      <c r="AR29" s="255"/>
       <c r="AS29" s="96"/>
       <c r="AT29" s="97"/>
       <c r="AW29" s="25"/>
@@ -7061,27 +7065,27 @@
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="1:59" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:59" ht="39.75" customHeight="1">
       <c r="A30" s="98"/>
-      <c r="M30" s="242" t="str">
+      <c r="M30" s="241" t="str">
         <f>AK24</f>
         <v/>
       </c>
-      <c r="N30" s="243"/>
-      <c r="O30" s="243"/>
-      <c r="P30" s="243"/>
-      <c r="Q30" s="243"/>
-      <c r="R30" s="243"/>
-      <c r="S30" s="243"/>
-      <c r="T30" s="244"/>
-      <c r="U30" s="254" t="s">
+      <c r="N30" s="242"/>
+      <c r="O30" s="242"/>
+      <c r="P30" s="242"/>
+      <c r="Q30" s="242"/>
+      <c r="R30" s="242"/>
+      <c r="S30" s="242"/>
+      <c r="T30" s="243"/>
+      <c r="U30" s="205" t="s">
         <v>28</v>
       </c>
-      <c r="V30" s="254"/>
-      <c r="W30" s="245" t="s">
+      <c r="V30" s="205"/>
+      <c r="W30" s="203" t="s">
         <v>44</v>
       </c>
-      <c r="X30" s="255"/>
+      <c r="X30" s="206"/>
       <c r="Y30" s="256"/>
       <c r="Z30" s="257"/>
       <c r="AA30" s="257"/>
@@ -7090,29 +7094,29 @@
       <c r="AD30" s="257"/>
       <c r="AE30" s="257"/>
       <c r="AF30" s="258"/>
-      <c r="AG30" s="254" t="s">
+      <c r="AG30" s="205" t="s">
         <v>60</v>
       </c>
-      <c r="AH30" s="254"/>
-      <c r="AI30" s="254" t="s">
+      <c r="AH30" s="205"/>
+      <c r="AI30" s="205" t="s">
         <v>46</v>
       </c>
-      <c r="AJ30" s="254"/>
-      <c r="AK30" s="242" t="str">
+      <c r="AJ30" s="205"/>
+      <c r="AK30" s="241" t="str">
         <f>IF(Y30="","",M30*Y30/100)</f>
         <v/>
       </c>
-      <c r="AL30" s="243"/>
-      <c r="AM30" s="243"/>
-      <c r="AN30" s="243"/>
-      <c r="AO30" s="243"/>
-      <c r="AP30" s="243"/>
-      <c r="AQ30" s="243"/>
-      <c r="AR30" s="244"/>
-      <c r="AS30" s="245" t="s">
+      <c r="AL30" s="242"/>
+      <c r="AM30" s="242"/>
+      <c r="AN30" s="242"/>
+      <c r="AO30" s="242"/>
+      <c r="AP30" s="242"/>
+      <c r="AQ30" s="242"/>
+      <c r="AR30" s="243"/>
+      <c r="AS30" s="203" t="s">
         <v>28</v>
       </c>
-      <c r="AT30" s="246"/>
+      <c r="AT30" s="248"/>
       <c r="AW30" s="26" t="s">
         <v>62</v>
       </c>
@@ -7123,7 +7127,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="31" spans="1:59" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:59" ht="18.75" customHeight="1">
       <c r="A31" s="98"/>
       <c r="B31" s="66"/>
       <c r="C31" s="3"/>
@@ -7180,7 +7184,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="1:59" ht="33.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:59" ht="33.75" customHeight="1">
       <c r="A32" s="99" t="s">
         <v>64</v>
       </c>
@@ -7239,7 +7243,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="33" spans="1:60" ht="18.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:60" ht="18.75" customHeight="1">
       <c r="A33" s="103"/>
       <c r="B33" s="64"/>
       <c r="C33" s="64"/>
@@ -7272,7 +7276,7 @@
       </c>
       <c r="BH33" s="2"/>
     </row>
-    <row r="34" spans="1:60" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:60" ht="18.75" customHeight="1">
       <c r="A34" s="106" t="s">
         <v>67</v>
       </c>
@@ -7327,8 +7331,8 @@
       <c r="AX34" s="27">
         <v>0.75</v>
       </c>
-      <c r="AZ34" s="247"/>
-      <c r="BA34" s="247"/>
+      <c r="AZ34" s="249"/>
+      <c r="BA34" s="249"/>
       <c r="BB34" s="16"/>
       <c r="BC34" s="16"/>
       <c r="BD34" s="16"/>
@@ -7336,7 +7340,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="35" spans="1:60" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:60" s="2" customFormat="1" ht="18.75" customHeight="1">
       <c r="A35" s="110"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -7349,44 +7353,44 @@
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
-      <c r="M35" s="211" t="s">
+      <c r="M35" s="240" t="s">
         <v>70</v>
       </c>
-      <c r="N35" s="211"/>
-      <c r="O35" s="211"/>
-      <c r="P35" s="211"/>
-      <c r="Q35" s="211"/>
-      <c r="R35" s="211"/>
-      <c r="S35" s="211"/>
-      <c r="T35" s="211"/>
+      <c r="N35" s="240"/>
+      <c r="O35" s="240"/>
+      <c r="P35" s="240"/>
+      <c r="Q35" s="240"/>
+      <c r="R35" s="240"/>
+      <c r="S35" s="240"/>
+      <c r="T35" s="240"/>
       <c r="U35" s="96"/>
       <c r="V35" s="96"/>
       <c r="W35" s="111"/>
       <c r="X35" s="1"/>
-      <c r="Y35" s="248" t="s">
+      <c r="Y35" s="250" t="s">
         <v>71</v>
       </c>
-      <c r="Z35" s="248"/>
-      <c r="AA35" s="248"/>
-      <c r="AB35" s="248"/>
-      <c r="AC35" s="248"/>
-      <c r="AD35" s="248"/>
-      <c r="AE35" s="248"/>
-      <c r="AF35" s="248"/>
+      <c r="Z35" s="250"/>
+      <c r="AA35" s="250"/>
+      <c r="AB35" s="250"/>
+      <c r="AC35" s="250"/>
+      <c r="AD35" s="250"/>
+      <c r="AE35" s="250"/>
+      <c r="AF35" s="250"/>
       <c r="AG35" s="111"/>
       <c r="AH35" s="111"/>
       <c r="AI35" s="96"/>
       <c r="AJ35" s="96"/>
-      <c r="AK35" s="249" t="s">
+      <c r="AK35" s="251" t="s">
         <v>72</v>
       </c>
-      <c r="AL35" s="249"/>
-      <c r="AM35" s="249"/>
-      <c r="AN35" s="249"/>
-      <c r="AO35" s="249"/>
-      <c r="AP35" s="249"/>
-      <c r="AQ35" s="249"/>
-      <c r="AR35" s="249"/>
+      <c r="AL35" s="251"/>
+      <c r="AM35" s="251"/>
+      <c r="AN35" s="251"/>
+      <c r="AO35" s="251"/>
+      <c r="AP35" s="251"/>
+      <c r="AQ35" s="251"/>
+      <c r="AR35" s="251"/>
       <c r="AS35" s="96"/>
       <c r="AT35" s="97"/>
       <c r="AW35" s="17" t="s">
@@ -7395,78 +7399,78 @@
       <c r="AX35" s="27">
         <v>0.15</v>
       </c>
-      <c r="BA35" s="250"/>
-      <c r="BB35" s="250"/>
-      <c r="BC35" s="250"/>
-      <c r="BD35" s="250"/>
-      <c r="BE35" s="250"/>
+      <c r="BA35" s="252"/>
+      <c r="BB35" s="252"/>
+      <c r="BC35" s="252"/>
+      <c r="BD35" s="252"/>
+      <c r="BE35" s="252"/>
       <c r="BF35" s="1"/>
       <c r="BG35" s="14" t="s">
         <v>79</v>
       </c>
       <c r="BH35" s="1"/>
     </row>
-    <row r="36" spans="1:60" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:60" ht="39.75" customHeight="1">
       <c r="A36" s="112"/>
-      <c r="M36" s="242" t="str">
+      <c r="M36" s="241" t="str">
         <f>AK30</f>
         <v/>
       </c>
-      <c r="N36" s="243"/>
-      <c r="O36" s="243"/>
-      <c r="P36" s="243"/>
-      <c r="Q36" s="243"/>
-      <c r="R36" s="243"/>
-      <c r="S36" s="243"/>
-      <c r="T36" s="244"/>
-      <c r="U36" s="254" t="s">
+      <c r="N36" s="242"/>
+      <c r="O36" s="242"/>
+      <c r="P36" s="242"/>
+      <c r="Q36" s="242"/>
+      <c r="R36" s="242"/>
+      <c r="S36" s="242"/>
+      <c r="T36" s="243"/>
+      <c r="U36" s="205" t="s">
         <v>28</v>
       </c>
-      <c r="V36" s="254"/>
-      <c r="W36" s="245" t="s">
+      <c r="V36" s="205"/>
+      <c r="W36" s="203" t="s">
         <v>44</v>
       </c>
-      <c r="X36" s="255"/>
-      <c r="Y36" s="265" t="s">
+      <c r="X36" s="206"/>
+      <c r="Y36" s="244" t="s">
         <v>65</v>
       </c>
-      <c r="Z36" s="266"/>
-      <c r="AA36" s="266"/>
-      <c r="AB36" s="266"/>
-      <c r="AC36" s="266"/>
-      <c r="AD36" s="266"/>
-      <c r="AE36" s="266"/>
-      <c r="AF36" s="267"/>
-      <c r="AG36" s="254" t="s">
+      <c r="Z36" s="245"/>
+      <c r="AA36" s="245"/>
+      <c r="AB36" s="245"/>
+      <c r="AC36" s="245"/>
+      <c r="AD36" s="245"/>
+      <c r="AE36" s="245"/>
+      <c r="AF36" s="246"/>
+      <c r="AG36" s="205" t="s">
         <v>60</v>
       </c>
-      <c r="AH36" s="254"/>
-      <c r="AI36" s="254" t="s">
+      <c r="AH36" s="205"/>
+      <c r="AI36" s="205" t="s">
         <v>46</v>
       </c>
-      <c r="AJ36" s="254"/>
-      <c r="AK36" s="259" t="e">
+      <c r="AJ36" s="205"/>
+      <c r="AK36" s="234" t="e">
         <f>IF(Y36="", "", ROUNDDOWN(M36 * VLOOKUP(Y36, AW30:AX35, 2, FALSE), -2))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AL36" s="260"/>
-      <c r="AM36" s="260"/>
-      <c r="AN36" s="260"/>
-      <c r="AO36" s="260"/>
-      <c r="AP36" s="260"/>
-      <c r="AQ36" s="260"/>
-      <c r="AR36" s="261"/>
-      <c r="AS36" s="262" t="s">
+      <c r="AL36" s="235"/>
+      <c r="AM36" s="235"/>
+      <c r="AN36" s="235"/>
+      <c r="AO36" s="235"/>
+      <c r="AP36" s="235"/>
+      <c r="AQ36" s="235"/>
+      <c r="AR36" s="236"/>
+      <c r="AS36" s="237" t="s">
         <v>28</v>
       </c>
-      <c r="AT36" s="263"/>
+      <c r="AT36" s="238"/>
       <c r="AW36" s="40"/>
       <c r="AX36" s="40"/>
       <c r="BG36" s="14" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="37" spans="1:60" ht="18.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:60" ht="18.75" customHeight="1">
       <c r="A37" s="86"/>
       <c r="C37" s="68"/>
       <c r="D37" s="68"/>
@@ -7498,20 +7502,20 @@
       <c r="AH37" s="2"/>
       <c r="AI37" s="104"/>
       <c r="AJ37" s="104"/>
-      <c r="AK37" s="264" t="s">
+      <c r="AK37" s="239" t="s">
         <v>77</v>
       </c>
-      <c r="AL37" s="264"/>
-      <c r="AM37" s="264"/>
-      <c r="AN37" s="264"/>
-      <c r="AO37" s="264"/>
-      <c r="AP37" s="264"/>
-      <c r="AQ37" s="264"/>
-      <c r="AR37" s="264"/>
+      <c r="AL37" s="239"/>
+      <c r="AM37" s="239"/>
+      <c r="AN37" s="239"/>
+      <c r="AO37" s="239"/>
+      <c r="AP37" s="239"/>
+      <c r="AQ37" s="239"/>
+      <c r="AR37" s="239"/>
       <c r="AS37" s="104"/>
       <c r="AT37" s="114"/>
     </row>
-    <row r="38" spans="1:60" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:60" ht="21" customHeight="1">
       <c r="A38" s="115" t="s">
         <v>80</v>
       </c>
@@ -7553,7 +7557,7 @@
       <c r="AQ38" s="119"/>
       <c r="AT38" s="105"/>
     </row>
-    <row r="39" spans="1:60" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:60" ht="18.75" customHeight="1">
       <c r="A39" s="86"/>
       <c r="B39" s="66"/>
       <c r="C39" s="66"/>
@@ -7565,18 +7569,18 @@
       <c r="I39" s="66"/>
       <c r="J39" s="87"/>
       <c r="K39" s="87"/>
-      <c r="L39" s="268" t="s">
+      <c r="L39" s="247" t="s">
         <v>138</v>
       </c>
-      <c r="M39" s="268"/>
-      <c r="N39" s="268"/>
-      <c r="O39" s="268"/>
-      <c r="P39" s="268"/>
-      <c r="Q39" s="268"/>
-      <c r="R39" s="268"/>
-      <c r="S39" s="268"/>
-      <c r="T39" s="268"/>
-      <c r="U39" s="268"/>
+      <c r="M39" s="247"/>
+      <c r="N39" s="247"/>
+      <c r="O39" s="247"/>
+      <c r="P39" s="247"/>
+      <c r="Q39" s="247"/>
+      <c r="R39" s="247"/>
+      <c r="S39" s="247"/>
+      <c r="T39" s="247"/>
+      <c r="U39" s="247"/>
       <c r="V39" s="66"/>
       <c r="W39" s="66"/>
       <c r="Y39" s="92" t="s">
@@ -7608,28 +7612,28 @@
       <c r="BG39" s="2"/>
       <c r="BH39" s="2"/>
     </row>
-    <row r="40" spans="1:60" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:60" ht="39.75" customHeight="1">
       <c r="A40" s="86"/>
-      <c r="B40" s="211" t="s">
+      <c r="B40" s="240" t="s">
         <v>81</v>
       </c>
-      <c r="C40" s="211"/>
-      <c r="D40" s="211"/>
-      <c r="E40" s="211"/>
-      <c r="F40" s="211"/>
-      <c r="G40" s="211"/>
-      <c r="H40" s="211"/>
+      <c r="C40" s="240"/>
+      <c r="D40" s="240"/>
+      <c r="E40" s="240"/>
+      <c r="F40" s="240"/>
+      <c r="G40" s="240"/>
+      <c r="H40" s="240"/>
       <c r="J40" s="88"/>
-      <c r="L40" s="268"/>
-      <c r="M40" s="268"/>
-      <c r="N40" s="268"/>
-      <c r="O40" s="268"/>
-      <c r="P40" s="268"/>
-      <c r="Q40" s="268"/>
-      <c r="R40" s="268"/>
-      <c r="S40" s="268"/>
-      <c r="T40" s="268"/>
-      <c r="U40" s="268"/>
+      <c r="L40" s="247"/>
+      <c r="M40" s="247"/>
+      <c r="N40" s="247"/>
+      <c r="O40" s="247"/>
+      <c r="P40" s="247"/>
+      <c r="Q40" s="247"/>
+      <c r="R40" s="247"/>
+      <c r="S40" s="247"/>
+      <c r="T40" s="247"/>
+      <c r="U40" s="247"/>
       <c r="V40" s="88"/>
       <c r="W40" s="88"/>
       <c r="X40" s="88"/>
@@ -7644,20 +7648,20 @@
       <c r="AD40" s="218"/>
       <c r="AE40" s="218"/>
       <c r="AF40" s="219"/>
-      <c r="AG40" s="215" t="s">
+      <c r="AG40" s="220" t="s">
         <v>16</v>
       </c>
-      <c r="AH40" s="216"/>
+      <c r="AH40" s="211"/>
       <c r="AI40" s="88"/>
       <c r="AJ40" s="88"/>
-      <c r="AK40" s="220"/>
-      <c r="AL40" s="220"/>
-      <c r="AM40" s="220"/>
-      <c r="AN40" s="220"/>
-      <c r="AO40" s="220"/>
-      <c r="AP40" s="220"/>
-      <c r="AQ40" s="220"/>
-      <c r="AR40" s="220"/>
+      <c r="AK40" s="202"/>
+      <c r="AL40" s="202"/>
+      <c r="AM40" s="202"/>
+      <c r="AN40" s="202"/>
+      <c r="AO40" s="202"/>
+      <c r="AP40" s="202"/>
+      <c r="AQ40" s="202"/>
+      <c r="AR40" s="202"/>
       <c r="AS40" s="82"/>
       <c r="AT40" s="73"/>
       <c r="BE40" s="2"/>
@@ -7665,45 +7669,45 @@
       <c r="BG40" s="2"/>
       <c r="BH40" s="2"/>
     </row>
-    <row r="41" spans="1:60" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:60" s="2" customFormat="1" ht="21" customHeight="1">
       <c r="A41" s="89"/>
-      <c r="B41" s="229" t="str">
+      <c r="B41" s="221" t="str">
         <f>IF(J7=0,"",J7)</f>
         <v/>
       </c>
-      <c r="C41" s="230"/>
-      <c r="D41" s="230"/>
-      <c r="E41" s="230"/>
-      <c r="F41" s="230"/>
-      <c r="G41" s="230"/>
-      <c r="H41" s="231"/>
-      <c r="I41" s="215" t="s">
+      <c r="C41" s="222"/>
+      <c r="D41" s="222"/>
+      <c r="E41" s="222"/>
+      <c r="F41" s="222"/>
+      <c r="G41" s="222"/>
+      <c r="H41" s="223"/>
+      <c r="I41" s="220" t="s">
         <v>45</v>
       </c>
-      <c r="J41" s="216"/>
-      <c r="K41" s="216" t="s">
+      <c r="J41" s="211"/>
+      <c r="K41" s="211" t="s">
         <v>118</v>
       </c>
-      <c r="L41" s="235"/>
-      <c r="M41" s="272" t="str">
+      <c r="L41" s="227"/>
+      <c r="M41" s="228" t="str">
         <f>IF(AP8="","",IF(BA8=BC8,AZ8+1,AZ8))</f>
         <v/>
       </c>
-      <c r="N41" s="273"/>
-      <c r="O41" s="273"/>
-      <c r="P41" s="273"/>
-      <c r="Q41" s="273"/>
-      <c r="R41" s="273"/>
-      <c r="S41" s="273"/>
-      <c r="T41" s="274"/>
-      <c r="U41" s="215" t="s">
+      <c r="N41" s="229"/>
+      <c r="O41" s="229"/>
+      <c r="P41" s="229"/>
+      <c r="Q41" s="229"/>
+      <c r="R41" s="229"/>
+      <c r="S41" s="229"/>
+      <c r="T41" s="230"/>
+      <c r="U41" s="220" t="s">
         <v>83</v>
       </c>
-      <c r="V41" s="216"/>
-      <c r="W41" s="216" t="s">
+      <c r="V41" s="211"/>
+      <c r="W41" s="211" t="s">
         <v>117</v>
       </c>
-      <c r="X41" s="216"/>
+      <c r="X41" s="211"/>
       <c r="Y41" s="90"/>
       <c r="Z41" s="90"/>
       <c r="AA41" s="90"/>
@@ -7714,44 +7718,44 @@
       <c r="AF41" s="90"/>
       <c r="AG41" s="91"/>
       <c r="AH41" s="91"/>
-      <c r="AI41" s="216" t="s">
+      <c r="AI41" s="211" t="s">
         <v>107</v>
       </c>
-      <c r="AJ41" s="216"/>
-      <c r="AL41" s="269" t="s">
+      <c r="AJ41" s="211"/>
+      <c r="AL41" s="213" t="s">
         <v>116</v>
       </c>
-      <c r="AM41" s="269"/>
-      <c r="AN41" s="269"/>
-      <c r="AO41" s="269"/>
-      <c r="AS41" s="270"/>
-      <c r="AT41" s="228"/>
+      <c r="AM41" s="213"/>
+      <c r="AN41" s="213"/>
+      <c r="AO41" s="213"/>
+      <c r="AS41" s="214"/>
+      <c r="AT41" s="215"/>
     </row>
-    <row r="42" spans="1:60" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:60" s="2" customFormat="1" ht="21" customHeight="1">
       <c r="A42" s="89"/>
-      <c r="B42" s="232"/>
-      <c r="C42" s="233"/>
-      <c r="D42" s="233"/>
-      <c r="E42" s="233"/>
-      <c r="F42" s="233"/>
-      <c r="G42" s="233"/>
-      <c r="H42" s="234"/>
-      <c r="I42" s="215"/>
-      <c r="J42" s="216"/>
-      <c r="K42" s="216"/>
-      <c r="L42" s="235"/>
-      <c r="M42" s="275"/>
-      <c r="N42" s="276"/>
-      <c r="O42" s="276"/>
-      <c r="P42" s="276"/>
-      <c r="Q42" s="276"/>
-      <c r="R42" s="276"/>
-      <c r="S42" s="276"/>
-      <c r="T42" s="277"/>
-      <c r="U42" s="215"/>
-      <c r="V42" s="216"/>
-      <c r="W42" s="216"/>
-      <c r="X42" s="216"/>
+      <c r="B42" s="224"/>
+      <c r="C42" s="225"/>
+      <c r="D42" s="225"/>
+      <c r="E42" s="225"/>
+      <c r="F42" s="225"/>
+      <c r="G42" s="225"/>
+      <c r="H42" s="226"/>
+      <c r="I42" s="220"/>
+      <c r="J42" s="211"/>
+      <c r="K42" s="211"/>
+      <c r="L42" s="227"/>
+      <c r="M42" s="231"/>
+      <c r="N42" s="232"/>
+      <c r="O42" s="232"/>
+      <c r="P42" s="232"/>
+      <c r="Q42" s="232"/>
+      <c r="R42" s="232"/>
+      <c r="S42" s="232"/>
+      <c r="T42" s="233"/>
+      <c r="U42" s="220"/>
+      <c r="V42" s="211"/>
+      <c r="W42" s="211"/>
+      <c r="X42" s="211"/>
       <c r="Y42" s="87"/>
       <c r="Z42" s="87"/>
       <c r="AA42" s="87"/>
@@ -7762,20 +7766,20 @@
       <c r="AF42" s="87"/>
       <c r="AG42" s="91"/>
       <c r="AH42" s="91"/>
-      <c r="AI42" s="216"/>
-      <c r="AJ42" s="216"/>
-      <c r="AL42" s="269"/>
-      <c r="AM42" s="269"/>
-      <c r="AN42" s="269"/>
-      <c r="AO42" s="269"/>
-      <c r="AS42" s="270"/>
-      <c r="AT42" s="228"/>
+      <c r="AI42" s="211"/>
+      <c r="AJ42" s="211"/>
+      <c r="AL42" s="213"/>
+      <c r="AM42" s="213"/>
+      <c r="AN42" s="213"/>
+      <c r="AO42" s="213"/>
+      <c r="AS42" s="214"/>
+      <c r="AT42" s="215"/>
       <c r="BE42" s="1"/>
       <c r="BF42" s="1"/>
       <c r="BG42" s="1"/>
       <c r="BH42" s="1"/>
     </row>
-    <row r="43" spans="1:60" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:60" s="2" customFormat="1" ht="18.75" customHeight="1">
       <c r="A43" s="89"/>
       <c r="B43" s="120"/>
       <c r="C43" s="120"/>
@@ -7825,7 +7829,7 @@
       <c r="BG43" s="1"/>
       <c r="BH43" s="1"/>
     </row>
-    <row r="44" spans="1:60" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:60" ht="39.75" customHeight="1">
       <c r="A44" s="95"/>
       <c r="B44" s="87"/>
       <c r="C44" s="87"/>
@@ -7838,14 +7842,14 @@
       <c r="J44" s="88"/>
       <c r="K44" s="88"/>
       <c r="L44" s="88"/>
-      <c r="M44" s="271"/>
-      <c r="N44" s="271"/>
-      <c r="O44" s="271"/>
-      <c r="P44" s="271"/>
-      <c r="Q44" s="271"/>
-      <c r="R44" s="271"/>
-      <c r="S44" s="271"/>
-      <c r="T44" s="271"/>
+      <c r="M44" s="216"/>
+      <c r="N44" s="216"/>
+      <c r="O44" s="216"/>
+      <c r="P44" s="216"/>
+      <c r="Q44" s="216"/>
+      <c r="R44" s="216"/>
+      <c r="S44" s="216"/>
+      <c r="T44" s="216"/>
       <c r="U44" s="88"/>
       <c r="V44" s="88"/>
       <c r="W44" s="88"/>
@@ -7861,10 +7865,10 @@
       <c r="AD44" s="218"/>
       <c r="AE44" s="218"/>
       <c r="AF44" s="219"/>
-      <c r="AG44" s="215" t="s">
+      <c r="AG44" s="220" t="s">
         <v>16</v>
       </c>
-      <c r="AH44" s="216"/>
+      <c r="AH44" s="211"/>
       <c r="AI44" s="88"/>
       <c r="AJ44" s="88"/>
       <c r="AK44" s="65"/>
@@ -7878,7 +7882,7 @@
       <c r="AS44" s="82"/>
       <c r="AT44" s="73"/>
     </row>
-    <row r="45" spans="1:60" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:60" ht="18.75" customHeight="1">
       <c r="A45" s="86"/>
       <c r="K45" s="123"/>
       <c r="L45" s="116"/>
@@ -7891,18 +7895,18 @@
       <c r="S45" s="124"/>
       <c r="T45" s="124"/>
       <c r="W45" s="123"/>
-      <c r="X45" s="283" t="s">
+      <c r="X45" s="212" t="s">
         <v>143</v>
       </c>
-      <c r="Y45" s="283"/>
-      <c r="Z45" s="283"/>
-      <c r="AA45" s="283"/>
-      <c r="AB45" s="283"/>
-      <c r="AC45" s="283"/>
-      <c r="AD45" s="283"/>
-      <c r="AE45" s="283"/>
-      <c r="AF45" s="283"/>
-      <c r="AG45" s="283"/>
+      <c r="Y45" s="212"/>
+      <c r="Z45" s="212"/>
+      <c r="AA45" s="212"/>
+      <c r="AB45" s="212"/>
+      <c r="AC45" s="212"/>
+      <c r="AD45" s="212"/>
+      <c r="AE45" s="212"/>
+      <c r="AF45" s="212"/>
+      <c r="AG45" s="212"/>
       <c r="AJ45" s="123"/>
       <c r="AK45" s="65"/>
       <c r="AL45" s="65"/>
@@ -7915,103 +7919,103 @@
       <c r="AS45" s="113"/>
       <c r="AT45" s="105"/>
     </row>
-    <row r="46" spans="1:60" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:60" ht="18.75" customHeight="1">
       <c r="A46" s="86"/>
       <c r="K46" s="123"/>
       <c r="L46" s="65"/>
-      <c r="M46" s="220" t="s">
+      <c r="M46" s="202" t="s">
         <v>82</v>
       </c>
-      <c r="N46" s="220"/>
-      <c r="O46" s="220"/>
-      <c r="P46" s="220"/>
-      <c r="Q46" s="220"/>
-      <c r="R46" s="220"/>
-      <c r="S46" s="220"/>
-      <c r="T46" s="220"/>
+      <c r="N46" s="202"/>
+      <c r="O46" s="202"/>
+      <c r="P46" s="202"/>
+      <c r="Q46" s="202"/>
+      <c r="R46" s="202"/>
+      <c r="S46" s="202"/>
+      <c r="T46" s="202"/>
       <c r="W46" s="123"/>
-      <c r="X46" s="283"/>
-      <c r="Y46" s="283"/>
-      <c r="Z46" s="283"/>
-      <c r="AA46" s="283"/>
-      <c r="AB46" s="283"/>
-      <c r="AC46" s="283"/>
-      <c r="AD46" s="283"/>
-      <c r="AE46" s="283"/>
-      <c r="AF46" s="283"/>
-      <c r="AG46" s="283"/>
+      <c r="X46" s="212"/>
+      <c r="Y46" s="212"/>
+      <c r="Z46" s="212"/>
+      <c r="AA46" s="212"/>
+      <c r="AB46" s="212"/>
+      <c r="AC46" s="212"/>
+      <c r="AD46" s="212"/>
+      <c r="AE46" s="212"/>
+      <c r="AF46" s="212"/>
+      <c r="AG46" s="212"/>
       <c r="AI46" s="88"/>
       <c r="AJ46" s="88"/>
-      <c r="AK46" s="220" t="s">
+      <c r="AK46" s="202" t="s">
         <v>84</v>
       </c>
-      <c r="AL46" s="220"/>
-      <c r="AM46" s="220"/>
-      <c r="AN46" s="220"/>
-      <c r="AO46" s="220"/>
-      <c r="AP46" s="220"/>
-      <c r="AQ46" s="220"/>
-      <c r="AR46" s="220"/>
+      <c r="AL46" s="202"/>
+      <c r="AM46" s="202"/>
+      <c r="AN46" s="202"/>
+      <c r="AO46" s="202"/>
+      <c r="AP46" s="202"/>
+      <c r="AQ46" s="202"/>
+      <c r="AR46" s="202"/>
       <c r="AS46" s="82"/>
       <c r="AT46" s="73"/>
     </row>
-    <row r="47" spans="1:60" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:60" ht="39.75" customHeight="1">
       <c r="A47" s="86"/>
-      <c r="K47" s="245" t="s">
+      <c r="K47" s="203" t="s">
         <v>44</v>
       </c>
-      <c r="L47" s="245"/>
-      <c r="M47" s="278">
+      <c r="L47" s="203"/>
+      <c r="M47" s="204">
         <v>20000</v>
       </c>
-      <c r="N47" s="278"/>
-      <c r="O47" s="278"/>
-      <c r="P47" s="278"/>
-      <c r="Q47" s="278"/>
-      <c r="R47" s="278"/>
-      <c r="S47" s="278"/>
-      <c r="T47" s="278"/>
-      <c r="U47" s="254" t="s">
+      <c r="N47" s="204"/>
+      <c r="O47" s="204"/>
+      <c r="P47" s="204"/>
+      <c r="Q47" s="204"/>
+      <c r="R47" s="204"/>
+      <c r="S47" s="204"/>
+      <c r="T47" s="204"/>
+      <c r="U47" s="205" t="s">
         <v>28</v>
       </c>
-      <c r="V47" s="254"/>
-      <c r="W47" s="245" t="s">
+      <c r="V47" s="205"/>
+      <c r="W47" s="203" t="s">
         <v>145</v>
       </c>
-      <c r="X47" s="255"/>
-      <c r="Y47" s="279"/>
-      <c r="Z47" s="280"/>
-      <c r="AA47" s="280"/>
-      <c r="AB47" s="280"/>
-      <c r="AC47" s="280"/>
-      <c r="AD47" s="280"/>
-      <c r="AE47" s="280"/>
-      <c r="AF47" s="281"/>
-      <c r="AG47" s="282" t="s">
+      <c r="X47" s="206"/>
+      <c r="Y47" s="207"/>
+      <c r="Z47" s="208"/>
+      <c r="AA47" s="208"/>
+      <c r="AB47" s="208"/>
+      <c r="AC47" s="208"/>
+      <c r="AD47" s="208"/>
+      <c r="AE47" s="208"/>
+      <c r="AF47" s="209"/>
+      <c r="AG47" s="210" t="s">
         <v>28</v>
       </c>
-      <c r="AH47" s="254"/>
-      <c r="AI47" s="216" t="s">
+      <c r="AH47" s="205"/>
+      <c r="AI47" s="211" t="s">
         <v>46</v>
       </c>
-      <c r="AJ47" s="216"/>
-      <c r="AK47" s="287" t="e">
+      <c r="AJ47" s="211"/>
+      <c r="AK47" s="195" t="e">
         <f>IF(Y36="", "", IF(B41*(M41+IF(Y44=0, 0,Y40/Y44)) *20000&lt;Y47,"エラー",ROUNDDOWN(B41*(M41+IF(Y44=0, 0,Y40/Y44)) *20000-IF(Y36=AW35,Y47,0), -2)))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AL47" s="287"/>
-      <c r="AM47" s="287"/>
-      <c r="AN47" s="287"/>
-      <c r="AO47" s="287"/>
-      <c r="AP47" s="287"/>
-      <c r="AQ47" s="287"/>
-      <c r="AR47" s="287"/>
+      <c r="AL47" s="195"/>
+      <c r="AM47" s="195"/>
+      <c r="AN47" s="195"/>
+      <c r="AO47" s="195"/>
+      <c r="AP47" s="195"/>
+      <c r="AQ47" s="195"/>
+      <c r="AR47" s="195"/>
       <c r="AS47" s="81" t="s">
         <v>28</v>
       </c>
       <c r="AT47" s="94"/>
     </row>
-    <row r="48" spans="1:60" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:60" ht="18.75" customHeight="1">
       <c r="A48" s="86"/>
       <c r="K48" s="123"/>
       <c r="L48" s="116"/>
@@ -8028,16 +8032,16 @@
       <c r="AF48" s="125"/>
       <c r="AI48" s="88"/>
       <c r="AJ48" s="88"/>
-      <c r="AK48" s="288" t="s">
+      <c r="AK48" s="196" t="s">
         <v>85</v>
       </c>
-      <c r="AL48" s="288"/>
-      <c r="AM48" s="288"/>
-      <c r="AN48" s="288"/>
-      <c r="AO48" s="288"/>
-      <c r="AP48" s="288"/>
-      <c r="AQ48" s="288"/>
-      <c r="AR48" s="288"/>
+      <c r="AL48" s="196"/>
+      <c r="AM48" s="196"/>
+      <c r="AN48" s="196"/>
+      <c r="AO48" s="196"/>
+      <c r="AP48" s="196"/>
+      <c r="AQ48" s="196"/>
+      <c r="AR48" s="196"/>
       <c r="AS48" s="65"/>
       <c r="AT48" s="94"/>
       <c r="BE48" s="7"/>
@@ -8045,7 +8049,7 @@
       <c r="BG48" s="5"/>
       <c r="BH48" s="5"/>
     </row>
-    <row r="49" spans="1:60" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:60" ht="13.5" customHeight="1" thickBot="1">
       <c r="A49" s="86"/>
       <c r="K49" s="123"/>
       <c r="L49" s="116"/>
@@ -8077,7 +8081,7 @@
       <c r="BG49" s="5"/>
       <c r="BH49" s="5"/>
     </row>
-    <row r="50" spans="1:60" ht="39.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:60" ht="39.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="A50" s="127" t="s">
         <v>113</v>
       </c>
@@ -8096,23 +8100,23 @@
       <c r="AH50" s="104"/>
       <c r="AI50" s="88"/>
       <c r="AJ50" s="129"/>
-      <c r="AK50" s="289" t="e">
+      <c r="AK50" s="197" t="e">
         <f>IF(AK47="","",IF(AK47="エラー","エラー",MIN(AK47,AK36 )))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AL50" s="290"/>
-      <c r="AM50" s="290"/>
-      <c r="AN50" s="290"/>
-      <c r="AO50" s="290"/>
-      <c r="AP50" s="290"/>
-      <c r="AQ50" s="290"/>
-      <c r="AR50" s="291"/>
+      <c r="AL50" s="198"/>
+      <c r="AM50" s="198"/>
+      <c r="AN50" s="198"/>
+      <c r="AO50" s="198"/>
+      <c r="AP50" s="198"/>
+      <c r="AQ50" s="198"/>
+      <c r="AR50" s="199"/>
       <c r="AS50" s="81" t="s">
         <v>28</v>
       </c>
       <c r="AT50" s="94"/>
     </row>
-    <row r="51" spans="1:60" s="5" customFormat="1" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:60" s="5" customFormat="1" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="A51" s="130"/>
       <c r="B51" s="131"/>
       <c r="C51" s="131"/>
@@ -8174,7 +8178,7 @@
       <c r="BG51" s="1"/>
       <c r="BH51" s="1"/>
     </row>
-    <row r="52" spans="1:60" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:60" ht="16.5" customHeight="1">
       <c r="A52" s="136" t="s">
         <v>86</v>
       </c>
@@ -8227,7 +8231,7 @@
       <c r="AV52" s="3"/>
       <c r="AW52" s="3"/>
     </row>
-    <row r="53" spans="1:60" ht="16.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="53" spans="1:60" ht="16.5" customHeight="1">
       <c r="A53" s="137" t="s">
         <v>157</v>
       </c>
@@ -8280,7 +8284,7 @@
       <c r="AV53" s="3"/>
       <c r="AW53" s="3"/>
     </row>
-    <row r="54" spans="1:60" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:60" ht="16.5" customHeight="1">
       <c r="A54" s="139"/>
       <c r="B54" s="138"/>
       <c r="C54" s="138"/>
@@ -8331,7 +8335,7 @@
       <c r="AV54" s="3"/>
       <c r="AW54" s="3"/>
     </row>
-    <row r="55" spans="1:60" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:60" ht="21.95" customHeight="1">
       <c r="A55" s="140" t="s">
         <v>87</v>
       </c>
@@ -8383,329 +8387,329 @@
       <c r="AU55" s="5"/>
       <c r="AV55" s="5"/>
     </row>
-    <row r="56" spans="1:60" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:60" ht="21.95" customHeight="1">
       <c r="A56" s="142" t="s">
         <v>0</v>
       </c>
-      <c r="B56" s="292" t="s">
+      <c r="B56" s="200" t="s">
         <v>146</v>
       </c>
-      <c r="C56" s="292"/>
-      <c r="D56" s="292"/>
-      <c r="E56" s="292"/>
-      <c r="F56" s="292"/>
-      <c r="G56" s="292"/>
-      <c r="H56" s="292"/>
-      <c r="I56" s="292"/>
-      <c r="J56" s="292"/>
-      <c r="K56" s="292"/>
-      <c r="L56" s="292"/>
-      <c r="M56" s="292"/>
-      <c r="N56" s="292"/>
-      <c r="O56" s="292"/>
-      <c r="P56" s="292"/>
-      <c r="Q56" s="292"/>
-      <c r="R56" s="292"/>
-      <c r="S56" s="292"/>
-      <c r="T56" s="292"/>
-      <c r="U56" s="292"/>
-      <c r="V56" s="292"/>
-      <c r="W56" s="292"/>
-      <c r="X56" s="292"/>
-      <c r="Y56" s="292"/>
-      <c r="Z56" s="292"/>
-      <c r="AA56" s="292"/>
-      <c r="AB56" s="292"/>
-      <c r="AC56" s="292"/>
-      <c r="AD56" s="292"/>
-      <c r="AE56" s="292"/>
-      <c r="AF56" s="292"/>
-      <c r="AG56" s="292"/>
-      <c r="AH56" s="292"/>
-      <c r="AI56" s="292"/>
-      <c r="AJ56" s="292"/>
-      <c r="AK56" s="292"/>
-      <c r="AL56" s="292"/>
-      <c r="AM56" s="292"/>
-      <c r="AN56" s="292"/>
-      <c r="AO56" s="292"/>
-      <c r="AP56" s="292"/>
-      <c r="AQ56" s="292"/>
-      <c r="AR56" s="292"/>
-      <c r="AS56" s="292"/>
-      <c r="AT56" s="292"/>
+      <c r="C56" s="200"/>
+      <c r="D56" s="200"/>
+      <c r="E56" s="200"/>
+      <c r="F56" s="200"/>
+      <c r="G56" s="200"/>
+      <c r="H56" s="200"/>
+      <c r="I56" s="200"/>
+      <c r="J56" s="200"/>
+      <c r="K56" s="200"/>
+      <c r="L56" s="200"/>
+      <c r="M56" s="200"/>
+      <c r="N56" s="200"/>
+      <c r="O56" s="200"/>
+      <c r="P56" s="200"/>
+      <c r="Q56" s="200"/>
+      <c r="R56" s="200"/>
+      <c r="S56" s="200"/>
+      <c r="T56" s="200"/>
+      <c r="U56" s="200"/>
+      <c r="V56" s="200"/>
+      <c r="W56" s="200"/>
+      <c r="X56" s="200"/>
+      <c r="Y56" s="200"/>
+      <c r="Z56" s="200"/>
+      <c r="AA56" s="200"/>
+      <c r="AB56" s="200"/>
+      <c r="AC56" s="200"/>
+      <c r="AD56" s="200"/>
+      <c r="AE56" s="200"/>
+      <c r="AF56" s="200"/>
+      <c r="AG56" s="200"/>
+      <c r="AH56" s="200"/>
+      <c r="AI56" s="200"/>
+      <c r="AJ56" s="200"/>
+      <c r="AK56" s="200"/>
+      <c r="AL56" s="200"/>
+      <c r="AM56" s="200"/>
+      <c r="AN56" s="200"/>
+      <c r="AO56" s="200"/>
+      <c r="AP56" s="200"/>
+      <c r="AQ56" s="200"/>
+      <c r="AR56" s="200"/>
+      <c r="AS56" s="200"/>
+      <c r="AT56" s="200"/>
       <c r="AU56" s="4"/>
       <c r="AV56" s="4"/>
       <c r="AW56" s="4"/>
     </row>
-    <row r="57" spans="1:60" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:60" ht="21.95" customHeight="1">
       <c r="A57" s="143" t="s">
         <v>88</v>
       </c>
-      <c r="B57" s="292" t="s">
+      <c r="B57" s="200" t="s">
         <v>147</v>
       </c>
-      <c r="C57" s="292"/>
-      <c r="D57" s="292"/>
-      <c r="E57" s="292"/>
-      <c r="F57" s="292"/>
-      <c r="G57" s="292"/>
-      <c r="H57" s="292"/>
-      <c r="I57" s="292"/>
-      <c r="J57" s="292"/>
-      <c r="K57" s="292"/>
-      <c r="L57" s="292"/>
-      <c r="M57" s="292"/>
-      <c r="N57" s="292"/>
-      <c r="O57" s="292"/>
-      <c r="P57" s="292"/>
-      <c r="Q57" s="292"/>
-      <c r="R57" s="292"/>
-      <c r="S57" s="292"/>
-      <c r="T57" s="292"/>
-      <c r="U57" s="292"/>
-      <c r="V57" s="292"/>
-      <c r="W57" s="292"/>
-      <c r="X57" s="292"/>
-      <c r="Y57" s="292"/>
-      <c r="Z57" s="292"/>
-      <c r="AA57" s="292"/>
-      <c r="AB57" s="292"/>
-      <c r="AC57" s="292"/>
-      <c r="AD57" s="292"/>
-      <c r="AE57" s="292"/>
-      <c r="AF57" s="292"/>
-      <c r="AG57" s="292"/>
-      <c r="AH57" s="292"/>
-      <c r="AI57" s="292"/>
-      <c r="AJ57" s="292"/>
-      <c r="AK57" s="292"/>
-      <c r="AL57" s="292"/>
-      <c r="AM57" s="292"/>
-      <c r="AN57" s="292"/>
-      <c r="AO57" s="292"/>
-      <c r="AP57" s="292"/>
-      <c r="AQ57" s="292"/>
-      <c r="AR57" s="292"/>
-      <c r="AS57" s="292"/>
-      <c r="AT57" s="292"/>
+      <c r="C57" s="200"/>
+      <c r="D57" s="200"/>
+      <c r="E57" s="200"/>
+      <c r="F57" s="200"/>
+      <c r="G57" s="200"/>
+      <c r="H57" s="200"/>
+      <c r="I57" s="200"/>
+      <c r="J57" s="200"/>
+      <c r="K57" s="200"/>
+      <c r="L57" s="200"/>
+      <c r="M57" s="200"/>
+      <c r="N57" s="200"/>
+      <c r="O57" s="200"/>
+      <c r="P57" s="200"/>
+      <c r="Q57" s="200"/>
+      <c r="R57" s="200"/>
+      <c r="S57" s="200"/>
+      <c r="T57" s="200"/>
+      <c r="U57" s="200"/>
+      <c r="V57" s="200"/>
+      <c r="W57" s="200"/>
+      <c r="X57" s="200"/>
+      <c r="Y57" s="200"/>
+      <c r="Z57" s="200"/>
+      <c r="AA57" s="200"/>
+      <c r="AB57" s="200"/>
+      <c r="AC57" s="200"/>
+      <c r="AD57" s="200"/>
+      <c r="AE57" s="200"/>
+      <c r="AF57" s="200"/>
+      <c r="AG57" s="200"/>
+      <c r="AH57" s="200"/>
+      <c r="AI57" s="200"/>
+      <c r="AJ57" s="200"/>
+      <c r="AK57" s="200"/>
+      <c r="AL57" s="200"/>
+      <c r="AM57" s="200"/>
+      <c r="AN57" s="200"/>
+      <c r="AO57" s="200"/>
+      <c r="AP57" s="200"/>
+      <c r="AQ57" s="200"/>
+      <c r="AR57" s="200"/>
+      <c r="AS57" s="200"/>
+      <c r="AT57" s="200"/>
       <c r="AU57" s="4"/>
       <c r="AV57" s="4"/>
       <c r="AW57" s="4"/>
     </row>
-    <row r="58" spans="1:60" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:60" ht="21.95" customHeight="1">
       <c r="A58" s="143" t="s">
         <v>89</v>
       </c>
-      <c r="B58" s="292" t="s">
+      <c r="B58" s="200" t="s">
         <v>148</v>
       </c>
-      <c r="C58" s="292"/>
-      <c r="D58" s="292"/>
-      <c r="E58" s="292"/>
-      <c r="F58" s="292"/>
-      <c r="G58" s="292"/>
-      <c r="H58" s="292"/>
-      <c r="I58" s="292"/>
-      <c r="J58" s="292"/>
-      <c r="K58" s="292"/>
-      <c r="L58" s="292"/>
-      <c r="M58" s="292"/>
-      <c r="N58" s="292"/>
-      <c r="O58" s="292"/>
-      <c r="P58" s="292"/>
-      <c r="Q58" s="292"/>
-      <c r="R58" s="292"/>
-      <c r="S58" s="292"/>
-      <c r="T58" s="292"/>
-      <c r="U58" s="292"/>
-      <c r="V58" s="292"/>
-      <c r="W58" s="292"/>
-      <c r="X58" s="292"/>
-      <c r="Y58" s="292"/>
-      <c r="Z58" s="292"/>
-      <c r="AA58" s="292"/>
-      <c r="AB58" s="292"/>
-      <c r="AC58" s="292"/>
-      <c r="AD58" s="292"/>
-      <c r="AE58" s="292"/>
-      <c r="AF58" s="292"/>
-      <c r="AG58" s="292"/>
-      <c r="AH58" s="292"/>
-      <c r="AI58" s="292"/>
-      <c r="AJ58" s="292"/>
-      <c r="AK58" s="292"/>
-      <c r="AL58" s="292"/>
-      <c r="AM58" s="292"/>
-      <c r="AN58" s="292"/>
-      <c r="AO58" s="292"/>
-      <c r="AP58" s="292"/>
-      <c r="AQ58" s="292"/>
-      <c r="AR58" s="292"/>
-      <c r="AS58" s="292"/>
-      <c r="AT58" s="292"/>
+      <c r="C58" s="200"/>
+      <c r="D58" s="200"/>
+      <c r="E58" s="200"/>
+      <c r="F58" s="200"/>
+      <c r="G58" s="200"/>
+      <c r="H58" s="200"/>
+      <c r="I58" s="200"/>
+      <c r="J58" s="200"/>
+      <c r="K58" s="200"/>
+      <c r="L58" s="200"/>
+      <c r="M58" s="200"/>
+      <c r="N58" s="200"/>
+      <c r="O58" s="200"/>
+      <c r="P58" s="200"/>
+      <c r="Q58" s="200"/>
+      <c r="R58" s="200"/>
+      <c r="S58" s="200"/>
+      <c r="T58" s="200"/>
+      <c r="U58" s="200"/>
+      <c r="V58" s="200"/>
+      <c r="W58" s="200"/>
+      <c r="X58" s="200"/>
+      <c r="Y58" s="200"/>
+      <c r="Z58" s="200"/>
+      <c r="AA58" s="200"/>
+      <c r="AB58" s="200"/>
+      <c r="AC58" s="200"/>
+      <c r="AD58" s="200"/>
+      <c r="AE58" s="200"/>
+      <c r="AF58" s="200"/>
+      <c r="AG58" s="200"/>
+      <c r="AH58" s="200"/>
+      <c r="AI58" s="200"/>
+      <c r="AJ58" s="200"/>
+      <c r="AK58" s="200"/>
+      <c r="AL58" s="200"/>
+      <c r="AM58" s="200"/>
+      <c r="AN58" s="200"/>
+      <c r="AO58" s="200"/>
+      <c r="AP58" s="200"/>
+      <c r="AQ58" s="200"/>
+      <c r="AR58" s="200"/>
+      <c r="AS58" s="200"/>
+      <c r="AT58" s="200"/>
       <c r="BE58" s="10"/>
       <c r="BF58" s="10"/>
       <c r="BG58" s="10"/>
       <c r="BH58" s="10"/>
     </row>
-    <row r="59" spans="1:60" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:60" ht="21.95" customHeight="1">
       <c r="A59" s="143" t="s">
         <v>90</v>
       </c>
-      <c r="B59" s="293" t="s">
+      <c r="B59" s="201" t="s">
         <v>161</v>
       </c>
-      <c r="C59" s="293"/>
-      <c r="D59" s="293"/>
-      <c r="E59" s="293"/>
-      <c r="F59" s="293"/>
-      <c r="G59" s="293"/>
-      <c r="H59" s="293"/>
-      <c r="I59" s="293"/>
-      <c r="J59" s="293"/>
-      <c r="K59" s="293"/>
-      <c r="L59" s="293"/>
-      <c r="M59" s="293"/>
-      <c r="N59" s="293"/>
-      <c r="O59" s="293"/>
-      <c r="P59" s="293"/>
-      <c r="Q59" s="293"/>
-      <c r="R59" s="293"/>
-      <c r="S59" s="293"/>
-      <c r="T59" s="293"/>
-      <c r="U59" s="293"/>
-      <c r="V59" s="293"/>
-      <c r="W59" s="293"/>
-      <c r="X59" s="293"/>
-      <c r="Y59" s="293"/>
-      <c r="Z59" s="293"/>
-      <c r="AA59" s="293"/>
-      <c r="AB59" s="293"/>
-      <c r="AC59" s="293"/>
-      <c r="AD59" s="293"/>
-      <c r="AE59" s="293"/>
-      <c r="AF59" s="293"/>
-      <c r="AG59" s="293"/>
-      <c r="AH59" s="293"/>
-      <c r="AI59" s="293"/>
-      <c r="AJ59" s="293"/>
-      <c r="AK59" s="293"/>
-      <c r="AL59" s="293"/>
-      <c r="AM59" s="293"/>
-      <c r="AN59" s="293"/>
-      <c r="AO59" s="293"/>
-      <c r="AP59" s="293"/>
-      <c r="AQ59" s="293"/>
-      <c r="AR59" s="293"/>
-      <c r="AS59" s="293"/>
-      <c r="AT59" s="293"/>
+      <c r="C59" s="201"/>
+      <c r="D59" s="201"/>
+      <c r="E59" s="201"/>
+      <c r="F59" s="201"/>
+      <c r="G59" s="201"/>
+      <c r="H59" s="201"/>
+      <c r="I59" s="201"/>
+      <c r="J59" s="201"/>
+      <c r="K59" s="201"/>
+      <c r="L59" s="201"/>
+      <c r="M59" s="201"/>
+      <c r="N59" s="201"/>
+      <c r="O59" s="201"/>
+      <c r="P59" s="201"/>
+      <c r="Q59" s="201"/>
+      <c r="R59" s="201"/>
+      <c r="S59" s="201"/>
+      <c r="T59" s="201"/>
+      <c r="U59" s="201"/>
+      <c r="V59" s="201"/>
+      <c r="W59" s="201"/>
+      <c r="X59" s="201"/>
+      <c r="Y59" s="201"/>
+      <c r="Z59" s="201"/>
+      <c r="AA59" s="201"/>
+      <c r="AB59" s="201"/>
+      <c r="AC59" s="201"/>
+      <c r="AD59" s="201"/>
+      <c r="AE59" s="201"/>
+      <c r="AF59" s="201"/>
+      <c r="AG59" s="201"/>
+      <c r="AH59" s="201"/>
+      <c r="AI59" s="201"/>
+      <c r="AJ59" s="201"/>
+      <c r="AK59" s="201"/>
+      <c r="AL59" s="201"/>
+      <c r="AM59" s="201"/>
+      <c r="AN59" s="201"/>
+      <c r="AO59" s="201"/>
+      <c r="AP59" s="201"/>
+      <c r="AQ59" s="201"/>
+      <c r="AR59" s="201"/>
+      <c r="AS59" s="201"/>
+      <c r="AT59" s="201"/>
     </row>
-    <row r="60" spans="1:60" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:60" ht="21.95" customHeight="1">
       <c r="A60" s="143"/>
-      <c r="B60" s="293"/>
-      <c r="C60" s="293"/>
-      <c r="D60" s="293"/>
-      <c r="E60" s="293"/>
-      <c r="F60" s="293"/>
-      <c r="G60" s="293"/>
-      <c r="H60" s="293"/>
-      <c r="I60" s="293"/>
-      <c r="J60" s="293"/>
-      <c r="K60" s="293"/>
-      <c r="L60" s="293"/>
-      <c r="M60" s="293"/>
-      <c r="N60" s="293"/>
-      <c r="O60" s="293"/>
-      <c r="P60" s="293"/>
-      <c r="Q60" s="293"/>
-      <c r="R60" s="293"/>
-      <c r="S60" s="293"/>
-      <c r="T60" s="293"/>
-      <c r="U60" s="293"/>
-      <c r="V60" s="293"/>
-      <c r="W60" s="293"/>
-      <c r="X60" s="293"/>
-      <c r="Y60" s="293"/>
-      <c r="Z60" s="293"/>
-      <c r="AA60" s="293"/>
-      <c r="AB60" s="293"/>
-      <c r="AC60" s="293"/>
-      <c r="AD60" s="293"/>
-      <c r="AE60" s="293"/>
-      <c r="AF60" s="293"/>
-      <c r="AG60" s="293"/>
-      <c r="AH60" s="293"/>
-      <c r="AI60" s="293"/>
-      <c r="AJ60" s="293"/>
-      <c r="AK60" s="293"/>
-      <c r="AL60" s="293"/>
-      <c r="AM60" s="293"/>
-      <c r="AN60" s="293"/>
-      <c r="AO60" s="293"/>
-      <c r="AP60" s="293"/>
-      <c r="AQ60" s="293"/>
-      <c r="AR60" s="293"/>
-      <c r="AS60" s="293"/>
-      <c r="AT60" s="293"/>
+      <c r="B60" s="201"/>
+      <c r="C60" s="201"/>
+      <c r="D60" s="201"/>
+      <c r="E60" s="201"/>
+      <c r="F60" s="201"/>
+      <c r="G60" s="201"/>
+      <c r="H60" s="201"/>
+      <c r="I60" s="201"/>
+      <c r="J60" s="201"/>
+      <c r="K60" s="201"/>
+      <c r="L60" s="201"/>
+      <c r="M60" s="201"/>
+      <c r="N60" s="201"/>
+      <c r="O60" s="201"/>
+      <c r="P60" s="201"/>
+      <c r="Q60" s="201"/>
+      <c r="R60" s="201"/>
+      <c r="S60" s="201"/>
+      <c r="T60" s="201"/>
+      <c r="U60" s="201"/>
+      <c r="V60" s="201"/>
+      <c r="W60" s="201"/>
+      <c r="X60" s="201"/>
+      <c r="Y60" s="201"/>
+      <c r="Z60" s="201"/>
+      <c r="AA60" s="201"/>
+      <c r="AB60" s="201"/>
+      <c r="AC60" s="201"/>
+      <c r="AD60" s="201"/>
+      <c r="AE60" s="201"/>
+      <c r="AF60" s="201"/>
+      <c r="AG60" s="201"/>
+      <c r="AH60" s="201"/>
+      <c r="AI60" s="201"/>
+      <c r="AJ60" s="201"/>
+      <c r="AK60" s="201"/>
+      <c r="AL60" s="201"/>
+      <c r="AM60" s="201"/>
+      <c r="AN60" s="201"/>
+      <c r="AO60" s="201"/>
+      <c r="AP60" s="201"/>
+      <c r="AQ60" s="201"/>
+      <c r="AR60" s="201"/>
+      <c r="AS60" s="201"/>
+      <c r="AT60" s="201"/>
     </row>
-    <row r="61" spans="1:60" s="10" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:60" s="10" customFormat="1" ht="21.95" customHeight="1">
       <c r="A61" s="143" t="s">
         <v>91</v>
       </c>
-      <c r="B61" s="284" t="s">
+      <c r="B61" s="193" t="s">
         <v>155</v>
       </c>
-      <c r="C61" s="284"/>
-      <c r="D61" s="284"/>
-      <c r="E61" s="284"/>
-      <c r="F61" s="284"/>
-      <c r="G61" s="284"/>
-      <c r="H61" s="284"/>
-      <c r="I61" s="284"/>
-      <c r="J61" s="284"/>
-      <c r="K61" s="284"/>
-      <c r="L61" s="284"/>
-      <c r="M61" s="284"/>
-      <c r="N61" s="284"/>
-      <c r="O61" s="284"/>
-      <c r="P61" s="284"/>
-      <c r="Q61" s="284"/>
-      <c r="R61" s="284"/>
-      <c r="S61" s="284"/>
-      <c r="T61" s="284"/>
-      <c r="U61" s="284"/>
-      <c r="V61" s="284"/>
-      <c r="W61" s="284"/>
-      <c r="X61" s="284"/>
-      <c r="Y61" s="284"/>
-      <c r="Z61" s="284"/>
-      <c r="AA61" s="284"/>
-      <c r="AB61" s="284"/>
-      <c r="AC61" s="284"/>
-      <c r="AD61" s="284"/>
-      <c r="AE61" s="284"/>
-      <c r="AF61" s="284"/>
-      <c r="AG61" s="284"/>
-      <c r="AH61" s="284"/>
-      <c r="AI61" s="284"/>
-      <c r="AJ61" s="284"/>
-      <c r="AK61" s="284"/>
-      <c r="AL61" s="284"/>
-      <c r="AM61" s="284"/>
-      <c r="AN61" s="284"/>
-      <c r="AO61" s="284"/>
-      <c r="AP61" s="284"/>
-      <c r="AQ61" s="284"/>
-      <c r="AR61" s="284"/>
-      <c r="AS61" s="284"/>
-      <c r="AT61" s="284"/>
+      <c r="C61" s="193"/>
+      <c r="D61" s="193"/>
+      <c r="E61" s="193"/>
+      <c r="F61" s="193"/>
+      <c r="G61" s="193"/>
+      <c r="H61" s="193"/>
+      <c r="I61" s="193"/>
+      <c r="J61" s="193"/>
+      <c r="K61" s="193"/>
+      <c r="L61" s="193"/>
+      <c r="M61" s="193"/>
+      <c r="N61" s="193"/>
+      <c r="O61" s="193"/>
+      <c r="P61" s="193"/>
+      <c r="Q61" s="193"/>
+      <c r="R61" s="193"/>
+      <c r="S61" s="193"/>
+      <c r="T61" s="193"/>
+      <c r="U61" s="193"/>
+      <c r="V61" s="193"/>
+      <c r="W61" s="193"/>
+      <c r="X61" s="193"/>
+      <c r="Y61" s="193"/>
+      <c r="Z61" s="193"/>
+      <c r="AA61" s="193"/>
+      <c r="AB61" s="193"/>
+      <c r="AC61" s="193"/>
+      <c r="AD61" s="193"/>
+      <c r="AE61" s="193"/>
+      <c r="AF61" s="193"/>
+      <c r="AG61" s="193"/>
+      <c r="AH61" s="193"/>
+      <c r="AI61" s="193"/>
+      <c r="AJ61" s="193"/>
+      <c r="AK61" s="193"/>
+      <c r="AL61" s="193"/>
+      <c r="AM61" s="193"/>
+      <c r="AN61" s="193"/>
+      <c r="AO61" s="193"/>
+      <c r="AP61" s="193"/>
+      <c r="AQ61" s="193"/>
+      <c r="AR61" s="193"/>
+      <c r="AS61" s="193"/>
+      <c r="AT61" s="193"/>
       <c r="BE61" s="1"/>
       <c r="BF61" s="1"/>
       <c r="BG61" s="1"/>
       <c r="BH61" s="1"/>
     </row>
-    <row r="62" spans="1:60" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:60" ht="21.95" customHeight="1">
       <c r="A62" s="143" t="s">
         <v>92</v>
       </c>
@@ -8757,111 +8761,111 @@
       <c r="AS62" s="144"/>
       <c r="AT62" s="144"/>
     </row>
-    <row r="63" spans="1:60" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:60" ht="21.95" customHeight="1">
       <c r="A63" s="143" t="s">
         <v>93</v>
       </c>
-      <c r="B63" s="285" t="s">
+      <c r="B63" s="192" t="s">
         <v>150</v>
       </c>
-      <c r="C63" s="285"/>
-      <c r="D63" s="285"/>
-      <c r="E63" s="285"/>
-      <c r="F63" s="285"/>
-      <c r="G63" s="285"/>
-      <c r="H63" s="285"/>
-      <c r="I63" s="285"/>
-      <c r="J63" s="285"/>
-      <c r="K63" s="285"/>
-      <c r="L63" s="285"/>
-      <c r="M63" s="285"/>
-      <c r="N63" s="285"/>
-      <c r="O63" s="285"/>
-      <c r="P63" s="285"/>
-      <c r="Q63" s="285"/>
-      <c r="R63" s="285"/>
-      <c r="S63" s="285"/>
-      <c r="T63" s="285"/>
-      <c r="U63" s="285"/>
-      <c r="V63" s="285"/>
-      <c r="W63" s="285"/>
-      <c r="X63" s="285"/>
-      <c r="Y63" s="285"/>
-      <c r="Z63" s="285"/>
-      <c r="AA63" s="285"/>
-      <c r="AB63" s="285"/>
-      <c r="AC63" s="285"/>
-      <c r="AD63" s="285"/>
-      <c r="AE63" s="285"/>
-      <c r="AF63" s="285"/>
-      <c r="AG63" s="285"/>
-      <c r="AH63" s="285"/>
-      <c r="AI63" s="285"/>
-      <c r="AJ63" s="285"/>
-      <c r="AK63" s="285"/>
-      <c r="AL63" s="285"/>
-      <c r="AM63" s="285"/>
-      <c r="AN63" s="285"/>
-      <c r="AO63" s="285"/>
-      <c r="AP63" s="285"/>
-      <c r="AQ63" s="285"/>
-      <c r="AR63" s="285"/>
-      <c r="AS63" s="285"/>
-      <c r="AT63" s="285"/>
+      <c r="C63" s="192"/>
+      <c r="D63" s="192"/>
+      <c r="E63" s="192"/>
+      <c r="F63" s="192"/>
+      <c r="G63" s="192"/>
+      <c r="H63" s="192"/>
+      <c r="I63" s="192"/>
+      <c r="J63" s="192"/>
+      <c r="K63" s="192"/>
+      <c r="L63" s="192"/>
+      <c r="M63" s="192"/>
+      <c r="N63" s="192"/>
+      <c r="O63" s="192"/>
+      <c r="P63" s="192"/>
+      <c r="Q63" s="192"/>
+      <c r="R63" s="192"/>
+      <c r="S63" s="192"/>
+      <c r="T63" s="192"/>
+      <c r="U63" s="192"/>
+      <c r="V63" s="192"/>
+      <c r="W63" s="192"/>
+      <c r="X63" s="192"/>
+      <c r="Y63" s="192"/>
+      <c r="Z63" s="192"/>
+      <c r="AA63" s="192"/>
+      <c r="AB63" s="192"/>
+      <c r="AC63" s="192"/>
+      <c r="AD63" s="192"/>
+      <c r="AE63" s="192"/>
+      <c r="AF63" s="192"/>
+      <c r="AG63" s="192"/>
+      <c r="AH63" s="192"/>
+      <c r="AI63" s="192"/>
+      <c r="AJ63" s="192"/>
+      <c r="AK63" s="192"/>
+      <c r="AL63" s="192"/>
+      <c r="AM63" s="192"/>
+      <c r="AN63" s="192"/>
+      <c r="AO63" s="192"/>
+      <c r="AP63" s="192"/>
+      <c r="AQ63" s="192"/>
+      <c r="AR63" s="192"/>
+      <c r="AS63" s="192"/>
+      <c r="AT63" s="192"/>
     </row>
-    <row r="64" spans="1:60" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:60" ht="21.95" customHeight="1">
       <c r="A64" s="143" t="s">
         <v>124</v>
       </c>
-      <c r="B64" s="286" t="s">
+      <c r="B64" s="194" t="s">
         <v>151</v>
       </c>
-      <c r="C64" s="284"/>
-      <c r="D64" s="284"/>
-      <c r="E64" s="284"/>
-      <c r="F64" s="284"/>
-      <c r="G64" s="284"/>
-      <c r="H64" s="284"/>
-      <c r="I64" s="284"/>
-      <c r="J64" s="284"/>
-      <c r="K64" s="284"/>
-      <c r="L64" s="284"/>
-      <c r="M64" s="284"/>
-      <c r="N64" s="284"/>
-      <c r="O64" s="284"/>
-      <c r="P64" s="284"/>
-      <c r="Q64" s="284"/>
-      <c r="R64" s="284"/>
-      <c r="S64" s="284"/>
-      <c r="T64" s="284"/>
-      <c r="U64" s="284"/>
-      <c r="V64" s="284"/>
-      <c r="W64" s="284"/>
-      <c r="X64" s="284"/>
-      <c r="Y64" s="284"/>
-      <c r="Z64" s="284"/>
-      <c r="AA64" s="284"/>
-      <c r="AB64" s="284"/>
-      <c r="AC64" s="284"/>
-      <c r="AD64" s="284"/>
-      <c r="AE64" s="284"/>
-      <c r="AF64" s="284"/>
-      <c r="AG64" s="284"/>
-      <c r="AH64" s="284"/>
-      <c r="AI64" s="284"/>
-      <c r="AJ64" s="284"/>
-      <c r="AK64" s="284"/>
-      <c r="AL64" s="284"/>
-      <c r="AM64" s="284"/>
-      <c r="AN64" s="284"/>
-      <c r="AO64" s="284"/>
-      <c r="AP64" s="284"/>
-      <c r="AQ64" s="284"/>
-      <c r="AR64" s="284"/>
-      <c r="AS64" s="284"/>
-      <c r="AT64" s="284"/>
+      <c r="C64" s="193"/>
+      <c r="D64" s="193"/>
+      <c r="E64" s="193"/>
+      <c r="F64" s="193"/>
+      <c r="G64" s="193"/>
+      <c r="H64" s="193"/>
+      <c r="I64" s="193"/>
+      <c r="J64" s="193"/>
+      <c r="K64" s="193"/>
+      <c r="L64" s="193"/>
+      <c r="M64" s="193"/>
+      <c r="N64" s="193"/>
+      <c r="O64" s="193"/>
+      <c r="P64" s="193"/>
+      <c r="Q64" s="193"/>
+      <c r="R64" s="193"/>
+      <c r="S64" s="193"/>
+      <c r="T64" s="193"/>
+      <c r="U64" s="193"/>
+      <c r="V64" s="193"/>
+      <c r="W64" s="193"/>
+      <c r="X64" s="193"/>
+      <c r="Y64" s="193"/>
+      <c r="Z64" s="193"/>
+      <c r="AA64" s="193"/>
+      <c r="AB64" s="193"/>
+      <c r="AC64" s="193"/>
+      <c r="AD64" s="193"/>
+      <c r="AE64" s="193"/>
+      <c r="AF64" s="193"/>
+      <c r="AG64" s="193"/>
+      <c r="AH64" s="193"/>
+      <c r="AI64" s="193"/>
+      <c r="AJ64" s="193"/>
+      <c r="AK64" s="193"/>
+      <c r="AL64" s="193"/>
+      <c r="AM64" s="193"/>
+      <c r="AN64" s="193"/>
+      <c r="AO64" s="193"/>
+      <c r="AP64" s="193"/>
+      <c r="AQ64" s="193"/>
+      <c r="AR64" s="193"/>
+      <c r="AS64" s="193"/>
+      <c r="AT64" s="193"/>
     </row>
-    <row r="65" spans="1:262" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:262" ht="21.95" customHeight="1">
       <c r="A65" s="143" t="s">
         <v>128</v>
       </c>
@@ -8913,211 +8917,211 @@
       <c r="AS65" s="144"/>
       <c r="AT65" s="144"/>
     </row>
-    <row r="66" spans="1:262" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:262" ht="21.95" customHeight="1">
       <c r="A66" s="144">
         <v>10</v>
       </c>
-      <c r="B66" s="285" t="s">
+      <c r="B66" s="192" t="s">
         <v>152</v>
       </c>
-      <c r="C66" s="285"/>
-      <c r="D66" s="285"/>
-      <c r="E66" s="285"/>
-      <c r="F66" s="285"/>
-      <c r="G66" s="285"/>
-      <c r="H66" s="285"/>
-      <c r="I66" s="285"/>
-      <c r="J66" s="285"/>
-      <c r="K66" s="285"/>
-      <c r="L66" s="285"/>
-      <c r="M66" s="285"/>
-      <c r="N66" s="285"/>
-      <c r="O66" s="285"/>
-      <c r="P66" s="285"/>
-      <c r="Q66" s="285"/>
-      <c r="R66" s="285"/>
-      <c r="S66" s="285"/>
-      <c r="T66" s="285"/>
-      <c r="U66" s="285"/>
-      <c r="V66" s="285"/>
-      <c r="W66" s="285"/>
-      <c r="X66" s="285"/>
-      <c r="Y66" s="285"/>
-      <c r="Z66" s="285"/>
-      <c r="AA66" s="285"/>
-      <c r="AB66" s="285"/>
-      <c r="AC66" s="285"/>
-      <c r="AD66" s="285"/>
-      <c r="AE66" s="285"/>
-      <c r="AF66" s="285"/>
-      <c r="AG66" s="285"/>
-      <c r="AH66" s="285"/>
-      <c r="AI66" s="285"/>
-      <c r="AJ66" s="285"/>
-      <c r="AK66" s="285"/>
-      <c r="AL66" s="285"/>
-      <c r="AM66" s="285"/>
-      <c r="AN66" s="285"/>
-      <c r="AO66" s="285"/>
-      <c r="AP66" s="285"/>
-      <c r="AQ66" s="285"/>
-      <c r="AR66" s="285"/>
-      <c r="AS66" s="285"/>
-      <c r="AT66" s="285"/>
+      <c r="C66" s="192"/>
+      <c r="D66" s="192"/>
+      <c r="E66" s="192"/>
+      <c r="F66" s="192"/>
+      <c r="G66" s="192"/>
+      <c r="H66" s="192"/>
+      <c r="I66" s="192"/>
+      <c r="J66" s="192"/>
+      <c r="K66" s="192"/>
+      <c r="L66" s="192"/>
+      <c r="M66" s="192"/>
+      <c r="N66" s="192"/>
+      <c r="O66" s="192"/>
+      <c r="P66" s="192"/>
+      <c r="Q66" s="192"/>
+      <c r="R66" s="192"/>
+      <c r="S66" s="192"/>
+      <c r="T66" s="192"/>
+      <c r="U66" s="192"/>
+      <c r="V66" s="192"/>
+      <c r="W66" s="192"/>
+      <c r="X66" s="192"/>
+      <c r="Y66" s="192"/>
+      <c r="Z66" s="192"/>
+      <c r="AA66" s="192"/>
+      <c r="AB66" s="192"/>
+      <c r="AC66" s="192"/>
+      <c r="AD66" s="192"/>
+      <c r="AE66" s="192"/>
+      <c r="AF66" s="192"/>
+      <c r="AG66" s="192"/>
+      <c r="AH66" s="192"/>
+      <c r="AI66" s="192"/>
+      <c r="AJ66" s="192"/>
+      <c r="AK66" s="192"/>
+      <c r="AL66" s="192"/>
+      <c r="AM66" s="192"/>
+      <c r="AN66" s="192"/>
+      <c r="AO66" s="192"/>
+      <c r="AP66" s="192"/>
+      <c r="AQ66" s="192"/>
+      <c r="AR66" s="192"/>
+      <c r="AS66" s="192"/>
+      <c r="AT66" s="192"/>
     </row>
-    <row r="67" spans="1:262" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:262" ht="29.25" customHeight="1">
       <c r="A67" s="144"/>
-      <c r="B67" s="294" t="s">
+      <c r="B67" s="177" t="s">
         <v>153</v>
       </c>
-      <c r="C67" s="294"/>
-      <c r="D67" s="294"/>
-      <c r="E67" s="294"/>
-      <c r="F67" s="294"/>
-      <c r="G67" s="294"/>
-      <c r="H67" s="294"/>
-      <c r="I67" s="294"/>
-      <c r="J67" s="294"/>
-      <c r="K67" s="294"/>
-      <c r="L67" s="294"/>
-      <c r="M67" s="294"/>
-      <c r="N67" s="294"/>
-      <c r="O67" s="294"/>
-      <c r="P67" s="294"/>
-      <c r="Q67" s="294"/>
-      <c r="R67" s="294"/>
-      <c r="S67" s="294"/>
-      <c r="T67" s="294"/>
-      <c r="U67" s="294"/>
-      <c r="V67" s="294"/>
-      <c r="W67" s="294"/>
-      <c r="X67" s="294"/>
-      <c r="Y67" s="294"/>
-      <c r="Z67" s="294"/>
-      <c r="AA67" s="294"/>
-      <c r="AB67" s="294"/>
-      <c r="AC67" s="294"/>
-      <c r="AD67" s="294"/>
-      <c r="AE67" s="294"/>
-      <c r="AF67" s="294"/>
-      <c r="AG67" s="294"/>
-      <c r="AH67" s="294"/>
-      <c r="AI67" s="294"/>
-      <c r="AJ67" s="294"/>
-      <c r="AK67" s="294"/>
-      <c r="AL67" s="294"/>
-      <c r="AM67" s="294"/>
-      <c r="AN67" s="294"/>
-      <c r="AO67" s="294"/>
-      <c r="AP67" s="294"/>
-      <c r="AQ67" s="294"/>
-      <c r="AR67" s="294"/>
-      <c r="AS67" s="294"/>
-      <c r="AT67" s="294"/>
+      <c r="C67" s="177"/>
+      <c r="D67" s="177"/>
+      <c r="E67" s="177"/>
+      <c r="F67" s="177"/>
+      <c r="G67" s="177"/>
+      <c r="H67" s="177"/>
+      <c r="I67" s="177"/>
+      <c r="J67" s="177"/>
+      <c r="K67" s="177"/>
+      <c r="L67" s="177"/>
+      <c r="M67" s="177"/>
+      <c r="N67" s="177"/>
+      <c r="O67" s="177"/>
+      <c r="P67" s="177"/>
+      <c r="Q67" s="177"/>
+      <c r="R67" s="177"/>
+      <c r="S67" s="177"/>
+      <c r="T67" s="177"/>
+      <c r="U67" s="177"/>
+      <c r="V67" s="177"/>
+      <c r="W67" s="177"/>
+      <c r="X67" s="177"/>
+      <c r="Y67" s="177"/>
+      <c r="Z67" s="177"/>
+      <c r="AA67" s="177"/>
+      <c r="AB67" s="177"/>
+      <c r="AC67" s="177"/>
+      <c r="AD67" s="177"/>
+      <c r="AE67" s="177"/>
+      <c r="AF67" s="177"/>
+      <c r="AG67" s="177"/>
+      <c r="AH67" s="177"/>
+      <c r="AI67" s="177"/>
+      <c r="AJ67" s="177"/>
+      <c r="AK67" s="177"/>
+      <c r="AL67" s="177"/>
+      <c r="AM67" s="177"/>
+      <c r="AN67" s="177"/>
+      <c r="AO67" s="177"/>
+      <c r="AP67" s="177"/>
+      <c r="AQ67" s="177"/>
+      <c r="AR67" s="177"/>
+      <c r="AS67" s="177"/>
+      <c r="AT67" s="177"/>
     </row>
-    <row r="68" spans="1:262" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:262" ht="21.75" customHeight="1">
       <c r="A68" s="144"/>
-      <c r="B68" s="294" t="s">
+      <c r="B68" s="177" t="s">
         <v>154</v>
       </c>
-      <c r="C68" s="294"/>
-      <c r="D68" s="294"/>
-      <c r="E68" s="294"/>
-      <c r="F68" s="294"/>
-      <c r="G68" s="294"/>
-      <c r="H68" s="294"/>
-      <c r="I68" s="294"/>
-      <c r="J68" s="294"/>
-      <c r="K68" s="294"/>
-      <c r="L68" s="294"/>
-      <c r="M68" s="294"/>
-      <c r="N68" s="294"/>
-      <c r="O68" s="294"/>
-      <c r="P68" s="294"/>
-      <c r="Q68" s="294"/>
-      <c r="R68" s="294"/>
-      <c r="S68" s="294"/>
-      <c r="T68" s="294"/>
-      <c r="U68" s="294"/>
-      <c r="V68" s="294"/>
-      <c r="W68" s="294"/>
-      <c r="X68" s="294"/>
-      <c r="Y68" s="294"/>
-      <c r="Z68" s="294"/>
-      <c r="AA68" s="294"/>
-      <c r="AB68" s="294"/>
-      <c r="AC68" s="294"/>
-      <c r="AD68" s="294"/>
-      <c r="AE68" s="294"/>
-      <c r="AF68" s="294"/>
-      <c r="AG68" s="294"/>
-      <c r="AH68" s="294"/>
-      <c r="AI68" s="294"/>
-      <c r="AJ68" s="294"/>
-      <c r="AK68" s="294"/>
-      <c r="AL68" s="294"/>
-      <c r="AM68" s="294"/>
-      <c r="AN68" s="294"/>
-      <c r="AO68" s="294"/>
-      <c r="AP68" s="294"/>
-      <c r="AQ68" s="294"/>
-      <c r="AR68" s="294"/>
-      <c r="AS68" s="294"/>
-      <c r="AT68" s="294"/>
+      <c r="C68" s="177"/>
+      <c r="D68" s="177"/>
+      <c r="E68" s="177"/>
+      <c r="F68" s="177"/>
+      <c r="G68" s="177"/>
+      <c r="H68" s="177"/>
+      <c r="I68" s="177"/>
+      <c r="J68" s="177"/>
+      <c r="K68" s="177"/>
+      <c r="L68" s="177"/>
+      <c r="M68" s="177"/>
+      <c r="N68" s="177"/>
+      <c r="O68" s="177"/>
+      <c r="P68" s="177"/>
+      <c r="Q68" s="177"/>
+      <c r="R68" s="177"/>
+      <c r="S68" s="177"/>
+      <c r="T68" s="177"/>
+      <c r="U68" s="177"/>
+      <c r="V68" s="177"/>
+      <c r="W68" s="177"/>
+      <c r="X68" s="177"/>
+      <c r="Y68" s="177"/>
+      <c r="Z68" s="177"/>
+      <c r="AA68" s="177"/>
+      <c r="AB68" s="177"/>
+      <c r="AC68" s="177"/>
+      <c r="AD68" s="177"/>
+      <c r="AE68" s="177"/>
+      <c r="AF68" s="177"/>
+      <c r="AG68" s="177"/>
+      <c r="AH68" s="177"/>
+      <c r="AI68" s="177"/>
+      <c r="AJ68" s="177"/>
+      <c r="AK68" s="177"/>
+      <c r="AL68" s="177"/>
+      <c r="AM68" s="177"/>
+      <c r="AN68" s="177"/>
+      <c r="AO68" s="177"/>
+      <c r="AP68" s="177"/>
+      <c r="AQ68" s="177"/>
+      <c r="AR68" s="177"/>
+      <c r="AS68" s="177"/>
+      <c r="AT68" s="177"/>
     </row>
-    <row r="69" spans="1:262" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:262" ht="21.95" customHeight="1">
       <c r="A69" s="144">
         <v>11</v>
       </c>
-      <c r="B69" s="294" t="s">
+      <c r="B69" s="177" t="s">
         <v>159</v>
       </c>
-      <c r="C69" s="294"/>
-      <c r="D69" s="294"/>
-      <c r="E69" s="294"/>
-      <c r="F69" s="294"/>
-      <c r="G69" s="294"/>
-      <c r="H69" s="294"/>
-      <c r="I69" s="294"/>
-      <c r="J69" s="294"/>
-      <c r="K69" s="294"/>
-      <c r="L69" s="294"/>
-      <c r="M69" s="294"/>
-      <c r="N69" s="294"/>
-      <c r="O69" s="294"/>
-      <c r="P69" s="294"/>
-      <c r="Q69" s="294"/>
-      <c r="R69" s="294"/>
-      <c r="S69" s="294"/>
-      <c r="T69" s="294"/>
-      <c r="U69" s="294"/>
-      <c r="V69" s="294"/>
-      <c r="W69" s="294"/>
-      <c r="X69" s="294"/>
-      <c r="Y69" s="294"/>
-      <c r="Z69" s="294"/>
-      <c r="AA69" s="294"/>
-      <c r="AB69" s="294"/>
-      <c r="AC69" s="294"/>
-      <c r="AD69" s="294"/>
-      <c r="AE69" s="294"/>
-      <c r="AF69" s="294"/>
-      <c r="AG69" s="294"/>
-      <c r="AH69" s="294"/>
-      <c r="AI69" s="294"/>
-      <c r="AJ69" s="294"/>
-      <c r="AK69" s="294"/>
-      <c r="AL69" s="294"/>
-      <c r="AM69" s="294"/>
-      <c r="AN69" s="294"/>
-      <c r="AO69" s="294"/>
-      <c r="AP69" s="294"/>
-      <c r="AQ69" s="294"/>
-      <c r="AR69" s="294"/>
-      <c r="AS69" s="294"/>
-      <c r="AT69" s="294"/>
+      <c r="C69" s="177"/>
+      <c r="D69" s="177"/>
+      <c r="E69" s="177"/>
+      <c r="F69" s="177"/>
+      <c r="G69" s="177"/>
+      <c r="H69" s="177"/>
+      <c r="I69" s="177"/>
+      <c r="J69" s="177"/>
+      <c r="K69" s="177"/>
+      <c r="L69" s="177"/>
+      <c r="M69" s="177"/>
+      <c r="N69" s="177"/>
+      <c r="O69" s="177"/>
+      <c r="P69" s="177"/>
+      <c r="Q69" s="177"/>
+      <c r="R69" s="177"/>
+      <c r="S69" s="177"/>
+      <c r="T69" s="177"/>
+      <c r="U69" s="177"/>
+      <c r="V69" s="177"/>
+      <c r="W69" s="177"/>
+      <c r="X69" s="177"/>
+      <c r="Y69" s="177"/>
+      <c r="Z69" s="177"/>
+      <c r="AA69" s="177"/>
+      <c r="AB69" s="177"/>
+      <c r="AC69" s="177"/>
+      <c r="AD69" s="177"/>
+      <c r="AE69" s="177"/>
+      <c r="AF69" s="177"/>
+      <c r="AG69" s="177"/>
+      <c r="AH69" s="177"/>
+      <c r="AI69" s="177"/>
+      <c r="AJ69" s="177"/>
+      <c r="AK69" s="177"/>
+      <c r="AL69" s="177"/>
+      <c r="AM69" s="177"/>
+      <c r="AN69" s="177"/>
+      <c r="AO69" s="177"/>
+      <c r="AP69" s="177"/>
+      <c r="AQ69" s="177"/>
+      <c r="AR69" s="177"/>
+      <c r="AS69" s="177"/>
+      <c r="AT69" s="177"/>
     </row>
-    <row r="70" spans="1:262" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:262" ht="16.5" customHeight="1">
       <c r="A70" s="143"/>
       <c r="B70" s="144" t="s">
         <v>126</v>
@@ -9167,7 +9171,7 @@
       <c r="AS70" s="144"/>
       <c r="AT70" s="144"/>
     </row>
-    <row r="71" spans="1:262" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:262" ht="16.5" customHeight="1">
       <c r="A71" s="143"/>
       <c r="B71" s="144" t="s">
         <v>127</v>
@@ -9217,7 +9221,7 @@
       <c r="AS71" s="144"/>
       <c r="AT71" s="144"/>
     </row>
-    <row r="72" spans="1:262" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:262" ht="16.5" customHeight="1">
       <c r="A72" s="143"/>
       <c r="B72" s="144" t="s">
         <v>131</v>
@@ -9267,7 +9271,7 @@
       <c r="AS72" s="144"/>
       <c r="AT72" s="144"/>
     </row>
-    <row r="73" spans="1:262" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:262" ht="16.5" customHeight="1">
       <c r="A73" s="143"/>
       <c r="B73" s="144" t="s">
         <v>132</v>
@@ -9317,7 +9321,7 @@
       <c r="AS73" s="144"/>
       <c r="AT73" s="144"/>
     </row>
-    <row r="74" spans="1:262" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:262" ht="16.5" customHeight="1">
       <c r="A74" s="143"/>
       <c r="B74" s="144"/>
       <c r="C74" s="144"/>
@@ -9365,7 +9369,7 @@
       <c r="AS74" s="144"/>
       <c r="AT74" s="144"/>
     </row>
-    <row r="75" spans="1:262" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:262" ht="21.95" customHeight="1">
       <c r="A75" s="144">
         <v>12</v>
       </c>
@@ -9417,63 +9421,63 @@
       <c r="AS75" s="146"/>
       <c r="AT75" s="146"/>
     </row>
-    <row r="76" spans="1:262" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:262" ht="60.75" customHeight="1">
       <c r="A76" s="144">
         <v>13</v>
       </c>
-      <c r="B76" s="294" t="s">
+      <c r="B76" s="177" t="s">
         <v>156</v>
       </c>
-      <c r="C76" s="294"/>
-      <c r="D76" s="294"/>
-      <c r="E76" s="294"/>
-      <c r="F76" s="294"/>
-      <c r="G76" s="294"/>
-      <c r="H76" s="294"/>
-      <c r="I76" s="294"/>
-      <c r="J76" s="294"/>
-      <c r="K76" s="294"/>
-      <c r="L76" s="294"/>
-      <c r="M76" s="294"/>
-      <c r="N76" s="294"/>
-      <c r="O76" s="294"/>
-      <c r="P76" s="294"/>
-      <c r="Q76" s="294"/>
-      <c r="R76" s="294"/>
-      <c r="S76" s="294"/>
-      <c r="T76" s="294"/>
-      <c r="U76" s="294"/>
-      <c r="V76" s="294"/>
-      <c r="W76" s="294"/>
-      <c r="X76" s="294"/>
-      <c r="Y76" s="294"/>
-      <c r="Z76" s="294"/>
-      <c r="AA76" s="294"/>
-      <c r="AB76" s="294"/>
-      <c r="AC76" s="294"/>
-      <c r="AD76" s="294"/>
-      <c r="AE76" s="294"/>
-      <c r="AF76" s="294"/>
-      <c r="AG76" s="294"/>
-      <c r="AH76" s="294"/>
-      <c r="AI76" s="294"/>
-      <c r="AJ76" s="294"/>
-      <c r="AK76" s="294"/>
-      <c r="AL76" s="294"/>
-      <c r="AM76" s="294"/>
-      <c r="AN76" s="294"/>
-      <c r="AO76" s="294"/>
-      <c r="AP76" s="294"/>
-      <c r="AQ76" s="294"/>
-      <c r="AR76" s="294"/>
-      <c r="AS76" s="294"/>
-      <c r="AT76" s="294"/>
+      <c r="C76" s="177"/>
+      <c r="D76" s="177"/>
+      <c r="E76" s="177"/>
+      <c r="F76" s="177"/>
+      <c r="G76" s="177"/>
+      <c r="H76" s="177"/>
+      <c r="I76" s="177"/>
+      <c r="J76" s="177"/>
+      <c r="K76" s="177"/>
+      <c r="L76" s="177"/>
+      <c r="M76" s="177"/>
+      <c r="N76" s="177"/>
+      <c r="O76" s="177"/>
+      <c r="P76" s="177"/>
+      <c r="Q76" s="177"/>
+      <c r="R76" s="177"/>
+      <c r="S76" s="177"/>
+      <c r="T76" s="177"/>
+      <c r="U76" s="177"/>
+      <c r="V76" s="177"/>
+      <c r="W76" s="177"/>
+      <c r="X76" s="177"/>
+      <c r="Y76" s="177"/>
+      <c r="Z76" s="177"/>
+      <c r="AA76" s="177"/>
+      <c r="AB76" s="177"/>
+      <c r="AC76" s="177"/>
+      <c r="AD76" s="177"/>
+      <c r="AE76" s="177"/>
+      <c r="AF76" s="177"/>
+      <c r="AG76" s="177"/>
+      <c r="AH76" s="177"/>
+      <c r="AI76" s="177"/>
+      <c r="AJ76" s="177"/>
+      <c r="AK76" s="177"/>
+      <c r="AL76" s="177"/>
+      <c r="AM76" s="177"/>
+      <c r="AN76" s="177"/>
+      <c r="AO76" s="177"/>
+      <c r="AP76" s="177"/>
+      <c r="AQ76" s="177"/>
+      <c r="AR76" s="177"/>
+      <c r="AS76" s="177"/>
+      <c r="AT76" s="177"/>
       <c r="BE76" s="9"/>
       <c r="BF76" s="9"/>
       <c r="BG76" s="5"/>
       <c r="BH76" s="5"/>
     </row>
-    <row r="77" spans="1:262" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:262" ht="20.25" customHeight="1">
       <c r="AU77" s="5"/>
       <c r="AV77" s="5"/>
       <c r="AW77" s="5"/>
@@ -9691,7 +9695,7 @@
       <c r="JA77" s="5"/>
       <c r="JB77" s="5"/>
     </row>
-    <row r="78" spans="1:262" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:262" ht="24" customHeight="1" thickBot="1">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
       <c r="C78" s="147" t="s">
@@ -9953,59 +9957,59 @@
       <c r="JA78" s="5"/>
       <c r="JB78" s="5"/>
     </row>
-    <row r="79" spans="1:262" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:262" ht="24" customHeight="1">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
-      <c r="C79" s="295" t="s">
+      <c r="C79" s="178" t="s">
         <v>95</v>
       </c>
-      <c r="D79" s="296"/>
-      <c r="E79" s="296"/>
-      <c r="F79" s="296"/>
-      <c r="G79" s="296"/>
-      <c r="H79" s="296"/>
-      <c r="I79" s="296"/>
-      <c r="J79" s="296"/>
-      <c r="K79" s="296"/>
-      <c r="L79" s="296"/>
-      <c r="M79" s="296"/>
-      <c r="N79" s="296"/>
-      <c r="O79" s="296"/>
-      <c r="P79" s="296" t="s">
+      <c r="D79" s="179"/>
+      <c r="E79" s="179"/>
+      <c r="F79" s="179"/>
+      <c r="G79" s="179"/>
+      <c r="H79" s="179"/>
+      <c r="I79" s="179"/>
+      <c r="J79" s="179"/>
+      <c r="K79" s="179"/>
+      <c r="L79" s="179"/>
+      <c r="M79" s="179"/>
+      <c r="N79" s="179"/>
+      <c r="O79" s="179"/>
+      <c r="P79" s="179" t="s">
         <v>96</v>
       </c>
-      <c r="Q79" s="296"/>
-      <c r="R79" s="296"/>
-      <c r="S79" s="296"/>
-      <c r="T79" s="299"/>
-      <c r="U79" s="302" t="s">
+      <c r="Q79" s="179"/>
+      <c r="R79" s="179"/>
+      <c r="S79" s="179"/>
+      <c r="T79" s="182"/>
+      <c r="U79" s="185" t="s">
         <v>97</v>
       </c>
-      <c r="V79" s="302"/>
-      <c r="W79" s="302"/>
-      <c r="X79" s="302"/>
-      <c r="Y79" s="302"/>
-      <c r="Z79" s="302"/>
-      <c r="AA79" s="302"/>
-      <c r="AB79" s="303"/>
-      <c r="AC79" s="303"/>
-      <c r="AD79" s="303"/>
-      <c r="AE79" s="303"/>
-      <c r="AF79" s="303"/>
-      <c r="AG79" s="303"/>
-      <c r="AH79" s="303"/>
-      <c r="AI79" s="302" t="s">
+      <c r="V79" s="185"/>
+      <c r="W79" s="185"/>
+      <c r="X79" s="185"/>
+      <c r="Y79" s="185"/>
+      <c r="Z79" s="185"/>
+      <c r="AA79" s="185"/>
+      <c r="AB79" s="186"/>
+      <c r="AC79" s="186"/>
+      <c r="AD79" s="186"/>
+      <c r="AE79" s="186"/>
+      <c r="AF79" s="186"/>
+      <c r="AG79" s="186"/>
+      <c r="AH79" s="186"/>
+      <c r="AI79" s="185" t="s">
         <v>98</v>
       </c>
-      <c r="AJ79" s="302"/>
-      <c r="AK79" s="302"/>
-      <c r="AL79" s="302"/>
-      <c r="AM79" s="302"/>
-      <c r="AN79" s="302"/>
-      <c r="AO79" s="302"/>
-      <c r="AP79" s="302"/>
-      <c r="AQ79" s="302"/>
-      <c r="AR79" s="304"/>
+      <c r="AJ79" s="185"/>
+      <c r="AK79" s="185"/>
+      <c r="AL79" s="185"/>
+      <c r="AM79" s="185"/>
+      <c r="AN79" s="185"/>
+      <c r="AO79" s="185"/>
+      <c r="AP79" s="185"/>
+      <c r="AQ79" s="185"/>
+      <c r="AR79" s="187"/>
       <c r="AS79" s="5"/>
       <c r="AT79" s="5"/>
       <c r="AU79" s="5"/>
@@ -10221,55 +10225,55 @@
       <c r="JA79" s="5"/>
       <c r="JB79" s="5"/>
     </row>
-    <row r="80" spans="1:262" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:262" ht="24" customHeight="1">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
-      <c r="C80" s="297"/>
-      <c r="D80" s="298"/>
-      <c r="E80" s="298"/>
-      <c r="F80" s="298"/>
-      <c r="G80" s="298"/>
-      <c r="H80" s="298"/>
-      <c r="I80" s="298"/>
-      <c r="J80" s="298"/>
-      <c r="K80" s="298"/>
-      <c r="L80" s="298"/>
-      <c r="M80" s="298"/>
-      <c r="N80" s="298"/>
-      <c r="O80" s="298"/>
-      <c r="P80" s="300"/>
-      <c r="Q80" s="300"/>
-      <c r="R80" s="300"/>
-      <c r="S80" s="300"/>
-      <c r="T80" s="301"/>
-      <c r="U80" s="306" t="s">
+      <c r="C80" s="180"/>
+      <c r="D80" s="181"/>
+      <c r="E80" s="181"/>
+      <c r="F80" s="181"/>
+      <c r="G80" s="181"/>
+      <c r="H80" s="181"/>
+      <c r="I80" s="181"/>
+      <c r="J80" s="181"/>
+      <c r="K80" s="181"/>
+      <c r="L80" s="181"/>
+      <c r="M80" s="181"/>
+      <c r="N80" s="181"/>
+      <c r="O80" s="181"/>
+      <c r="P80" s="183"/>
+      <c r="Q80" s="183"/>
+      <c r="R80" s="183"/>
+      <c r="S80" s="183"/>
+      <c r="T80" s="184"/>
+      <c r="U80" s="189" t="s">
         <v>99</v>
       </c>
-      <c r="V80" s="306"/>
-      <c r="W80" s="306"/>
-      <c r="X80" s="306"/>
-      <c r="Y80" s="306"/>
-      <c r="Z80" s="306"/>
-      <c r="AA80" s="308"/>
-      <c r="AB80" s="306" t="s">
+      <c r="V80" s="189"/>
+      <c r="W80" s="189"/>
+      <c r="X80" s="189"/>
+      <c r="Y80" s="189"/>
+      <c r="Z80" s="189"/>
+      <c r="AA80" s="191"/>
+      <c r="AB80" s="189" t="s">
         <v>100</v>
       </c>
-      <c r="AC80" s="306"/>
-      <c r="AD80" s="306"/>
-      <c r="AE80" s="306"/>
-      <c r="AF80" s="306"/>
-      <c r="AG80" s="306"/>
-      <c r="AH80" s="306"/>
-      <c r="AI80" s="305"/>
-      <c r="AJ80" s="306"/>
-      <c r="AK80" s="306"/>
-      <c r="AL80" s="306"/>
-      <c r="AM80" s="306"/>
-      <c r="AN80" s="306"/>
-      <c r="AO80" s="306"/>
-      <c r="AP80" s="306"/>
-      <c r="AQ80" s="306"/>
-      <c r="AR80" s="307"/>
+      <c r="AC80" s="189"/>
+      <c r="AD80" s="189"/>
+      <c r="AE80" s="189"/>
+      <c r="AF80" s="189"/>
+      <c r="AG80" s="189"/>
+      <c r="AH80" s="189"/>
+      <c r="AI80" s="188"/>
+      <c r="AJ80" s="189"/>
+      <c r="AK80" s="189"/>
+      <c r="AL80" s="189"/>
+      <c r="AM80" s="189"/>
+      <c r="AN80" s="189"/>
+      <c r="AO80" s="189"/>
+      <c r="AP80" s="189"/>
+      <c r="AQ80" s="189"/>
+      <c r="AR80" s="190"/>
       <c r="AS80" s="5"/>
       <c r="AT80" s="5"/>
       <c r="AU80" s="5"/>
@@ -10485,61 +10489,61 @@
       <c r="JA80" s="5"/>
       <c r="JB80" s="5"/>
     </row>
-    <row r="81" spans="1:262" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:262" ht="23.25" customHeight="1">
       <c r="A81" s="5"/>
       <c r="B81" s="5"/>
-      <c r="C81" s="309" t="s">
+      <c r="C81" s="160" t="s">
         <v>3</v>
       </c>
-      <c r="D81" s="310"/>
-      <c r="E81" s="310"/>
-      <c r="F81" s="310"/>
-      <c r="G81" s="310"/>
-      <c r="H81" s="310"/>
-      <c r="I81" s="310"/>
-      <c r="J81" s="310"/>
-      <c r="K81" s="310"/>
-      <c r="L81" s="310"/>
-      <c r="M81" s="310"/>
-      <c r="N81" s="310"/>
-      <c r="O81" s="311"/>
-      <c r="P81" s="310" t="s">
+      <c r="D81" s="158"/>
+      <c r="E81" s="158"/>
+      <c r="F81" s="158"/>
+      <c r="G81" s="158"/>
+      <c r="H81" s="158"/>
+      <c r="I81" s="158"/>
+      <c r="J81" s="158"/>
+      <c r="K81" s="158"/>
+      <c r="L81" s="158"/>
+      <c r="M81" s="158"/>
+      <c r="N81" s="158"/>
+      <c r="O81" s="159"/>
+      <c r="P81" s="158" t="s">
         <v>101</v>
       </c>
-      <c r="Q81" s="310"/>
-      <c r="R81" s="310"/>
-      <c r="S81" s="310"/>
-      <c r="T81" s="310"/>
-      <c r="U81" s="312">
+      <c r="Q81" s="158"/>
+      <c r="R81" s="158"/>
+      <c r="S81" s="158"/>
+      <c r="T81" s="158"/>
+      <c r="U81" s="166">
         <v>0.6</v>
       </c>
-      <c r="V81" s="313"/>
-      <c r="W81" s="313"/>
-      <c r="X81" s="313"/>
-      <c r="Y81" s="313"/>
-      <c r="Z81" s="313"/>
-      <c r="AA81" s="313"/>
-      <c r="AB81" s="314">
+      <c r="V81" s="163"/>
+      <c r="W81" s="163"/>
+      <c r="X81" s="163"/>
+      <c r="Y81" s="163"/>
+      <c r="Z81" s="163"/>
+      <c r="AA81" s="163"/>
+      <c r="AB81" s="167">
         <v>0.15</v>
       </c>
-      <c r="AC81" s="314"/>
-      <c r="AD81" s="314"/>
-      <c r="AE81" s="314"/>
-      <c r="AF81" s="314"/>
-      <c r="AG81" s="314"/>
-      <c r="AH81" s="314"/>
-      <c r="AI81" s="315" t="s">
+      <c r="AC81" s="167"/>
+      <c r="AD81" s="167"/>
+      <c r="AE81" s="167"/>
+      <c r="AF81" s="167"/>
+      <c r="AG81" s="167"/>
+      <c r="AH81" s="167"/>
+      <c r="AI81" s="152" t="s">
         <v>102</v>
       </c>
-      <c r="AJ81" s="316"/>
-      <c r="AK81" s="316"/>
-      <c r="AL81" s="316"/>
-      <c r="AM81" s="316"/>
-      <c r="AN81" s="316"/>
-      <c r="AO81" s="316"/>
-      <c r="AP81" s="316"/>
-      <c r="AQ81" s="316"/>
-      <c r="AR81" s="317"/>
+      <c r="AJ81" s="153"/>
+      <c r="AK81" s="153"/>
+      <c r="AL81" s="153"/>
+      <c r="AM81" s="153"/>
+      <c r="AN81" s="153"/>
+      <c r="AO81" s="153"/>
+      <c r="AP81" s="153"/>
+      <c r="AQ81" s="153"/>
+      <c r="AR81" s="168"/>
       <c r="AS81" s="5"/>
       <c r="AT81" s="5"/>
       <c r="AU81" s="5"/>
@@ -10755,55 +10759,55 @@
       <c r="JA81" s="5"/>
       <c r="JB81" s="5"/>
     </row>
-    <row r="82" spans="1:262" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:262" ht="23.25" customHeight="1">
       <c r="A82" s="5"/>
       <c r="B82" s="5"/>
-      <c r="C82" s="309"/>
-      <c r="D82" s="310"/>
-      <c r="E82" s="310"/>
-      <c r="F82" s="310"/>
-      <c r="G82" s="310"/>
-      <c r="H82" s="310"/>
-      <c r="I82" s="310"/>
-      <c r="J82" s="310"/>
-      <c r="K82" s="310"/>
-      <c r="L82" s="310"/>
-      <c r="M82" s="310"/>
-      <c r="N82" s="310"/>
-      <c r="O82" s="311"/>
-      <c r="P82" s="310" t="s">
+      <c r="C82" s="160"/>
+      <c r="D82" s="158"/>
+      <c r="E82" s="158"/>
+      <c r="F82" s="158"/>
+      <c r="G82" s="158"/>
+      <c r="H82" s="158"/>
+      <c r="I82" s="158"/>
+      <c r="J82" s="158"/>
+      <c r="K82" s="158"/>
+      <c r="L82" s="158"/>
+      <c r="M82" s="158"/>
+      <c r="N82" s="158"/>
+      <c r="O82" s="159"/>
+      <c r="P82" s="158" t="s">
         <v>103</v>
       </c>
-      <c r="Q82" s="310"/>
-      <c r="R82" s="310"/>
-      <c r="S82" s="310"/>
-      <c r="T82" s="310"/>
-      <c r="U82" s="312">
+      <c r="Q82" s="158"/>
+      <c r="R82" s="158"/>
+      <c r="S82" s="158"/>
+      <c r="T82" s="158"/>
+      <c r="U82" s="166">
         <v>0.45</v>
       </c>
-      <c r="V82" s="313"/>
-      <c r="W82" s="313"/>
-      <c r="X82" s="313"/>
-      <c r="Y82" s="313"/>
-      <c r="Z82" s="313"/>
-      <c r="AA82" s="313"/>
-      <c r="AB82" s="313"/>
-      <c r="AC82" s="313"/>
-      <c r="AD82" s="313"/>
-      <c r="AE82" s="313"/>
-      <c r="AF82" s="313"/>
-      <c r="AG82" s="313"/>
-      <c r="AH82" s="313"/>
-      <c r="AI82" s="318"/>
-      <c r="AJ82" s="319"/>
-      <c r="AK82" s="319"/>
-      <c r="AL82" s="319"/>
-      <c r="AM82" s="319"/>
-      <c r="AN82" s="319"/>
-      <c r="AO82" s="319"/>
-      <c r="AP82" s="319"/>
-      <c r="AQ82" s="319"/>
-      <c r="AR82" s="320"/>
+      <c r="V82" s="163"/>
+      <c r="W82" s="163"/>
+      <c r="X82" s="163"/>
+      <c r="Y82" s="163"/>
+      <c r="Z82" s="163"/>
+      <c r="AA82" s="163"/>
+      <c r="AB82" s="163"/>
+      <c r="AC82" s="163"/>
+      <c r="AD82" s="163"/>
+      <c r="AE82" s="163"/>
+      <c r="AF82" s="163"/>
+      <c r="AG82" s="163"/>
+      <c r="AH82" s="163"/>
+      <c r="AI82" s="169"/>
+      <c r="AJ82" s="170"/>
+      <c r="AK82" s="170"/>
+      <c r="AL82" s="170"/>
+      <c r="AM82" s="170"/>
+      <c r="AN82" s="170"/>
+      <c r="AO82" s="170"/>
+      <c r="AP82" s="170"/>
+      <c r="AQ82" s="170"/>
+      <c r="AR82" s="171"/>
       <c r="AS82" s="5"/>
       <c r="AT82" s="5"/>
       <c r="AU82" s="5"/>
@@ -11019,57 +11023,57 @@
       <c r="JA82" s="5"/>
       <c r="JB82" s="5"/>
     </row>
-    <row r="83" spans="1:262" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:262" ht="23.25" customHeight="1">
       <c r="A83" s="5"/>
       <c r="B83" s="5"/>
-      <c r="C83" s="309" t="s">
+      <c r="C83" s="160" t="s">
         <v>104</v>
       </c>
-      <c r="D83" s="310"/>
-      <c r="E83" s="310"/>
-      <c r="F83" s="310"/>
-      <c r="G83" s="310"/>
-      <c r="H83" s="310"/>
-      <c r="I83" s="310"/>
-      <c r="J83" s="310"/>
-      <c r="K83" s="310"/>
-      <c r="L83" s="310"/>
-      <c r="M83" s="310"/>
-      <c r="N83" s="310"/>
-      <c r="O83" s="310"/>
-      <c r="P83" s="324" t="s">
+      <c r="D83" s="158"/>
+      <c r="E83" s="158"/>
+      <c r="F83" s="158"/>
+      <c r="G83" s="158"/>
+      <c r="H83" s="158"/>
+      <c r="I83" s="158"/>
+      <c r="J83" s="158"/>
+      <c r="K83" s="158"/>
+      <c r="L83" s="158"/>
+      <c r="M83" s="158"/>
+      <c r="N83" s="158"/>
+      <c r="O83" s="158"/>
+      <c r="P83" s="175" t="s">
         <v>101</v>
       </c>
-      <c r="Q83" s="324"/>
-      <c r="R83" s="324"/>
-      <c r="S83" s="324"/>
-      <c r="T83" s="325"/>
-      <c r="U83" s="315">
+      <c r="Q83" s="175"/>
+      <c r="R83" s="175"/>
+      <c r="S83" s="175"/>
+      <c r="T83" s="176"/>
+      <c r="U83" s="152">
         <v>0.45</v>
       </c>
-      <c r="V83" s="316"/>
-      <c r="W83" s="316"/>
-      <c r="X83" s="316"/>
-      <c r="Y83" s="316"/>
-      <c r="Z83" s="316"/>
-      <c r="AA83" s="327"/>
-      <c r="AB83" s="313"/>
-      <c r="AC83" s="313"/>
-      <c r="AD83" s="313"/>
-      <c r="AE83" s="313"/>
-      <c r="AF83" s="313"/>
-      <c r="AG83" s="313"/>
-      <c r="AH83" s="313"/>
-      <c r="AI83" s="318"/>
-      <c r="AJ83" s="319"/>
-      <c r="AK83" s="319"/>
-      <c r="AL83" s="319"/>
-      <c r="AM83" s="319"/>
-      <c r="AN83" s="319"/>
-      <c r="AO83" s="319"/>
-      <c r="AP83" s="319"/>
-      <c r="AQ83" s="319"/>
-      <c r="AR83" s="320"/>
+      <c r="V83" s="153"/>
+      <c r="W83" s="153"/>
+      <c r="X83" s="153"/>
+      <c r="Y83" s="153"/>
+      <c r="Z83" s="153"/>
+      <c r="AA83" s="154"/>
+      <c r="AB83" s="163"/>
+      <c r="AC83" s="163"/>
+      <c r="AD83" s="163"/>
+      <c r="AE83" s="163"/>
+      <c r="AF83" s="163"/>
+      <c r="AG83" s="163"/>
+      <c r="AH83" s="163"/>
+      <c r="AI83" s="169"/>
+      <c r="AJ83" s="170"/>
+      <c r="AK83" s="170"/>
+      <c r="AL83" s="170"/>
+      <c r="AM83" s="170"/>
+      <c r="AN83" s="170"/>
+      <c r="AO83" s="170"/>
+      <c r="AP83" s="170"/>
+      <c r="AQ83" s="170"/>
+      <c r="AR83" s="171"/>
       <c r="AS83" s="5"/>
       <c r="AT83" s="5"/>
       <c r="AU83" s="5"/>
@@ -11285,53 +11289,53 @@
       <c r="JA83" s="5"/>
       <c r="JB83" s="5"/>
     </row>
-    <row r="84" spans="1:262" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:262" ht="23.25" customHeight="1">
       <c r="A84" s="5"/>
       <c r="B84" s="5"/>
-      <c r="C84" s="309"/>
-      <c r="D84" s="310"/>
-      <c r="E84" s="310"/>
-      <c r="F84" s="310"/>
-      <c r="G84" s="310"/>
-      <c r="H84" s="310"/>
-      <c r="I84" s="310"/>
-      <c r="J84" s="310"/>
-      <c r="K84" s="310"/>
-      <c r="L84" s="310"/>
-      <c r="M84" s="310"/>
-      <c r="N84" s="310"/>
-      <c r="O84" s="310"/>
-      <c r="P84" s="310" t="s">
+      <c r="C84" s="160"/>
+      <c r="D84" s="158"/>
+      <c r="E84" s="158"/>
+      <c r="F84" s="158"/>
+      <c r="G84" s="158"/>
+      <c r="H84" s="158"/>
+      <c r="I84" s="158"/>
+      <c r="J84" s="158"/>
+      <c r="K84" s="158"/>
+      <c r="L84" s="158"/>
+      <c r="M84" s="158"/>
+      <c r="N84" s="158"/>
+      <c r="O84" s="158"/>
+      <c r="P84" s="158" t="s">
         <v>103</v>
       </c>
-      <c r="Q84" s="310"/>
-      <c r="R84" s="310"/>
-      <c r="S84" s="310"/>
-      <c r="T84" s="311"/>
-      <c r="U84" s="328"/>
-      <c r="V84" s="329"/>
-      <c r="W84" s="329"/>
-      <c r="X84" s="329"/>
-      <c r="Y84" s="329"/>
-      <c r="Z84" s="329"/>
-      <c r="AA84" s="330"/>
-      <c r="AB84" s="313"/>
-      <c r="AC84" s="313"/>
-      <c r="AD84" s="313"/>
-      <c r="AE84" s="313"/>
-      <c r="AF84" s="313"/>
-      <c r="AG84" s="313"/>
-      <c r="AH84" s="313"/>
-      <c r="AI84" s="318"/>
-      <c r="AJ84" s="319"/>
-      <c r="AK84" s="319"/>
-      <c r="AL84" s="319"/>
-      <c r="AM84" s="319"/>
-      <c r="AN84" s="319"/>
-      <c r="AO84" s="319"/>
-      <c r="AP84" s="319"/>
-      <c r="AQ84" s="319"/>
-      <c r="AR84" s="320"/>
+      <c r="Q84" s="158"/>
+      <c r="R84" s="158"/>
+      <c r="S84" s="158"/>
+      <c r="T84" s="159"/>
+      <c r="U84" s="155"/>
+      <c r="V84" s="156"/>
+      <c r="W84" s="156"/>
+      <c r="X84" s="156"/>
+      <c r="Y84" s="156"/>
+      <c r="Z84" s="156"/>
+      <c r="AA84" s="157"/>
+      <c r="AB84" s="163"/>
+      <c r="AC84" s="163"/>
+      <c r="AD84" s="163"/>
+      <c r="AE84" s="163"/>
+      <c r="AF84" s="163"/>
+      <c r="AG84" s="163"/>
+      <c r="AH84" s="163"/>
+      <c r="AI84" s="169"/>
+      <c r="AJ84" s="170"/>
+      <c r="AK84" s="170"/>
+      <c r="AL84" s="170"/>
+      <c r="AM84" s="170"/>
+      <c r="AN84" s="170"/>
+      <c r="AO84" s="170"/>
+      <c r="AP84" s="170"/>
+      <c r="AQ84" s="170"/>
+      <c r="AR84" s="171"/>
       <c r="AS84" s="5"/>
       <c r="AT84" s="5"/>
       <c r="AU84" s="5"/>
@@ -11547,111 +11551,111 @@
       <c r="JA84" s="5"/>
       <c r="JB84" s="5"/>
     </row>
-    <row r="85" spans="1:262" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:262" ht="23.25" customHeight="1">
       <c r="A85" s="5"/>
       <c r="B85" s="5"/>
-      <c r="C85" s="309" t="s">
+      <c r="C85" s="160" t="s">
         <v>105</v>
       </c>
-      <c r="D85" s="310"/>
-      <c r="E85" s="310"/>
-      <c r="F85" s="310"/>
-      <c r="G85" s="310"/>
-      <c r="H85" s="310"/>
-      <c r="I85" s="310"/>
-      <c r="J85" s="310"/>
-      <c r="K85" s="310"/>
-      <c r="L85" s="310"/>
-      <c r="M85" s="310"/>
-      <c r="N85" s="310"/>
-      <c r="O85" s="310"/>
-      <c r="P85" s="310" t="s">
+      <c r="D85" s="158"/>
+      <c r="E85" s="158"/>
+      <c r="F85" s="158"/>
+      <c r="G85" s="158"/>
+      <c r="H85" s="158"/>
+      <c r="I85" s="158"/>
+      <c r="J85" s="158"/>
+      <c r="K85" s="158"/>
+      <c r="L85" s="158"/>
+      <c r="M85" s="158"/>
+      <c r="N85" s="158"/>
+      <c r="O85" s="158"/>
+      <c r="P85" s="158" t="s">
         <v>101</v>
       </c>
-      <c r="Q85" s="310"/>
-      <c r="R85" s="310"/>
-      <c r="S85" s="310"/>
-      <c r="T85" s="311"/>
-      <c r="U85" s="313">
+      <c r="Q85" s="158"/>
+      <c r="R85" s="158"/>
+      <c r="S85" s="158"/>
+      <c r="T85" s="159"/>
+      <c r="U85" s="163">
         <v>0.75</v>
       </c>
-      <c r="V85" s="313"/>
-      <c r="W85" s="313"/>
-      <c r="X85" s="313"/>
-      <c r="Y85" s="313"/>
-      <c r="Z85" s="313"/>
-      <c r="AA85" s="313"/>
-      <c r="AB85" s="313" t="s">
+      <c r="V85" s="163"/>
+      <c r="W85" s="163"/>
+      <c r="X85" s="163"/>
+      <c r="Y85" s="163"/>
+      <c r="Z85" s="163"/>
+      <c r="AA85" s="163"/>
+      <c r="AB85" s="163" t="s">
         <v>106</v>
       </c>
-      <c r="AC85" s="313"/>
-      <c r="AD85" s="313"/>
-      <c r="AE85" s="313"/>
-      <c r="AF85" s="313"/>
-      <c r="AG85" s="313"/>
-      <c r="AH85" s="313"/>
-      <c r="AI85" s="318"/>
-      <c r="AJ85" s="319"/>
-      <c r="AK85" s="319"/>
-      <c r="AL85" s="319"/>
-      <c r="AM85" s="319"/>
-      <c r="AN85" s="319"/>
-      <c r="AO85" s="319"/>
-      <c r="AP85" s="319"/>
-      <c r="AQ85" s="319"/>
-      <c r="AR85" s="320"/>
+      <c r="AC85" s="163"/>
+      <c r="AD85" s="163"/>
+      <c r="AE85" s="163"/>
+      <c r="AF85" s="163"/>
+      <c r="AG85" s="163"/>
+      <c r="AH85" s="163"/>
+      <c r="AI85" s="169"/>
+      <c r="AJ85" s="170"/>
+      <c r="AK85" s="170"/>
+      <c r="AL85" s="170"/>
+      <c r="AM85" s="170"/>
+      <c r="AN85" s="170"/>
+      <c r="AO85" s="170"/>
+      <c r="AP85" s="170"/>
+      <c r="AQ85" s="170"/>
+      <c r="AR85" s="171"/>
       <c r="AS85" s="5"/>
       <c r="AT85" s="5"/>
     </row>
-    <row r="86" spans="1:262" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C86" s="331"/>
-      <c r="D86" s="332"/>
-      <c r="E86" s="332"/>
-      <c r="F86" s="332"/>
-      <c r="G86" s="332"/>
-      <c r="H86" s="332"/>
-      <c r="I86" s="332"/>
-      <c r="J86" s="332"/>
-      <c r="K86" s="332"/>
-      <c r="L86" s="332"/>
-      <c r="M86" s="332"/>
-      <c r="N86" s="332"/>
-      <c r="O86" s="332"/>
-      <c r="P86" s="332" t="s">
+    <row r="86" spans="1:262" ht="23.25" customHeight="1" thickBot="1">
+      <c r="C86" s="161"/>
+      <c r="D86" s="162"/>
+      <c r="E86" s="162"/>
+      <c r="F86" s="162"/>
+      <c r="G86" s="162"/>
+      <c r="H86" s="162"/>
+      <c r="I86" s="162"/>
+      <c r="J86" s="162"/>
+      <c r="K86" s="162"/>
+      <c r="L86" s="162"/>
+      <c r="M86" s="162"/>
+      <c r="N86" s="162"/>
+      <c r="O86" s="162"/>
+      <c r="P86" s="162" t="s">
         <v>103</v>
       </c>
-      <c r="Q86" s="332"/>
-      <c r="R86" s="332"/>
-      <c r="S86" s="332"/>
-      <c r="T86" s="334"/>
-      <c r="U86" s="333">
+      <c r="Q86" s="162"/>
+      <c r="R86" s="162"/>
+      <c r="S86" s="162"/>
+      <c r="T86" s="165"/>
+      <c r="U86" s="164">
         <v>0.6</v>
       </c>
-      <c r="V86" s="333"/>
-      <c r="W86" s="333"/>
-      <c r="X86" s="333"/>
-      <c r="Y86" s="333"/>
-      <c r="Z86" s="333"/>
-      <c r="AA86" s="333"/>
-      <c r="AB86" s="333"/>
-      <c r="AC86" s="333"/>
-      <c r="AD86" s="333"/>
-      <c r="AE86" s="333"/>
-      <c r="AF86" s="333"/>
-      <c r="AG86" s="333"/>
-      <c r="AH86" s="333"/>
-      <c r="AI86" s="321"/>
-      <c r="AJ86" s="322"/>
-      <c r="AK86" s="322"/>
-      <c r="AL86" s="322"/>
-      <c r="AM86" s="322"/>
-      <c r="AN86" s="322"/>
-      <c r="AO86" s="322"/>
-      <c r="AP86" s="322"/>
-      <c r="AQ86" s="322"/>
-      <c r="AR86" s="323"/>
+      <c r="V86" s="164"/>
+      <c r="W86" s="164"/>
+      <c r="X86" s="164"/>
+      <c r="Y86" s="164"/>
+      <c r="Z86" s="164"/>
+      <c r="AA86" s="164"/>
+      <c r="AB86" s="164"/>
+      <c r="AC86" s="164"/>
+      <c r="AD86" s="164"/>
+      <c r="AE86" s="164"/>
+      <c r="AF86" s="164"/>
+      <c r="AG86" s="164"/>
+      <c r="AH86" s="164"/>
+      <c r="AI86" s="172"/>
+      <c r="AJ86" s="173"/>
+      <c r="AK86" s="173"/>
+      <c r="AL86" s="173"/>
+      <c r="AM86" s="173"/>
+      <c r="AN86" s="173"/>
+      <c r="AO86" s="173"/>
+      <c r="AP86" s="173"/>
+      <c r="AQ86" s="173"/>
+      <c r="AR86" s="174"/>
     </row>
-    <row r="87" spans="1:262" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:262" ht="23.25" customHeight="1">
       <c r="C87" s="148"/>
       <c r="D87" s="148"/>
       <c r="E87" s="148"/>
@@ -11695,193 +11699,84 @@
       <c r="AQ87" s="150"/>
       <c r="AR87" s="150"/>
     </row>
-    <row r="88" spans="1:262" ht="103.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="326" t="s">
+    <row r="88" spans="1:262" ht="103.5" customHeight="1">
+      <c r="A88" s="151" t="s">
         <v>162</v>
       </c>
-      <c r="B88" s="326"/>
-      <c r="C88" s="326"/>
-      <c r="D88" s="326"/>
-      <c r="E88" s="326"/>
-      <c r="F88" s="326"/>
-      <c r="G88" s="326"/>
-      <c r="H88" s="326"/>
-      <c r="I88" s="326"/>
-      <c r="J88" s="326"/>
-      <c r="K88" s="326"/>
-      <c r="L88" s="326"/>
-      <c r="M88" s="326"/>
-      <c r="N88" s="326"/>
-      <c r="O88" s="326"/>
-      <c r="P88" s="326"/>
-      <c r="Q88" s="326"/>
-      <c r="R88" s="326"/>
-      <c r="S88" s="326"/>
-      <c r="T88" s="326"/>
-      <c r="U88" s="326"/>
-      <c r="V88" s="326"/>
-      <c r="W88" s="326"/>
-      <c r="X88" s="326"/>
-      <c r="Y88" s="326"/>
-      <c r="Z88" s="326"/>
-      <c r="AA88" s="326"/>
-      <c r="AB88" s="326"/>
-      <c r="AC88" s="326"/>
-      <c r="AD88" s="326"/>
-      <c r="AE88" s="326"/>
-      <c r="AF88" s="326"/>
-      <c r="AG88" s="326"/>
-      <c r="AH88" s="326"/>
-      <c r="AI88" s="326"/>
-      <c r="AJ88" s="326"/>
-      <c r="AK88" s="326"/>
-      <c r="AL88" s="326"/>
-      <c r="AM88" s="326"/>
-      <c r="AN88" s="326"/>
-      <c r="AO88" s="326"/>
-      <c r="AP88" s="326"/>
-      <c r="AQ88" s="326"/>
-      <c r="AR88" s="326"/>
-      <c r="AS88" s="326"/>
-      <c r="AT88" s="326"/>
+      <c r="B88" s="151"/>
+      <c r="C88" s="151"/>
+      <c r="D88" s="151"/>
+      <c r="E88" s="151"/>
+      <c r="F88" s="151"/>
+      <c r="G88" s="151"/>
+      <c r="H88" s="151"/>
+      <c r="I88" s="151"/>
+      <c r="J88" s="151"/>
+      <c r="K88" s="151"/>
+      <c r="L88" s="151"/>
+      <c r="M88" s="151"/>
+      <c r="N88" s="151"/>
+      <c r="O88" s="151"/>
+      <c r="P88" s="151"/>
+      <c r="Q88" s="151"/>
+      <c r="R88" s="151"/>
+      <c r="S88" s="151"/>
+      <c r="T88" s="151"/>
+      <c r="U88" s="151"/>
+      <c r="V88" s="151"/>
+      <c r="W88" s="151"/>
+      <c r="X88" s="151"/>
+      <c r="Y88" s="151"/>
+      <c r="Z88" s="151"/>
+      <c r="AA88" s="151"/>
+      <c r="AB88" s="151"/>
+      <c r="AC88" s="151"/>
+      <c r="AD88" s="151"/>
+      <c r="AE88" s="151"/>
+      <c r="AF88" s="151"/>
+      <c r="AG88" s="151"/>
+      <c r="AH88" s="151"/>
+      <c r="AI88" s="151"/>
+      <c r="AJ88" s="151"/>
+      <c r="AK88" s="151"/>
+      <c r="AL88" s="151"/>
+      <c r="AM88" s="151"/>
+      <c r="AN88" s="151"/>
+      <c r="AO88" s="151"/>
+      <c r="AP88" s="151"/>
+      <c r="AQ88" s="151"/>
+      <c r="AR88" s="151"/>
+      <c r="AS88" s="151"/>
+      <c r="AT88" s="151"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="3hf+o31UQX3AtRQqUcV/RJd+3mfAaN5O7rXRVlKzh0JlAGpwVg9GgTEDb5nIDRpf5tJqbuQU2oD4kp3qAWPpmw==" saltValue="ZVxQSEzeTaLWm4syF5vRTg==" spinCount="100000" sheet="1" scenarios="1"/>
   <mergeCells count="182">
-    <mergeCell ref="A88:AT88"/>
-    <mergeCell ref="U83:AA84"/>
-    <mergeCell ref="P84:T84"/>
-    <mergeCell ref="C85:O86"/>
-    <mergeCell ref="P85:T85"/>
-    <mergeCell ref="U85:AA85"/>
-    <mergeCell ref="AB85:AH86"/>
-    <mergeCell ref="P86:T86"/>
-    <mergeCell ref="U86:AA86"/>
-    <mergeCell ref="C81:O82"/>
-    <mergeCell ref="P81:T81"/>
-    <mergeCell ref="U81:AA81"/>
-    <mergeCell ref="AB81:AH84"/>
-    <mergeCell ref="AI81:AR86"/>
-    <mergeCell ref="P82:T82"/>
-    <mergeCell ref="U82:AA82"/>
-    <mergeCell ref="C83:O84"/>
-    <mergeCell ref="P83:T83"/>
-    <mergeCell ref="B76:AT76"/>
-    <mergeCell ref="C79:O80"/>
-    <mergeCell ref="P79:T80"/>
-    <mergeCell ref="U79:AH79"/>
-    <mergeCell ref="AI79:AR80"/>
-    <mergeCell ref="U80:AA80"/>
-    <mergeCell ref="AB80:AH80"/>
-    <mergeCell ref="B66:AT66"/>
-    <mergeCell ref="B67:AT67"/>
-    <mergeCell ref="B68:AT68"/>
-    <mergeCell ref="B69:AT69"/>
-    <mergeCell ref="B61:AT61"/>
-    <mergeCell ref="B63:AT63"/>
-    <mergeCell ref="B64:AT64"/>
-    <mergeCell ref="AK47:AR47"/>
-    <mergeCell ref="AK48:AR48"/>
-    <mergeCell ref="AK50:AR50"/>
-    <mergeCell ref="B56:AT56"/>
-    <mergeCell ref="B57:AT57"/>
-    <mergeCell ref="B58:AT58"/>
-    <mergeCell ref="B59:AT60"/>
-    <mergeCell ref="M46:T46"/>
-    <mergeCell ref="AK46:AR46"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="M47:T47"/>
-    <mergeCell ref="U47:V47"/>
-    <mergeCell ref="W47:X47"/>
-    <mergeCell ref="Y47:AF47"/>
-    <mergeCell ref="AG47:AH47"/>
-    <mergeCell ref="AI47:AJ47"/>
-    <mergeCell ref="X45:AG46"/>
-    <mergeCell ref="AI41:AJ42"/>
-    <mergeCell ref="AL41:AO42"/>
-    <mergeCell ref="AS41:AT42"/>
-    <mergeCell ref="M44:T44"/>
-    <mergeCell ref="Y44:AF44"/>
-    <mergeCell ref="AG44:AH44"/>
-    <mergeCell ref="B41:H42"/>
-    <mergeCell ref="I41:J42"/>
-    <mergeCell ref="K41:L42"/>
-    <mergeCell ref="M41:T42"/>
-    <mergeCell ref="U41:V42"/>
-    <mergeCell ref="W41:X42"/>
-    <mergeCell ref="AK36:AR36"/>
-    <mergeCell ref="AS36:AT36"/>
-    <mergeCell ref="AK37:AR37"/>
-    <mergeCell ref="B40:H40"/>
-    <mergeCell ref="Y40:AF40"/>
-    <mergeCell ref="AG40:AH40"/>
-    <mergeCell ref="AK40:AR40"/>
-    <mergeCell ref="M36:T36"/>
-    <mergeCell ref="U36:V36"/>
-    <mergeCell ref="W36:X36"/>
-    <mergeCell ref="Y36:AF36"/>
-    <mergeCell ref="AG36:AH36"/>
-    <mergeCell ref="AI36:AJ36"/>
-    <mergeCell ref="L39:U40"/>
-    <mergeCell ref="AK30:AR30"/>
-    <mergeCell ref="AS30:AT30"/>
-    <mergeCell ref="AZ34:BA34"/>
-    <mergeCell ref="M35:T35"/>
-    <mergeCell ref="Y35:AF35"/>
-    <mergeCell ref="AK35:AR35"/>
-    <mergeCell ref="BA35:BE35"/>
-    <mergeCell ref="AW28:AX28"/>
-    <mergeCell ref="M29:T29"/>
-    <mergeCell ref="X29:AH29"/>
-    <mergeCell ref="AK29:AR29"/>
-    <mergeCell ref="M30:T30"/>
-    <mergeCell ref="U30:V30"/>
-    <mergeCell ref="W30:X30"/>
-    <mergeCell ref="Y30:AF30"/>
-    <mergeCell ref="AG30:AH30"/>
-    <mergeCell ref="AI30:AJ30"/>
-    <mergeCell ref="AS24:AT25"/>
-    <mergeCell ref="M26:T26"/>
-    <mergeCell ref="Y26:AF26"/>
-    <mergeCell ref="M27:T27"/>
-    <mergeCell ref="U27:V27"/>
-    <mergeCell ref="Y27:AF27"/>
-    <mergeCell ref="AG27:AH27"/>
-    <mergeCell ref="B24:H25"/>
-    <mergeCell ref="I24:J25"/>
-    <mergeCell ref="K24:L25"/>
-    <mergeCell ref="W24:X25"/>
-    <mergeCell ref="AI24:AJ25"/>
-    <mergeCell ref="AK24:AR25"/>
-    <mergeCell ref="B23:H23"/>
-    <mergeCell ref="M23:T23"/>
-    <mergeCell ref="U23:V23"/>
-    <mergeCell ref="Y23:AF23"/>
-    <mergeCell ref="AG23:AH23"/>
-    <mergeCell ref="AK23:AR23"/>
-    <mergeCell ref="B19:AA19"/>
-    <mergeCell ref="AB19:AQ19"/>
-    <mergeCell ref="AR19:AS19"/>
-    <mergeCell ref="M22:T22"/>
-    <mergeCell ref="Y22:AF22"/>
-    <mergeCell ref="AK22:AR22"/>
-    <mergeCell ref="J17:AA17"/>
-    <mergeCell ref="AB17:AQ17"/>
-    <mergeCell ref="AR17:AS17"/>
-    <mergeCell ref="C18:I18"/>
-    <mergeCell ref="J18:AA18"/>
-    <mergeCell ref="AB18:AQ18"/>
-    <mergeCell ref="AR18:AS18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="C14:I17"/>
-    <mergeCell ref="J14:AA14"/>
-    <mergeCell ref="AB14:AS14"/>
-    <mergeCell ref="J15:AA15"/>
-    <mergeCell ref="AB15:AQ15"/>
-    <mergeCell ref="AR15:AS15"/>
-    <mergeCell ref="J16:AA16"/>
-    <mergeCell ref="AB16:AQ16"/>
-    <mergeCell ref="AR16:AS16"/>
+    <mergeCell ref="AO1:AT1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="AO2:AT2"/>
+    <mergeCell ref="A3:AT3"/>
+    <mergeCell ref="BE4:BG4"/>
+    <mergeCell ref="B5:I5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="M5:U5"/>
+    <mergeCell ref="V5:W5"/>
+    <mergeCell ref="Y5:AG5"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="J7:U7"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="Y7:AF7"/>
+    <mergeCell ref="AG7:AR7"/>
+    <mergeCell ref="AS7:AT7"/>
+    <mergeCell ref="AH5:AI5"/>
+    <mergeCell ref="AK5:AT5"/>
+    <mergeCell ref="AV5:BC5"/>
+    <mergeCell ref="B6:I6"/>
+    <mergeCell ref="J6:W6"/>
+    <mergeCell ref="Y6:AF6"/>
+    <mergeCell ref="AG6:AT6"/>
+    <mergeCell ref="AW6:AX6"/>
+    <mergeCell ref="AZ6:BC6"/>
     <mergeCell ref="AK9:AN9"/>
     <mergeCell ref="AP9:AS9"/>
     <mergeCell ref="B10:I10"/>
@@ -11905,31 +11800,140 @@
     <mergeCell ref="R8:U8"/>
     <mergeCell ref="W8:Z8"/>
     <mergeCell ref="AB8:AE8"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="J7:U7"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="Y7:AF7"/>
-    <mergeCell ref="AG7:AR7"/>
-    <mergeCell ref="AS7:AT7"/>
-    <mergeCell ref="AH5:AI5"/>
-    <mergeCell ref="AK5:AT5"/>
-    <mergeCell ref="AV5:BC5"/>
-    <mergeCell ref="B6:I6"/>
-    <mergeCell ref="J6:W6"/>
-    <mergeCell ref="Y6:AF6"/>
-    <mergeCell ref="AG6:AT6"/>
-    <mergeCell ref="AW6:AX6"/>
-    <mergeCell ref="AZ6:BC6"/>
-    <mergeCell ref="AO1:AT1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="AO2:AT2"/>
-    <mergeCell ref="A3:AT3"/>
-    <mergeCell ref="BE4:BG4"/>
-    <mergeCell ref="B5:I5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="M5:U5"/>
-    <mergeCell ref="V5:W5"/>
-    <mergeCell ref="Y5:AG5"/>
+    <mergeCell ref="J17:AA17"/>
+    <mergeCell ref="AB17:AQ17"/>
+    <mergeCell ref="AR17:AS17"/>
+    <mergeCell ref="C18:I18"/>
+    <mergeCell ref="J18:AA18"/>
+    <mergeCell ref="AB18:AQ18"/>
+    <mergeCell ref="AR18:AS18"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="C14:I17"/>
+    <mergeCell ref="J14:AA14"/>
+    <mergeCell ref="AB14:AS14"/>
+    <mergeCell ref="J15:AA15"/>
+    <mergeCell ref="AB15:AQ15"/>
+    <mergeCell ref="AR15:AS15"/>
+    <mergeCell ref="J16:AA16"/>
+    <mergeCell ref="AB16:AQ16"/>
+    <mergeCell ref="AR16:AS16"/>
+    <mergeCell ref="B23:H23"/>
+    <mergeCell ref="M23:T23"/>
+    <mergeCell ref="U23:V23"/>
+    <mergeCell ref="Y23:AF23"/>
+    <mergeCell ref="AG23:AH23"/>
+    <mergeCell ref="AK23:AR23"/>
+    <mergeCell ref="B19:AA19"/>
+    <mergeCell ref="AB19:AQ19"/>
+    <mergeCell ref="AR19:AS19"/>
+    <mergeCell ref="M22:T22"/>
+    <mergeCell ref="Y22:AF22"/>
+    <mergeCell ref="AK22:AR22"/>
+    <mergeCell ref="AS24:AT25"/>
+    <mergeCell ref="M26:T26"/>
+    <mergeCell ref="Y26:AF26"/>
+    <mergeCell ref="M27:T27"/>
+    <mergeCell ref="U27:V27"/>
+    <mergeCell ref="Y27:AF27"/>
+    <mergeCell ref="AG27:AH27"/>
+    <mergeCell ref="B24:H25"/>
+    <mergeCell ref="I24:J25"/>
+    <mergeCell ref="K24:L25"/>
+    <mergeCell ref="W24:X25"/>
+    <mergeCell ref="AI24:AJ25"/>
+    <mergeCell ref="AK24:AR25"/>
+    <mergeCell ref="AK30:AR30"/>
+    <mergeCell ref="AS30:AT30"/>
+    <mergeCell ref="AZ34:BA34"/>
+    <mergeCell ref="M35:T35"/>
+    <mergeCell ref="Y35:AF35"/>
+    <mergeCell ref="AK35:AR35"/>
+    <mergeCell ref="BA35:BE35"/>
+    <mergeCell ref="AW28:AX28"/>
+    <mergeCell ref="M29:T29"/>
+    <mergeCell ref="X29:AH29"/>
+    <mergeCell ref="AK29:AR29"/>
+    <mergeCell ref="M30:T30"/>
+    <mergeCell ref="U30:V30"/>
+    <mergeCell ref="W30:X30"/>
+    <mergeCell ref="Y30:AF30"/>
+    <mergeCell ref="AG30:AH30"/>
+    <mergeCell ref="AI30:AJ30"/>
+    <mergeCell ref="AK36:AR36"/>
+    <mergeCell ref="AS36:AT36"/>
+    <mergeCell ref="AK37:AR37"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="Y40:AF40"/>
+    <mergeCell ref="AG40:AH40"/>
+    <mergeCell ref="AK40:AR40"/>
+    <mergeCell ref="M36:T36"/>
+    <mergeCell ref="U36:V36"/>
+    <mergeCell ref="W36:X36"/>
+    <mergeCell ref="Y36:AF36"/>
+    <mergeCell ref="AG36:AH36"/>
+    <mergeCell ref="AI36:AJ36"/>
+    <mergeCell ref="L39:U40"/>
+    <mergeCell ref="AI41:AJ42"/>
+    <mergeCell ref="AL41:AO42"/>
+    <mergeCell ref="AS41:AT42"/>
+    <mergeCell ref="M44:T44"/>
+    <mergeCell ref="Y44:AF44"/>
+    <mergeCell ref="AG44:AH44"/>
+    <mergeCell ref="B41:H42"/>
+    <mergeCell ref="I41:J42"/>
+    <mergeCell ref="K41:L42"/>
+    <mergeCell ref="M41:T42"/>
+    <mergeCell ref="U41:V42"/>
+    <mergeCell ref="W41:X42"/>
+    <mergeCell ref="M46:T46"/>
+    <mergeCell ref="AK46:AR46"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="M47:T47"/>
+    <mergeCell ref="U47:V47"/>
+    <mergeCell ref="W47:X47"/>
+    <mergeCell ref="Y47:AF47"/>
+    <mergeCell ref="AG47:AH47"/>
+    <mergeCell ref="AI47:AJ47"/>
+    <mergeCell ref="X45:AG46"/>
+    <mergeCell ref="B61:AT61"/>
+    <mergeCell ref="B63:AT63"/>
+    <mergeCell ref="B64:AT64"/>
+    <mergeCell ref="AK47:AR47"/>
+    <mergeCell ref="AK48:AR48"/>
+    <mergeCell ref="AK50:AR50"/>
+    <mergeCell ref="B56:AT56"/>
+    <mergeCell ref="B57:AT57"/>
+    <mergeCell ref="B58:AT58"/>
+    <mergeCell ref="B59:AT60"/>
+    <mergeCell ref="B76:AT76"/>
+    <mergeCell ref="C79:O80"/>
+    <mergeCell ref="P79:T80"/>
+    <mergeCell ref="U79:AH79"/>
+    <mergeCell ref="AI79:AR80"/>
+    <mergeCell ref="U80:AA80"/>
+    <mergeCell ref="AB80:AH80"/>
+    <mergeCell ref="B66:AT66"/>
+    <mergeCell ref="B67:AT67"/>
+    <mergeCell ref="B68:AT68"/>
+    <mergeCell ref="B69:AT69"/>
+    <mergeCell ref="C81:O82"/>
+    <mergeCell ref="P81:T81"/>
+    <mergeCell ref="U81:AA81"/>
+    <mergeCell ref="AB81:AH84"/>
+    <mergeCell ref="AI81:AR86"/>
+    <mergeCell ref="P82:T82"/>
+    <mergeCell ref="U82:AA82"/>
+    <mergeCell ref="C83:O84"/>
+    <mergeCell ref="P83:T83"/>
+    <mergeCell ref="A88:AT88"/>
+    <mergeCell ref="U83:AA84"/>
+    <mergeCell ref="P84:T84"/>
+    <mergeCell ref="C85:O86"/>
+    <mergeCell ref="P85:T85"/>
+    <mergeCell ref="U85:AA85"/>
+    <mergeCell ref="AB85:AH86"/>
+    <mergeCell ref="P86:T86"/>
+    <mergeCell ref="U86:AA86"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="4">
@@ -12043,6 +12047,24 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="263dbbe5-076b-4606-a03b-9598f5f2f35a" xsi:nil="true"/>
+    <Owner xmlns="2bc05441-ecb8-41d0-9872-2862fef3ebb0">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Owner>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2bc05441-ecb8-41d0-9872-2862fef3ebb0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101004F04D70F81502745934EEFA6067428B0" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="e4b1285e22ba7abc44906dbb08eaf091">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2bc05441-ecb8-41d0-9872-2862fef3ebb0" xmlns:ns3="263dbbe5-076b-4606-a03b-9598f5f2f35a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f178929248ea575f95a3ed45aedf7b59" ns2:_="" ns3:_="">
     <xsd:import namespace="2bc05441-ecb8-41d0-9872-2862fef3ebb0"/>
@@ -12263,24 +12285,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="263dbbe5-076b-4606-a03b-9598f5f2f35a" xsi:nil="true"/>
-    <Owner xmlns="2bc05441-ecb8-41d0-9872-2862fef3ebb0">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Owner>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2bc05441-ecb8-41d0-9872-2862fef3ebb0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31F2529B-DA47-47B2-9E29-6A6C8AE8452E}">
   <ds:schemaRefs>
@@ -12290,6 +12294,23 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70DCB08F-36BD-4CC4-A1F7-88A1F6838D51}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="2bc05441-ecb8-41d0-9872-2862fef3ebb0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="263dbbe5-076b-4606-a03b-9598f5f2f35a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4F4A13C-7815-4AED-8003-ADDB7A2195C8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12306,21 +12327,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70DCB08F-36BD-4CC4-A1F7-88A1F6838D51}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="2bc05441-ecb8-41d0-9872-2862fef3ebb0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="263dbbe5-076b-4606-a03b-9598f5f2f35a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/templates/R80302書式/支給申請/03_定額制サービスによる訓練に関する経費助成の内訳(様式第6-3号)※定額制.xlsx
+++ b/templates/R80302書式/支給申請/03_定額制サービスによる訓練に関する経費助成の内訳(様式第6-3号)※定額制.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://agri0001-my.sharepoint.com/personal/dxhr024_agri0001_onmicrosoft_com/Documents/デスクトップ/document_generator_new/templates/R80302書式/支給申請/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="13_ncr:1_{97D5BD46-7B48-4514-A0B8-0C020D6B3C7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A39B408-E183-464A-A4F1-F43111DBC59A}"/>
+  <xr:revisionPtr revIDLastSave="88" documentId="13_ncr:1_{97D5BD46-7B48-4514-A0B8-0C020D6B3C7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CC11171-A5B6-4632-A234-FFA5F28DC232}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22276" windowHeight="13276" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="166">
   <si>
     <t>１</t>
     <phoneticPr fontId="2"/>
@@ -2584,6 +2584,9 @@
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>01</t>
+  </si>
 </sst>
 </file>
 
@@ -2594,7 +2597,7 @@
     <numFmt numFmtId="177" formatCode="yyyy/m/d;@"/>
     <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -4140,172 +4143,408 @@
     <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="19" fillId="4" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="2" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="13" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="5" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="24" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="5" borderId="58" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="5" borderId="59" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="10" fillId="5" borderId="60" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="57" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="19" fillId="4" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="19" fillId="4" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="57" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="57" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="19" fillId="9" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="19" fillId="9" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="36" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="9" borderId="37" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="9" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="9" borderId="38" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="9" borderId="36" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="9" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="5" borderId="37" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="5" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="5" borderId="38" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="5" borderId="36" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="5" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="5" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="9" borderId="13" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="9" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="19" fillId="0" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="5" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="5" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="5" borderId="8" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="38" fontId="5" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="10" fillId="5" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="19" fillId="0" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="19" fillId="4" borderId="13" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4323,397 +4562,161 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="38" fontId="5" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="5" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="24" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="5" borderId="58" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="10" fillId="5" borderId="59" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="10" fillId="5" borderId="60" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="10" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="9" borderId="37" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="9" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="9" borderId="38" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="9" borderId="36" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="9" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="10" fillId="5" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="5" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="5" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="5" borderId="8" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="9" borderId="13" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="9" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="36" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="5" borderId="37" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="5" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="5" borderId="38" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="5" borderId="36" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="5" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="10" fillId="5" borderId="39" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="19" fillId="9" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="19" fillId="9" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="57" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="57" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="19" fillId="4" borderId="57" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="19" fillId="4" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="57" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="2" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="2" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="57" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="29" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="38" fontId="19" fillId="4" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -5314,7 +5317,7 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:JB88"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="46" width="3.1328125" style="1" customWidth="1"/>
     <col min="47" max="47" width="1.3984375" style="1" customWidth="1"/>
@@ -5324,173 +5327,173 @@
     <col min="60" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:67" ht="17.25" customHeight="1">
+    <row r="1" spans="1:67" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="44" t="s">
         <v>164</v>
       </c>
-      <c r="AO1" s="319"/>
-      <c r="AP1" s="319"/>
-      <c r="AQ1" s="319"/>
-      <c r="AR1" s="319"/>
-      <c r="AS1" s="319"/>
-      <c r="AT1" s="319"/>
+      <c r="AO1" s="151"/>
+      <c r="AP1" s="151"/>
+      <c r="AQ1" s="151"/>
+      <c r="AR1" s="151"/>
+      <c r="AS1" s="151"/>
+      <c r="AT1" s="151"/>
     </row>
-    <row r="2" spans="1:67" ht="16.5">
-      <c r="A2" s="320"/>
-      <c r="B2" s="320"/>
-      <c r="C2" s="320"/>
-      <c r="D2" s="320"/>
-      <c r="E2" s="320"/>
-      <c r="F2" s="320"/>
-      <c r="G2" s="320"/>
-      <c r="H2" s="320"/>
-      <c r="I2" s="320"/>
-      <c r="J2" s="320"/>
-      <c r="K2" s="320"/>
-      <c r="L2" s="320"/>
-      <c r="M2" s="320"/>
-      <c r="AO2" s="319"/>
-      <c r="AP2" s="319"/>
-      <c r="AQ2" s="319"/>
-      <c r="AR2" s="319"/>
-      <c r="AS2" s="319"/>
-      <c r="AT2" s="319"/>
+    <row r="2" spans="1:67" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="152"/>
+      <c r="B2" s="152"/>
+      <c r="C2" s="152"/>
+      <c r="D2" s="152"/>
+      <c r="E2" s="152"/>
+      <c r="F2" s="152"/>
+      <c r="G2" s="152"/>
+      <c r="H2" s="152"/>
+      <c r="I2" s="152"/>
+      <c r="J2" s="152"/>
+      <c r="K2" s="152"/>
+      <c r="L2" s="152"/>
+      <c r="M2" s="152"/>
+      <c r="AO2" s="151"/>
+      <c r="AP2" s="151"/>
+      <c r="AQ2" s="151"/>
+      <c r="AR2" s="151"/>
+      <c r="AS2" s="151"/>
+      <c r="AT2" s="151"/>
     </row>
-    <row r="3" spans="1:67" ht="50.25" customHeight="1">
-      <c r="A3" s="321" t="s">
+    <row r="3" spans="1:67" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="153" t="s">
         <v>114</v>
       </c>
-      <c r="B3" s="322"/>
-      <c r="C3" s="322"/>
-      <c r="D3" s="322"/>
-      <c r="E3" s="322"/>
-      <c r="F3" s="322"/>
-      <c r="G3" s="322"/>
-      <c r="H3" s="322"/>
-      <c r="I3" s="322"/>
-      <c r="J3" s="322"/>
-      <c r="K3" s="322"/>
-      <c r="L3" s="322"/>
-      <c r="M3" s="322"/>
-      <c r="N3" s="322"/>
-      <c r="O3" s="322"/>
-      <c r="P3" s="322"/>
-      <c r="Q3" s="322"/>
-      <c r="R3" s="322"/>
-      <c r="S3" s="322"/>
-      <c r="T3" s="322"/>
-      <c r="U3" s="322"/>
-      <c r="V3" s="322"/>
-      <c r="W3" s="322"/>
-      <c r="X3" s="322"/>
-      <c r="Y3" s="322"/>
-      <c r="Z3" s="322"/>
-      <c r="AA3" s="322"/>
-      <c r="AB3" s="322"/>
-      <c r="AC3" s="322"/>
-      <c r="AD3" s="322"/>
-      <c r="AE3" s="322"/>
-      <c r="AF3" s="322"/>
-      <c r="AG3" s="322"/>
-      <c r="AH3" s="322"/>
-      <c r="AI3" s="322"/>
-      <c r="AJ3" s="322"/>
-      <c r="AK3" s="322"/>
-      <c r="AL3" s="322"/>
-      <c r="AM3" s="322"/>
-      <c r="AN3" s="322"/>
-      <c r="AO3" s="322"/>
-      <c r="AP3" s="322"/>
-      <c r="AQ3" s="322"/>
-      <c r="AR3" s="322"/>
-      <c r="AS3" s="322"/>
-      <c r="AT3" s="322"/>
+      <c r="B3" s="154"/>
+      <c r="C3" s="154"/>
+      <c r="D3" s="154"/>
+      <c r="E3" s="154"/>
+      <c r="F3" s="154"/>
+      <c r="G3" s="154"/>
+      <c r="H3" s="154"/>
+      <c r="I3" s="154"/>
+      <c r="J3" s="154"/>
+      <c r="K3" s="154"/>
+      <c r="L3" s="154"/>
+      <c r="M3" s="154"/>
+      <c r="N3" s="154"/>
+      <c r="O3" s="154"/>
+      <c r="P3" s="154"/>
+      <c r="Q3" s="154"/>
+      <c r="R3" s="154"/>
+      <c r="S3" s="154"/>
+      <c r="T3" s="154"/>
+      <c r="U3" s="154"/>
+      <c r="V3" s="154"/>
+      <c r="W3" s="154"/>
+      <c r="X3" s="154"/>
+      <c r="Y3" s="154"/>
+      <c r="Z3" s="154"/>
+      <c r="AA3" s="154"/>
+      <c r="AB3" s="154"/>
+      <c r="AC3" s="154"/>
+      <c r="AD3" s="154"/>
+      <c r="AE3" s="154"/>
+      <c r="AF3" s="154"/>
+      <c r="AG3" s="154"/>
+      <c r="AH3" s="154"/>
+      <c r="AI3" s="154"/>
+      <c r="AJ3" s="154"/>
+      <c r="AK3" s="154"/>
+      <c r="AL3" s="154"/>
+      <c r="AM3" s="154"/>
+      <c r="AN3" s="154"/>
+      <c r="AO3" s="154"/>
+      <c r="AP3" s="154"/>
+      <c r="AQ3" s="154"/>
+      <c r="AR3" s="154"/>
+      <c r="AS3" s="154"/>
+      <c r="AT3" s="154"/>
     </row>
-    <row r="4" spans="1:67" ht="18.75" customHeight="1" thickBot="1">
+    <row r="4" spans="1:67" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>137</v>
       </c>
       <c r="AT4" s="45"/>
-      <c r="BE4" s="323" t="s">
+      <c r="BE4" s="155" t="s">
         <v>123</v>
       </c>
-      <c r="BF4" s="324"/>
-      <c r="BG4" s="325"/>
+      <c r="BF4" s="156"/>
+      <c r="BG4" s="157"/>
     </row>
-    <row r="5" spans="1:67" s="5" customFormat="1" ht="56.25" customHeight="1">
+    <row r="5" spans="1:67" s="5" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="326" t="s">
+      <c r="B5" s="158" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="326"/>
-      <c r="D5" s="326"/>
-      <c r="E5" s="326"/>
-      <c r="F5" s="326"/>
-      <c r="G5" s="326"/>
-      <c r="H5" s="326"/>
-      <c r="I5" s="327"/>
-      <c r="J5" s="328"/>
-      <c r="K5" s="329"/>
+      <c r="C5" s="158"/>
+      <c r="D5" s="158"/>
+      <c r="E5" s="158"/>
+      <c r="F5" s="158"/>
+      <c r="G5" s="158"/>
+      <c r="H5" s="158"/>
+      <c r="I5" s="159"/>
+      <c r="J5" s="160"/>
+      <c r="K5" s="161"/>
       <c r="L5" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="M5" s="330" t="s">
+      <c r="M5" s="162" t="s">
         <v>115</v>
       </c>
-      <c r="N5" s="330"/>
-      <c r="O5" s="330"/>
-      <c r="P5" s="330"/>
-      <c r="Q5" s="330"/>
-      <c r="R5" s="330"/>
-      <c r="S5" s="330"/>
-      <c r="T5" s="330"/>
-      <c r="U5" s="330"/>
-      <c r="V5" s="331"/>
-      <c r="W5" s="332"/>
+      <c r="N5" s="162"/>
+      <c r="O5" s="162"/>
+      <c r="P5" s="162"/>
+      <c r="Q5" s="162"/>
+      <c r="R5" s="162"/>
+      <c r="S5" s="162"/>
+      <c r="T5" s="162"/>
+      <c r="U5" s="162"/>
+      <c r="V5" s="163"/>
+      <c r="W5" s="164"/>
       <c r="X5" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="Y5" s="333" t="s">
+      <c r="Y5" s="165" t="s">
         <v>5</v>
       </c>
-      <c r="Z5" s="333"/>
-      <c r="AA5" s="333"/>
-      <c r="AB5" s="333"/>
-      <c r="AC5" s="333"/>
-      <c r="AD5" s="333"/>
-      <c r="AE5" s="333"/>
-      <c r="AF5" s="333"/>
-      <c r="AG5" s="334"/>
-      <c r="AH5" s="308"/>
-      <c r="AI5" s="309"/>
+      <c r="Z5" s="165"/>
+      <c r="AA5" s="165"/>
+      <c r="AB5" s="165"/>
+      <c r="AC5" s="165"/>
+      <c r="AD5" s="165"/>
+      <c r="AE5" s="165"/>
+      <c r="AF5" s="165"/>
+      <c r="AG5" s="166"/>
+      <c r="AH5" s="172"/>
+      <c r="AI5" s="173"/>
       <c r="AJ5" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="AK5" s="310" t="s">
+      <c r="AK5" s="174" t="s">
         <v>163</v>
       </c>
-      <c r="AL5" s="310"/>
-      <c r="AM5" s="310"/>
-      <c r="AN5" s="310"/>
-      <c r="AO5" s="310"/>
-      <c r="AP5" s="310"/>
-      <c r="AQ5" s="310"/>
-      <c r="AR5" s="310"/>
-      <c r="AS5" s="310"/>
-      <c r="AT5" s="311"/>
+      <c r="AL5" s="174"/>
+      <c r="AM5" s="174"/>
+      <c r="AN5" s="174"/>
+      <c r="AO5" s="174"/>
+      <c r="AP5" s="174"/>
+      <c r="AQ5" s="174"/>
+      <c r="AR5" s="174"/>
+      <c r="AS5" s="174"/>
+      <c r="AT5" s="175"/>
       <c r="AU5" s="15"/>
-      <c r="AV5" s="312" t="s">
+      <c r="AV5" s="176" t="s">
         <v>133</v>
       </c>
-      <c r="AW5" s="312"/>
-      <c r="AX5" s="312"/>
-      <c r="AY5" s="312"/>
-      <c r="AZ5" s="312"/>
-      <c r="BA5" s="312"/>
-      <c r="BB5" s="312"/>
-      <c r="BC5" s="312"/>
+      <c r="AW5" s="176"/>
+      <c r="AX5" s="176"/>
+      <c r="AY5" s="176"/>
+      <c r="AZ5" s="176"/>
+      <c r="BA5" s="176"/>
+      <c r="BB5" s="176"/>
+      <c r="BC5" s="176"/>
       <c r="BD5" s="1"/>
       <c r="BE5" s="32"/>
       <c r="BF5" s="32"/>
@@ -5504,76 +5507,76 @@
       <c r="BN5" s="15"/>
       <c r="BO5" s="15"/>
     </row>
-    <row r="6" spans="1:67" s="5" customFormat="1" ht="36.75" customHeight="1">
+    <row r="6" spans="1:67" s="5" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="50">
         <v>2</v>
       </c>
-      <c r="B6" s="313" t="s">
+      <c r="B6" s="177" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="280"/>
-      <c r="D6" s="280"/>
-      <c r="E6" s="280"/>
-      <c r="F6" s="280"/>
-      <c r="G6" s="280"/>
-      <c r="H6" s="280"/>
-      <c r="I6" s="281"/>
-      <c r="J6" s="314"/>
-      <c r="K6" s="314"/>
-      <c r="L6" s="314"/>
-      <c r="M6" s="314"/>
-      <c r="N6" s="314"/>
-      <c r="O6" s="314"/>
-      <c r="P6" s="314"/>
-      <c r="Q6" s="314"/>
-      <c r="R6" s="314"/>
-      <c r="S6" s="314"/>
-      <c r="T6" s="314"/>
-      <c r="U6" s="314"/>
-      <c r="V6" s="314"/>
-      <c r="W6" s="314"/>
+      <c r="C6" s="167"/>
+      <c r="D6" s="167"/>
+      <c r="E6" s="167"/>
+      <c r="F6" s="167"/>
+      <c r="G6" s="167"/>
+      <c r="H6" s="167"/>
+      <c r="I6" s="168"/>
+      <c r="J6" s="178"/>
+      <c r="K6" s="178"/>
+      <c r="L6" s="178"/>
+      <c r="M6" s="178"/>
+      <c r="N6" s="178"/>
+      <c r="O6" s="178"/>
+      <c r="P6" s="178"/>
+      <c r="Q6" s="178"/>
+      <c r="R6" s="178"/>
+      <c r="S6" s="178"/>
+      <c r="T6" s="178"/>
+      <c r="U6" s="178"/>
+      <c r="V6" s="178"/>
+      <c r="W6" s="178"/>
       <c r="X6" s="51">
         <v>3</v>
       </c>
-      <c r="Y6" s="280" t="s">
+      <c r="Y6" s="167" t="s">
         <v>139</v>
       </c>
-      <c r="Z6" s="280"/>
-      <c r="AA6" s="280"/>
-      <c r="AB6" s="280"/>
-      <c r="AC6" s="280"/>
-      <c r="AD6" s="280"/>
-      <c r="AE6" s="280"/>
-      <c r="AF6" s="281"/>
-      <c r="AG6" s="314"/>
-      <c r="AH6" s="314"/>
-      <c r="AI6" s="314"/>
-      <c r="AJ6" s="314"/>
-      <c r="AK6" s="314"/>
-      <c r="AL6" s="314"/>
-      <c r="AM6" s="314"/>
-      <c r="AN6" s="314"/>
-      <c r="AO6" s="314"/>
-      <c r="AP6" s="314"/>
-      <c r="AQ6" s="314"/>
-      <c r="AR6" s="314"/>
-      <c r="AS6" s="314"/>
-      <c r="AT6" s="315"/>
+      <c r="Z6" s="167"/>
+      <c r="AA6" s="167"/>
+      <c r="AB6" s="167"/>
+      <c r="AC6" s="167"/>
+      <c r="AD6" s="167"/>
+      <c r="AE6" s="167"/>
+      <c r="AF6" s="168"/>
+      <c r="AG6" s="178"/>
+      <c r="AH6" s="178"/>
+      <c r="AI6" s="178"/>
+      <c r="AJ6" s="178"/>
+      <c r="AK6" s="178"/>
+      <c r="AL6" s="178"/>
+      <c r="AM6" s="178"/>
+      <c r="AN6" s="178"/>
+      <c r="AO6" s="178"/>
+      <c r="AP6" s="178"/>
+      <c r="AQ6" s="178"/>
+      <c r="AR6" s="178"/>
+      <c r="AS6" s="178"/>
+      <c r="AT6" s="179"/>
       <c r="AU6" s="9"/>
       <c r="AV6" s="31"/>
-      <c r="AW6" s="316" t="s">
+      <c r="AW6" s="180" t="s">
         <v>140</v>
       </c>
-      <c r="AX6" s="317"/>
+      <c r="AX6" s="181"/>
       <c r="AY6" s="34" t="s">
         <v>134</v>
       </c>
-      <c r="AZ6" s="316" t="s">
+      <c r="AZ6" s="180" t="s">
         <v>135</v>
       </c>
-      <c r="BA6" s="317"/>
-      <c r="BB6" s="317"/>
-      <c r="BC6" s="318"/>
+      <c r="BA6" s="181"/>
+      <c r="BB6" s="181"/>
+      <c r="BC6" s="182"/>
       <c r="BD6" s="1"/>
       <c r="BE6" s="1">
         <v>2023</v>
@@ -5586,65 +5589,69 @@
       </c>
       <c r="BH6" s="19"/>
     </row>
-    <row r="7" spans="1:67" ht="36.75" customHeight="1">
+    <row r="7" spans="1:67" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="52">
         <v>4</v>
       </c>
-      <c r="B7" s="280" t="s">
+      <c r="B7" s="167" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="280"/>
-      <c r="D7" s="280"/>
-      <c r="E7" s="280"/>
-      <c r="F7" s="280"/>
-      <c r="G7" s="280"/>
-      <c r="H7" s="280"/>
-      <c r="I7" s="281"/>
-      <c r="J7" s="305"/>
-      <c r="K7" s="305"/>
-      <c r="L7" s="305"/>
-      <c r="M7" s="305"/>
-      <c r="N7" s="305"/>
-      <c r="O7" s="305"/>
-      <c r="P7" s="305"/>
-      <c r="Q7" s="305"/>
-      <c r="R7" s="305"/>
-      <c r="S7" s="305"/>
-      <c r="T7" s="305"/>
-      <c r="U7" s="305"/>
-      <c r="V7" s="306" t="s">
+      <c r="C7" s="167"/>
+      <c r="D7" s="167"/>
+      <c r="E7" s="167"/>
+      <c r="F7" s="167"/>
+      <c r="G7" s="167"/>
+      <c r="H7" s="167"/>
+      <c r="I7" s="168"/>
+      <c r="J7" s="169">
+        <v>5</v>
+      </c>
+      <c r="K7" s="169"/>
+      <c r="L7" s="169"/>
+      <c r="M7" s="169"/>
+      <c r="N7" s="169"/>
+      <c r="O7" s="169"/>
+      <c r="P7" s="169"/>
+      <c r="Q7" s="169"/>
+      <c r="R7" s="169"/>
+      <c r="S7" s="169"/>
+      <c r="T7" s="169"/>
+      <c r="U7" s="169"/>
+      <c r="V7" s="170" t="s">
         <v>10</v>
       </c>
-      <c r="W7" s="306"/>
+      <c r="W7" s="170"/>
       <c r="X7" s="51">
         <v>5</v>
       </c>
-      <c r="Y7" s="280" t="s">
+      <c r="Y7" s="167" t="s">
         <v>122</v>
       </c>
-      <c r="Z7" s="280"/>
-      <c r="AA7" s="280"/>
-      <c r="AB7" s="280"/>
-      <c r="AC7" s="280"/>
-      <c r="AD7" s="280"/>
-      <c r="AE7" s="280"/>
-      <c r="AF7" s="281"/>
-      <c r="AG7" s="305"/>
-      <c r="AH7" s="305"/>
-      <c r="AI7" s="305"/>
-      <c r="AJ7" s="305"/>
-      <c r="AK7" s="305"/>
-      <c r="AL7" s="305"/>
-      <c r="AM7" s="305"/>
-      <c r="AN7" s="305"/>
-      <c r="AO7" s="305"/>
-      <c r="AP7" s="305"/>
-      <c r="AQ7" s="305"/>
-      <c r="AR7" s="305"/>
-      <c r="AS7" s="306" t="s">
+      <c r="Z7" s="167"/>
+      <c r="AA7" s="167"/>
+      <c r="AB7" s="167"/>
+      <c r="AC7" s="167"/>
+      <c r="AD7" s="167"/>
+      <c r="AE7" s="167"/>
+      <c r="AF7" s="168"/>
+      <c r="AG7" s="169">
+        <v>5</v>
+      </c>
+      <c r="AH7" s="169"/>
+      <c r="AI7" s="169"/>
+      <c r="AJ7" s="169"/>
+      <c r="AK7" s="169"/>
+      <c r="AL7" s="169"/>
+      <c r="AM7" s="169"/>
+      <c r="AN7" s="169"/>
+      <c r="AO7" s="169"/>
+      <c r="AP7" s="169"/>
+      <c r="AQ7" s="169"/>
+      <c r="AR7" s="169"/>
+      <c r="AS7" s="170" t="s">
         <v>10</v>
       </c>
-      <c r="AT7" s="307"/>
+      <c r="AT7" s="171"/>
       <c r="AV7" s="17"/>
       <c r="AW7" s="33" t="s">
         <v>13</v>
@@ -5679,70 +5686,82 @@
       </c>
       <c r="BH7" s="20"/>
     </row>
-    <row r="8" spans="1:67" ht="36.75" customHeight="1">
+    <row r="8" spans="1:67" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="52">
         <v>6</v>
       </c>
-      <c r="B8" s="280" t="s">
+      <c r="B8" s="167" t="s">
         <v>121</v>
       </c>
-      <c r="C8" s="280"/>
-      <c r="D8" s="280"/>
-      <c r="E8" s="280"/>
-      <c r="F8" s="280"/>
-      <c r="G8" s="280"/>
-      <c r="H8" s="280"/>
-      <c r="I8" s="281"/>
-      <c r="J8" s="302" t="s">
+      <c r="C8" s="167"/>
+      <c r="D8" s="167"/>
+      <c r="E8" s="167"/>
+      <c r="F8" s="167"/>
+      <c r="G8" s="167"/>
+      <c r="H8" s="167"/>
+      <c r="I8" s="168"/>
+      <c r="J8" s="197" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="303"/>
-      <c r="L8" s="304"/>
-      <c r="M8" s="298"/>
-      <c r="N8" s="292"/>
-      <c r="O8" s="292"/>
-      <c r="P8" s="292"/>
+      <c r="K8" s="198"/>
+      <c r="L8" s="199"/>
+      <c r="M8" s="193">
+        <v>2026</v>
+      </c>
+      <c r="N8" s="183"/>
+      <c r="O8" s="183"/>
+      <c r="P8" s="183"/>
       <c r="Q8" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="R8" s="292"/>
-      <c r="S8" s="292"/>
-      <c r="T8" s="292"/>
-      <c r="U8" s="292"/>
+      <c r="R8" s="183" t="s">
+        <v>23</v>
+      </c>
+      <c r="S8" s="183"/>
+      <c r="T8" s="183"/>
+      <c r="U8" s="183"/>
       <c r="V8" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="W8" s="292"/>
-      <c r="X8" s="292"/>
-      <c r="Y8" s="292"/>
-      <c r="Z8" s="292"/>
+      <c r="W8" s="183" t="s">
+        <v>165</v>
+      </c>
+      <c r="X8" s="183"/>
+      <c r="Y8" s="183"/>
+      <c r="Z8" s="183"/>
       <c r="AA8" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="AB8" s="302" t="s">
+      <c r="AB8" s="197" t="s">
         <v>17</v>
       </c>
-      <c r="AC8" s="303"/>
-      <c r="AD8" s="303"/>
-      <c r="AE8" s="304"/>
-      <c r="AF8" s="298"/>
-      <c r="AG8" s="292"/>
-      <c r="AH8" s="292"/>
-      <c r="AI8" s="292"/>
+      <c r="AC8" s="198"/>
+      <c r="AD8" s="198"/>
+      <c r="AE8" s="199"/>
+      <c r="AF8" s="193">
+        <v>2027</v>
+      </c>
+      <c r="AG8" s="183"/>
+      <c r="AH8" s="183"/>
+      <c r="AI8" s="183"/>
       <c r="AJ8" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="AK8" s="292"/>
-      <c r="AL8" s="292"/>
-      <c r="AM8" s="292"/>
-      <c r="AN8" s="292"/>
+      <c r="AK8" s="183" t="s">
+        <v>20</v>
+      </c>
+      <c r="AL8" s="183"/>
+      <c r="AM8" s="183"/>
+      <c r="AN8" s="183"/>
       <c r="AO8" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="AP8" s="292"/>
-      <c r="AQ8" s="292"/>
-      <c r="AR8" s="292"/>
-      <c r="AS8" s="292"/>
+      <c r="AP8" s="183" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ8" s="183"/>
+      <c r="AR8" s="183"/>
+      <c r="AS8" s="183"/>
       <c r="AT8" s="54" t="s">
         <v>16</v>
       </c>
@@ -5751,31 +5770,31 @@
       </c>
       <c r="AW8" s="33" t="str">
         <f>M8&amp;"/"&amp;R8&amp;"/"&amp;W8</f>
-        <v>//</v>
+        <v>2026/04/01</v>
       </c>
       <c r="AX8" s="38" t="str">
         <f>AF8&amp;"/"&amp;AK8&amp;"/"&amp;AP8</f>
-        <v>//</v>
-      </c>
-      <c r="AY8" s="36" t="e">
+        <v>2027/03/31</v>
+      </c>
+      <c r="AY8" s="36">
         <f>DATEDIF(AW8,AX8,"d")+1</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AZ8" s="23" t="e">
+        <v>365</v>
+      </c>
+      <c r="AZ8" s="23">
         <f>DATEDIF(AW8,AX8,"M")</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="BA8" s="29" t="e">
+        <v>11</v>
+      </c>
+      <c r="BA8" s="29">
         <f>DATEDIF(AW8,AX8,"MD")+1</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="BB8" s="39" t="e">
+        <v>31</v>
+      </c>
+      <c r="BB8" s="39" t="str">
         <f>IF(R8+AZ8&gt;12,M8+1&amp;"/"&amp;R8+AZ8-12&amp;"/"&amp;W8,M8&amp;"/"&amp;R8+AZ8&amp;"/"&amp;W8)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="BC8" s="30" t="e">
+        <v>2027/3/01</v>
+      </c>
+      <c r="BC8" s="30">
         <f>DAY(EOMONTH(BB8, 0))</f>
-        <v>#VALUE!</v>
+        <v>31</v>
       </c>
       <c r="BE8" s="1">
         <v>2025</v>
@@ -5787,70 +5806,82 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:67" ht="36.75" customHeight="1">
+    <row r="9" spans="1:67" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="50">
         <v>7</v>
       </c>
-      <c r="B9" s="280" t="s">
+      <c r="B9" s="167" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="280"/>
-      <c r="D9" s="280"/>
-      <c r="E9" s="280"/>
-      <c r="F9" s="280"/>
-      <c r="G9" s="280"/>
-      <c r="H9" s="280"/>
-      <c r="I9" s="281"/>
-      <c r="J9" s="299" t="s">
+      <c r="C9" s="167"/>
+      <c r="D9" s="167"/>
+      <c r="E9" s="167"/>
+      <c r="F9" s="167"/>
+      <c r="G9" s="167"/>
+      <c r="H9" s="167"/>
+      <c r="I9" s="168"/>
+      <c r="J9" s="194" t="s">
         <v>13</v>
       </c>
-      <c r="K9" s="300"/>
-      <c r="L9" s="301"/>
-      <c r="M9" s="298"/>
-      <c r="N9" s="292"/>
-      <c r="O9" s="292"/>
-      <c r="P9" s="292"/>
+      <c r="K9" s="195"/>
+      <c r="L9" s="196"/>
+      <c r="M9" s="193">
+        <v>2026</v>
+      </c>
+      <c r="N9" s="183"/>
+      <c r="O9" s="183"/>
+      <c r="P9" s="183"/>
       <c r="Q9" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="R9" s="292"/>
-      <c r="S9" s="292"/>
-      <c r="T9" s="292"/>
-      <c r="U9" s="292"/>
+      <c r="R9" s="183" t="s">
+        <v>23</v>
+      </c>
+      <c r="S9" s="183"/>
+      <c r="T9" s="183"/>
+      <c r="U9" s="183"/>
       <c r="V9" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="W9" s="292"/>
-      <c r="X9" s="292"/>
-      <c r="Y9" s="292"/>
-      <c r="Z9" s="292"/>
+      <c r="W9" s="183" t="s">
+        <v>165</v>
+      </c>
+      <c r="X9" s="183"/>
+      <c r="Y9" s="183"/>
+      <c r="Z9" s="183"/>
       <c r="AA9" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="AB9" s="302" t="s">
+      <c r="AB9" s="197" t="s">
         <v>17</v>
       </c>
-      <c r="AC9" s="303"/>
-      <c r="AD9" s="303"/>
-      <c r="AE9" s="304"/>
-      <c r="AF9" s="298"/>
-      <c r="AG9" s="292"/>
-      <c r="AH9" s="292"/>
-      <c r="AI9" s="292"/>
+      <c r="AC9" s="198"/>
+      <c r="AD9" s="198"/>
+      <c r="AE9" s="199"/>
+      <c r="AF9" s="193">
+        <v>2027</v>
+      </c>
+      <c r="AG9" s="183"/>
+      <c r="AH9" s="183"/>
+      <c r="AI9" s="183"/>
       <c r="AJ9" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="AK9" s="292"/>
-      <c r="AL9" s="292"/>
-      <c r="AM9" s="292"/>
-      <c r="AN9" s="292"/>
+      <c r="AK9" s="183" t="s">
+        <v>20</v>
+      </c>
+      <c r="AL9" s="183"/>
+      <c r="AM9" s="183"/>
+      <c r="AN9" s="183"/>
       <c r="AO9" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="AP9" s="292"/>
-      <c r="AQ9" s="292"/>
-      <c r="AR9" s="292"/>
-      <c r="AS9" s="292"/>
+      <c r="AP9" s="183" t="s">
+        <v>19</v>
+      </c>
+      <c r="AQ9" s="183"/>
+      <c r="AR9" s="183"/>
+      <c r="AS9" s="183"/>
       <c r="AT9" s="54" t="s">
         <v>16</v>
       </c>
@@ -5859,15 +5890,15 @@
       </c>
       <c r="AW9" s="33" t="str">
         <f>M9&amp;"/"&amp;R9&amp;"/"&amp;W9</f>
-        <v>//</v>
+        <v>2026/04/01</v>
       </c>
       <c r="AX9" s="38" t="str">
         <f>AF9&amp;"/"&amp;AK9&amp;"/"&amp;AP9</f>
-        <v>//</v>
-      </c>
-      <c r="AY9" s="36" t="e">
+        <v>2027/03/31</v>
+      </c>
+      <c r="AY9" s="36">
         <f>DATEDIF(AW9,AX9,"d")+1</f>
-        <v>#VALUE!</v>
+        <v>365</v>
       </c>
       <c r="AZ9" s="41"/>
       <c r="BA9" s="42"/>
@@ -5884,20 +5915,20 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:67" ht="33" customHeight="1">
+    <row r="10" spans="1:67" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="55">
         <v>8</v>
       </c>
-      <c r="B10" s="293" t="s">
+      <c r="B10" s="184" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="293"/>
-      <c r="D10" s="293"/>
-      <c r="E10" s="293"/>
-      <c r="F10" s="293"/>
-      <c r="G10" s="293"/>
-      <c r="H10" s="293"/>
-      <c r="I10" s="293"/>
+      <c r="C10" s="184"/>
+      <c r="D10" s="184"/>
+      <c r="E10" s="184"/>
+      <c r="F10" s="184"/>
+      <c r="G10" s="184"/>
+      <c r="H10" s="184"/>
+      <c r="I10" s="184"/>
       <c r="J10" s="56"/>
       <c r="K10" s="57"/>
       <c r="L10" s="57"/>
@@ -5945,7 +5976,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:67" ht="9.75" customHeight="1">
+    <row r="11" spans="1:67" ht="9.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="62"/>
       <c r="B11" s="63"/>
       <c r="C11" s="63"/>
@@ -6010,55 +6041,55 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:67" ht="18.75" customHeight="1">
-      <c r="A12" s="294" t="s">
+    <row r="12" spans="1:67" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="185" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="295"/>
-      <c r="C12" s="295"/>
-      <c r="D12" s="295"/>
-      <c r="E12" s="295"/>
-      <c r="F12" s="295"/>
-      <c r="G12" s="295"/>
-      <c r="H12" s="295"/>
-      <c r="I12" s="295"/>
-      <c r="J12" s="295"/>
-      <c r="K12" s="295"/>
-      <c r="L12" s="295"/>
-      <c r="M12" s="295"/>
-      <c r="N12" s="295"/>
-      <c r="O12" s="295"/>
-      <c r="P12" s="295"/>
-      <c r="Q12" s="295"/>
-      <c r="R12" s="295"/>
-      <c r="S12" s="295"/>
-      <c r="T12" s="295"/>
-      <c r="U12" s="295"/>
-      <c r="V12" s="295"/>
-      <c r="W12" s="295"/>
-      <c r="X12" s="295"/>
-      <c r="Y12" s="295"/>
-      <c r="Z12" s="295"/>
-      <c r="AA12" s="295"/>
-      <c r="AB12" s="295"/>
-      <c r="AC12" s="295"/>
-      <c r="AD12" s="295"/>
-      <c r="AE12" s="295"/>
-      <c r="AF12" s="295"/>
-      <c r="AG12" s="295"/>
-      <c r="AH12" s="295"/>
-      <c r="AI12" s="295"/>
-      <c r="AJ12" s="295"/>
-      <c r="AK12" s="295"/>
-      <c r="AL12" s="295"/>
-      <c r="AM12" s="295"/>
-      <c r="AN12" s="295"/>
-      <c r="AO12" s="295"/>
-      <c r="AP12" s="295"/>
-      <c r="AQ12" s="295"/>
-      <c r="AR12" s="295"/>
-      <c r="AS12" s="295"/>
-      <c r="AT12" s="296"/>
+      <c r="B12" s="186"/>
+      <c r="C12" s="186"/>
+      <c r="D12" s="186"/>
+      <c r="E12" s="186"/>
+      <c r="F12" s="186"/>
+      <c r="G12" s="186"/>
+      <c r="H12" s="186"/>
+      <c r="I12" s="186"/>
+      <c r="J12" s="186"/>
+      <c r="K12" s="186"/>
+      <c r="L12" s="186"/>
+      <c r="M12" s="186"/>
+      <c r="N12" s="186"/>
+      <c r="O12" s="186"/>
+      <c r="P12" s="186"/>
+      <c r="Q12" s="186"/>
+      <c r="R12" s="186"/>
+      <c r="S12" s="186"/>
+      <c r="T12" s="186"/>
+      <c r="U12" s="186"/>
+      <c r="V12" s="186"/>
+      <c r="W12" s="186"/>
+      <c r="X12" s="186"/>
+      <c r="Y12" s="186"/>
+      <c r="Z12" s="186"/>
+      <c r="AA12" s="186"/>
+      <c r="AB12" s="186"/>
+      <c r="AC12" s="186"/>
+      <c r="AD12" s="186"/>
+      <c r="AE12" s="186"/>
+      <c r="AF12" s="186"/>
+      <c r="AG12" s="186"/>
+      <c r="AH12" s="186"/>
+      <c r="AI12" s="186"/>
+      <c r="AJ12" s="186"/>
+      <c r="AK12" s="186"/>
+      <c r="AL12" s="186"/>
+      <c r="AM12" s="186"/>
+      <c r="AN12" s="186"/>
+      <c r="AO12" s="186"/>
+      <c r="AP12" s="186"/>
+      <c r="AQ12" s="186"/>
+      <c r="AR12" s="186"/>
+      <c r="AS12" s="186"/>
+      <c r="AT12" s="187"/>
       <c r="AW12" s="16"/>
       <c r="AX12" s="16"/>
       <c r="AY12" s="16"/>
@@ -6077,58 +6108,61 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:67" ht="39.75" customHeight="1">
+    <row r="13" spans="1:67" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="70"/>
       <c r="B13" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="281" t="s">
+      <c r="C13" s="168" t="s">
         <v>125</v>
       </c>
-      <c r="D13" s="297"/>
-      <c r="E13" s="297"/>
-      <c r="F13" s="297"/>
-      <c r="G13" s="297"/>
-      <c r="H13" s="297"/>
-      <c r="I13" s="297"/>
-      <c r="J13" s="297"/>
-      <c r="K13" s="297"/>
-      <c r="L13" s="297"/>
-      <c r="M13" s="297"/>
-      <c r="N13" s="297"/>
-      <c r="O13" s="297"/>
-      <c r="P13" s="297"/>
-      <c r="Q13" s="297"/>
-      <c r="R13" s="297"/>
-      <c r="S13" s="297"/>
-      <c r="T13" s="297"/>
-      <c r="U13" s="297"/>
-      <c r="V13" s="297"/>
-      <c r="W13" s="297"/>
-      <c r="X13" s="297"/>
-      <c r="Y13" s="297"/>
-      <c r="Z13" s="297"/>
-      <c r="AA13" s="297"/>
-      <c r="AB13" s="278"/>
-      <c r="AC13" s="278"/>
-      <c r="AD13" s="278"/>
-      <c r="AE13" s="278"/>
-      <c r="AF13" s="278"/>
-      <c r="AG13" s="278"/>
-      <c r="AH13" s="278"/>
-      <c r="AI13" s="278"/>
-      <c r="AJ13" s="278"/>
-      <c r="AK13" s="278"/>
-      <c r="AL13" s="278"/>
-      <c r="AM13" s="278"/>
-      <c r="AN13" s="278"/>
-      <c r="AO13" s="278"/>
-      <c r="AP13" s="278"/>
-      <c r="AQ13" s="279"/>
-      <c r="AR13" s="273" t="s">
+      <c r="D13" s="188"/>
+      <c r="E13" s="188"/>
+      <c r="F13" s="188"/>
+      <c r="G13" s="188"/>
+      <c r="H13" s="188"/>
+      <c r="I13" s="188"/>
+      <c r="J13" s="188"/>
+      <c r="K13" s="188"/>
+      <c r="L13" s="188"/>
+      <c r="M13" s="188"/>
+      <c r="N13" s="188"/>
+      <c r="O13" s="188"/>
+      <c r="P13" s="188"/>
+      <c r="Q13" s="188"/>
+      <c r="R13" s="188"/>
+      <c r="S13" s="188"/>
+      <c r="T13" s="188"/>
+      <c r="U13" s="188"/>
+      <c r="V13" s="188"/>
+      <c r="W13" s="188"/>
+      <c r="X13" s="188"/>
+      <c r="Y13" s="188"/>
+      <c r="Z13" s="188"/>
+      <c r="AA13" s="188"/>
+      <c r="AB13" s="189">
+        <f>330000*5</f>
+        <v>1650000</v>
+      </c>
+      <c r="AC13" s="189"/>
+      <c r="AD13" s="189"/>
+      <c r="AE13" s="189"/>
+      <c r="AF13" s="189"/>
+      <c r="AG13" s="189"/>
+      <c r="AH13" s="189"/>
+      <c r="AI13" s="189"/>
+      <c r="AJ13" s="189"/>
+      <c r="AK13" s="189"/>
+      <c r="AL13" s="189"/>
+      <c r="AM13" s="189"/>
+      <c r="AN13" s="189"/>
+      <c r="AO13" s="189"/>
+      <c r="AP13" s="189"/>
+      <c r="AQ13" s="190"/>
+      <c r="AR13" s="191" t="s">
         <v>28</v>
       </c>
-      <c r="AS13" s="274"/>
+      <c r="AS13" s="192"/>
       <c r="AT13" s="72"/>
       <c r="AW13" s="16"/>
       <c r="AX13" s="16"/>
@@ -6142,60 +6176,60 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:67" ht="21" customHeight="1">
+    <row r="14" spans="1:67" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="70"/>
-      <c r="B14" s="282" t="s">
+      <c r="B14" s="201" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="285" t="s">
+      <c r="C14" s="204" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="285"/>
-      <c r="E14" s="285"/>
-      <c r="F14" s="285"/>
-      <c r="G14" s="285"/>
-      <c r="H14" s="285"/>
-      <c r="I14" s="286"/>
-      <c r="J14" s="291" t="s">
+      <c r="D14" s="204"/>
+      <c r="E14" s="204"/>
+      <c r="F14" s="204"/>
+      <c r="G14" s="204"/>
+      <c r="H14" s="204"/>
+      <c r="I14" s="205"/>
+      <c r="J14" s="210" t="s">
         <v>31</v>
       </c>
-      <c r="K14" s="291"/>
-      <c r="L14" s="291"/>
-      <c r="M14" s="291"/>
-      <c r="N14" s="291"/>
-      <c r="O14" s="291"/>
-      <c r="P14" s="291"/>
-      <c r="Q14" s="291"/>
-      <c r="R14" s="291"/>
-      <c r="S14" s="291"/>
-      <c r="T14" s="291"/>
-      <c r="U14" s="291"/>
-      <c r="V14" s="291"/>
-      <c r="W14" s="291"/>
-      <c r="X14" s="291"/>
-      <c r="Y14" s="291"/>
-      <c r="Z14" s="291"/>
-      <c r="AA14" s="291"/>
-      <c r="AB14" s="291" t="s">
+      <c r="K14" s="210"/>
+      <c r="L14" s="210"/>
+      <c r="M14" s="210"/>
+      <c r="N14" s="210"/>
+      <c r="O14" s="210"/>
+      <c r="P14" s="210"/>
+      <c r="Q14" s="210"/>
+      <c r="R14" s="210"/>
+      <c r="S14" s="210"/>
+      <c r="T14" s="210"/>
+      <c r="U14" s="210"/>
+      <c r="V14" s="210"/>
+      <c r="W14" s="210"/>
+      <c r="X14" s="210"/>
+      <c r="Y14" s="210"/>
+      <c r="Z14" s="210"/>
+      <c r="AA14" s="210"/>
+      <c r="AB14" s="210" t="s">
         <v>30</v>
       </c>
-      <c r="AC14" s="291"/>
-      <c r="AD14" s="291"/>
-      <c r="AE14" s="291"/>
-      <c r="AF14" s="291"/>
-      <c r="AG14" s="291"/>
-      <c r="AH14" s="291"/>
-      <c r="AI14" s="291"/>
-      <c r="AJ14" s="291"/>
-      <c r="AK14" s="291"/>
-      <c r="AL14" s="291"/>
-      <c r="AM14" s="291"/>
-      <c r="AN14" s="291"/>
-      <c r="AO14" s="291"/>
-      <c r="AP14" s="291"/>
-      <c r="AQ14" s="291"/>
-      <c r="AR14" s="291"/>
-      <c r="AS14" s="291"/>
+      <c r="AC14" s="210"/>
+      <c r="AD14" s="210"/>
+      <c r="AE14" s="210"/>
+      <c r="AF14" s="210"/>
+      <c r="AG14" s="210"/>
+      <c r="AH14" s="210"/>
+      <c r="AI14" s="210"/>
+      <c r="AJ14" s="210"/>
+      <c r="AK14" s="210"/>
+      <c r="AL14" s="210"/>
+      <c r="AM14" s="210"/>
+      <c r="AN14" s="210"/>
+      <c r="AO14" s="210"/>
+      <c r="AP14" s="210"/>
+      <c r="AQ14" s="210"/>
+      <c r="AR14" s="210"/>
+      <c r="AS14" s="210"/>
       <c r="AT14" s="72"/>
       <c r="AW14" s="24"/>
       <c r="AX14" s="16"/>
@@ -6215,54 +6249,54 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:67" ht="39.75" customHeight="1">
+    <row r="15" spans="1:67" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="70"/>
-      <c r="B15" s="283"/>
-      <c r="C15" s="287"/>
-      <c r="D15" s="287"/>
-      <c r="E15" s="287"/>
-      <c r="F15" s="287"/>
-      <c r="G15" s="287"/>
-      <c r="H15" s="287"/>
-      <c r="I15" s="288"/>
-      <c r="J15" s="277"/>
-      <c r="K15" s="277"/>
-      <c r="L15" s="277"/>
-      <c r="M15" s="277"/>
-      <c r="N15" s="277"/>
-      <c r="O15" s="277"/>
-      <c r="P15" s="277"/>
-      <c r="Q15" s="277"/>
-      <c r="R15" s="277"/>
-      <c r="S15" s="277"/>
-      <c r="T15" s="277"/>
-      <c r="U15" s="277"/>
-      <c r="V15" s="277"/>
-      <c r="W15" s="277"/>
-      <c r="X15" s="277"/>
-      <c r="Y15" s="277"/>
-      <c r="Z15" s="277"/>
-      <c r="AA15" s="277"/>
-      <c r="AB15" s="278"/>
-      <c r="AC15" s="278"/>
-      <c r="AD15" s="278"/>
-      <c r="AE15" s="278"/>
-      <c r="AF15" s="278"/>
-      <c r="AG15" s="278"/>
-      <c r="AH15" s="278"/>
-      <c r="AI15" s="278"/>
-      <c r="AJ15" s="278"/>
-      <c r="AK15" s="278"/>
-      <c r="AL15" s="278"/>
-      <c r="AM15" s="278"/>
-      <c r="AN15" s="278"/>
-      <c r="AO15" s="278"/>
-      <c r="AP15" s="278"/>
-      <c r="AQ15" s="279"/>
-      <c r="AR15" s="273" t="s">
+      <c r="B15" s="202"/>
+      <c r="C15" s="206"/>
+      <c r="D15" s="206"/>
+      <c r="E15" s="206"/>
+      <c r="F15" s="206"/>
+      <c r="G15" s="206"/>
+      <c r="H15" s="206"/>
+      <c r="I15" s="207"/>
+      <c r="J15" s="200"/>
+      <c r="K15" s="200"/>
+      <c r="L15" s="200"/>
+      <c r="M15" s="200"/>
+      <c r="N15" s="200"/>
+      <c r="O15" s="200"/>
+      <c r="P15" s="200"/>
+      <c r="Q15" s="200"/>
+      <c r="R15" s="200"/>
+      <c r="S15" s="200"/>
+      <c r="T15" s="200"/>
+      <c r="U15" s="200"/>
+      <c r="V15" s="200"/>
+      <c r="W15" s="200"/>
+      <c r="X15" s="200"/>
+      <c r="Y15" s="200"/>
+      <c r="Z15" s="200"/>
+      <c r="AA15" s="200"/>
+      <c r="AB15" s="189"/>
+      <c r="AC15" s="189"/>
+      <c r="AD15" s="189"/>
+      <c r="AE15" s="189"/>
+      <c r="AF15" s="189"/>
+      <c r="AG15" s="189"/>
+      <c r="AH15" s="189"/>
+      <c r="AI15" s="189"/>
+      <c r="AJ15" s="189"/>
+      <c r="AK15" s="189"/>
+      <c r="AL15" s="189"/>
+      <c r="AM15" s="189"/>
+      <c r="AN15" s="189"/>
+      <c r="AO15" s="189"/>
+      <c r="AP15" s="189"/>
+      <c r="AQ15" s="190"/>
+      <c r="AR15" s="191" t="s">
         <v>28</v>
       </c>
-      <c r="AS15" s="274"/>
+      <c r="AS15" s="192"/>
       <c r="AT15" s="72"/>
       <c r="AW15" s="16"/>
       <c r="AY15" s="16"/>
@@ -6281,54 +6315,54 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:67" ht="39.75" customHeight="1">
+    <row r="16" spans="1:67" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="70"/>
-      <c r="B16" s="283"/>
-      <c r="C16" s="287"/>
-      <c r="D16" s="287"/>
-      <c r="E16" s="287"/>
-      <c r="F16" s="287"/>
-      <c r="G16" s="287"/>
-      <c r="H16" s="287"/>
-      <c r="I16" s="288"/>
-      <c r="J16" s="277"/>
-      <c r="K16" s="277"/>
-      <c r="L16" s="277"/>
-      <c r="M16" s="277"/>
-      <c r="N16" s="277"/>
-      <c r="O16" s="277"/>
-      <c r="P16" s="277"/>
-      <c r="Q16" s="277"/>
-      <c r="R16" s="277"/>
-      <c r="S16" s="277"/>
-      <c r="T16" s="277"/>
-      <c r="U16" s="277"/>
-      <c r="V16" s="277"/>
-      <c r="W16" s="277"/>
-      <c r="X16" s="277"/>
-      <c r="Y16" s="277"/>
-      <c r="Z16" s="277"/>
-      <c r="AA16" s="277"/>
-      <c r="AB16" s="278"/>
-      <c r="AC16" s="278"/>
-      <c r="AD16" s="278"/>
-      <c r="AE16" s="278"/>
-      <c r="AF16" s="278"/>
-      <c r="AG16" s="278"/>
-      <c r="AH16" s="278"/>
-      <c r="AI16" s="278"/>
-      <c r="AJ16" s="278"/>
-      <c r="AK16" s="278"/>
-      <c r="AL16" s="278"/>
-      <c r="AM16" s="278"/>
-      <c r="AN16" s="278"/>
-      <c r="AO16" s="278"/>
-      <c r="AP16" s="278"/>
-      <c r="AQ16" s="279"/>
-      <c r="AR16" s="273" t="s">
+      <c r="B16" s="202"/>
+      <c r="C16" s="206"/>
+      <c r="D16" s="206"/>
+      <c r="E16" s="206"/>
+      <c r="F16" s="206"/>
+      <c r="G16" s="206"/>
+      <c r="H16" s="206"/>
+      <c r="I16" s="207"/>
+      <c r="J16" s="200"/>
+      <c r="K16" s="200"/>
+      <c r="L16" s="200"/>
+      <c r="M16" s="200"/>
+      <c r="N16" s="200"/>
+      <c r="O16" s="200"/>
+      <c r="P16" s="200"/>
+      <c r="Q16" s="200"/>
+      <c r="R16" s="200"/>
+      <c r="S16" s="200"/>
+      <c r="T16" s="200"/>
+      <c r="U16" s="200"/>
+      <c r="V16" s="200"/>
+      <c r="W16" s="200"/>
+      <c r="X16" s="200"/>
+      <c r="Y16" s="200"/>
+      <c r="Z16" s="200"/>
+      <c r="AA16" s="200"/>
+      <c r="AB16" s="189"/>
+      <c r="AC16" s="189"/>
+      <c r="AD16" s="189"/>
+      <c r="AE16" s="189"/>
+      <c r="AF16" s="189"/>
+      <c r="AG16" s="189"/>
+      <c r="AH16" s="189"/>
+      <c r="AI16" s="189"/>
+      <c r="AJ16" s="189"/>
+      <c r="AK16" s="189"/>
+      <c r="AL16" s="189"/>
+      <c r="AM16" s="189"/>
+      <c r="AN16" s="189"/>
+      <c r="AO16" s="189"/>
+      <c r="AP16" s="189"/>
+      <c r="AQ16" s="190"/>
+      <c r="AR16" s="191" t="s">
         <v>28</v>
       </c>
-      <c r="AS16" s="274"/>
+      <c r="AS16" s="192"/>
       <c r="AT16" s="72"/>
       <c r="AW16" s="16"/>
       <c r="AX16" s="16"/>
@@ -6339,54 +6373,54 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:59" ht="39.75" customHeight="1">
+    <row r="17" spans="1:59" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="70"/>
-      <c r="B17" s="284"/>
-      <c r="C17" s="289"/>
-      <c r="D17" s="289"/>
-      <c r="E17" s="289"/>
-      <c r="F17" s="289"/>
-      <c r="G17" s="289"/>
-      <c r="H17" s="289"/>
-      <c r="I17" s="290"/>
-      <c r="J17" s="277"/>
-      <c r="K17" s="277"/>
-      <c r="L17" s="277"/>
-      <c r="M17" s="277"/>
-      <c r="N17" s="277"/>
-      <c r="O17" s="277"/>
-      <c r="P17" s="277"/>
-      <c r="Q17" s="277"/>
-      <c r="R17" s="277"/>
-      <c r="S17" s="277"/>
-      <c r="T17" s="277"/>
-      <c r="U17" s="277"/>
-      <c r="V17" s="277"/>
-      <c r="W17" s="277"/>
-      <c r="X17" s="277"/>
-      <c r="Y17" s="277"/>
-      <c r="Z17" s="277"/>
-      <c r="AA17" s="277"/>
-      <c r="AB17" s="278"/>
-      <c r="AC17" s="278"/>
-      <c r="AD17" s="278"/>
-      <c r="AE17" s="278"/>
-      <c r="AF17" s="278"/>
-      <c r="AG17" s="278"/>
-      <c r="AH17" s="278"/>
-      <c r="AI17" s="278"/>
-      <c r="AJ17" s="278"/>
-      <c r="AK17" s="278"/>
-      <c r="AL17" s="278"/>
-      <c r="AM17" s="278"/>
-      <c r="AN17" s="278"/>
-      <c r="AO17" s="278"/>
-      <c r="AP17" s="278"/>
-      <c r="AQ17" s="279"/>
-      <c r="AR17" s="273" t="s">
+      <c r="B17" s="203"/>
+      <c r="C17" s="208"/>
+      <c r="D17" s="208"/>
+      <c r="E17" s="208"/>
+      <c r="F17" s="208"/>
+      <c r="G17" s="208"/>
+      <c r="H17" s="208"/>
+      <c r="I17" s="209"/>
+      <c r="J17" s="200"/>
+      <c r="K17" s="200"/>
+      <c r="L17" s="200"/>
+      <c r="M17" s="200"/>
+      <c r="N17" s="200"/>
+      <c r="O17" s="200"/>
+      <c r="P17" s="200"/>
+      <c r="Q17" s="200"/>
+      <c r="R17" s="200"/>
+      <c r="S17" s="200"/>
+      <c r="T17" s="200"/>
+      <c r="U17" s="200"/>
+      <c r="V17" s="200"/>
+      <c r="W17" s="200"/>
+      <c r="X17" s="200"/>
+      <c r="Y17" s="200"/>
+      <c r="Z17" s="200"/>
+      <c r="AA17" s="200"/>
+      <c r="AB17" s="189"/>
+      <c r="AC17" s="189"/>
+      <c r="AD17" s="189"/>
+      <c r="AE17" s="189"/>
+      <c r="AF17" s="189"/>
+      <c r="AG17" s="189"/>
+      <c r="AH17" s="189"/>
+      <c r="AI17" s="189"/>
+      <c r="AJ17" s="189"/>
+      <c r="AK17" s="189"/>
+      <c r="AL17" s="189"/>
+      <c r="AM17" s="189"/>
+      <c r="AN17" s="189"/>
+      <c r="AO17" s="189"/>
+      <c r="AP17" s="189"/>
+      <c r="AQ17" s="190"/>
+      <c r="AR17" s="191" t="s">
         <v>28</v>
       </c>
-      <c r="AS17" s="274"/>
+      <c r="AS17" s="192"/>
       <c r="AT17" s="73"/>
       <c r="AW17" s="13"/>
       <c r="AX17" s="16"/>
@@ -6397,58 +6431,58 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:59" ht="39.75" customHeight="1">
+    <row r="18" spans="1:59" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="70"/>
       <c r="B18" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="280" t="s">
+      <c r="C18" s="167" t="s">
         <v>130</v>
       </c>
-      <c r="D18" s="280"/>
-      <c r="E18" s="280"/>
-      <c r="F18" s="280"/>
-      <c r="G18" s="280"/>
-      <c r="H18" s="280"/>
-      <c r="I18" s="281"/>
-      <c r="J18" s="277"/>
-      <c r="K18" s="277"/>
-      <c r="L18" s="277"/>
-      <c r="M18" s="277"/>
-      <c r="N18" s="277"/>
-      <c r="O18" s="277"/>
-      <c r="P18" s="277"/>
-      <c r="Q18" s="277"/>
-      <c r="R18" s="277"/>
-      <c r="S18" s="277"/>
-      <c r="T18" s="277"/>
-      <c r="U18" s="277"/>
-      <c r="V18" s="277"/>
-      <c r="W18" s="277"/>
-      <c r="X18" s="277"/>
-      <c r="Y18" s="277"/>
-      <c r="Z18" s="277"/>
-      <c r="AA18" s="277"/>
-      <c r="AB18" s="278"/>
-      <c r="AC18" s="278"/>
-      <c r="AD18" s="278"/>
-      <c r="AE18" s="278"/>
-      <c r="AF18" s="278"/>
-      <c r="AG18" s="278"/>
-      <c r="AH18" s="278"/>
-      <c r="AI18" s="278"/>
-      <c r="AJ18" s="278"/>
-      <c r="AK18" s="278"/>
-      <c r="AL18" s="278"/>
-      <c r="AM18" s="278"/>
-      <c r="AN18" s="278"/>
-      <c r="AO18" s="278"/>
-      <c r="AP18" s="278"/>
-      <c r="AQ18" s="279"/>
-      <c r="AR18" s="273" t="s">
+      <c r="D18" s="167"/>
+      <c r="E18" s="167"/>
+      <c r="F18" s="167"/>
+      <c r="G18" s="167"/>
+      <c r="H18" s="167"/>
+      <c r="I18" s="168"/>
+      <c r="J18" s="200"/>
+      <c r="K18" s="200"/>
+      <c r="L18" s="200"/>
+      <c r="M18" s="200"/>
+      <c r="N18" s="200"/>
+      <c r="O18" s="200"/>
+      <c r="P18" s="200"/>
+      <c r="Q18" s="200"/>
+      <c r="R18" s="200"/>
+      <c r="S18" s="200"/>
+      <c r="T18" s="200"/>
+      <c r="U18" s="200"/>
+      <c r="V18" s="200"/>
+      <c r="W18" s="200"/>
+      <c r="X18" s="200"/>
+      <c r="Y18" s="200"/>
+      <c r="Z18" s="200"/>
+      <c r="AA18" s="200"/>
+      <c r="AB18" s="189"/>
+      <c r="AC18" s="189"/>
+      <c r="AD18" s="189"/>
+      <c r="AE18" s="189"/>
+      <c r="AF18" s="189"/>
+      <c r="AG18" s="189"/>
+      <c r="AH18" s="189"/>
+      <c r="AI18" s="189"/>
+      <c r="AJ18" s="189"/>
+      <c r="AK18" s="189"/>
+      <c r="AL18" s="189"/>
+      <c r="AM18" s="189"/>
+      <c r="AN18" s="189"/>
+      <c r="AO18" s="189"/>
+      <c r="AP18" s="189"/>
+      <c r="AQ18" s="190"/>
+      <c r="AR18" s="191" t="s">
         <v>28</v>
       </c>
-      <c r="AS18" s="274"/>
+      <c r="AS18" s="192"/>
       <c r="AT18" s="73"/>
       <c r="AW18" s="13"/>
       <c r="AX18" s="16"/>
@@ -6456,65 +6490,65 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:59" ht="39.75" customHeight="1">
+    <row r="19" spans="1:59" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="75"/>
-      <c r="B19" s="270" t="s">
+      <c r="B19" s="221" t="s">
         <v>136</v>
       </c>
-      <c r="C19" s="270"/>
-      <c r="D19" s="270"/>
-      <c r="E19" s="270"/>
-      <c r="F19" s="270"/>
-      <c r="G19" s="270"/>
-      <c r="H19" s="270"/>
-      <c r="I19" s="270"/>
-      <c r="J19" s="270"/>
-      <c r="K19" s="270"/>
-      <c r="L19" s="270"/>
-      <c r="M19" s="270"/>
-      <c r="N19" s="270"/>
-      <c r="O19" s="270"/>
-      <c r="P19" s="270"/>
-      <c r="Q19" s="270"/>
-      <c r="R19" s="270"/>
-      <c r="S19" s="270"/>
-      <c r="T19" s="270"/>
-      <c r="U19" s="270"/>
-      <c r="V19" s="270"/>
-      <c r="W19" s="270"/>
-      <c r="X19" s="270"/>
-      <c r="Y19" s="270"/>
-      <c r="Z19" s="270"/>
-      <c r="AA19" s="270"/>
-      <c r="AB19" s="271" t="str">
+      <c r="C19" s="221"/>
+      <c r="D19" s="221"/>
+      <c r="E19" s="221"/>
+      <c r="F19" s="221"/>
+      <c r="G19" s="221"/>
+      <c r="H19" s="221"/>
+      <c r="I19" s="221"/>
+      <c r="J19" s="221"/>
+      <c r="K19" s="221"/>
+      <c r="L19" s="221"/>
+      <c r="M19" s="221"/>
+      <c r="N19" s="221"/>
+      <c r="O19" s="221"/>
+      <c r="P19" s="221"/>
+      <c r="Q19" s="221"/>
+      <c r="R19" s="221"/>
+      <c r="S19" s="221"/>
+      <c r="T19" s="221"/>
+      <c r="U19" s="221"/>
+      <c r="V19" s="221"/>
+      <c r="W19" s="221"/>
+      <c r="X19" s="221"/>
+      <c r="Y19" s="221"/>
+      <c r="Z19" s="221"/>
+      <c r="AA19" s="221"/>
+      <c r="AB19" s="222">
         <f>IF(SUM(AB13,AB15:AQ17,-AB18)&gt;0,SUM(AB13,AB15:AQ17,-AB18), "" )</f>
-        <v/>
-      </c>
-      <c r="AC19" s="271"/>
-      <c r="AD19" s="271"/>
-      <c r="AE19" s="271"/>
-      <c r="AF19" s="271"/>
-      <c r="AG19" s="271"/>
-      <c r="AH19" s="271"/>
-      <c r="AI19" s="271"/>
-      <c r="AJ19" s="271"/>
-      <c r="AK19" s="271"/>
-      <c r="AL19" s="271"/>
-      <c r="AM19" s="271"/>
-      <c r="AN19" s="271"/>
-      <c r="AO19" s="271"/>
-      <c r="AP19" s="271"/>
-      <c r="AQ19" s="272"/>
-      <c r="AR19" s="273" t="s">
+        <v>1650000</v>
+      </c>
+      <c r="AC19" s="222"/>
+      <c r="AD19" s="222"/>
+      <c r="AE19" s="222"/>
+      <c r="AF19" s="222"/>
+      <c r="AG19" s="222"/>
+      <c r="AH19" s="222"/>
+      <c r="AI19" s="222"/>
+      <c r="AJ19" s="222"/>
+      <c r="AK19" s="222"/>
+      <c r="AL19" s="222"/>
+      <c r="AM19" s="222"/>
+      <c r="AN19" s="222"/>
+      <c r="AO19" s="222"/>
+      <c r="AP19" s="222"/>
+      <c r="AQ19" s="223"/>
+      <c r="AR19" s="191" t="s">
         <v>28</v>
       </c>
-      <c r="AS19" s="274"/>
+      <c r="AS19" s="192"/>
       <c r="AT19" s="73"/>
       <c r="BG19" s="14" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:59" ht="17.25" customHeight="1">
+    <row r="20" spans="1:59" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="76"/>
       <c r="B20" s="77"/>
       <c r="C20" s="78"/>
@@ -6566,7 +6600,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:59" ht="18.75" customHeight="1">
+    <row r="21" spans="1:59" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="83" t="s">
         <v>38</v>
       </c>
@@ -6619,7 +6653,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:59" ht="18.75" customHeight="1">
+    <row r="22" spans="1:59" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="86"/>
       <c r="B22" s="66"/>
       <c r="C22" s="66"/>
@@ -6632,80 +6666,80 @@
       <c r="J22" s="87"/>
       <c r="K22" s="87"/>
       <c r="L22" s="87"/>
-      <c r="M22" s="275" t="s">
+      <c r="M22" s="224" t="s">
         <v>40</v>
       </c>
-      <c r="N22" s="275"/>
-      <c r="O22" s="275"/>
-      <c r="P22" s="275"/>
-      <c r="Q22" s="275"/>
-      <c r="R22" s="275"/>
-      <c r="S22" s="275"/>
-      <c r="T22" s="275"/>
+      <c r="N22" s="224"/>
+      <c r="O22" s="224"/>
+      <c r="P22" s="224"/>
+      <c r="Q22" s="224"/>
+      <c r="R22" s="224"/>
+      <c r="S22" s="224"/>
+      <c r="T22" s="224"/>
       <c r="U22" s="66"/>
       <c r="V22" s="66"/>
       <c r="W22" s="66"/>
       <c r="X22" s="66"/>
-      <c r="Y22" s="260" t="s">
+      <c r="Y22" s="225" t="s">
         <v>41</v>
       </c>
-      <c r="Z22" s="260"/>
-      <c r="AA22" s="260"/>
-      <c r="AB22" s="260"/>
-      <c r="AC22" s="260"/>
-      <c r="AD22" s="260"/>
-      <c r="AE22" s="260"/>
-      <c r="AF22" s="260"/>
+      <c r="Z22" s="225"/>
+      <c r="AA22" s="225"/>
+      <c r="AB22" s="225"/>
+      <c r="AC22" s="225"/>
+      <c r="AD22" s="225"/>
+      <c r="AE22" s="225"/>
+      <c r="AF22" s="225"/>
       <c r="AG22" s="87"/>
       <c r="AH22" s="87"/>
       <c r="AI22" s="87"/>
       <c r="AJ22" s="87"/>
-      <c r="AK22" s="276"/>
-      <c r="AL22" s="276"/>
-      <c r="AM22" s="276"/>
-      <c r="AN22" s="276"/>
-      <c r="AO22" s="276"/>
-      <c r="AP22" s="276"/>
-      <c r="AQ22" s="276"/>
-      <c r="AR22" s="276"/>
+      <c r="AK22" s="226"/>
+      <c r="AL22" s="226"/>
+      <c r="AM22" s="226"/>
+      <c r="AN22" s="226"/>
+      <c r="AO22" s="226"/>
+      <c r="AP22" s="226"/>
+      <c r="AQ22" s="226"/>
+      <c r="AR22" s="226"/>
       <c r="AS22" s="82"/>
       <c r="AT22" s="73"/>
       <c r="BG22" s="14" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:59" ht="39.75" customHeight="1">
+    <row r="23" spans="1:59" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="86"/>
-      <c r="B23" s="240" t="s">
+      <c r="B23" s="211" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="240"/>
-      <c r="D23" s="240"/>
-      <c r="E23" s="240"/>
-      <c r="F23" s="240"/>
-      <c r="G23" s="240"/>
-      <c r="H23" s="240"/>
+      <c r="C23" s="211"/>
+      <c r="D23" s="211"/>
+      <c r="E23" s="211"/>
+      <c r="F23" s="211"/>
+      <c r="G23" s="211"/>
+      <c r="H23" s="211"/>
       <c r="J23" s="88"/>
       <c r="L23" s="88"/>
-      <c r="M23" s="261" t="str">
+      <c r="M23" s="212">
         <f>IF(J7=0,"",J7)</f>
-        <v/>
-      </c>
-      <c r="N23" s="262"/>
-      <c r="O23" s="262"/>
-      <c r="P23" s="262"/>
-      <c r="Q23" s="262"/>
-      <c r="R23" s="262"/>
-      <c r="S23" s="262"/>
-      <c r="T23" s="263"/>
-      <c r="U23" s="220" t="s">
+        <v>5</v>
+      </c>
+      <c r="N23" s="213"/>
+      <c r="O23" s="213"/>
+      <c r="P23" s="213"/>
+      <c r="Q23" s="213"/>
+      <c r="R23" s="213"/>
+      <c r="S23" s="213"/>
+      <c r="T23" s="214"/>
+      <c r="U23" s="215" t="s">
         <v>45</v>
       </c>
-      <c r="V23" s="211"/>
+      <c r="V23" s="216"/>
       <c r="X23" s="88"/>
-      <c r="Y23" s="217" t="str">
+      <c r="Y23" s="217">
         <f>IF(AP8="","",AY8)</f>
-        <v/>
+        <v>365</v>
       </c>
       <c r="Z23" s="218"/>
       <c r="AA23" s="218"/>
@@ -6714,21 +6748,21 @@
       <c r="AD23" s="218"/>
       <c r="AE23" s="218"/>
       <c r="AF23" s="219"/>
-      <c r="AG23" s="220" t="s">
+      <c r="AG23" s="215" t="s">
         <v>16</v>
       </c>
-      <c r="AH23" s="211"/>
+      <c r="AH23" s="216"/>
       <c r="AJ23" s="88"/>
-      <c r="AK23" s="202" t="s">
+      <c r="AK23" s="220" t="s">
         <v>47</v>
       </c>
-      <c r="AL23" s="202"/>
-      <c r="AM23" s="202"/>
-      <c r="AN23" s="202"/>
-      <c r="AO23" s="202"/>
-      <c r="AP23" s="202"/>
-      <c r="AQ23" s="202"/>
-      <c r="AR23" s="202"/>
+      <c r="AL23" s="220"/>
+      <c r="AM23" s="220"/>
+      <c r="AN23" s="220"/>
+      <c r="AO23" s="220"/>
+      <c r="AP23" s="220"/>
+      <c r="AQ23" s="220"/>
+      <c r="AR23" s="220"/>
       <c r="AS23" s="82"/>
       <c r="AT23" s="73"/>
       <c r="AX23" s="11"/>
@@ -6736,26 +6770,26 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:59" ht="19.5" customHeight="1">
+    <row r="24" spans="1:59" ht="19.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A24" s="89"/>
-      <c r="B24" s="221" t="str">
+      <c r="B24" s="229">
         <f>AB19</f>
-        <v/>
-      </c>
-      <c r="C24" s="222"/>
-      <c r="D24" s="222"/>
-      <c r="E24" s="222"/>
-      <c r="F24" s="222"/>
-      <c r="G24" s="222"/>
-      <c r="H24" s="223"/>
-      <c r="I24" s="220" t="s">
+        <v>1650000</v>
+      </c>
+      <c r="C24" s="230"/>
+      <c r="D24" s="230"/>
+      <c r="E24" s="230"/>
+      <c r="F24" s="230"/>
+      <c r="G24" s="230"/>
+      <c r="H24" s="231"/>
+      <c r="I24" s="215" t="s">
         <v>28</v>
       </c>
-      <c r="J24" s="211"/>
-      <c r="K24" s="211" t="s">
+      <c r="J24" s="216"/>
+      <c r="K24" s="216" t="s">
         <v>44</v>
       </c>
-      <c r="L24" s="211"/>
+      <c r="L24" s="216"/>
       <c r="M24" s="90"/>
       <c r="N24" s="90"/>
       <c r="O24" s="90"/>
@@ -6766,10 +6800,10 @@
       <c r="T24" s="90"/>
       <c r="U24" s="88"/>
       <c r="V24" s="88"/>
-      <c r="W24" s="211" t="s">
+      <c r="W24" s="216" t="s">
         <v>44</v>
       </c>
-      <c r="X24" s="211"/>
+      <c r="X24" s="216"/>
       <c r="Y24" s="90"/>
       <c r="Z24" s="90"/>
       <c r="AA24" s="90"/>
@@ -6780,42 +6814,42 @@
       <c r="AF24" s="90"/>
       <c r="AG24" s="91"/>
       <c r="AH24" s="91"/>
-      <c r="AI24" s="211" t="s">
+      <c r="AI24" s="216" t="s">
         <v>46</v>
       </c>
-      <c r="AJ24" s="227"/>
-      <c r="AK24" s="264" t="str">
+      <c r="AJ24" s="235"/>
+      <c r="AK24" s="236">
         <f>IF(B24="","",B24*M23/M27*Y23/Y27)</f>
-        <v/>
-      </c>
-      <c r="AL24" s="265"/>
-      <c r="AM24" s="265"/>
-      <c r="AN24" s="265"/>
-      <c r="AO24" s="265"/>
-      <c r="AP24" s="265"/>
-      <c r="AQ24" s="265"/>
-      <c r="AR24" s="266"/>
-      <c r="AS24" s="259" t="s">
+        <v>1650000</v>
+      </c>
+      <c r="AL24" s="237"/>
+      <c r="AM24" s="237"/>
+      <c r="AN24" s="237"/>
+      <c r="AO24" s="237"/>
+      <c r="AP24" s="237"/>
+      <c r="AQ24" s="237"/>
+      <c r="AR24" s="238"/>
+      <c r="AS24" s="227" t="s">
         <v>28</v>
       </c>
-      <c r="AT24" s="215"/>
+      <c r="AT24" s="228"/>
       <c r="BG24" s="14" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:59" ht="19.5" customHeight="1">
+    <row r="25" spans="1:59" ht="19.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A25" s="89"/>
-      <c r="B25" s="224"/>
-      <c r="C25" s="225"/>
-      <c r="D25" s="225"/>
-      <c r="E25" s="225"/>
-      <c r="F25" s="225"/>
-      <c r="G25" s="225"/>
-      <c r="H25" s="226"/>
-      <c r="I25" s="220"/>
-      <c r="J25" s="211"/>
-      <c r="K25" s="211"/>
-      <c r="L25" s="211"/>
+      <c r="B25" s="232"/>
+      <c r="C25" s="233"/>
+      <c r="D25" s="233"/>
+      <c r="E25" s="233"/>
+      <c r="F25" s="233"/>
+      <c r="G25" s="233"/>
+      <c r="H25" s="234"/>
+      <c r="I25" s="215"/>
+      <c r="J25" s="216"/>
+      <c r="K25" s="216"/>
+      <c r="L25" s="216"/>
       <c r="M25" s="87"/>
       <c r="N25" s="87"/>
       <c r="O25" s="87"/>
@@ -6826,8 +6860,8 @@
       <c r="T25" s="87"/>
       <c r="U25" s="88"/>
       <c r="V25" s="88"/>
-      <c r="W25" s="211"/>
-      <c r="X25" s="211"/>
+      <c r="W25" s="216"/>
+      <c r="X25" s="216"/>
       <c r="Y25" s="87"/>
       <c r="Z25" s="87"/>
       <c r="AA25" s="87"/>
@@ -6838,23 +6872,23 @@
       <c r="AF25" s="87"/>
       <c r="AG25" s="91"/>
       <c r="AH25" s="91"/>
-      <c r="AI25" s="211"/>
-      <c r="AJ25" s="227"/>
-      <c r="AK25" s="267"/>
-      <c r="AL25" s="268"/>
-      <c r="AM25" s="268"/>
-      <c r="AN25" s="268"/>
-      <c r="AO25" s="268"/>
-      <c r="AP25" s="268"/>
-      <c r="AQ25" s="268"/>
-      <c r="AR25" s="269"/>
-      <c r="AS25" s="259"/>
-      <c r="AT25" s="215"/>
+      <c r="AI25" s="216"/>
+      <c r="AJ25" s="235"/>
+      <c r="AK25" s="239"/>
+      <c r="AL25" s="240"/>
+      <c r="AM25" s="240"/>
+      <c r="AN25" s="240"/>
+      <c r="AO25" s="240"/>
+      <c r="AP25" s="240"/>
+      <c r="AQ25" s="240"/>
+      <c r="AR25" s="241"/>
+      <c r="AS25" s="227"/>
+      <c r="AT25" s="228"/>
       <c r="BG25" s="14" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:59" ht="18.75" customHeight="1">
+    <row r="26" spans="1:59" ht="18.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A26" s="89"/>
       <c r="B26" s="93"/>
       <c r="C26" s="93"/>
@@ -6867,30 +6901,30 @@
       <c r="J26" s="88"/>
       <c r="K26" s="88"/>
       <c r="L26" s="88"/>
-      <c r="M26" s="260" t="s">
+      <c r="M26" s="225" t="s">
         <v>51</v>
       </c>
-      <c r="N26" s="260"/>
-      <c r="O26" s="260"/>
-      <c r="P26" s="260"/>
-      <c r="Q26" s="260"/>
-      <c r="R26" s="260"/>
-      <c r="S26" s="260"/>
-      <c r="T26" s="260"/>
+      <c r="N26" s="225"/>
+      <c r="O26" s="225"/>
+      <c r="P26" s="225"/>
+      <c r="Q26" s="225"/>
+      <c r="R26" s="225"/>
+      <c r="S26" s="225"/>
+      <c r="T26" s="225"/>
       <c r="U26" s="88"/>
       <c r="V26" s="88"/>
       <c r="W26" s="88"/>
       <c r="X26" s="88"/>
-      <c r="Y26" s="260" t="s">
+      <c r="Y26" s="225" t="s">
         <v>52</v>
       </c>
-      <c r="Z26" s="260"/>
-      <c r="AA26" s="260"/>
-      <c r="AB26" s="260"/>
-      <c r="AC26" s="260"/>
-      <c r="AD26" s="260"/>
-      <c r="AE26" s="260"/>
-      <c r="AF26" s="260"/>
+      <c r="Z26" s="225"/>
+      <c r="AA26" s="225"/>
+      <c r="AB26" s="225"/>
+      <c r="AC26" s="225"/>
+      <c r="AD26" s="225"/>
+      <c r="AE26" s="225"/>
+      <c r="AF26" s="225"/>
       <c r="AG26" s="91"/>
       <c r="AH26" s="91"/>
       <c r="AI26" s="88"/>
@@ -6909,7 +6943,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:59" ht="39.75" customHeight="1">
+    <row r="27" spans="1:59" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="95"/>
       <c r="B27" s="87"/>
       <c r="C27" s="87"/>
@@ -6922,26 +6956,26 @@
       <c r="J27" s="88"/>
       <c r="K27" s="88"/>
       <c r="L27" s="88"/>
-      <c r="M27" s="261" t="str">
+      <c r="M27" s="212">
         <f>IF(AG7=0,"",IF(M23&gt;AG7,"エラー",AG7))</f>
-        <v/>
-      </c>
-      <c r="N27" s="262"/>
-      <c r="O27" s="262"/>
-      <c r="P27" s="262"/>
-      <c r="Q27" s="262"/>
-      <c r="R27" s="262"/>
-      <c r="S27" s="262"/>
-      <c r="T27" s="263"/>
-      <c r="U27" s="220" t="s">
+        <v>5</v>
+      </c>
+      <c r="N27" s="213"/>
+      <c r="O27" s="213"/>
+      <c r="P27" s="213"/>
+      <c r="Q27" s="213"/>
+      <c r="R27" s="213"/>
+      <c r="S27" s="213"/>
+      <c r="T27" s="214"/>
+      <c r="U27" s="215" t="s">
         <v>45</v>
       </c>
-      <c r="V27" s="211"/>
+      <c r="V27" s="216"/>
       <c r="W27" s="88"/>
       <c r="X27" s="88"/>
-      <c r="Y27" s="217" t="str">
+      <c r="Y27" s="217">
         <f>IF(AP9="","",IF(Y23&gt;AY9,"エラー",AY9))</f>
-        <v/>
+        <v>365</v>
       </c>
       <c r="Z27" s="218"/>
       <c r="AA27" s="218"/>
@@ -6950,10 +6984,10 @@
       <c r="AD27" s="218"/>
       <c r="AE27" s="218"/>
       <c r="AF27" s="219"/>
-      <c r="AG27" s="220" t="s">
+      <c r="AG27" s="215" t="s">
         <v>16</v>
       </c>
-      <c r="AH27" s="211"/>
+      <c r="AH27" s="216"/>
       <c r="AI27" s="88"/>
       <c r="AJ27" s="88"/>
       <c r="AS27" s="82"/>
@@ -6962,7 +6996,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:59" ht="18.75" customHeight="1">
+    <row r="28" spans="1:59" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="83" t="s">
         <v>55</v>
       </c>
@@ -7010,53 +7044,53 @@
       <c r="AR28" s="81"/>
       <c r="AS28" s="82"/>
       <c r="AT28" s="73"/>
-      <c r="AW28" s="253" t="s">
+      <c r="AW28" s="251" t="s">
         <v>129</v>
       </c>
-      <c r="AX28" s="253"/>
+      <c r="AX28" s="251"/>
       <c r="BG28" s="14" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="29" spans="1:59" ht="39.75" customHeight="1">
+    <row r="29" spans="1:59" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="86"/>
-      <c r="M29" s="251" t="s">
+      <c r="M29" s="249" t="s">
         <v>57</v>
       </c>
-      <c r="N29" s="251"/>
-      <c r="O29" s="251"/>
-      <c r="P29" s="251"/>
-      <c r="Q29" s="251"/>
-      <c r="R29" s="251"/>
-      <c r="S29" s="251"/>
-      <c r="T29" s="251"/>
+      <c r="N29" s="249"/>
+      <c r="O29" s="249"/>
+      <c r="P29" s="249"/>
+      <c r="Q29" s="249"/>
+      <c r="R29" s="249"/>
+      <c r="S29" s="249"/>
+      <c r="T29" s="249"/>
       <c r="U29" s="96"/>
       <c r="W29" s="96"/>
-      <c r="X29" s="254" t="s">
+      <c r="X29" s="252" t="s">
         <v>144</v>
       </c>
-      <c r="Y29" s="254"/>
-      <c r="Z29" s="254"/>
-      <c r="AA29" s="254"/>
-      <c r="AB29" s="254"/>
-      <c r="AC29" s="254"/>
-      <c r="AD29" s="254"/>
-      <c r="AE29" s="254"/>
-      <c r="AF29" s="254"/>
-      <c r="AG29" s="254"/>
-      <c r="AH29" s="254"/>
+      <c r="Y29" s="252"/>
+      <c r="Z29" s="252"/>
+      <c r="AA29" s="252"/>
+      <c r="AB29" s="252"/>
+      <c r="AC29" s="252"/>
+      <c r="AD29" s="252"/>
+      <c r="AE29" s="252"/>
+      <c r="AF29" s="252"/>
+      <c r="AG29" s="252"/>
+      <c r="AH29" s="252"/>
       <c r="AI29" s="96"/>
       <c r="AJ29" s="96"/>
-      <c r="AK29" s="255" t="s">
+      <c r="AK29" s="253" t="s">
         <v>58</v>
       </c>
-      <c r="AL29" s="255"/>
-      <c r="AM29" s="255"/>
-      <c r="AN29" s="255"/>
-      <c r="AO29" s="255"/>
-      <c r="AP29" s="255"/>
-      <c r="AQ29" s="255"/>
-      <c r="AR29" s="255"/>
+      <c r="AL29" s="253"/>
+      <c r="AM29" s="253"/>
+      <c r="AN29" s="253"/>
+      <c r="AO29" s="253"/>
+      <c r="AP29" s="253"/>
+      <c r="AQ29" s="253"/>
+      <c r="AR29" s="253"/>
       <c r="AS29" s="96"/>
       <c r="AT29" s="97"/>
       <c r="AW29" s="25"/>
@@ -7065,28 +7099,30 @@
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="1:59" ht="39.75" customHeight="1">
+    <row r="30" spans="1:59" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="98"/>
-      <c r="M30" s="241" t="str">
+      <c r="M30" s="242">
         <f>AK24</f>
-        <v/>
-      </c>
-      <c r="N30" s="242"/>
-      <c r="O30" s="242"/>
-      <c r="P30" s="242"/>
-      <c r="Q30" s="242"/>
-      <c r="R30" s="242"/>
-      <c r="S30" s="242"/>
-      <c r="T30" s="243"/>
-      <c r="U30" s="205" t="s">
+        <v>1650000</v>
+      </c>
+      <c r="N30" s="243"/>
+      <c r="O30" s="243"/>
+      <c r="P30" s="243"/>
+      <c r="Q30" s="243"/>
+      <c r="R30" s="243"/>
+      <c r="S30" s="243"/>
+      <c r="T30" s="244"/>
+      <c r="U30" s="254" t="s">
         <v>28</v>
       </c>
-      <c r="V30" s="205"/>
-      <c r="W30" s="203" t="s">
+      <c r="V30" s="254"/>
+      <c r="W30" s="245" t="s">
         <v>44</v>
       </c>
-      <c r="X30" s="206"/>
-      <c r="Y30" s="256"/>
+      <c r="X30" s="255"/>
+      <c r="Y30" s="256">
+        <v>100</v>
+      </c>
       <c r="Z30" s="257"/>
       <c r="AA30" s="257"/>
       <c r="AB30" s="257"/>
@@ -7094,29 +7130,29 @@
       <c r="AD30" s="257"/>
       <c r="AE30" s="257"/>
       <c r="AF30" s="258"/>
-      <c r="AG30" s="205" t="s">
+      <c r="AG30" s="254" t="s">
         <v>60</v>
       </c>
-      <c r="AH30" s="205"/>
-      <c r="AI30" s="205" t="s">
+      <c r="AH30" s="254"/>
+      <c r="AI30" s="254" t="s">
         <v>46</v>
       </c>
-      <c r="AJ30" s="205"/>
-      <c r="AK30" s="241" t="str">
+      <c r="AJ30" s="254"/>
+      <c r="AK30" s="242">
         <f>IF(Y30="","",M30*Y30/100)</f>
-        <v/>
-      </c>
-      <c r="AL30" s="242"/>
-      <c r="AM30" s="242"/>
-      <c r="AN30" s="242"/>
-      <c r="AO30" s="242"/>
-      <c r="AP30" s="242"/>
-      <c r="AQ30" s="242"/>
-      <c r="AR30" s="243"/>
-      <c r="AS30" s="203" t="s">
+        <v>1650000</v>
+      </c>
+      <c r="AL30" s="243"/>
+      <c r="AM30" s="243"/>
+      <c r="AN30" s="243"/>
+      <c r="AO30" s="243"/>
+      <c r="AP30" s="243"/>
+      <c r="AQ30" s="243"/>
+      <c r="AR30" s="244"/>
+      <c r="AS30" s="245" t="s">
         <v>28</v>
       </c>
-      <c r="AT30" s="248"/>
+      <c r="AT30" s="246"/>
       <c r="AW30" s="26" t="s">
         <v>62</v>
       </c>
@@ -7127,7 +7163,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="31" spans="1:59" ht="18.75" customHeight="1">
+    <row r="31" spans="1:59" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="98"/>
       <c r="B31" s="66"/>
       <c r="C31" s="3"/>
@@ -7184,7 +7220,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="1:59" ht="33.75" customHeight="1">
+    <row r="32" spans="1:59" ht="33.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A32" s="99" t="s">
         <v>64</v>
       </c>
@@ -7243,7 +7279,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="33" spans="1:60" ht="18.75" customHeight="1">
+    <row r="33" spans="1:60" ht="18.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A33" s="103"/>
       <c r="B33" s="64"/>
       <c r="C33" s="64"/>
@@ -7276,7 +7312,7 @@
       </c>
       <c r="BH33" s="2"/>
     </row>
-    <row r="34" spans="1:60" ht="18.75" customHeight="1">
+    <row r="34" spans="1:60" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="106" t="s">
         <v>67</v>
       </c>
@@ -7331,8 +7367,8 @@
       <c r="AX34" s="27">
         <v>0.75</v>
       </c>
-      <c r="AZ34" s="249"/>
-      <c r="BA34" s="249"/>
+      <c r="AZ34" s="247"/>
+      <c r="BA34" s="247"/>
       <c r="BB34" s="16"/>
       <c r="BC34" s="16"/>
       <c r="BD34" s="16"/>
@@ -7340,7 +7376,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="35" spans="1:60" s="2" customFormat="1" ht="18.75" customHeight="1">
+    <row r="35" spans="1:60" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="110"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -7353,44 +7389,44 @@
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
-      <c r="M35" s="240" t="s">
+      <c r="M35" s="211" t="s">
         <v>70</v>
       </c>
-      <c r="N35" s="240"/>
-      <c r="O35" s="240"/>
-      <c r="P35" s="240"/>
-      <c r="Q35" s="240"/>
-      <c r="R35" s="240"/>
-      <c r="S35" s="240"/>
-      <c r="T35" s="240"/>
+      <c r="N35" s="211"/>
+      <c r="O35" s="211"/>
+      <c r="P35" s="211"/>
+      <c r="Q35" s="211"/>
+      <c r="R35" s="211"/>
+      <c r="S35" s="211"/>
+      <c r="T35" s="211"/>
       <c r="U35" s="96"/>
       <c r="V35" s="96"/>
       <c r="W35" s="111"/>
       <c r="X35" s="1"/>
-      <c r="Y35" s="250" t="s">
+      <c r="Y35" s="248" t="s">
         <v>71</v>
       </c>
-      <c r="Z35" s="250"/>
-      <c r="AA35" s="250"/>
-      <c r="AB35" s="250"/>
-      <c r="AC35" s="250"/>
-      <c r="AD35" s="250"/>
-      <c r="AE35" s="250"/>
-      <c r="AF35" s="250"/>
+      <c r="Z35" s="248"/>
+      <c r="AA35" s="248"/>
+      <c r="AB35" s="248"/>
+      <c r="AC35" s="248"/>
+      <c r="AD35" s="248"/>
+      <c r="AE35" s="248"/>
+      <c r="AF35" s="248"/>
       <c r="AG35" s="111"/>
       <c r="AH35" s="111"/>
       <c r="AI35" s="96"/>
       <c r="AJ35" s="96"/>
-      <c r="AK35" s="251" t="s">
+      <c r="AK35" s="249" t="s">
         <v>72</v>
       </c>
-      <c r="AL35" s="251"/>
-      <c r="AM35" s="251"/>
-      <c r="AN35" s="251"/>
-      <c r="AO35" s="251"/>
-      <c r="AP35" s="251"/>
-      <c r="AQ35" s="251"/>
-      <c r="AR35" s="251"/>
+      <c r="AL35" s="249"/>
+      <c r="AM35" s="249"/>
+      <c r="AN35" s="249"/>
+      <c r="AO35" s="249"/>
+      <c r="AP35" s="249"/>
+      <c r="AQ35" s="249"/>
+      <c r="AR35" s="249"/>
       <c r="AS35" s="96"/>
       <c r="AT35" s="97"/>
       <c r="AW35" s="17" t="s">
@@ -7399,78 +7435,78 @@
       <c r="AX35" s="27">
         <v>0.15</v>
       </c>
-      <c r="BA35" s="252"/>
-      <c r="BB35" s="252"/>
-      <c r="BC35" s="252"/>
-      <c r="BD35" s="252"/>
-      <c r="BE35" s="252"/>
+      <c r="BA35" s="250"/>
+      <c r="BB35" s="250"/>
+      <c r="BC35" s="250"/>
+      <c r="BD35" s="250"/>
+      <c r="BE35" s="250"/>
       <c r="BF35" s="1"/>
       <c r="BG35" s="14" t="s">
         <v>79</v>
       </c>
       <c r="BH35" s="1"/>
     </row>
-    <row r="36" spans="1:60" ht="39.75" customHeight="1">
+    <row r="36" spans="1:60" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="112"/>
-      <c r="M36" s="241" t="str">
+      <c r="M36" s="242">
         <f>AK30</f>
-        <v/>
-      </c>
-      <c r="N36" s="242"/>
-      <c r="O36" s="242"/>
-      <c r="P36" s="242"/>
-      <c r="Q36" s="242"/>
-      <c r="R36" s="242"/>
-      <c r="S36" s="242"/>
-      <c r="T36" s="243"/>
-      <c r="U36" s="205" t="s">
+        <v>1650000</v>
+      </c>
+      <c r="N36" s="243"/>
+      <c r="O36" s="243"/>
+      <c r="P36" s="243"/>
+      <c r="Q36" s="243"/>
+      <c r="R36" s="243"/>
+      <c r="S36" s="243"/>
+      <c r="T36" s="244"/>
+      <c r="U36" s="254" t="s">
         <v>28</v>
       </c>
-      <c r="V36" s="205"/>
-      <c r="W36" s="203" t="s">
+      <c r="V36" s="254"/>
+      <c r="W36" s="245" t="s">
         <v>44</v>
       </c>
-      <c r="X36" s="206"/>
-      <c r="Y36" s="244" t="s">
-        <v>65</v>
-      </c>
-      <c r="Z36" s="245"/>
-      <c r="AA36" s="245"/>
-      <c r="AB36" s="245"/>
-      <c r="AC36" s="245"/>
-      <c r="AD36" s="245"/>
-      <c r="AE36" s="245"/>
-      <c r="AF36" s="246"/>
-      <c r="AG36" s="205" t="s">
+      <c r="X36" s="255"/>
+      <c r="Y36" s="265" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z36" s="266"/>
+      <c r="AA36" s="266"/>
+      <c r="AB36" s="266"/>
+      <c r="AC36" s="266"/>
+      <c r="AD36" s="266"/>
+      <c r="AE36" s="266"/>
+      <c r="AF36" s="267"/>
+      <c r="AG36" s="254" t="s">
         <v>60</v>
       </c>
-      <c r="AH36" s="205"/>
-      <c r="AI36" s="205" t="s">
+      <c r="AH36" s="254"/>
+      <c r="AI36" s="254" t="s">
         <v>46</v>
       </c>
-      <c r="AJ36" s="205"/>
-      <c r="AK36" s="234" t="e">
+      <c r="AJ36" s="254"/>
+      <c r="AK36" s="259">
         <f>IF(Y36="", "", ROUNDDOWN(M36 * VLOOKUP(Y36, AW30:AX35, 2, FALSE), -2))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AL36" s="235"/>
-      <c r="AM36" s="235"/>
-      <c r="AN36" s="235"/>
-      <c r="AO36" s="235"/>
-      <c r="AP36" s="235"/>
-      <c r="AQ36" s="235"/>
-      <c r="AR36" s="236"/>
-      <c r="AS36" s="237" t="s">
+        <v>1237500</v>
+      </c>
+      <c r="AL36" s="260"/>
+      <c r="AM36" s="260"/>
+      <c r="AN36" s="260"/>
+      <c r="AO36" s="260"/>
+      <c r="AP36" s="260"/>
+      <c r="AQ36" s="260"/>
+      <c r="AR36" s="261"/>
+      <c r="AS36" s="262" t="s">
         <v>28</v>
       </c>
-      <c r="AT36" s="238"/>
+      <c r="AT36" s="263"/>
       <c r="AW36" s="40"/>
       <c r="AX36" s="40"/>
       <c r="BG36" s="14" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="37" spans="1:60" ht="18.75" customHeight="1">
+    <row r="37" spans="1:60" ht="18.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A37" s="86"/>
       <c r="C37" s="68"/>
       <c r="D37" s="68"/>
@@ -7502,20 +7538,20 @@
       <c r="AH37" s="2"/>
       <c r="AI37" s="104"/>
       <c r="AJ37" s="104"/>
-      <c r="AK37" s="239" t="s">
+      <c r="AK37" s="264" t="s">
         <v>77</v>
       </c>
-      <c r="AL37" s="239"/>
-      <c r="AM37" s="239"/>
-      <c r="AN37" s="239"/>
-      <c r="AO37" s="239"/>
-      <c r="AP37" s="239"/>
-      <c r="AQ37" s="239"/>
-      <c r="AR37" s="239"/>
+      <c r="AL37" s="264"/>
+      <c r="AM37" s="264"/>
+      <c r="AN37" s="264"/>
+      <c r="AO37" s="264"/>
+      <c r="AP37" s="264"/>
+      <c r="AQ37" s="264"/>
+      <c r="AR37" s="264"/>
       <c r="AS37" s="104"/>
       <c r="AT37" s="114"/>
     </row>
-    <row r="38" spans="1:60" ht="21" customHeight="1">
+    <row r="38" spans="1:60" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="115" t="s">
         <v>80</v>
       </c>
@@ -7557,7 +7593,7 @@
       <c r="AQ38" s="119"/>
       <c r="AT38" s="105"/>
     </row>
-    <row r="39" spans="1:60" ht="18.75" customHeight="1">
+    <row r="39" spans="1:60" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="86"/>
       <c r="B39" s="66"/>
       <c r="C39" s="66"/>
@@ -7569,18 +7605,18 @@
       <c r="I39" s="66"/>
       <c r="J39" s="87"/>
       <c r="K39" s="87"/>
-      <c r="L39" s="247" t="s">
+      <c r="L39" s="268" t="s">
         <v>138</v>
       </c>
-      <c r="M39" s="247"/>
-      <c r="N39" s="247"/>
-      <c r="O39" s="247"/>
-      <c r="P39" s="247"/>
-      <c r="Q39" s="247"/>
-      <c r="R39" s="247"/>
-      <c r="S39" s="247"/>
-      <c r="T39" s="247"/>
-      <c r="U39" s="247"/>
+      <c r="M39" s="268"/>
+      <c r="N39" s="268"/>
+      <c r="O39" s="268"/>
+      <c r="P39" s="268"/>
+      <c r="Q39" s="268"/>
+      <c r="R39" s="268"/>
+      <c r="S39" s="268"/>
+      <c r="T39" s="268"/>
+      <c r="U39" s="268"/>
       <c r="V39" s="66"/>
       <c r="W39" s="66"/>
       <c r="Y39" s="92" t="s">
@@ -7612,34 +7648,34 @@
       <c r="BG39" s="2"/>
       <c r="BH39" s="2"/>
     </row>
-    <row r="40" spans="1:60" ht="39.75" customHeight="1">
+    <row r="40" spans="1:60" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="86"/>
-      <c r="B40" s="240" t="s">
+      <c r="B40" s="211" t="s">
         <v>81</v>
       </c>
-      <c r="C40" s="240"/>
-      <c r="D40" s="240"/>
-      <c r="E40" s="240"/>
-      <c r="F40" s="240"/>
-      <c r="G40" s="240"/>
-      <c r="H40" s="240"/>
+      <c r="C40" s="211"/>
+      <c r="D40" s="211"/>
+      <c r="E40" s="211"/>
+      <c r="F40" s="211"/>
+      <c r="G40" s="211"/>
+      <c r="H40" s="211"/>
       <c r="J40" s="88"/>
-      <c r="L40" s="247"/>
-      <c r="M40" s="247"/>
-      <c r="N40" s="247"/>
-      <c r="O40" s="247"/>
-      <c r="P40" s="247"/>
-      <c r="Q40" s="247"/>
-      <c r="R40" s="247"/>
-      <c r="S40" s="247"/>
-      <c r="T40" s="247"/>
-      <c r="U40" s="247"/>
+      <c r="L40" s="268"/>
+      <c r="M40" s="268"/>
+      <c r="N40" s="268"/>
+      <c r="O40" s="268"/>
+      <c r="P40" s="268"/>
+      <c r="Q40" s="268"/>
+      <c r="R40" s="268"/>
+      <c r="S40" s="268"/>
+      <c r="T40" s="268"/>
+      <c r="U40" s="268"/>
       <c r="V40" s="88"/>
       <c r="W40" s="88"/>
       <c r="X40" s="88"/>
-      <c r="Y40" s="217" t="str">
+      <c r="Y40" s="217">
         <f>IF(AP8="","",IF(BA8=BC8,0,BA8))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Z40" s="218"/>
       <c r="AA40" s="218"/>
@@ -7648,20 +7684,20 @@
       <c r="AD40" s="218"/>
       <c r="AE40" s="218"/>
       <c r="AF40" s="219"/>
-      <c r="AG40" s="220" t="s">
+      <c r="AG40" s="215" t="s">
         <v>16</v>
       </c>
-      <c r="AH40" s="211"/>
+      <c r="AH40" s="216"/>
       <c r="AI40" s="88"/>
       <c r="AJ40" s="88"/>
-      <c r="AK40" s="202"/>
-      <c r="AL40" s="202"/>
-      <c r="AM40" s="202"/>
-      <c r="AN40" s="202"/>
-      <c r="AO40" s="202"/>
-      <c r="AP40" s="202"/>
-      <c r="AQ40" s="202"/>
-      <c r="AR40" s="202"/>
+      <c r="AK40" s="220"/>
+      <c r="AL40" s="220"/>
+      <c r="AM40" s="220"/>
+      <c r="AN40" s="220"/>
+      <c r="AO40" s="220"/>
+      <c r="AP40" s="220"/>
+      <c r="AQ40" s="220"/>
+      <c r="AR40" s="220"/>
       <c r="AS40" s="82"/>
       <c r="AT40" s="73"/>
       <c r="BE40" s="2"/>
@@ -7669,45 +7705,45 @@
       <c r="BG40" s="2"/>
       <c r="BH40" s="2"/>
     </row>
-    <row r="41" spans="1:60" s="2" customFormat="1" ht="21" customHeight="1">
+    <row r="41" spans="1:60" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A41" s="89"/>
-      <c r="B41" s="221" t="str">
+      <c r="B41" s="229">
         <f>IF(J7=0,"",J7)</f>
-        <v/>
-      </c>
-      <c r="C41" s="222"/>
-      <c r="D41" s="222"/>
-      <c r="E41" s="222"/>
-      <c r="F41" s="222"/>
-      <c r="G41" s="222"/>
-      <c r="H41" s="223"/>
-      <c r="I41" s="220" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" s="230"/>
+      <c r="D41" s="230"/>
+      <c r="E41" s="230"/>
+      <c r="F41" s="230"/>
+      <c r="G41" s="230"/>
+      <c r="H41" s="231"/>
+      <c r="I41" s="215" t="s">
         <v>45</v>
       </c>
-      <c r="J41" s="211"/>
-      <c r="K41" s="211" t="s">
+      <c r="J41" s="216"/>
+      <c r="K41" s="216" t="s">
         <v>118</v>
       </c>
-      <c r="L41" s="227"/>
-      <c r="M41" s="228" t="str">
+      <c r="L41" s="235"/>
+      <c r="M41" s="272">
         <f>IF(AP8="","",IF(BA8=BC8,AZ8+1,AZ8))</f>
-        <v/>
-      </c>
-      <c r="N41" s="229"/>
-      <c r="O41" s="229"/>
-      <c r="P41" s="229"/>
-      <c r="Q41" s="229"/>
-      <c r="R41" s="229"/>
-      <c r="S41" s="229"/>
-      <c r="T41" s="230"/>
-      <c r="U41" s="220" t="s">
+        <v>12</v>
+      </c>
+      <c r="N41" s="273"/>
+      <c r="O41" s="273"/>
+      <c r="P41" s="273"/>
+      <c r="Q41" s="273"/>
+      <c r="R41" s="273"/>
+      <c r="S41" s="273"/>
+      <c r="T41" s="274"/>
+      <c r="U41" s="215" t="s">
         <v>83</v>
       </c>
-      <c r="V41" s="211"/>
-      <c r="W41" s="211" t="s">
+      <c r="V41" s="216"/>
+      <c r="W41" s="216" t="s">
         <v>117</v>
       </c>
-      <c r="X41" s="211"/>
+      <c r="X41" s="216"/>
       <c r="Y41" s="90"/>
       <c r="Z41" s="90"/>
       <c r="AA41" s="90"/>
@@ -7718,44 +7754,44 @@
       <c r="AF41" s="90"/>
       <c r="AG41" s="91"/>
       <c r="AH41" s="91"/>
-      <c r="AI41" s="211" t="s">
+      <c r="AI41" s="216" t="s">
         <v>107</v>
       </c>
-      <c r="AJ41" s="211"/>
-      <c r="AL41" s="213" t="s">
+      <c r="AJ41" s="216"/>
+      <c r="AL41" s="269" t="s">
         <v>116</v>
       </c>
-      <c r="AM41" s="213"/>
-      <c r="AN41" s="213"/>
-      <c r="AO41" s="213"/>
-      <c r="AS41" s="214"/>
-      <c r="AT41" s="215"/>
+      <c r="AM41" s="269"/>
+      <c r="AN41" s="269"/>
+      <c r="AO41" s="269"/>
+      <c r="AS41" s="270"/>
+      <c r="AT41" s="228"/>
     </row>
-    <row r="42" spans="1:60" s="2" customFormat="1" ht="21" customHeight="1">
+    <row r="42" spans="1:60" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A42" s="89"/>
-      <c r="B42" s="224"/>
-      <c r="C42" s="225"/>
-      <c r="D42" s="225"/>
-      <c r="E42" s="225"/>
-      <c r="F42" s="225"/>
-      <c r="G42" s="225"/>
-      <c r="H42" s="226"/>
-      <c r="I42" s="220"/>
-      <c r="J42" s="211"/>
-      <c r="K42" s="211"/>
-      <c r="L42" s="227"/>
-      <c r="M42" s="231"/>
-      <c r="N42" s="232"/>
-      <c r="O42" s="232"/>
-      <c r="P42" s="232"/>
-      <c r="Q42" s="232"/>
-      <c r="R42" s="232"/>
-      <c r="S42" s="232"/>
-      <c r="T42" s="233"/>
-      <c r="U42" s="220"/>
-      <c r="V42" s="211"/>
-      <c r="W42" s="211"/>
-      <c r="X42" s="211"/>
+      <c r="B42" s="232"/>
+      <c r="C42" s="233"/>
+      <c r="D42" s="233"/>
+      <c r="E42" s="233"/>
+      <c r="F42" s="233"/>
+      <c r="G42" s="233"/>
+      <c r="H42" s="234"/>
+      <c r="I42" s="215"/>
+      <c r="J42" s="216"/>
+      <c r="K42" s="216"/>
+      <c r="L42" s="235"/>
+      <c r="M42" s="275"/>
+      <c r="N42" s="276"/>
+      <c r="O42" s="276"/>
+      <c r="P42" s="276"/>
+      <c r="Q42" s="276"/>
+      <c r="R42" s="276"/>
+      <c r="S42" s="276"/>
+      <c r="T42" s="277"/>
+      <c r="U42" s="215"/>
+      <c r="V42" s="216"/>
+      <c r="W42" s="216"/>
+      <c r="X42" s="216"/>
       <c r="Y42" s="87"/>
       <c r="Z42" s="87"/>
       <c r="AA42" s="87"/>
@@ -7766,20 +7802,20 @@
       <c r="AF42" s="87"/>
       <c r="AG42" s="91"/>
       <c r="AH42" s="91"/>
-      <c r="AI42" s="211"/>
-      <c r="AJ42" s="211"/>
-      <c r="AL42" s="213"/>
-      <c r="AM42" s="213"/>
-      <c r="AN42" s="213"/>
-      <c r="AO42" s="213"/>
-      <c r="AS42" s="214"/>
-      <c r="AT42" s="215"/>
+      <c r="AI42" s="216"/>
+      <c r="AJ42" s="216"/>
+      <c r="AL42" s="269"/>
+      <c r="AM42" s="269"/>
+      <c r="AN42" s="269"/>
+      <c r="AO42" s="269"/>
+      <c r="AS42" s="270"/>
+      <c r="AT42" s="228"/>
       <c r="BE42" s="1"/>
       <c r="BF42" s="1"/>
       <c r="BG42" s="1"/>
       <c r="BH42" s="1"/>
     </row>
-    <row r="43" spans="1:60" s="2" customFormat="1" ht="18.75" customHeight="1">
+    <row r="43" spans="1:60" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="89"/>
       <c r="B43" s="120"/>
       <c r="C43" s="120"/>
@@ -7829,7 +7865,7 @@
       <c r="BG43" s="1"/>
       <c r="BH43" s="1"/>
     </row>
-    <row r="44" spans="1:60" ht="39.75" customHeight="1">
+    <row r="44" spans="1:60" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" s="95"/>
       <c r="B44" s="87"/>
       <c r="C44" s="87"/>
@@ -7842,21 +7878,21 @@
       <c r="J44" s="88"/>
       <c r="K44" s="88"/>
       <c r="L44" s="88"/>
-      <c r="M44" s="216"/>
-      <c r="N44" s="216"/>
-      <c r="O44" s="216"/>
-      <c r="P44" s="216"/>
-      <c r="Q44" s="216"/>
-      <c r="R44" s="216"/>
-      <c r="S44" s="216"/>
-      <c r="T44" s="216"/>
+      <c r="M44" s="271"/>
+      <c r="N44" s="271"/>
+      <c r="O44" s="271"/>
+      <c r="P44" s="271"/>
+      <c r="Q44" s="271"/>
+      <c r="R44" s="271"/>
+      <c r="S44" s="271"/>
+      <c r="T44" s="271"/>
       <c r="U44" s="88"/>
       <c r="V44" s="88"/>
       <c r="W44" s="88"/>
       <c r="X44" s="88"/>
-      <c r="Y44" s="217" t="str">
+      <c r="Y44" s="217">
         <f>IF(AP8="","",IF(BA8=BC8,0,IF(BC8=28,28,IF(BC8=29,29,IF(BC8=30,30,IF(BC8=31,31,))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Z44" s="218"/>
       <c r="AA44" s="218"/>
@@ -7865,10 +7901,10 @@
       <c r="AD44" s="218"/>
       <c r="AE44" s="218"/>
       <c r="AF44" s="219"/>
-      <c r="AG44" s="220" t="s">
+      <c r="AG44" s="215" t="s">
         <v>16</v>
       </c>
-      <c r="AH44" s="211"/>
+      <c r="AH44" s="216"/>
       <c r="AI44" s="88"/>
       <c r="AJ44" s="88"/>
       <c r="AK44" s="65"/>
@@ -7882,7 +7918,7 @@
       <c r="AS44" s="82"/>
       <c r="AT44" s="73"/>
     </row>
-    <row r="45" spans="1:60" ht="18.75" customHeight="1">
+    <row r="45" spans="1:60" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="86"/>
       <c r="K45" s="123"/>
       <c r="L45" s="116"/>
@@ -7895,18 +7931,18 @@
       <c r="S45" s="124"/>
       <c r="T45" s="124"/>
       <c r="W45" s="123"/>
-      <c r="X45" s="212" t="s">
+      <c r="X45" s="283" t="s">
         <v>143</v>
       </c>
-      <c r="Y45" s="212"/>
-      <c r="Z45" s="212"/>
-      <c r="AA45" s="212"/>
-      <c r="AB45" s="212"/>
-      <c r="AC45" s="212"/>
-      <c r="AD45" s="212"/>
-      <c r="AE45" s="212"/>
-      <c r="AF45" s="212"/>
-      <c r="AG45" s="212"/>
+      <c r="Y45" s="283"/>
+      <c r="Z45" s="283"/>
+      <c r="AA45" s="283"/>
+      <c r="AB45" s="283"/>
+      <c r="AC45" s="283"/>
+      <c r="AD45" s="283"/>
+      <c r="AE45" s="283"/>
+      <c r="AF45" s="283"/>
+      <c r="AG45" s="283"/>
       <c r="AJ45" s="123"/>
       <c r="AK45" s="65"/>
       <c r="AL45" s="65"/>
@@ -7919,103 +7955,105 @@
       <c r="AS45" s="113"/>
       <c r="AT45" s="105"/>
     </row>
-    <row r="46" spans="1:60" ht="18.75" customHeight="1">
+    <row r="46" spans="1:60" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="86"/>
       <c r="K46" s="123"/>
       <c r="L46" s="65"/>
-      <c r="M46" s="202" t="s">
+      <c r="M46" s="220" t="s">
         <v>82</v>
       </c>
-      <c r="N46" s="202"/>
-      <c r="O46" s="202"/>
-      <c r="P46" s="202"/>
-      <c r="Q46" s="202"/>
-      <c r="R46" s="202"/>
-      <c r="S46" s="202"/>
-      <c r="T46" s="202"/>
+      <c r="N46" s="220"/>
+      <c r="O46" s="220"/>
+      <c r="P46" s="220"/>
+      <c r="Q46" s="220"/>
+      <c r="R46" s="220"/>
+      <c r="S46" s="220"/>
+      <c r="T46" s="220"/>
       <c r="W46" s="123"/>
-      <c r="X46" s="212"/>
-      <c r="Y46" s="212"/>
-      <c r="Z46" s="212"/>
-      <c r="AA46" s="212"/>
-      <c r="AB46" s="212"/>
-      <c r="AC46" s="212"/>
-      <c r="AD46" s="212"/>
-      <c r="AE46" s="212"/>
-      <c r="AF46" s="212"/>
-      <c r="AG46" s="212"/>
+      <c r="X46" s="283"/>
+      <c r="Y46" s="283"/>
+      <c r="Z46" s="283"/>
+      <c r="AA46" s="283"/>
+      <c r="AB46" s="283"/>
+      <c r="AC46" s="283"/>
+      <c r="AD46" s="283"/>
+      <c r="AE46" s="283"/>
+      <c r="AF46" s="283"/>
+      <c r="AG46" s="283"/>
       <c r="AI46" s="88"/>
       <c r="AJ46" s="88"/>
-      <c r="AK46" s="202" t="s">
+      <c r="AK46" s="220" t="s">
         <v>84</v>
       </c>
-      <c r="AL46" s="202"/>
-      <c r="AM46" s="202"/>
-      <c r="AN46" s="202"/>
-      <c r="AO46" s="202"/>
-      <c r="AP46" s="202"/>
-      <c r="AQ46" s="202"/>
-      <c r="AR46" s="202"/>
+      <c r="AL46" s="220"/>
+      <c r="AM46" s="220"/>
+      <c r="AN46" s="220"/>
+      <c r="AO46" s="220"/>
+      <c r="AP46" s="220"/>
+      <c r="AQ46" s="220"/>
+      <c r="AR46" s="220"/>
       <c r="AS46" s="82"/>
       <c r="AT46" s="73"/>
     </row>
-    <row r="47" spans="1:60" ht="39.75" customHeight="1">
+    <row r="47" spans="1:60" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="86"/>
-      <c r="K47" s="203" t="s">
+      <c r="K47" s="245" t="s">
         <v>44</v>
       </c>
-      <c r="L47" s="203"/>
-      <c r="M47" s="204">
+      <c r="L47" s="245"/>
+      <c r="M47" s="278">
         <v>20000</v>
       </c>
-      <c r="N47" s="204"/>
-      <c r="O47" s="204"/>
-      <c r="P47" s="204"/>
-      <c r="Q47" s="204"/>
-      <c r="R47" s="204"/>
-      <c r="S47" s="204"/>
-      <c r="T47" s="204"/>
-      <c r="U47" s="205" t="s">
+      <c r="N47" s="278"/>
+      <c r="O47" s="278"/>
+      <c r="P47" s="278"/>
+      <c r="Q47" s="278"/>
+      <c r="R47" s="278"/>
+      <c r="S47" s="278"/>
+      <c r="T47" s="278"/>
+      <c r="U47" s="254" t="s">
         <v>28</v>
       </c>
-      <c r="V47" s="205"/>
-      <c r="W47" s="203" t="s">
+      <c r="V47" s="254"/>
+      <c r="W47" s="245" t="s">
         <v>145</v>
       </c>
-      <c r="X47" s="206"/>
-      <c r="Y47" s="207"/>
-      <c r="Z47" s="208"/>
-      <c r="AA47" s="208"/>
-      <c r="AB47" s="208"/>
-      <c r="AC47" s="208"/>
-      <c r="AD47" s="208"/>
-      <c r="AE47" s="208"/>
-      <c r="AF47" s="209"/>
-      <c r="AG47" s="210" t="s">
+      <c r="X47" s="255"/>
+      <c r="Y47" s="279">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="280"/>
+      <c r="AA47" s="280"/>
+      <c r="AB47" s="280"/>
+      <c r="AC47" s="280"/>
+      <c r="AD47" s="280"/>
+      <c r="AE47" s="280"/>
+      <c r="AF47" s="281"/>
+      <c r="AG47" s="282" t="s">
         <v>28</v>
       </c>
-      <c r="AH47" s="205"/>
-      <c r="AI47" s="211" t="s">
+      <c r="AH47" s="254"/>
+      <c r="AI47" s="216" t="s">
         <v>46</v>
       </c>
-      <c r="AJ47" s="211"/>
-      <c r="AK47" s="195" t="e">
+      <c r="AJ47" s="216"/>
+      <c r="AK47" s="287">
         <f>IF(Y36="", "", IF(B41*(M41+IF(Y44=0, 0,Y40/Y44)) *20000&lt;Y47,"エラー",ROUNDDOWN(B41*(M41+IF(Y44=0, 0,Y40/Y44)) *20000-IF(Y36=AW35,Y47,0), -2)))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AL47" s="195"/>
-      <c r="AM47" s="195"/>
-      <c r="AN47" s="195"/>
-      <c r="AO47" s="195"/>
-      <c r="AP47" s="195"/>
-      <c r="AQ47" s="195"/>
-      <c r="AR47" s="195"/>
+        <v>1200000</v>
+      </c>
+      <c r="AL47" s="287"/>
+      <c r="AM47" s="287"/>
+      <c r="AN47" s="287"/>
+      <c r="AO47" s="287"/>
+      <c r="AP47" s="287"/>
+      <c r="AQ47" s="287"/>
+      <c r="AR47" s="287"/>
       <c r="AS47" s="81" t="s">
         <v>28</v>
       </c>
       <c r="AT47" s="94"/>
     </row>
-    <row r="48" spans="1:60" ht="18.75" customHeight="1">
+    <row r="48" spans="1:60" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="86"/>
       <c r="K48" s="123"/>
       <c r="L48" s="116"/>
@@ -8032,16 +8070,16 @@
       <c r="AF48" s="125"/>
       <c r="AI48" s="88"/>
       <c r="AJ48" s="88"/>
-      <c r="AK48" s="196" t="s">
+      <c r="AK48" s="288" t="s">
         <v>85</v>
       </c>
-      <c r="AL48" s="196"/>
-      <c r="AM48" s="196"/>
-      <c r="AN48" s="196"/>
-      <c r="AO48" s="196"/>
-      <c r="AP48" s="196"/>
-      <c r="AQ48" s="196"/>
-      <c r="AR48" s="196"/>
+      <c r="AL48" s="288"/>
+      <c r="AM48" s="288"/>
+      <c r="AN48" s="288"/>
+      <c r="AO48" s="288"/>
+      <c r="AP48" s="288"/>
+      <c r="AQ48" s="288"/>
+      <c r="AR48" s="288"/>
       <c r="AS48" s="65"/>
       <c r="AT48" s="94"/>
       <c r="BE48" s="7"/>
@@ -8049,7 +8087,7 @@
       <c r="BG48" s="5"/>
       <c r="BH48" s="5"/>
     </row>
-    <row r="49" spans="1:60" ht="13.5" customHeight="1" thickBot="1">
+    <row r="49" spans="1:60" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="86"/>
       <c r="K49" s="123"/>
       <c r="L49" s="116"/>
@@ -8081,7 +8119,7 @@
       <c r="BG49" s="5"/>
       <c r="BH49" s="5"/>
     </row>
-    <row r="50" spans="1:60" ht="39.75" customHeight="1" thickTop="1" thickBot="1">
+    <row r="50" spans="1:60" ht="39.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="127" t="s">
         <v>113</v>
       </c>
@@ -8100,23 +8138,23 @@
       <c r="AH50" s="104"/>
       <c r="AI50" s="88"/>
       <c r="AJ50" s="129"/>
-      <c r="AK50" s="197" t="e">
+      <c r="AK50" s="289">
         <f>IF(AK47="","",IF(AK47="エラー","エラー",MIN(AK47,AK36 )))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AL50" s="198"/>
-      <c r="AM50" s="198"/>
-      <c r="AN50" s="198"/>
-      <c r="AO50" s="198"/>
-      <c r="AP50" s="198"/>
-      <c r="AQ50" s="198"/>
-      <c r="AR50" s="199"/>
+        <v>1200000</v>
+      </c>
+      <c r="AL50" s="290"/>
+      <c r="AM50" s="290"/>
+      <c r="AN50" s="290"/>
+      <c r="AO50" s="290"/>
+      <c r="AP50" s="290"/>
+      <c r="AQ50" s="290"/>
+      <c r="AR50" s="291"/>
       <c r="AS50" s="81" t="s">
         <v>28</v>
       </c>
       <c r="AT50" s="94"/>
     </row>
-    <row r="51" spans="1:60" s="5" customFormat="1" ht="15.75" customHeight="1" thickTop="1" thickBot="1">
+    <row r="51" spans="1:60" s="5" customFormat="1" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="130"/>
       <c r="B51" s="131"/>
       <c r="C51" s="131"/>
@@ -8178,7 +8216,7 @@
       <c r="BG51" s="1"/>
       <c r="BH51" s="1"/>
     </row>
-    <row r="52" spans="1:60" ht="16.5" customHeight="1">
+    <row r="52" spans="1:60" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" s="136" t="s">
         <v>86</v>
       </c>
@@ -8231,7 +8269,7 @@
       <c r="AV52" s="3"/>
       <c r="AW52" s="3"/>
     </row>
-    <row r="53" spans="1:60" ht="16.5" customHeight="1">
+    <row r="53" spans="1:60" ht="16.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A53" s="137" t="s">
         <v>157</v>
       </c>
@@ -8284,7 +8322,7 @@
       <c r="AV53" s="3"/>
       <c r="AW53" s="3"/>
     </row>
-    <row r="54" spans="1:60" ht="16.5" customHeight="1">
+    <row r="54" spans="1:60" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A54" s="139"/>
       <c r="B54" s="138"/>
       <c r="C54" s="138"/>
@@ -8335,7 +8373,7 @@
       <c r="AV54" s="3"/>
       <c r="AW54" s="3"/>
     </row>
-    <row r="55" spans="1:60" ht="21.95" customHeight="1">
+    <row r="55" spans="1:60" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="140" t="s">
         <v>87</v>
       </c>
@@ -8387,329 +8425,329 @@
       <c r="AU55" s="5"/>
       <c r="AV55" s="5"/>
     </row>
-    <row r="56" spans="1:60" ht="21.95" customHeight="1">
+    <row r="56" spans="1:60" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="142" t="s">
         <v>0</v>
       </c>
-      <c r="B56" s="200" t="s">
+      <c r="B56" s="292" t="s">
         <v>146</v>
       </c>
-      <c r="C56" s="200"/>
-      <c r="D56" s="200"/>
-      <c r="E56" s="200"/>
-      <c r="F56" s="200"/>
-      <c r="G56" s="200"/>
-      <c r="H56" s="200"/>
-      <c r="I56" s="200"/>
-      <c r="J56" s="200"/>
-      <c r="K56" s="200"/>
-      <c r="L56" s="200"/>
-      <c r="M56" s="200"/>
-      <c r="N56" s="200"/>
-      <c r="O56" s="200"/>
-      <c r="P56" s="200"/>
-      <c r="Q56" s="200"/>
-      <c r="R56" s="200"/>
-      <c r="S56" s="200"/>
-      <c r="T56" s="200"/>
-      <c r="U56" s="200"/>
-      <c r="V56" s="200"/>
-      <c r="W56" s="200"/>
-      <c r="X56" s="200"/>
-      <c r="Y56" s="200"/>
-      <c r="Z56" s="200"/>
-      <c r="AA56" s="200"/>
-      <c r="AB56" s="200"/>
-      <c r="AC56" s="200"/>
-      <c r="AD56" s="200"/>
-      <c r="AE56" s="200"/>
-      <c r="AF56" s="200"/>
-      <c r="AG56" s="200"/>
-      <c r="AH56" s="200"/>
-      <c r="AI56" s="200"/>
-      <c r="AJ56" s="200"/>
-      <c r="AK56" s="200"/>
-      <c r="AL56" s="200"/>
-      <c r="AM56" s="200"/>
-      <c r="AN56" s="200"/>
-      <c r="AO56" s="200"/>
-      <c r="AP56" s="200"/>
-      <c r="AQ56" s="200"/>
-      <c r="AR56" s="200"/>
-      <c r="AS56" s="200"/>
-      <c r="AT56" s="200"/>
+      <c r="C56" s="292"/>
+      <c r="D56" s="292"/>
+      <c r="E56" s="292"/>
+      <c r="F56" s="292"/>
+      <c r="G56" s="292"/>
+      <c r="H56" s="292"/>
+      <c r="I56" s="292"/>
+      <c r="J56" s="292"/>
+      <c r="K56" s="292"/>
+      <c r="L56" s="292"/>
+      <c r="M56" s="292"/>
+      <c r="N56" s="292"/>
+      <c r="O56" s="292"/>
+      <c r="P56" s="292"/>
+      <c r="Q56" s="292"/>
+      <c r="R56" s="292"/>
+      <c r="S56" s="292"/>
+      <c r="T56" s="292"/>
+      <c r="U56" s="292"/>
+      <c r="V56" s="292"/>
+      <c r="W56" s="292"/>
+      <c r="X56" s="292"/>
+      <c r="Y56" s="292"/>
+      <c r="Z56" s="292"/>
+      <c r="AA56" s="292"/>
+      <c r="AB56" s="292"/>
+      <c r="AC56" s="292"/>
+      <c r="AD56" s="292"/>
+      <c r="AE56" s="292"/>
+      <c r="AF56" s="292"/>
+      <c r="AG56" s="292"/>
+      <c r="AH56" s="292"/>
+      <c r="AI56" s="292"/>
+      <c r="AJ56" s="292"/>
+      <c r="AK56" s="292"/>
+      <c r="AL56" s="292"/>
+      <c r="AM56" s="292"/>
+      <c r="AN56" s="292"/>
+      <c r="AO56" s="292"/>
+      <c r="AP56" s="292"/>
+      <c r="AQ56" s="292"/>
+      <c r="AR56" s="292"/>
+      <c r="AS56" s="292"/>
+      <c r="AT56" s="292"/>
       <c r="AU56" s="4"/>
       <c r="AV56" s="4"/>
       <c r="AW56" s="4"/>
     </row>
-    <row r="57" spans="1:60" ht="21.95" customHeight="1">
+    <row r="57" spans="1:60" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="143" t="s">
         <v>88</v>
       </c>
-      <c r="B57" s="200" t="s">
+      <c r="B57" s="292" t="s">
         <v>147</v>
       </c>
-      <c r="C57" s="200"/>
-      <c r="D57" s="200"/>
-      <c r="E57" s="200"/>
-      <c r="F57" s="200"/>
-      <c r="G57" s="200"/>
-      <c r="H57" s="200"/>
-      <c r="I57" s="200"/>
-      <c r="J57" s="200"/>
-      <c r="K57" s="200"/>
-      <c r="L57" s="200"/>
-      <c r="M57" s="200"/>
-      <c r="N57" s="200"/>
-      <c r="O57" s="200"/>
-      <c r="P57" s="200"/>
-      <c r="Q57" s="200"/>
-      <c r="R57" s="200"/>
-      <c r="S57" s="200"/>
-      <c r="T57" s="200"/>
-      <c r="U57" s="200"/>
-      <c r="V57" s="200"/>
-      <c r="W57" s="200"/>
-      <c r="X57" s="200"/>
-      <c r="Y57" s="200"/>
-      <c r="Z57" s="200"/>
-      <c r="AA57" s="200"/>
-      <c r="AB57" s="200"/>
-      <c r="AC57" s="200"/>
-      <c r="AD57" s="200"/>
-      <c r="AE57" s="200"/>
-      <c r="AF57" s="200"/>
-      <c r="AG57" s="200"/>
-      <c r="AH57" s="200"/>
-      <c r="AI57" s="200"/>
-      <c r="AJ57" s="200"/>
-      <c r="AK57" s="200"/>
-      <c r="AL57" s="200"/>
-      <c r="AM57" s="200"/>
-      <c r="AN57" s="200"/>
-      <c r="AO57" s="200"/>
-      <c r="AP57" s="200"/>
-      <c r="AQ57" s="200"/>
-      <c r="AR57" s="200"/>
-      <c r="AS57" s="200"/>
-      <c r="AT57" s="200"/>
+      <c r="C57" s="292"/>
+      <c r="D57" s="292"/>
+      <c r="E57" s="292"/>
+      <c r="F57" s="292"/>
+      <c r="G57" s="292"/>
+      <c r="H57" s="292"/>
+      <c r="I57" s="292"/>
+      <c r="J57" s="292"/>
+      <c r="K57" s="292"/>
+      <c r="L57" s="292"/>
+      <c r="M57" s="292"/>
+      <c r="N57" s="292"/>
+      <c r="O57" s="292"/>
+      <c r="P57" s="292"/>
+      <c r="Q57" s="292"/>
+      <c r="R57" s="292"/>
+      <c r="S57" s="292"/>
+      <c r="T57" s="292"/>
+      <c r="U57" s="292"/>
+      <c r="V57" s="292"/>
+      <c r="W57" s="292"/>
+      <c r="X57" s="292"/>
+      <c r="Y57" s="292"/>
+      <c r="Z57" s="292"/>
+      <c r="AA57" s="292"/>
+      <c r="AB57" s="292"/>
+      <c r="AC57" s="292"/>
+      <c r="AD57" s="292"/>
+      <c r="AE57" s="292"/>
+      <c r="AF57" s="292"/>
+      <c r="AG57" s="292"/>
+      <c r="AH57" s="292"/>
+      <c r="AI57" s="292"/>
+      <c r="AJ57" s="292"/>
+      <c r="AK57" s="292"/>
+      <c r="AL57" s="292"/>
+      <c r="AM57" s="292"/>
+      <c r="AN57" s="292"/>
+      <c r="AO57" s="292"/>
+      <c r="AP57" s="292"/>
+      <c r="AQ57" s="292"/>
+      <c r="AR57" s="292"/>
+      <c r="AS57" s="292"/>
+      <c r="AT57" s="292"/>
       <c r="AU57" s="4"/>
       <c r="AV57" s="4"/>
       <c r="AW57" s="4"/>
     </row>
-    <row r="58" spans="1:60" ht="21.95" customHeight="1">
+    <row r="58" spans="1:60" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="143" t="s">
         <v>89</v>
       </c>
-      <c r="B58" s="200" t="s">
+      <c r="B58" s="292" t="s">
         <v>148</v>
       </c>
-      <c r="C58" s="200"/>
-      <c r="D58" s="200"/>
-      <c r="E58" s="200"/>
-      <c r="F58" s="200"/>
-      <c r="G58" s="200"/>
-      <c r="H58" s="200"/>
-      <c r="I58" s="200"/>
-      <c r="J58" s="200"/>
-      <c r="K58" s="200"/>
-      <c r="L58" s="200"/>
-      <c r="M58" s="200"/>
-      <c r="N58" s="200"/>
-      <c r="O58" s="200"/>
-      <c r="P58" s="200"/>
-      <c r="Q58" s="200"/>
-      <c r="R58" s="200"/>
-      <c r="S58" s="200"/>
-      <c r="T58" s="200"/>
-      <c r="U58" s="200"/>
-      <c r="V58" s="200"/>
-      <c r="W58" s="200"/>
-      <c r="X58" s="200"/>
-      <c r="Y58" s="200"/>
-      <c r="Z58" s="200"/>
-      <c r="AA58" s="200"/>
-      <c r="AB58" s="200"/>
-      <c r="AC58" s="200"/>
-      <c r="AD58" s="200"/>
-      <c r="AE58" s="200"/>
-      <c r="AF58" s="200"/>
-      <c r="AG58" s="200"/>
-      <c r="AH58" s="200"/>
-      <c r="AI58" s="200"/>
-      <c r="AJ58" s="200"/>
-      <c r="AK58" s="200"/>
-      <c r="AL58" s="200"/>
-      <c r="AM58" s="200"/>
-      <c r="AN58" s="200"/>
-      <c r="AO58" s="200"/>
-      <c r="AP58" s="200"/>
-      <c r="AQ58" s="200"/>
-      <c r="AR58" s="200"/>
-      <c r="AS58" s="200"/>
-      <c r="AT58" s="200"/>
+      <c r="C58" s="292"/>
+      <c r="D58" s="292"/>
+      <c r="E58" s="292"/>
+      <c r="F58" s="292"/>
+      <c r="G58" s="292"/>
+      <c r="H58" s="292"/>
+      <c r="I58" s="292"/>
+      <c r="J58" s="292"/>
+      <c r="K58" s="292"/>
+      <c r="L58" s="292"/>
+      <c r="M58" s="292"/>
+      <c r="N58" s="292"/>
+      <c r="O58" s="292"/>
+      <c r="P58" s="292"/>
+      <c r="Q58" s="292"/>
+      <c r="R58" s="292"/>
+      <c r="S58" s="292"/>
+      <c r="T58" s="292"/>
+      <c r="U58" s="292"/>
+      <c r="V58" s="292"/>
+      <c r="W58" s="292"/>
+      <c r="X58" s="292"/>
+      <c r="Y58" s="292"/>
+      <c r="Z58" s="292"/>
+      <c r="AA58" s="292"/>
+      <c r="AB58" s="292"/>
+      <c r="AC58" s="292"/>
+      <c r="AD58" s="292"/>
+      <c r="AE58" s="292"/>
+      <c r="AF58" s="292"/>
+      <c r="AG58" s="292"/>
+      <c r="AH58" s="292"/>
+      <c r="AI58" s="292"/>
+      <c r="AJ58" s="292"/>
+      <c r="AK58" s="292"/>
+      <c r="AL58" s="292"/>
+      <c r="AM58" s="292"/>
+      <c r="AN58" s="292"/>
+      <c r="AO58" s="292"/>
+      <c r="AP58" s="292"/>
+      <c r="AQ58" s="292"/>
+      <c r="AR58" s="292"/>
+      <c r="AS58" s="292"/>
+      <c r="AT58" s="292"/>
       <c r="BE58" s="10"/>
       <c r="BF58" s="10"/>
       <c r="BG58" s="10"/>
       <c r="BH58" s="10"/>
     </row>
-    <row r="59" spans="1:60" ht="21.95" customHeight="1">
+    <row r="59" spans="1:60" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="143" t="s">
         <v>90</v>
       </c>
-      <c r="B59" s="201" t="s">
+      <c r="B59" s="293" t="s">
         <v>161</v>
       </c>
-      <c r="C59" s="201"/>
-      <c r="D59" s="201"/>
-      <c r="E59" s="201"/>
-      <c r="F59" s="201"/>
-      <c r="G59" s="201"/>
-      <c r="H59" s="201"/>
-      <c r="I59" s="201"/>
-      <c r="J59" s="201"/>
-      <c r="K59" s="201"/>
-      <c r="L59" s="201"/>
-      <c r="M59" s="201"/>
-      <c r="N59" s="201"/>
-      <c r="O59" s="201"/>
-      <c r="P59" s="201"/>
-      <c r="Q59" s="201"/>
-      <c r="R59" s="201"/>
-      <c r="S59" s="201"/>
-      <c r="T59" s="201"/>
-      <c r="U59" s="201"/>
-      <c r="V59" s="201"/>
-      <c r="W59" s="201"/>
-      <c r="X59" s="201"/>
-      <c r="Y59" s="201"/>
-      <c r="Z59" s="201"/>
-      <c r="AA59" s="201"/>
-      <c r="AB59" s="201"/>
-      <c r="AC59" s="201"/>
-      <c r="AD59" s="201"/>
-      <c r="AE59" s="201"/>
-      <c r="AF59" s="201"/>
-      <c r="AG59" s="201"/>
-      <c r="AH59" s="201"/>
-      <c r="AI59" s="201"/>
-      <c r="AJ59" s="201"/>
-      <c r="AK59" s="201"/>
-      <c r="AL59" s="201"/>
-      <c r="AM59" s="201"/>
-      <c r="AN59" s="201"/>
-      <c r="AO59" s="201"/>
-      <c r="AP59" s="201"/>
-      <c r="AQ59" s="201"/>
-      <c r="AR59" s="201"/>
-      <c r="AS59" s="201"/>
-      <c r="AT59" s="201"/>
+      <c r="C59" s="293"/>
+      <c r="D59" s="293"/>
+      <c r="E59" s="293"/>
+      <c r="F59" s="293"/>
+      <c r="G59" s="293"/>
+      <c r="H59" s="293"/>
+      <c r="I59" s="293"/>
+      <c r="J59" s="293"/>
+      <c r="K59" s="293"/>
+      <c r="L59" s="293"/>
+      <c r="M59" s="293"/>
+      <c r="N59" s="293"/>
+      <c r="O59" s="293"/>
+      <c r="P59" s="293"/>
+      <c r="Q59" s="293"/>
+      <c r="R59" s="293"/>
+      <c r="S59" s="293"/>
+      <c r="T59" s="293"/>
+      <c r="U59" s="293"/>
+      <c r="V59" s="293"/>
+      <c r="W59" s="293"/>
+      <c r="X59" s="293"/>
+      <c r="Y59" s="293"/>
+      <c r="Z59" s="293"/>
+      <c r="AA59" s="293"/>
+      <c r="AB59" s="293"/>
+      <c r="AC59" s="293"/>
+      <c r="AD59" s="293"/>
+      <c r="AE59" s="293"/>
+      <c r="AF59" s="293"/>
+      <c r="AG59" s="293"/>
+      <c r="AH59" s="293"/>
+      <c r="AI59" s="293"/>
+      <c r="AJ59" s="293"/>
+      <c r="AK59" s="293"/>
+      <c r="AL59" s="293"/>
+      <c r="AM59" s="293"/>
+      <c r="AN59" s="293"/>
+      <c r="AO59" s="293"/>
+      <c r="AP59" s="293"/>
+      <c r="AQ59" s="293"/>
+      <c r="AR59" s="293"/>
+      <c r="AS59" s="293"/>
+      <c r="AT59" s="293"/>
     </row>
-    <row r="60" spans="1:60" ht="21.95" customHeight="1">
+    <row r="60" spans="1:60" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="143"/>
-      <c r="B60" s="201"/>
-      <c r="C60" s="201"/>
-      <c r="D60" s="201"/>
-      <c r="E60" s="201"/>
-      <c r="F60" s="201"/>
-      <c r="G60" s="201"/>
-      <c r="H60" s="201"/>
-      <c r="I60" s="201"/>
-      <c r="J60" s="201"/>
-      <c r="K60" s="201"/>
-      <c r="L60" s="201"/>
-      <c r="M60" s="201"/>
-      <c r="N60" s="201"/>
-      <c r="O60" s="201"/>
-      <c r="P60" s="201"/>
-      <c r="Q60" s="201"/>
-      <c r="R60" s="201"/>
-      <c r="S60" s="201"/>
-      <c r="T60" s="201"/>
-      <c r="U60" s="201"/>
-      <c r="V60" s="201"/>
-      <c r="W60" s="201"/>
-      <c r="X60" s="201"/>
-      <c r="Y60" s="201"/>
-      <c r="Z60" s="201"/>
-      <c r="AA60" s="201"/>
-      <c r="AB60" s="201"/>
-      <c r="AC60" s="201"/>
-      <c r="AD60" s="201"/>
-      <c r="AE60" s="201"/>
-      <c r="AF60" s="201"/>
-      <c r="AG60" s="201"/>
-      <c r="AH60" s="201"/>
-      <c r="AI60" s="201"/>
-      <c r="AJ60" s="201"/>
-      <c r="AK60" s="201"/>
-      <c r="AL60" s="201"/>
-      <c r="AM60" s="201"/>
-      <c r="AN60" s="201"/>
-      <c r="AO60" s="201"/>
-      <c r="AP60" s="201"/>
-      <c r="AQ60" s="201"/>
-      <c r="AR60" s="201"/>
-      <c r="AS60" s="201"/>
-      <c r="AT60" s="201"/>
+      <c r="B60" s="293"/>
+      <c r="C60" s="293"/>
+      <c r="D60" s="293"/>
+      <c r="E60" s="293"/>
+      <c r="F60" s="293"/>
+      <c r="G60" s="293"/>
+      <c r="H60" s="293"/>
+      <c r="I60" s="293"/>
+      <c r="J60" s="293"/>
+      <c r="K60" s="293"/>
+      <c r="L60" s="293"/>
+      <c r="M60" s="293"/>
+      <c r="N60" s="293"/>
+      <c r="O60" s="293"/>
+      <c r="P60" s="293"/>
+      <c r="Q60" s="293"/>
+      <c r="R60" s="293"/>
+      <c r="S60" s="293"/>
+      <c r="T60" s="293"/>
+      <c r="U60" s="293"/>
+      <c r="V60" s="293"/>
+      <c r="W60" s="293"/>
+      <c r="X60" s="293"/>
+      <c r="Y60" s="293"/>
+      <c r="Z60" s="293"/>
+      <c r="AA60" s="293"/>
+      <c r="AB60" s="293"/>
+      <c r="AC60" s="293"/>
+      <c r="AD60" s="293"/>
+      <c r="AE60" s="293"/>
+      <c r="AF60" s="293"/>
+      <c r="AG60" s="293"/>
+      <c r="AH60" s="293"/>
+      <c r="AI60" s="293"/>
+      <c r="AJ60" s="293"/>
+      <c r="AK60" s="293"/>
+      <c r="AL60" s="293"/>
+      <c r="AM60" s="293"/>
+      <c r="AN60" s="293"/>
+      <c r="AO60" s="293"/>
+      <c r="AP60" s="293"/>
+      <c r="AQ60" s="293"/>
+      <c r="AR60" s="293"/>
+      <c r="AS60" s="293"/>
+      <c r="AT60" s="293"/>
     </row>
-    <row r="61" spans="1:60" s="10" customFormat="1" ht="21.95" customHeight="1">
+    <row r="61" spans="1:60" s="10" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="143" t="s">
         <v>91</v>
       </c>
-      <c r="B61" s="193" t="s">
+      <c r="B61" s="284" t="s">
         <v>155</v>
       </c>
-      <c r="C61" s="193"/>
-      <c r="D61" s="193"/>
-      <c r="E61" s="193"/>
-      <c r="F61" s="193"/>
-      <c r="G61" s="193"/>
-      <c r="H61" s="193"/>
-      <c r="I61" s="193"/>
-      <c r="J61" s="193"/>
-      <c r="K61" s="193"/>
-      <c r="L61" s="193"/>
-      <c r="M61" s="193"/>
-      <c r="N61" s="193"/>
-      <c r="O61" s="193"/>
-      <c r="P61" s="193"/>
-      <c r="Q61" s="193"/>
-      <c r="R61" s="193"/>
-      <c r="S61" s="193"/>
-      <c r="T61" s="193"/>
-      <c r="U61" s="193"/>
-      <c r="V61" s="193"/>
-      <c r="W61" s="193"/>
-      <c r="X61" s="193"/>
-      <c r="Y61" s="193"/>
-      <c r="Z61" s="193"/>
-      <c r="AA61" s="193"/>
-      <c r="AB61" s="193"/>
-      <c r="AC61" s="193"/>
-      <c r="AD61" s="193"/>
-      <c r="AE61" s="193"/>
-      <c r="AF61" s="193"/>
-      <c r="AG61" s="193"/>
-      <c r="AH61" s="193"/>
-      <c r="AI61" s="193"/>
-      <c r="AJ61" s="193"/>
-      <c r="AK61" s="193"/>
-      <c r="AL61" s="193"/>
-      <c r="AM61" s="193"/>
-      <c r="AN61" s="193"/>
-      <c r="AO61" s="193"/>
-      <c r="AP61" s="193"/>
-      <c r="AQ61" s="193"/>
-      <c r="AR61" s="193"/>
-      <c r="AS61" s="193"/>
-      <c r="AT61" s="193"/>
+      <c r="C61" s="284"/>
+      <c r="D61" s="284"/>
+      <c r="E61" s="284"/>
+      <c r="F61" s="284"/>
+      <c r="G61" s="284"/>
+      <c r="H61" s="284"/>
+      <c r="I61" s="284"/>
+      <c r="J61" s="284"/>
+      <c r="K61" s="284"/>
+      <c r="L61" s="284"/>
+      <c r="M61" s="284"/>
+      <c r="N61" s="284"/>
+      <c r="O61" s="284"/>
+      <c r="P61" s="284"/>
+      <c r="Q61" s="284"/>
+      <c r="R61" s="284"/>
+      <c r="S61" s="284"/>
+      <c r="T61" s="284"/>
+      <c r="U61" s="284"/>
+      <c r="V61" s="284"/>
+      <c r="W61" s="284"/>
+      <c r="X61" s="284"/>
+      <c r="Y61" s="284"/>
+      <c r="Z61" s="284"/>
+      <c r="AA61" s="284"/>
+      <c r="AB61" s="284"/>
+      <c r="AC61" s="284"/>
+      <c r="AD61" s="284"/>
+      <c r="AE61" s="284"/>
+      <c r="AF61" s="284"/>
+      <c r="AG61" s="284"/>
+      <c r="AH61" s="284"/>
+      <c r="AI61" s="284"/>
+      <c r="AJ61" s="284"/>
+      <c r="AK61" s="284"/>
+      <c r="AL61" s="284"/>
+      <c r="AM61" s="284"/>
+      <c r="AN61" s="284"/>
+      <c r="AO61" s="284"/>
+      <c r="AP61" s="284"/>
+      <c r="AQ61" s="284"/>
+      <c r="AR61" s="284"/>
+      <c r="AS61" s="284"/>
+      <c r="AT61" s="284"/>
       <c r="BE61" s="1"/>
       <c r="BF61" s="1"/>
       <c r="BG61" s="1"/>
       <c r="BH61" s="1"/>
     </row>
-    <row r="62" spans="1:60" ht="21.95" customHeight="1">
+    <row r="62" spans="1:60" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="143" t="s">
         <v>92</v>
       </c>
@@ -8761,111 +8799,111 @@
       <c r="AS62" s="144"/>
       <c r="AT62" s="144"/>
     </row>
-    <row r="63" spans="1:60" ht="21.95" customHeight="1">
+    <row r="63" spans="1:60" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="143" t="s">
         <v>93</v>
       </c>
-      <c r="B63" s="192" t="s">
+      <c r="B63" s="285" t="s">
         <v>150</v>
       </c>
-      <c r="C63" s="192"/>
-      <c r="D63" s="192"/>
-      <c r="E63" s="192"/>
-      <c r="F63" s="192"/>
-      <c r="G63" s="192"/>
-      <c r="H63" s="192"/>
-      <c r="I63" s="192"/>
-      <c r="J63" s="192"/>
-      <c r="K63" s="192"/>
-      <c r="L63" s="192"/>
-      <c r="M63" s="192"/>
-      <c r="N63" s="192"/>
-      <c r="O63" s="192"/>
-      <c r="P63" s="192"/>
-      <c r="Q63" s="192"/>
-      <c r="R63" s="192"/>
-      <c r="S63" s="192"/>
-      <c r="T63" s="192"/>
-      <c r="U63" s="192"/>
-      <c r="V63" s="192"/>
-      <c r="W63" s="192"/>
-      <c r="X63" s="192"/>
-      <c r="Y63" s="192"/>
-      <c r="Z63" s="192"/>
-      <c r="AA63" s="192"/>
-      <c r="AB63" s="192"/>
-      <c r="AC63" s="192"/>
-      <c r="AD63" s="192"/>
-      <c r="AE63" s="192"/>
-      <c r="AF63" s="192"/>
-      <c r="AG63" s="192"/>
-      <c r="AH63" s="192"/>
-      <c r="AI63" s="192"/>
-      <c r="AJ63" s="192"/>
-      <c r="AK63" s="192"/>
-      <c r="AL63" s="192"/>
-      <c r="AM63" s="192"/>
-      <c r="AN63" s="192"/>
-      <c r="AO63" s="192"/>
-      <c r="AP63" s="192"/>
-      <c r="AQ63" s="192"/>
-      <c r="AR63" s="192"/>
-      <c r="AS63" s="192"/>
-      <c r="AT63" s="192"/>
+      <c r="C63" s="285"/>
+      <c r="D63" s="285"/>
+      <c r="E63" s="285"/>
+      <c r="F63" s="285"/>
+      <c r="G63" s="285"/>
+      <c r="H63" s="285"/>
+      <c r="I63" s="285"/>
+      <c r="J63" s="285"/>
+      <c r="K63" s="285"/>
+      <c r="L63" s="285"/>
+      <c r="M63" s="285"/>
+      <c r="N63" s="285"/>
+      <c r="O63" s="285"/>
+      <c r="P63" s="285"/>
+      <c r="Q63" s="285"/>
+      <c r="R63" s="285"/>
+      <c r="S63" s="285"/>
+      <c r="T63" s="285"/>
+      <c r="U63" s="285"/>
+      <c r="V63" s="285"/>
+      <c r="W63" s="285"/>
+      <c r="X63" s="285"/>
+      <c r="Y63" s="285"/>
+      <c r="Z63" s="285"/>
+      <c r="AA63" s="285"/>
+      <c r="AB63" s="285"/>
+      <c r="AC63" s="285"/>
+      <c r="AD63" s="285"/>
+      <c r="AE63" s="285"/>
+      <c r="AF63" s="285"/>
+      <c r="AG63" s="285"/>
+      <c r="AH63" s="285"/>
+      <c r="AI63" s="285"/>
+      <c r="AJ63" s="285"/>
+      <c r="AK63" s="285"/>
+      <c r="AL63" s="285"/>
+      <c r="AM63" s="285"/>
+      <c r="AN63" s="285"/>
+      <c r="AO63" s="285"/>
+      <c r="AP63" s="285"/>
+      <c r="AQ63" s="285"/>
+      <c r="AR63" s="285"/>
+      <c r="AS63" s="285"/>
+      <c r="AT63" s="285"/>
     </row>
-    <row r="64" spans="1:60" ht="21.95" customHeight="1">
+    <row r="64" spans="1:60" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="143" t="s">
         <v>124</v>
       </c>
-      <c r="B64" s="194" t="s">
+      <c r="B64" s="286" t="s">
         <v>151</v>
       </c>
-      <c r="C64" s="193"/>
-      <c r="D64" s="193"/>
-      <c r="E64" s="193"/>
-      <c r="F64" s="193"/>
-      <c r="G64" s="193"/>
-      <c r="H64" s="193"/>
-      <c r="I64" s="193"/>
-      <c r="J64" s="193"/>
-      <c r="K64" s="193"/>
-      <c r="L64" s="193"/>
-      <c r="M64" s="193"/>
-      <c r="N64" s="193"/>
-      <c r="O64" s="193"/>
-      <c r="P64" s="193"/>
-      <c r="Q64" s="193"/>
-      <c r="R64" s="193"/>
-      <c r="S64" s="193"/>
-      <c r="T64" s="193"/>
-      <c r="U64" s="193"/>
-      <c r="V64" s="193"/>
-      <c r="W64" s="193"/>
-      <c r="X64" s="193"/>
-      <c r="Y64" s="193"/>
-      <c r="Z64" s="193"/>
-      <c r="AA64" s="193"/>
-      <c r="AB64" s="193"/>
-      <c r="AC64" s="193"/>
-      <c r="AD64" s="193"/>
-      <c r="AE64" s="193"/>
-      <c r="AF64" s="193"/>
-      <c r="AG64" s="193"/>
-      <c r="AH64" s="193"/>
-      <c r="AI64" s="193"/>
-      <c r="AJ64" s="193"/>
-      <c r="AK64" s="193"/>
-      <c r="AL64" s="193"/>
-      <c r="AM64" s="193"/>
-      <c r="AN64" s="193"/>
-      <c r="AO64" s="193"/>
-      <c r="AP64" s="193"/>
-      <c r="AQ64" s="193"/>
-      <c r="AR64" s="193"/>
-      <c r="AS64" s="193"/>
-      <c r="AT64" s="193"/>
+      <c r="C64" s="284"/>
+      <c r="D64" s="284"/>
+      <c r="E64" s="284"/>
+      <c r="F64" s="284"/>
+      <c r="G64" s="284"/>
+      <c r="H64" s="284"/>
+      <c r="I64" s="284"/>
+      <c r="J64" s="284"/>
+      <c r="K64" s="284"/>
+      <c r="L64" s="284"/>
+      <c r="M64" s="284"/>
+      <c r="N64" s="284"/>
+      <c r="O64" s="284"/>
+      <c r="P64" s="284"/>
+      <c r="Q64" s="284"/>
+      <c r="R64" s="284"/>
+      <c r="S64" s="284"/>
+      <c r="T64" s="284"/>
+      <c r="U64" s="284"/>
+      <c r="V64" s="284"/>
+      <c r="W64" s="284"/>
+      <c r="X64" s="284"/>
+      <c r="Y64" s="284"/>
+      <c r="Z64" s="284"/>
+      <c r="AA64" s="284"/>
+      <c r="AB64" s="284"/>
+      <c r="AC64" s="284"/>
+      <c r="AD64" s="284"/>
+      <c r="AE64" s="284"/>
+      <c r="AF64" s="284"/>
+      <c r="AG64" s="284"/>
+      <c r="AH64" s="284"/>
+      <c r="AI64" s="284"/>
+      <c r="AJ64" s="284"/>
+      <c r="AK64" s="284"/>
+      <c r="AL64" s="284"/>
+      <c r="AM64" s="284"/>
+      <c r="AN64" s="284"/>
+      <c r="AO64" s="284"/>
+      <c r="AP64" s="284"/>
+      <c r="AQ64" s="284"/>
+      <c r="AR64" s="284"/>
+      <c r="AS64" s="284"/>
+      <c r="AT64" s="284"/>
     </row>
-    <row r="65" spans="1:262" ht="21.95" customHeight="1">
+    <row r="65" spans="1:262" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="143" t="s">
         <v>128</v>
       </c>
@@ -8917,211 +8955,211 @@
       <c r="AS65" s="144"/>
       <c r="AT65" s="144"/>
     </row>
-    <row r="66" spans="1:262" ht="21.95" customHeight="1">
+    <row r="66" spans="1:262" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="144">
         <v>10</v>
       </c>
-      <c r="B66" s="192" t="s">
+      <c r="B66" s="285" t="s">
         <v>152</v>
       </c>
-      <c r="C66" s="192"/>
-      <c r="D66" s="192"/>
-      <c r="E66" s="192"/>
-      <c r="F66" s="192"/>
-      <c r="G66" s="192"/>
-      <c r="H66" s="192"/>
-      <c r="I66" s="192"/>
-      <c r="J66" s="192"/>
-      <c r="K66" s="192"/>
-      <c r="L66" s="192"/>
-      <c r="M66" s="192"/>
-      <c r="N66" s="192"/>
-      <c r="O66" s="192"/>
-      <c r="P66" s="192"/>
-      <c r="Q66" s="192"/>
-      <c r="R66" s="192"/>
-      <c r="S66" s="192"/>
-      <c r="T66" s="192"/>
-      <c r="U66" s="192"/>
-      <c r="V66" s="192"/>
-      <c r="W66" s="192"/>
-      <c r="X66" s="192"/>
-      <c r="Y66" s="192"/>
-      <c r="Z66" s="192"/>
-      <c r="AA66" s="192"/>
-      <c r="AB66" s="192"/>
-      <c r="AC66" s="192"/>
-      <c r="AD66" s="192"/>
-      <c r="AE66" s="192"/>
-      <c r="AF66" s="192"/>
-      <c r="AG66" s="192"/>
-      <c r="AH66" s="192"/>
-      <c r="AI66" s="192"/>
-      <c r="AJ66" s="192"/>
-      <c r="AK66" s="192"/>
-      <c r="AL66" s="192"/>
-      <c r="AM66" s="192"/>
-      <c r="AN66" s="192"/>
-      <c r="AO66" s="192"/>
-      <c r="AP66" s="192"/>
-      <c r="AQ66" s="192"/>
-      <c r="AR66" s="192"/>
-      <c r="AS66" s="192"/>
-      <c r="AT66" s="192"/>
+      <c r="C66" s="285"/>
+      <c r="D66" s="285"/>
+      <c r="E66" s="285"/>
+      <c r="F66" s="285"/>
+      <c r="G66" s="285"/>
+      <c r="H66" s="285"/>
+      <c r="I66" s="285"/>
+      <c r="J66" s="285"/>
+      <c r="K66" s="285"/>
+      <c r="L66" s="285"/>
+      <c r="M66" s="285"/>
+      <c r="N66" s="285"/>
+      <c r="O66" s="285"/>
+      <c r="P66" s="285"/>
+      <c r="Q66" s="285"/>
+      <c r="R66" s="285"/>
+      <c r="S66" s="285"/>
+      <c r="T66" s="285"/>
+      <c r="U66" s="285"/>
+      <c r="V66" s="285"/>
+      <c r="W66" s="285"/>
+      <c r="X66" s="285"/>
+      <c r="Y66" s="285"/>
+      <c r="Z66" s="285"/>
+      <c r="AA66" s="285"/>
+      <c r="AB66" s="285"/>
+      <c r="AC66" s="285"/>
+      <c r="AD66" s="285"/>
+      <c r="AE66" s="285"/>
+      <c r="AF66" s="285"/>
+      <c r="AG66" s="285"/>
+      <c r="AH66" s="285"/>
+      <c r="AI66" s="285"/>
+      <c r="AJ66" s="285"/>
+      <c r="AK66" s="285"/>
+      <c r="AL66" s="285"/>
+      <c r="AM66" s="285"/>
+      <c r="AN66" s="285"/>
+      <c r="AO66" s="285"/>
+      <c r="AP66" s="285"/>
+      <c r="AQ66" s="285"/>
+      <c r="AR66" s="285"/>
+      <c r="AS66" s="285"/>
+      <c r="AT66" s="285"/>
     </row>
-    <row r="67" spans="1:262" ht="29.25" customHeight="1">
+    <row r="67" spans="1:262" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="144"/>
-      <c r="B67" s="177" t="s">
+      <c r="B67" s="294" t="s">
         <v>153</v>
       </c>
-      <c r="C67" s="177"/>
-      <c r="D67" s="177"/>
-      <c r="E67" s="177"/>
-      <c r="F67" s="177"/>
-      <c r="G67" s="177"/>
-      <c r="H67" s="177"/>
-      <c r="I67" s="177"/>
-      <c r="J67" s="177"/>
-      <c r="K67" s="177"/>
-      <c r="L67" s="177"/>
-      <c r="M67" s="177"/>
-      <c r="N67" s="177"/>
-      <c r="O67" s="177"/>
-      <c r="P67" s="177"/>
-      <c r="Q67" s="177"/>
-      <c r="R67" s="177"/>
-      <c r="S67" s="177"/>
-      <c r="T67" s="177"/>
-      <c r="U67" s="177"/>
-      <c r="V67" s="177"/>
-      <c r="W67" s="177"/>
-      <c r="X67" s="177"/>
-      <c r="Y67" s="177"/>
-      <c r="Z67" s="177"/>
-      <c r="AA67" s="177"/>
-      <c r="AB67" s="177"/>
-      <c r="AC67" s="177"/>
-      <c r="AD67" s="177"/>
-      <c r="AE67" s="177"/>
-      <c r="AF67" s="177"/>
-      <c r="AG67" s="177"/>
-      <c r="AH67" s="177"/>
-      <c r="AI67" s="177"/>
-      <c r="AJ67" s="177"/>
-      <c r="AK67" s="177"/>
-      <c r="AL67" s="177"/>
-      <c r="AM67" s="177"/>
-      <c r="AN67" s="177"/>
-      <c r="AO67" s="177"/>
-      <c r="AP67" s="177"/>
-      <c r="AQ67" s="177"/>
-      <c r="AR67" s="177"/>
-      <c r="AS67" s="177"/>
-      <c r="AT67" s="177"/>
+      <c r="C67" s="294"/>
+      <c r="D67" s="294"/>
+      <c r="E67" s="294"/>
+      <c r="F67" s="294"/>
+      <c r="G67" s="294"/>
+      <c r="H67" s="294"/>
+      <c r="I67" s="294"/>
+      <c r="J67" s="294"/>
+      <c r="K67" s="294"/>
+      <c r="L67" s="294"/>
+      <c r="M67" s="294"/>
+      <c r="N67" s="294"/>
+      <c r="O67" s="294"/>
+      <c r="P67" s="294"/>
+      <c r="Q67" s="294"/>
+      <c r="R67" s="294"/>
+      <c r="S67" s="294"/>
+      <c r="T67" s="294"/>
+      <c r="U67" s="294"/>
+      <c r="V67" s="294"/>
+      <c r="W67" s="294"/>
+      <c r="X67" s="294"/>
+      <c r="Y67" s="294"/>
+      <c r="Z67" s="294"/>
+      <c r="AA67" s="294"/>
+      <c r="AB67" s="294"/>
+      <c r="AC67" s="294"/>
+      <c r="AD67" s="294"/>
+      <c r="AE67" s="294"/>
+      <c r="AF67" s="294"/>
+      <c r="AG67" s="294"/>
+      <c r="AH67" s="294"/>
+      <c r="AI67" s="294"/>
+      <c r="AJ67" s="294"/>
+      <c r="AK67" s="294"/>
+      <c r="AL67" s="294"/>
+      <c r="AM67" s="294"/>
+      <c r="AN67" s="294"/>
+      <c r="AO67" s="294"/>
+      <c r="AP67" s="294"/>
+      <c r="AQ67" s="294"/>
+      <c r="AR67" s="294"/>
+      <c r="AS67" s="294"/>
+      <c r="AT67" s="294"/>
     </row>
-    <row r="68" spans="1:262" ht="21.75" customHeight="1">
+    <row r="68" spans="1:262" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="144"/>
-      <c r="B68" s="177" t="s">
+      <c r="B68" s="294" t="s">
         <v>154</v>
       </c>
-      <c r="C68" s="177"/>
-      <c r="D68" s="177"/>
-      <c r="E68" s="177"/>
-      <c r="F68" s="177"/>
-      <c r="G68" s="177"/>
-      <c r="H68" s="177"/>
-      <c r="I68" s="177"/>
-      <c r="J68" s="177"/>
-      <c r="K68" s="177"/>
-      <c r="L68" s="177"/>
-      <c r="M68" s="177"/>
-      <c r="N68" s="177"/>
-      <c r="O68" s="177"/>
-      <c r="P68" s="177"/>
-      <c r="Q68" s="177"/>
-      <c r="R68" s="177"/>
-      <c r="S68" s="177"/>
-      <c r="T68" s="177"/>
-      <c r="U68" s="177"/>
-      <c r="V68" s="177"/>
-      <c r="W68" s="177"/>
-      <c r="X68" s="177"/>
-      <c r="Y68" s="177"/>
-      <c r="Z68" s="177"/>
-      <c r="AA68" s="177"/>
-      <c r="AB68" s="177"/>
-      <c r="AC68" s="177"/>
-      <c r="AD68" s="177"/>
-      <c r="AE68" s="177"/>
-      <c r="AF68" s="177"/>
-      <c r="AG68" s="177"/>
-      <c r="AH68" s="177"/>
-      <c r="AI68" s="177"/>
-      <c r="AJ68" s="177"/>
-      <c r="AK68" s="177"/>
-      <c r="AL68" s="177"/>
-      <c r="AM68" s="177"/>
-      <c r="AN68" s="177"/>
-      <c r="AO68" s="177"/>
-      <c r="AP68" s="177"/>
-      <c r="AQ68" s="177"/>
-      <c r="AR68" s="177"/>
-      <c r="AS68" s="177"/>
-      <c r="AT68" s="177"/>
+      <c r="C68" s="294"/>
+      <c r="D68" s="294"/>
+      <c r="E68" s="294"/>
+      <c r="F68" s="294"/>
+      <c r="G68" s="294"/>
+      <c r="H68" s="294"/>
+      <c r="I68" s="294"/>
+      <c r="J68" s="294"/>
+      <c r="K68" s="294"/>
+      <c r="L68" s="294"/>
+      <c r="M68" s="294"/>
+      <c r="N68" s="294"/>
+      <c r="O68" s="294"/>
+      <c r="P68" s="294"/>
+      <c r="Q68" s="294"/>
+      <c r="R68" s="294"/>
+      <c r="S68" s="294"/>
+      <c r="T68" s="294"/>
+      <c r="U68" s="294"/>
+      <c r="V68" s="294"/>
+      <c r="W68" s="294"/>
+      <c r="X68" s="294"/>
+      <c r="Y68" s="294"/>
+      <c r="Z68" s="294"/>
+      <c r="AA68" s="294"/>
+      <c r="AB68" s="294"/>
+      <c r="AC68" s="294"/>
+      <c r="AD68" s="294"/>
+      <c r="AE68" s="294"/>
+      <c r="AF68" s="294"/>
+      <c r="AG68" s="294"/>
+      <c r="AH68" s="294"/>
+      <c r="AI68" s="294"/>
+      <c r="AJ68" s="294"/>
+      <c r="AK68" s="294"/>
+      <c r="AL68" s="294"/>
+      <c r="AM68" s="294"/>
+      <c r="AN68" s="294"/>
+      <c r="AO68" s="294"/>
+      <c r="AP68" s="294"/>
+      <c r="AQ68" s="294"/>
+      <c r="AR68" s="294"/>
+      <c r="AS68" s="294"/>
+      <c r="AT68" s="294"/>
     </row>
-    <row r="69" spans="1:262" ht="21.95" customHeight="1">
+    <row r="69" spans="1:262" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="144">
         <v>11</v>
       </c>
-      <c r="B69" s="177" t="s">
+      <c r="B69" s="294" t="s">
         <v>159</v>
       </c>
-      <c r="C69" s="177"/>
-      <c r="D69" s="177"/>
-      <c r="E69" s="177"/>
-      <c r="F69" s="177"/>
-      <c r="G69" s="177"/>
-      <c r="H69" s="177"/>
-      <c r="I69" s="177"/>
-      <c r="J69" s="177"/>
-      <c r="K69" s="177"/>
-      <c r="L69" s="177"/>
-      <c r="M69" s="177"/>
-      <c r="N69" s="177"/>
-      <c r="O69" s="177"/>
-      <c r="P69" s="177"/>
-      <c r="Q69" s="177"/>
-      <c r="R69" s="177"/>
-      <c r="S69" s="177"/>
-      <c r="T69" s="177"/>
-      <c r="U69" s="177"/>
-      <c r="V69" s="177"/>
-      <c r="W69" s="177"/>
-      <c r="X69" s="177"/>
-      <c r="Y69" s="177"/>
-      <c r="Z69" s="177"/>
-      <c r="AA69" s="177"/>
-      <c r="AB69" s="177"/>
-      <c r="AC69" s="177"/>
-      <c r="AD69" s="177"/>
-      <c r="AE69" s="177"/>
-      <c r="AF69" s="177"/>
-      <c r="AG69" s="177"/>
-      <c r="AH69" s="177"/>
-      <c r="AI69" s="177"/>
-      <c r="AJ69" s="177"/>
-      <c r="AK69" s="177"/>
-      <c r="AL69" s="177"/>
-      <c r="AM69" s="177"/>
-      <c r="AN69" s="177"/>
-      <c r="AO69" s="177"/>
-      <c r="AP69" s="177"/>
-      <c r="AQ69" s="177"/>
-      <c r="AR69" s="177"/>
-      <c r="AS69" s="177"/>
-      <c r="AT69" s="177"/>
+      <c r="C69" s="294"/>
+      <c r="D69" s="294"/>
+      <c r="E69" s="294"/>
+      <c r="F69" s="294"/>
+      <c r="G69" s="294"/>
+      <c r="H69" s="294"/>
+      <c r="I69" s="294"/>
+      <c r="J69" s="294"/>
+      <c r="K69" s="294"/>
+      <c r="L69" s="294"/>
+      <c r="M69" s="294"/>
+      <c r="N69" s="294"/>
+      <c r="O69" s="294"/>
+      <c r="P69" s="294"/>
+      <c r="Q69" s="294"/>
+      <c r="R69" s="294"/>
+      <c r="S69" s="294"/>
+      <c r="T69" s="294"/>
+      <c r="U69" s="294"/>
+      <c r="V69" s="294"/>
+      <c r="W69" s="294"/>
+      <c r="X69" s="294"/>
+      <c r="Y69" s="294"/>
+      <c r="Z69" s="294"/>
+      <c r="AA69" s="294"/>
+      <c r="AB69" s="294"/>
+      <c r="AC69" s="294"/>
+      <c r="AD69" s="294"/>
+      <c r="AE69" s="294"/>
+      <c r="AF69" s="294"/>
+      <c r="AG69" s="294"/>
+      <c r="AH69" s="294"/>
+      <c r="AI69" s="294"/>
+      <c r="AJ69" s="294"/>
+      <c r="AK69" s="294"/>
+      <c r="AL69" s="294"/>
+      <c r="AM69" s="294"/>
+      <c r="AN69" s="294"/>
+      <c r="AO69" s="294"/>
+      <c r="AP69" s="294"/>
+      <c r="AQ69" s="294"/>
+      <c r="AR69" s="294"/>
+      <c r="AS69" s="294"/>
+      <c r="AT69" s="294"/>
     </row>
-    <row r="70" spans="1:262" ht="16.5" customHeight="1">
+    <row r="70" spans="1:262" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="143"/>
       <c r="B70" s="144" t="s">
         <v>126</v>
@@ -9171,7 +9209,7 @@
       <c r="AS70" s="144"/>
       <c r="AT70" s="144"/>
     </row>
-    <row r="71" spans="1:262" ht="16.5" customHeight="1">
+    <row r="71" spans="1:262" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="143"/>
       <c r="B71" s="144" t="s">
         <v>127</v>
@@ -9221,7 +9259,7 @@
       <c r="AS71" s="144"/>
       <c r="AT71" s="144"/>
     </row>
-    <row r="72" spans="1:262" ht="16.5" customHeight="1">
+    <row r="72" spans="1:262" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="143"/>
       <c r="B72" s="144" t="s">
         <v>131</v>
@@ -9271,7 +9309,7 @@
       <c r="AS72" s="144"/>
       <c r="AT72" s="144"/>
     </row>
-    <row r="73" spans="1:262" ht="16.5" customHeight="1">
+    <row r="73" spans="1:262" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="143"/>
       <c r="B73" s="144" t="s">
         <v>132</v>
@@ -9321,7 +9359,7 @@
       <c r="AS73" s="144"/>
       <c r="AT73" s="144"/>
     </row>
-    <row r="74" spans="1:262" ht="16.5" customHeight="1">
+    <row r="74" spans="1:262" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="143"/>
       <c r="B74" s="144"/>
       <c r="C74" s="144"/>
@@ -9369,7 +9407,7 @@
       <c r="AS74" s="144"/>
       <c r="AT74" s="144"/>
     </row>
-    <row r="75" spans="1:262" ht="21.95" customHeight="1">
+    <row r="75" spans="1:262" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="144">
         <v>12</v>
       </c>
@@ -9421,63 +9459,63 @@
       <c r="AS75" s="146"/>
       <c r="AT75" s="146"/>
     </row>
-    <row r="76" spans="1:262" ht="60.75" customHeight="1">
+    <row r="76" spans="1:262" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="144">
         <v>13</v>
       </c>
-      <c r="B76" s="177" t="s">
+      <c r="B76" s="294" t="s">
         <v>156</v>
       </c>
-      <c r="C76" s="177"/>
-      <c r="D76" s="177"/>
-      <c r="E76" s="177"/>
-      <c r="F76" s="177"/>
-      <c r="G76" s="177"/>
-      <c r="H76" s="177"/>
-      <c r="I76" s="177"/>
-      <c r="J76" s="177"/>
-      <c r="K76" s="177"/>
-      <c r="L76" s="177"/>
-      <c r="M76" s="177"/>
-      <c r="N76" s="177"/>
-      <c r="O76" s="177"/>
-      <c r="P76" s="177"/>
-      <c r="Q76" s="177"/>
-      <c r="R76" s="177"/>
-      <c r="S76" s="177"/>
-      <c r="T76" s="177"/>
-      <c r="U76" s="177"/>
-      <c r="V76" s="177"/>
-      <c r="W76" s="177"/>
-      <c r="X76" s="177"/>
-      <c r="Y76" s="177"/>
-      <c r="Z76" s="177"/>
-      <c r="AA76" s="177"/>
-      <c r="AB76" s="177"/>
-      <c r="AC76" s="177"/>
-      <c r="AD76" s="177"/>
-      <c r="AE76" s="177"/>
-      <c r="AF76" s="177"/>
-      <c r="AG76" s="177"/>
-      <c r="AH76" s="177"/>
-      <c r="AI76" s="177"/>
-      <c r="AJ76" s="177"/>
-      <c r="AK76" s="177"/>
-      <c r="AL76" s="177"/>
-      <c r="AM76" s="177"/>
-      <c r="AN76" s="177"/>
-      <c r="AO76" s="177"/>
-      <c r="AP76" s="177"/>
-      <c r="AQ76" s="177"/>
-      <c r="AR76" s="177"/>
-      <c r="AS76" s="177"/>
-      <c r="AT76" s="177"/>
+      <c r="C76" s="294"/>
+      <c r="D76" s="294"/>
+      <c r="E76" s="294"/>
+      <c r="F76" s="294"/>
+      <c r="G76" s="294"/>
+      <c r="H76" s="294"/>
+      <c r="I76" s="294"/>
+      <c r="J76" s="294"/>
+      <c r="K76" s="294"/>
+      <c r="L76" s="294"/>
+      <c r="M76" s="294"/>
+      <c r="N76" s="294"/>
+      <c r="O76" s="294"/>
+      <c r="P76" s="294"/>
+      <c r="Q76" s="294"/>
+      <c r="R76" s="294"/>
+      <c r="S76" s="294"/>
+      <c r="T76" s="294"/>
+      <c r="U76" s="294"/>
+      <c r="V76" s="294"/>
+      <c r="W76" s="294"/>
+      <c r="X76" s="294"/>
+      <c r="Y76" s="294"/>
+      <c r="Z76" s="294"/>
+      <c r="AA76" s="294"/>
+      <c r="AB76" s="294"/>
+      <c r="AC76" s="294"/>
+      <c r="AD76" s="294"/>
+      <c r="AE76" s="294"/>
+      <c r="AF76" s="294"/>
+      <c r="AG76" s="294"/>
+      <c r="AH76" s="294"/>
+      <c r="AI76" s="294"/>
+      <c r="AJ76" s="294"/>
+      <c r="AK76" s="294"/>
+      <c r="AL76" s="294"/>
+      <c r="AM76" s="294"/>
+      <c r="AN76" s="294"/>
+      <c r="AO76" s="294"/>
+      <c r="AP76" s="294"/>
+      <c r="AQ76" s="294"/>
+      <c r="AR76" s="294"/>
+      <c r="AS76" s="294"/>
+      <c r="AT76" s="294"/>
       <c r="BE76" s="9"/>
       <c r="BF76" s="9"/>
       <c r="BG76" s="5"/>
       <c r="BH76" s="5"/>
     </row>
-    <row r="77" spans="1:262" ht="20.25" customHeight="1">
+    <row r="77" spans="1:262" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AU77" s="5"/>
       <c r="AV77" s="5"/>
       <c r="AW77" s="5"/>
@@ -9695,7 +9733,7 @@
       <c r="JA77" s="5"/>
       <c r="JB77" s="5"/>
     </row>
-    <row r="78" spans="1:262" ht="24" customHeight="1" thickBot="1">
+    <row r="78" spans="1:262" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
       <c r="C78" s="147" t="s">
@@ -9957,59 +9995,59 @@
       <c r="JA78" s="5"/>
       <c r="JB78" s="5"/>
     </row>
-    <row r="79" spans="1:262" ht="24" customHeight="1">
+    <row r="79" spans="1:262" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
-      <c r="C79" s="178" t="s">
+      <c r="C79" s="295" t="s">
         <v>95</v>
       </c>
-      <c r="D79" s="179"/>
-      <c r="E79" s="179"/>
-      <c r="F79" s="179"/>
-      <c r="G79" s="179"/>
-      <c r="H79" s="179"/>
-      <c r="I79" s="179"/>
-      <c r="J79" s="179"/>
-      <c r="K79" s="179"/>
-      <c r="L79" s="179"/>
-      <c r="M79" s="179"/>
-      <c r="N79" s="179"/>
-      <c r="O79" s="179"/>
-      <c r="P79" s="179" t="s">
+      <c r="D79" s="296"/>
+      <c r="E79" s="296"/>
+      <c r="F79" s="296"/>
+      <c r="G79" s="296"/>
+      <c r="H79" s="296"/>
+      <c r="I79" s="296"/>
+      <c r="J79" s="296"/>
+      <c r="K79" s="296"/>
+      <c r="L79" s="296"/>
+      <c r="M79" s="296"/>
+      <c r="N79" s="296"/>
+      <c r="O79" s="296"/>
+      <c r="P79" s="296" t="s">
         <v>96</v>
       </c>
-      <c r="Q79" s="179"/>
-      <c r="R79" s="179"/>
-      <c r="S79" s="179"/>
-      <c r="T79" s="182"/>
-      <c r="U79" s="185" t="s">
+      <c r="Q79" s="296"/>
+      <c r="R79" s="296"/>
+      <c r="S79" s="296"/>
+      <c r="T79" s="299"/>
+      <c r="U79" s="302" t="s">
         <v>97</v>
       </c>
-      <c r="V79" s="185"/>
-      <c r="W79" s="185"/>
-      <c r="X79" s="185"/>
-      <c r="Y79" s="185"/>
-      <c r="Z79" s="185"/>
-      <c r="AA79" s="185"/>
-      <c r="AB79" s="186"/>
-      <c r="AC79" s="186"/>
-      <c r="AD79" s="186"/>
-      <c r="AE79" s="186"/>
-      <c r="AF79" s="186"/>
-      <c r="AG79" s="186"/>
-      <c r="AH79" s="186"/>
-      <c r="AI79" s="185" t="s">
+      <c r="V79" s="302"/>
+      <c r="W79" s="302"/>
+      <c r="X79" s="302"/>
+      <c r="Y79" s="302"/>
+      <c r="Z79" s="302"/>
+      <c r="AA79" s="302"/>
+      <c r="AB79" s="303"/>
+      <c r="AC79" s="303"/>
+      <c r="AD79" s="303"/>
+      <c r="AE79" s="303"/>
+      <c r="AF79" s="303"/>
+      <c r="AG79" s="303"/>
+      <c r="AH79" s="303"/>
+      <c r="AI79" s="302" t="s">
         <v>98</v>
       </c>
-      <c r="AJ79" s="185"/>
-      <c r="AK79" s="185"/>
-      <c r="AL79" s="185"/>
-      <c r="AM79" s="185"/>
-      <c r="AN79" s="185"/>
-      <c r="AO79" s="185"/>
-      <c r="AP79" s="185"/>
-      <c r="AQ79" s="185"/>
-      <c r="AR79" s="187"/>
+      <c r="AJ79" s="302"/>
+      <c r="AK79" s="302"/>
+      <c r="AL79" s="302"/>
+      <c r="AM79" s="302"/>
+      <c r="AN79" s="302"/>
+      <c r="AO79" s="302"/>
+      <c r="AP79" s="302"/>
+      <c r="AQ79" s="302"/>
+      <c r="AR79" s="304"/>
       <c r="AS79" s="5"/>
       <c r="AT79" s="5"/>
       <c r="AU79" s="5"/>
@@ -10225,55 +10263,55 @@
       <c r="JA79" s="5"/>
       <c r="JB79" s="5"/>
     </row>
-    <row r="80" spans="1:262" ht="24" customHeight="1">
+    <row r="80" spans="1:262" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
-      <c r="C80" s="180"/>
-      <c r="D80" s="181"/>
-      <c r="E80" s="181"/>
-      <c r="F80" s="181"/>
-      <c r="G80" s="181"/>
-      <c r="H80" s="181"/>
-      <c r="I80" s="181"/>
-      <c r="J80" s="181"/>
-      <c r="K80" s="181"/>
-      <c r="L80" s="181"/>
-      <c r="M80" s="181"/>
-      <c r="N80" s="181"/>
-      <c r="O80" s="181"/>
-      <c r="P80" s="183"/>
-      <c r="Q80" s="183"/>
-      <c r="R80" s="183"/>
-      <c r="S80" s="183"/>
-      <c r="T80" s="184"/>
-      <c r="U80" s="189" t="s">
+      <c r="C80" s="297"/>
+      <c r="D80" s="298"/>
+      <c r="E80" s="298"/>
+      <c r="F80" s="298"/>
+      <c r="G80" s="298"/>
+      <c r="H80" s="298"/>
+      <c r="I80" s="298"/>
+      <c r="J80" s="298"/>
+      <c r="K80" s="298"/>
+      <c r="L80" s="298"/>
+      <c r="M80" s="298"/>
+      <c r="N80" s="298"/>
+      <c r="O80" s="298"/>
+      <c r="P80" s="300"/>
+      <c r="Q80" s="300"/>
+      <c r="R80" s="300"/>
+      <c r="S80" s="300"/>
+      <c r="T80" s="301"/>
+      <c r="U80" s="306" t="s">
         <v>99</v>
       </c>
-      <c r="V80" s="189"/>
-      <c r="W80" s="189"/>
-      <c r="X80" s="189"/>
-      <c r="Y80" s="189"/>
-      <c r="Z80" s="189"/>
-      <c r="AA80" s="191"/>
-      <c r="AB80" s="189" t="s">
+      <c r="V80" s="306"/>
+      <c r="W80" s="306"/>
+      <c r="X80" s="306"/>
+      <c r="Y80" s="306"/>
+      <c r="Z80" s="306"/>
+      <c r="AA80" s="308"/>
+      <c r="AB80" s="306" t="s">
         <v>100</v>
       </c>
-      <c r="AC80" s="189"/>
-      <c r="AD80" s="189"/>
-      <c r="AE80" s="189"/>
-      <c r="AF80" s="189"/>
-      <c r="AG80" s="189"/>
-      <c r="AH80" s="189"/>
-      <c r="AI80" s="188"/>
-      <c r="AJ80" s="189"/>
-      <c r="AK80" s="189"/>
-      <c r="AL80" s="189"/>
-      <c r="AM80" s="189"/>
-      <c r="AN80" s="189"/>
-      <c r="AO80" s="189"/>
-      <c r="AP80" s="189"/>
-      <c r="AQ80" s="189"/>
-      <c r="AR80" s="190"/>
+      <c r="AC80" s="306"/>
+      <c r="AD80" s="306"/>
+      <c r="AE80" s="306"/>
+      <c r="AF80" s="306"/>
+      <c r="AG80" s="306"/>
+      <c r="AH80" s="306"/>
+      <c r="AI80" s="305"/>
+      <c r="AJ80" s="306"/>
+      <c r="AK80" s="306"/>
+      <c r="AL80" s="306"/>
+      <c r="AM80" s="306"/>
+      <c r="AN80" s="306"/>
+      <c r="AO80" s="306"/>
+      <c r="AP80" s="306"/>
+      <c r="AQ80" s="306"/>
+      <c r="AR80" s="307"/>
       <c r="AS80" s="5"/>
       <c r="AT80" s="5"/>
       <c r="AU80" s="5"/>
@@ -10489,61 +10527,61 @@
       <c r="JA80" s="5"/>
       <c r="JB80" s="5"/>
     </row>
-    <row r="81" spans="1:262" ht="23.25" customHeight="1">
+    <row r="81" spans="1:262" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="5"/>
       <c r="B81" s="5"/>
-      <c r="C81" s="160" t="s">
+      <c r="C81" s="309" t="s">
         <v>3</v>
       </c>
-      <c r="D81" s="158"/>
-      <c r="E81" s="158"/>
-      <c r="F81" s="158"/>
-      <c r="G81" s="158"/>
-      <c r="H81" s="158"/>
-      <c r="I81" s="158"/>
-      <c r="J81" s="158"/>
-      <c r="K81" s="158"/>
-      <c r="L81" s="158"/>
-      <c r="M81" s="158"/>
-      <c r="N81" s="158"/>
-      <c r="O81" s="159"/>
-      <c r="P81" s="158" t="s">
+      <c r="D81" s="310"/>
+      <c r="E81" s="310"/>
+      <c r="F81" s="310"/>
+      <c r="G81" s="310"/>
+      <c r="H81" s="310"/>
+      <c r="I81" s="310"/>
+      <c r="J81" s="310"/>
+      <c r="K81" s="310"/>
+      <c r="L81" s="310"/>
+      <c r="M81" s="310"/>
+      <c r="N81" s="310"/>
+      <c r="O81" s="311"/>
+      <c r="P81" s="310" t="s">
         <v>101</v>
       </c>
-      <c r="Q81" s="158"/>
-      <c r="R81" s="158"/>
-      <c r="S81" s="158"/>
-      <c r="T81" s="158"/>
-      <c r="U81" s="166">
+      <c r="Q81" s="310"/>
+      <c r="R81" s="310"/>
+      <c r="S81" s="310"/>
+      <c r="T81" s="310"/>
+      <c r="U81" s="312">
         <v>0.6</v>
       </c>
-      <c r="V81" s="163"/>
-      <c r="W81" s="163"/>
-      <c r="X81" s="163"/>
-      <c r="Y81" s="163"/>
-      <c r="Z81" s="163"/>
-      <c r="AA81" s="163"/>
-      <c r="AB81" s="167">
+      <c r="V81" s="313"/>
+      <c r="W81" s="313"/>
+      <c r="X81" s="313"/>
+      <c r="Y81" s="313"/>
+      <c r="Z81" s="313"/>
+      <c r="AA81" s="313"/>
+      <c r="AB81" s="314">
         <v>0.15</v>
       </c>
-      <c r="AC81" s="167"/>
-      <c r="AD81" s="167"/>
-      <c r="AE81" s="167"/>
-      <c r="AF81" s="167"/>
-      <c r="AG81" s="167"/>
-      <c r="AH81" s="167"/>
-      <c r="AI81" s="152" t="s">
+      <c r="AC81" s="314"/>
+      <c r="AD81" s="314"/>
+      <c r="AE81" s="314"/>
+      <c r="AF81" s="314"/>
+      <c r="AG81" s="314"/>
+      <c r="AH81" s="314"/>
+      <c r="AI81" s="315" t="s">
         <v>102</v>
       </c>
-      <c r="AJ81" s="153"/>
-      <c r="AK81" s="153"/>
-      <c r="AL81" s="153"/>
-      <c r="AM81" s="153"/>
-      <c r="AN81" s="153"/>
-      <c r="AO81" s="153"/>
-      <c r="AP81" s="153"/>
-      <c r="AQ81" s="153"/>
-      <c r="AR81" s="168"/>
+      <c r="AJ81" s="316"/>
+      <c r="AK81" s="316"/>
+      <c r="AL81" s="316"/>
+      <c r="AM81" s="316"/>
+      <c r="AN81" s="316"/>
+      <c r="AO81" s="316"/>
+      <c r="AP81" s="316"/>
+      <c r="AQ81" s="316"/>
+      <c r="AR81" s="317"/>
       <c r="AS81" s="5"/>
       <c r="AT81" s="5"/>
       <c r="AU81" s="5"/>
@@ -10759,55 +10797,55 @@
       <c r="JA81" s="5"/>
       <c r="JB81" s="5"/>
     </row>
-    <row r="82" spans="1:262" ht="23.25" customHeight="1">
+    <row r="82" spans="1:262" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="5"/>
       <c r="B82" s="5"/>
-      <c r="C82" s="160"/>
-      <c r="D82" s="158"/>
-      <c r="E82" s="158"/>
-      <c r="F82" s="158"/>
-      <c r="G82" s="158"/>
-      <c r="H82" s="158"/>
-      <c r="I82" s="158"/>
-      <c r="J82" s="158"/>
-      <c r="K82" s="158"/>
-      <c r="L82" s="158"/>
-      <c r="M82" s="158"/>
-      <c r="N82" s="158"/>
-      <c r="O82" s="159"/>
-      <c r="P82" s="158" t="s">
+      <c r="C82" s="309"/>
+      <c r="D82" s="310"/>
+      <c r="E82" s="310"/>
+      <c r="F82" s="310"/>
+      <c r="G82" s="310"/>
+      <c r="H82" s="310"/>
+      <c r="I82" s="310"/>
+      <c r="J82" s="310"/>
+      <c r="K82" s="310"/>
+      <c r="L82" s="310"/>
+      <c r="M82" s="310"/>
+      <c r="N82" s="310"/>
+      <c r="O82" s="311"/>
+      <c r="P82" s="310" t="s">
         <v>103</v>
       </c>
-      <c r="Q82" s="158"/>
-      <c r="R82" s="158"/>
-      <c r="S82" s="158"/>
-      <c r="T82" s="158"/>
-      <c r="U82" s="166">
+      <c r="Q82" s="310"/>
+      <c r="R82" s="310"/>
+      <c r="S82" s="310"/>
+      <c r="T82" s="310"/>
+      <c r="U82" s="312">
         <v>0.45</v>
       </c>
-      <c r="V82" s="163"/>
-      <c r="W82" s="163"/>
-      <c r="X82" s="163"/>
-      <c r="Y82" s="163"/>
-      <c r="Z82" s="163"/>
-      <c r="AA82" s="163"/>
-      <c r="AB82" s="163"/>
-      <c r="AC82" s="163"/>
-      <c r="AD82" s="163"/>
-      <c r="AE82" s="163"/>
-      <c r="AF82" s="163"/>
-      <c r="AG82" s="163"/>
-      <c r="AH82" s="163"/>
-      <c r="AI82" s="169"/>
-      <c r="AJ82" s="170"/>
-      <c r="AK82" s="170"/>
-      <c r="AL82" s="170"/>
-      <c r="AM82" s="170"/>
-      <c r="AN82" s="170"/>
-      <c r="AO82" s="170"/>
-      <c r="AP82" s="170"/>
-      <c r="AQ82" s="170"/>
-      <c r="AR82" s="171"/>
+      <c r="V82" s="313"/>
+      <c r="W82" s="313"/>
+      <c r="X82" s="313"/>
+      <c r="Y82" s="313"/>
+      <c r="Z82" s="313"/>
+      <c r="AA82" s="313"/>
+      <c r="AB82" s="313"/>
+      <c r="AC82" s="313"/>
+      <c r="AD82" s="313"/>
+      <c r="AE82" s="313"/>
+      <c r="AF82" s="313"/>
+      <c r="AG82" s="313"/>
+      <c r="AH82" s="313"/>
+      <c r="AI82" s="318"/>
+      <c r="AJ82" s="319"/>
+      <c r="AK82" s="319"/>
+      <c r="AL82" s="319"/>
+      <c r="AM82" s="319"/>
+      <c r="AN82" s="319"/>
+      <c r="AO82" s="319"/>
+      <c r="AP82" s="319"/>
+      <c r="AQ82" s="319"/>
+      <c r="AR82" s="320"/>
       <c r="AS82" s="5"/>
       <c r="AT82" s="5"/>
       <c r="AU82" s="5"/>
@@ -11023,57 +11061,57 @@
       <c r="JA82" s="5"/>
       <c r="JB82" s="5"/>
     </row>
-    <row r="83" spans="1:262" ht="23.25" customHeight="1">
+    <row r="83" spans="1:262" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="5"/>
       <c r="B83" s="5"/>
-      <c r="C83" s="160" t="s">
+      <c r="C83" s="309" t="s">
         <v>104</v>
       </c>
-      <c r="D83" s="158"/>
-      <c r="E83" s="158"/>
-      <c r="F83" s="158"/>
-      <c r="G83" s="158"/>
-      <c r="H83" s="158"/>
-      <c r="I83" s="158"/>
-      <c r="J83" s="158"/>
-      <c r="K83" s="158"/>
-      <c r="L83" s="158"/>
-      <c r="M83" s="158"/>
-      <c r="N83" s="158"/>
-      <c r="O83" s="158"/>
-      <c r="P83" s="175" t="s">
+      <c r="D83" s="310"/>
+      <c r="E83" s="310"/>
+      <c r="F83" s="310"/>
+      <c r="G83" s="310"/>
+      <c r="H83" s="310"/>
+      <c r="I83" s="310"/>
+      <c r="J83" s="310"/>
+      <c r="K83" s="310"/>
+      <c r="L83" s="310"/>
+      <c r="M83" s="310"/>
+      <c r="N83" s="310"/>
+      <c r="O83" s="310"/>
+      <c r="P83" s="324" t="s">
         <v>101</v>
       </c>
-      <c r="Q83" s="175"/>
-      <c r="R83" s="175"/>
-      <c r="S83" s="175"/>
-      <c r="T83" s="176"/>
-      <c r="U83" s="152">
+      <c r="Q83" s="324"/>
+      <c r="R83" s="324"/>
+      <c r="S83" s="324"/>
+      <c r="T83" s="325"/>
+      <c r="U83" s="315">
         <v>0.45</v>
       </c>
-      <c r="V83" s="153"/>
-      <c r="W83" s="153"/>
-      <c r="X83" s="153"/>
-      <c r="Y83" s="153"/>
-      <c r="Z83" s="153"/>
-      <c r="AA83" s="154"/>
-      <c r="AB83" s="163"/>
-      <c r="AC83" s="163"/>
-      <c r="AD83" s="163"/>
-      <c r="AE83" s="163"/>
-      <c r="AF83" s="163"/>
-      <c r="AG83" s="163"/>
-      <c r="AH83" s="163"/>
-      <c r="AI83" s="169"/>
-      <c r="AJ83" s="170"/>
-      <c r="AK83" s="170"/>
-      <c r="AL83" s="170"/>
-      <c r="AM83" s="170"/>
-      <c r="AN83" s="170"/>
-      <c r="AO83" s="170"/>
-      <c r="AP83" s="170"/>
-      <c r="AQ83" s="170"/>
-      <c r="AR83" s="171"/>
+      <c r="V83" s="316"/>
+      <c r="W83" s="316"/>
+      <c r="X83" s="316"/>
+      <c r="Y83" s="316"/>
+      <c r="Z83" s="316"/>
+      <c r="AA83" s="327"/>
+      <c r="AB83" s="313"/>
+      <c r="AC83" s="313"/>
+      <c r="AD83" s="313"/>
+      <c r="AE83" s="313"/>
+      <c r="AF83" s="313"/>
+      <c r="AG83" s="313"/>
+      <c r="AH83" s="313"/>
+      <c r="AI83" s="318"/>
+      <c r="AJ83" s="319"/>
+      <c r="AK83" s="319"/>
+      <c r="AL83" s="319"/>
+      <c r="AM83" s="319"/>
+      <c r="AN83" s="319"/>
+      <c r="AO83" s="319"/>
+      <c r="AP83" s="319"/>
+      <c r="AQ83" s="319"/>
+      <c r="AR83" s="320"/>
       <c r="AS83" s="5"/>
       <c r="AT83" s="5"/>
       <c r="AU83" s="5"/>
@@ -11289,53 +11327,53 @@
       <c r="JA83" s="5"/>
       <c r="JB83" s="5"/>
     </row>
-    <row r="84" spans="1:262" ht="23.25" customHeight="1">
+    <row r="84" spans="1:262" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="5"/>
       <c r="B84" s="5"/>
-      <c r="C84" s="160"/>
-      <c r="D84" s="158"/>
-      <c r="E84" s="158"/>
-      <c r="F84" s="158"/>
-      <c r="G84" s="158"/>
-      <c r="H84" s="158"/>
-      <c r="I84" s="158"/>
-      <c r="J84" s="158"/>
-      <c r="K84" s="158"/>
-      <c r="L84" s="158"/>
-      <c r="M84" s="158"/>
-      <c r="N84" s="158"/>
-      <c r="O84" s="158"/>
-      <c r="P84" s="158" t="s">
+      <c r="C84" s="309"/>
+      <c r="D84" s="310"/>
+      <c r="E84" s="310"/>
+      <c r="F84" s="310"/>
+      <c r="G84" s="310"/>
+      <c r="H84" s="310"/>
+      <c r="I84" s="310"/>
+      <c r="J84" s="310"/>
+      <c r="K84" s="310"/>
+      <c r="L84" s="310"/>
+      <c r="M84" s="310"/>
+      <c r="N84" s="310"/>
+      <c r="O84" s="310"/>
+      <c r="P84" s="310" t="s">
         <v>103</v>
       </c>
-      <c r="Q84" s="158"/>
-      <c r="R84" s="158"/>
-      <c r="S84" s="158"/>
-      <c r="T84" s="159"/>
-      <c r="U84" s="155"/>
-      <c r="V84" s="156"/>
-      <c r="W84" s="156"/>
-      <c r="X84" s="156"/>
-      <c r="Y84" s="156"/>
-      <c r="Z84" s="156"/>
-      <c r="AA84" s="157"/>
-      <c r="AB84" s="163"/>
-      <c r="AC84" s="163"/>
-      <c r="AD84" s="163"/>
-      <c r="AE84" s="163"/>
-      <c r="AF84" s="163"/>
-      <c r="AG84" s="163"/>
-      <c r="AH84" s="163"/>
-      <c r="AI84" s="169"/>
-      <c r="AJ84" s="170"/>
-      <c r="AK84" s="170"/>
-      <c r="AL84" s="170"/>
-      <c r="AM84" s="170"/>
-      <c r="AN84" s="170"/>
-      <c r="AO84" s="170"/>
-      <c r="AP84" s="170"/>
-      <c r="AQ84" s="170"/>
-      <c r="AR84" s="171"/>
+      <c r="Q84" s="310"/>
+      <c r="R84" s="310"/>
+      <c r="S84" s="310"/>
+      <c r="T84" s="311"/>
+      <c r="U84" s="328"/>
+      <c r="V84" s="329"/>
+      <c r="W84" s="329"/>
+      <c r="X84" s="329"/>
+      <c r="Y84" s="329"/>
+      <c r="Z84" s="329"/>
+      <c r="AA84" s="330"/>
+      <c r="AB84" s="313"/>
+      <c r="AC84" s="313"/>
+      <c r="AD84" s="313"/>
+      <c r="AE84" s="313"/>
+      <c r="AF84" s="313"/>
+      <c r="AG84" s="313"/>
+      <c r="AH84" s="313"/>
+      <c r="AI84" s="318"/>
+      <c r="AJ84" s="319"/>
+      <c r="AK84" s="319"/>
+      <c r="AL84" s="319"/>
+      <c r="AM84" s="319"/>
+      <c r="AN84" s="319"/>
+      <c r="AO84" s="319"/>
+      <c r="AP84" s="319"/>
+      <c r="AQ84" s="319"/>
+      <c r="AR84" s="320"/>
       <c r="AS84" s="5"/>
       <c r="AT84" s="5"/>
       <c r="AU84" s="5"/>
@@ -11551,111 +11589,111 @@
       <c r="JA84" s="5"/>
       <c r="JB84" s="5"/>
     </row>
-    <row r="85" spans="1:262" ht="23.25" customHeight="1">
+    <row r="85" spans="1:262" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="5"/>
       <c r="B85" s="5"/>
-      <c r="C85" s="160" t="s">
+      <c r="C85" s="309" t="s">
         <v>105</v>
       </c>
-      <c r="D85" s="158"/>
-      <c r="E85" s="158"/>
-      <c r="F85" s="158"/>
-      <c r="G85" s="158"/>
-      <c r="H85" s="158"/>
-      <c r="I85" s="158"/>
-      <c r="J85" s="158"/>
-      <c r="K85" s="158"/>
-      <c r="L85" s="158"/>
-      <c r="M85" s="158"/>
-      <c r="N85" s="158"/>
-      <c r="O85" s="158"/>
-      <c r="P85" s="158" t="s">
+      <c r="D85" s="310"/>
+      <c r="E85" s="310"/>
+      <c r="F85" s="310"/>
+      <c r="G85" s="310"/>
+      <c r="H85" s="310"/>
+      <c r="I85" s="310"/>
+      <c r="J85" s="310"/>
+      <c r="K85" s="310"/>
+      <c r="L85" s="310"/>
+      <c r="M85" s="310"/>
+      <c r="N85" s="310"/>
+      <c r="O85" s="310"/>
+      <c r="P85" s="310" t="s">
         <v>101</v>
       </c>
-      <c r="Q85" s="158"/>
-      <c r="R85" s="158"/>
-      <c r="S85" s="158"/>
-      <c r="T85" s="159"/>
-      <c r="U85" s="163">
+      <c r="Q85" s="310"/>
+      <c r="R85" s="310"/>
+      <c r="S85" s="310"/>
+      <c r="T85" s="311"/>
+      <c r="U85" s="313">
         <v>0.75</v>
       </c>
-      <c r="V85" s="163"/>
-      <c r="W85" s="163"/>
-      <c r="X85" s="163"/>
-      <c r="Y85" s="163"/>
-      <c r="Z85" s="163"/>
-      <c r="AA85" s="163"/>
-      <c r="AB85" s="163" t="s">
+      <c r="V85" s="313"/>
+      <c r="W85" s="313"/>
+      <c r="X85" s="313"/>
+      <c r="Y85" s="313"/>
+      <c r="Z85" s="313"/>
+      <c r="AA85" s="313"/>
+      <c r="AB85" s="313" t="s">
         <v>106</v>
       </c>
-      <c r="AC85" s="163"/>
-      <c r="AD85" s="163"/>
-      <c r="AE85" s="163"/>
-      <c r="AF85" s="163"/>
-      <c r="AG85" s="163"/>
-      <c r="AH85" s="163"/>
-      <c r="AI85" s="169"/>
-      <c r="AJ85" s="170"/>
-      <c r="AK85" s="170"/>
-      <c r="AL85" s="170"/>
-      <c r="AM85" s="170"/>
-      <c r="AN85" s="170"/>
-      <c r="AO85" s="170"/>
-      <c r="AP85" s="170"/>
-      <c r="AQ85" s="170"/>
-      <c r="AR85" s="171"/>
+      <c r="AC85" s="313"/>
+      <c r="AD85" s="313"/>
+      <c r="AE85" s="313"/>
+      <c r="AF85" s="313"/>
+      <c r="AG85" s="313"/>
+      <c r="AH85" s="313"/>
+      <c r="AI85" s="318"/>
+      <c r="AJ85" s="319"/>
+      <c r="AK85" s="319"/>
+      <c r="AL85" s="319"/>
+      <c r="AM85" s="319"/>
+      <c r="AN85" s="319"/>
+      <c r="AO85" s="319"/>
+      <c r="AP85" s="319"/>
+      <c r="AQ85" s="319"/>
+      <c r="AR85" s="320"/>
       <c r="AS85" s="5"/>
       <c r="AT85" s="5"/>
     </row>
-    <row r="86" spans="1:262" ht="23.25" customHeight="1" thickBot="1">
-      <c r="C86" s="161"/>
-      <c r="D86" s="162"/>
-      <c r="E86" s="162"/>
-      <c r="F86" s="162"/>
-      <c r="G86" s="162"/>
-      <c r="H86" s="162"/>
-      <c r="I86" s="162"/>
-      <c r="J86" s="162"/>
-      <c r="K86" s="162"/>
-      <c r="L86" s="162"/>
-      <c r="M86" s="162"/>
-      <c r="N86" s="162"/>
-      <c r="O86" s="162"/>
-      <c r="P86" s="162" t="s">
+    <row r="86" spans="1:262" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C86" s="331"/>
+      <c r="D86" s="332"/>
+      <c r="E86" s="332"/>
+      <c r="F86" s="332"/>
+      <c r="G86" s="332"/>
+      <c r="H86" s="332"/>
+      <c r="I86" s="332"/>
+      <c r="J86" s="332"/>
+      <c r="K86" s="332"/>
+      <c r="L86" s="332"/>
+      <c r="M86" s="332"/>
+      <c r="N86" s="332"/>
+      <c r="O86" s="332"/>
+      <c r="P86" s="332" t="s">
         <v>103</v>
       </c>
-      <c r="Q86" s="162"/>
-      <c r="R86" s="162"/>
-      <c r="S86" s="162"/>
-      <c r="T86" s="165"/>
-      <c r="U86" s="164">
+      <c r="Q86" s="332"/>
+      <c r="R86" s="332"/>
+      <c r="S86" s="332"/>
+      <c r="T86" s="334"/>
+      <c r="U86" s="333">
         <v>0.6</v>
       </c>
-      <c r="V86" s="164"/>
-      <c r="W86" s="164"/>
-      <c r="X86" s="164"/>
-      <c r="Y86" s="164"/>
-      <c r="Z86" s="164"/>
-      <c r="AA86" s="164"/>
-      <c r="AB86" s="164"/>
-      <c r="AC86" s="164"/>
-      <c r="AD86" s="164"/>
-      <c r="AE86" s="164"/>
-      <c r="AF86" s="164"/>
-      <c r="AG86" s="164"/>
-      <c r="AH86" s="164"/>
-      <c r="AI86" s="172"/>
-      <c r="AJ86" s="173"/>
-      <c r="AK86" s="173"/>
-      <c r="AL86" s="173"/>
-      <c r="AM86" s="173"/>
-      <c r="AN86" s="173"/>
-      <c r="AO86" s="173"/>
-      <c r="AP86" s="173"/>
-      <c r="AQ86" s="173"/>
-      <c r="AR86" s="174"/>
+      <c r="V86" s="333"/>
+      <c r="W86" s="333"/>
+      <c r="X86" s="333"/>
+      <c r="Y86" s="333"/>
+      <c r="Z86" s="333"/>
+      <c r="AA86" s="333"/>
+      <c r="AB86" s="333"/>
+      <c r="AC86" s="333"/>
+      <c r="AD86" s="333"/>
+      <c r="AE86" s="333"/>
+      <c r="AF86" s="333"/>
+      <c r="AG86" s="333"/>
+      <c r="AH86" s="333"/>
+      <c r="AI86" s="321"/>
+      <c r="AJ86" s="322"/>
+      <c r="AK86" s="322"/>
+      <c r="AL86" s="322"/>
+      <c r="AM86" s="322"/>
+      <c r="AN86" s="322"/>
+      <c r="AO86" s="322"/>
+      <c r="AP86" s="322"/>
+      <c r="AQ86" s="322"/>
+      <c r="AR86" s="323"/>
     </row>
-    <row r="87" spans="1:262" ht="23.25" customHeight="1">
+    <row r="87" spans="1:262" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C87" s="148"/>
       <c r="D87" s="148"/>
       <c r="E87" s="148"/>
@@ -11699,84 +11737,193 @@
       <c r="AQ87" s="150"/>
       <c r="AR87" s="150"/>
     </row>
-    <row r="88" spans="1:262" ht="103.5" customHeight="1">
-      <c r="A88" s="151" t="s">
+    <row r="88" spans="1:262" ht="103.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="326" t="s">
         <v>162</v>
       </c>
-      <c r="B88" s="151"/>
-      <c r="C88" s="151"/>
-      <c r="D88" s="151"/>
-      <c r="E88" s="151"/>
-      <c r="F88" s="151"/>
-      <c r="G88" s="151"/>
-      <c r="H88" s="151"/>
-      <c r="I88" s="151"/>
-      <c r="J88" s="151"/>
-      <c r="K88" s="151"/>
-      <c r="L88" s="151"/>
-      <c r="M88" s="151"/>
-      <c r="N88" s="151"/>
-      <c r="O88" s="151"/>
-      <c r="P88" s="151"/>
-      <c r="Q88" s="151"/>
-      <c r="R88" s="151"/>
-      <c r="S88" s="151"/>
-      <c r="T88" s="151"/>
-      <c r="U88" s="151"/>
-      <c r="V88" s="151"/>
-      <c r="W88" s="151"/>
-      <c r="X88" s="151"/>
-      <c r="Y88" s="151"/>
-      <c r="Z88" s="151"/>
-      <c r="AA88" s="151"/>
-      <c r="AB88" s="151"/>
-      <c r="AC88" s="151"/>
-      <c r="AD88" s="151"/>
-      <c r="AE88" s="151"/>
-      <c r="AF88" s="151"/>
-      <c r="AG88" s="151"/>
-      <c r="AH88" s="151"/>
-      <c r="AI88" s="151"/>
-      <c r="AJ88" s="151"/>
-      <c r="AK88" s="151"/>
-      <c r="AL88" s="151"/>
-      <c r="AM88" s="151"/>
-      <c r="AN88" s="151"/>
-      <c r="AO88" s="151"/>
-      <c r="AP88" s="151"/>
-      <c r="AQ88" s="151"/>
-      <c r="AR88" s="151"/>
-      <c r="AS88" s="151"/>
-      <c r="AT88" s="151"/>
+      <c r="B88" s="326"/>
+      <c r="C88" s="326"/>
+      <c r="D88" s="326"/>
+      <c r="E88" s="326"/>
+      <c r="F88" s="326"/>
+      <c r="G88" s="326"/>
+      <c r="H88" s="326"/>
+      <c r="I88" s="326"/>
+      <c r="J88" s="326"/>
+      <c r="K88" s="326"/>
+      <c r="L88" s="326"/>
+      <c r="M88" s="326"/>
+      <c r="N88" s="326"/>
+      <c r="O88" s="326"/>
+      <c r="P88" s="326"/>
+      <c r="Q88" s="326"/>
+      <c r="R88" s="326"/>
+      <c r="S88" s="326"/>
+      <c r="T88" s="326"/>
+      <c r="U88" s="326"/>
+      <c r="V88" s="326"/>
+      <c r="W88" s="326"/>
+      <c r="X88" s="326"/>
+      <c r="Y88" s="326"/>
+      <c r="Z88" s="326"/>
+      <c r="AA88" s="326"/>
+      <c r="AB88" s="326"/>
+      <c r="AC88" s="326"/>
+      <c r="AD88" s="326"/>
+      <c r="AE88" s="326"/>
+      <c r="AF88" s="326"/>
+      <c r="AG88" s="326"/>
+      <c r="AH88" s="326"/>
+      <c r="AI88" s="326"/>
+      <c r="AJ88" s="326"/>
+      <c r="AK88" s="326"/>
+      <c r="AL88" s="326"/>
+      <c r="AM88" s="326"/>
+      <c r="AN88" s="326"/>
+      <c r="AO88" s="326"/>
+      <c r="AP88" s="326"/>
+      <c r="AQ88" s="326"/>
+      <c r="AR88" s="326"/>
+      <c r="AS88" s="326"/>
+      <c r="AT88" s="326"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="3hf+o31UQX3AtRQqUcV/RJd+3mfAaN5O7rXRVlKzh0JlAGpwVg9GgTEDb5nIDRpf5tJqbuQU2oD4kp3qAWPpmw==" saltValue="ZVxQSEzeTaLWm4syF5vRTg==" spinCount="100000" sheet="1" scenarios="1"/>
   <mergeCells count="182">
-    <mergeCell ref="AO1:AT1"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="AO2:AT2"/>
-    <mergeCell ref="A3:AT3"/>
-    <mergeCell ref="BE4:BG4"/>
-    <mergeCell ref="B5:I5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="M5:U5"/>
-    <mergeCell ref="V5:W5"/>
-    <mergeCell ref="Y5:AG5"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="J7:U7"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="Y7:AF7"/>
-    <mergeCell ref="AG7:AR7"/>
-    <mergeCell ref="AS7:AT7"/>
-    <mergeCell ref="AH5:AI5"/>
-    <mergeCell ref="AK5:AT5"/>
-    <mergeCell ref="AV5:BC5"/>
-    <mergeCell ref="B6:I6"/>
-    <mergeCell ref="J6:W6"/>
-    <mergeCell ref="Y6:AF6"/>
-    <mergeCell ref="AG6:AT6"/>
-    <mergeCell ref="AW6:AX6"/>
-    <mergeCell ref="AZ6:BC6"/>
+    <mergeCell ref="A88:AT88"/>
+    <mergeCell ref="U83:AA84"/>
+    <mergeCell ref="P84:T84"/>
+    <mergeCell ref="C85:O86"/>
+    <mergeCell ref="P85:T85"/>
+    <mergeCell ref="U85:AA85"/>
+    <mergeCell ref="AB85:AH86"/>
+    <mergeCell ref="P86:T86"/>
+    <mergeCell ref="U86:AA86"/>
+    <mergeCell ref="C81:O82"/>
+    <mergeCell ref="P81:T81"/>
+    <mergeCell ref="U81:AA81"/>
+    <mergeCell ref="AB81:AH84"/>
+    <mergeCell ref="AI81:AR86"/>
+    <mergeCell ref="P82:T82"/>
+    <mergeCell ref="U82:AA82"/>
+    <mergeCell ref="C83:O84"/>
+    <mergeCell ref="P83:T83"/>
+    <mergeCell ref="B76:AT76"/>
+    <mergeCell ref="C79:O80"/>
+    <mergeCell ref="P79:T80"/>
+    <mergeCell ref="U79:AH79"/>
+    <mergeCell ref="AI79:AR80"/>
+    <mergeCell ref="U80:AA80"/>
+    <mergeCell ref="AB80:AH80"/>
+    <mergeCell ref="B66:AT66"/>
+    <mergeCell ref="B67:AT67"/>
+    <mergeCell ref="B68:AT68"/>
+    <mergeCell ref="B69:AT69"/>
+    <mergeCell ref="B61:AT61"/>
+    <mergeCell ref="B63:AT63"/>
+    <mergeCell ref="B64:AT64"/>
+    <mergeCell ref="AK47:AR47"/>
+    <mergeCell ref="AK48:AR48"/>
+    <mergeCell ref="AK50:AR50"/>
+    <mergeCell ref="B56:AT56"/>
+    <mergeCell ref="B57:AT57"/>
+    <mergeCell ref="B58:AT58"/>
+    <mergeCell ref="B59:AT60"/>
+    <mergeCell ref="M46:T46"/>
+    <mergeCell ref="AK46:AR46"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="M47:T47"/>
+    <mergeCell ref="U47:V47"/>
+    <mergeCell ref="W47:X47"/>
+    <mergeCell ref="Y47:AF47"/>
+    <mergeCell ref="AG47:AH47"/>
+    <mergeCell ref="AI47:AJ47"/>
+    <mergeCell ref="X45:AG46"/>
+    <mergeCell ref="AI41:AJ42"/>
+    <mergeCell ref="AL41:AO42"/>
+    <mergeCell ref="AS41:AT42"/>
+    <mergeCell ref="M44:T44"/>
+    <mergeCell ref="Y44:AF44"/>
+    <mergeCell ref="AG44:AH44"/>
+    <mergeCell ref="B41:H42"/>
+    <mergeCell ref="I41:J42"/>
+    <mergeCell ref="K41:L42"/>
+    <mergeCell ref="M41:T42"/>
+    <mergeCell ref="U41:V42"/>
+    <mergeCell ref="W41:X42"/>
+    <mergeCell ref="AK36:AR36"/>
+    <mergeCell ref="AS36:AT36"/>
+    <mergeCell ref="AK37:AR37"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="Y40:AF40"/>
+    <mergeCell ref="AG40:AH40"/>
+    <mergeCell ref="AK40:AR40"/>
+    <mergeCell ref="M36:T36"/>
+    <mergeCell ref="U36:V36"/>
+    <mergeCell ref="W36:X36"/>
+    <mergeCell ref="Y36:AF36"/>
+    <mergeCell ref="AG36:AH36"/>
+    <mergeCell ref="AI36:AJ36"/>
+    <mergeCell ref="L39:U40"/>
+    <mergeCell ref="AK30:AR30"/>
+    <mergeCell ref="AS30:AT30"/>
+    <mergeCell ref="AZ34:BA34"/>
+    <mergeCell ref="M35:T35"/>
+    <mergeCell ref="Y35:AF35"/>
+    <mergeCell ref="AK35:AR35"/>
+    <mergeCell ref="BA35:BE35"/>
+    <mergeCell ref="AW28:AX28"/>
+    <mergeCell ref="M29:T29"/>
+    <mergeCell ref="X29:AH29"/>
+    <mergeCell ref="AK29:AR29"/>
+    <mergeCell ref="M30:T30"/>
+    <mergeCell ref="U30:V30"/>
+    <mergeCell ref="W30:X30"/>
+    <mergeCell ref="Y30:AF30"/>
+    <mergeCell ref="AG30:AH30"/>
+    <mergeCell ref="AI30:AJ30"/>
+    <mergeCell ref="AS24:AT25"/>
+    <mergeCell ref="M26:T26"/>
+    <mergeCell ref="Y26:AF26"/>
+    <mergeCell ref="M27:T27"/>
+    <mergeCell ref="U27:V27"/>
+    <mergeCell ref="Y27:AF27"/>
+    <mergeCell ref="AG27:AH27"/>
+    <mergeCell ref="B24:H25"/>
+    <mergeCell ref="I24:J25"/>
+    <mergeCell ref="K24:L25"/>
+    <mergeCell ref="W24:X25"/>
+    <mergeCell ref="AI24:AJ25"/>
+    <mergeCell ref="AK24:AR25"/>
+    <mergeCell ref="B23:H23"/>
+    <mergeCell ref="M23:T23"/>
+    <mergeCell ref="U23:V23"/>
+    <mergeCell ref="Y23:AF23"/>
+    <mergeCell ref="AG23:AH23"/>
+    <mergeCell ref="AK23:AR23"/>
+    <mergeCell ref="B19:AA19"/>
+    <mergeCell ref="AB19:AQ19"/>
+    <mergeCell ref="AR19:AS19"/>
+    <mergeCell ref="M22:T22"/>
+    <mergeCell ref="Y22:AF22"/>
+    <mergeCell ref="AK22:AR22"/>
+    <mergeCell ref="J17:AA17"/>
+    <mergeCell ref="AB17:AQ17"/>
+    <mergeCell ref="AR17:AS17"/>
+    <mergeCell ref="C18:I18"/>
+    <mergeCell ref="J18:AA18"/>
+    <mergeCell ref="AB18:AQ18"/>
+    <mergeCell ref="AR18:AS18"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="C14:I17"/>
+    <mergeCell ref="J14:AA14"/>
+    <mergeCell ref="AB14:AS14"/>
+    <mergeCell ref="J15:AA15"/>
+    <mergeCell ref="AB15:AQ15"/>
+    <mergeCell ref="AR15:AS15"/>
+    <mergeCell ref="J16:AA16"/>
+    <mergeCell ref="AB16:AQ16"/>
+    <mergeCell ref="AR16:AS16"/>
     <mergeCell ref="AK9:AN9"/>
     <mergeCell ref="AP9:AS9"/>
     <mergeCell ref="B10:I10"/>
@@ -11800,140 +11947,31 @@
     <mergeCell ref="R8:U8"/>
     <mergeCell ref="W8:Z8"/>
     <mergeCell ref="AB8:AE8"/>
-    <mergeCell ref="J17:AA17"/>
-    <mergeCell ref="AB17:AQ17"/>
-    <mergeCell ref="AR17:AS17"/>
-    <mergeCell ref="C18:I18"/>
-    <mergeCell ref="J18:AA18"/>
-    <mergeCell ref="AB18:AQ18"/>
-    <mergeCell ref="AR18:AS18"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="C14:I17"/>
-    <mergeCell ref="J14:AA14"/>
-    <mergeCell ref="AB14:AS14"/>
-    <mergeCell ref="J15:AA15"/>
-    <mergeCell ref="AB15:AQ15"/>
-    <mergeCell ref="AR15:AS15"/>
-    <mergeCell ref="J16:AA16"/>
-    <mergeCell ref="AB16:AQ16"/>
-    <mergeCell ref="AR16:AS16"/>
-    <mergeCell ref="B23:H23"/>
-    <mergeCell ref="M23:T23"/>
-    <mergeCell ref="U23:V23"/>
-    <mergeCell ref="Y23:AF23"/>
-    <mergeCell ref="AG23:AH23"/>
-    <mergeCell ref="AK23:AR23"/>
-    <mergeCell ref="B19:AA19"/>
-    <mergeCell ref="AB19:AQ19"/>
-    <mergeCell ref="AR19:AS19"/>
-    <mergeCell ref="M22:T22"/>
-    <mergeCell ref="Y22:AF22"/>
-    <mergeCell ref="AK22:AR22"/>
-    <mergeCell ref="AS24:AT25"/>
-    <mergeCell ref="M26:T26"/>
-    <mergeCell ref="Y26:AF26"/>
-    <mergeCell ref="M27:T27"/>
-    <mergeCell ref="U27:V27"/>
-    <mergeCell ref="Y27:AF27"/>
-    <mergeCell ref="AG27:AH27"/>
-    <mergeCell ref="B24:H25"/>
-    <mergeCell ref="I24:J25"/>
-    <mergeCell ref="K24:L25"/>
-    <mergeCell ref="W24:X25"/>
-    <mergeCell ref="AI24:AJ25"/>
-    <mergeCell ref="AK24:AR25"/>
-    <mergeCell ref="AK30:AR30"/>
-    <mergeCell ref="AS30:AT30"/>
-    <mergeCell ref="AZ34:BA34"/>
-    <mergeCell ref="M35:T35"/>
-    <mergeCell ref="Y35:AF35"/>
-    <mergeCell ref="AK35:AR35"/>
-    <mergeCell ref="BA35:BE35"/>
-    <mergeCell ref="AW28:AX28"/>
-    <mergeCell ref="M29:T29"/>
-    <mergeCell ref="X29:AH29"/>
-    <mergeCell ref="AK29:AR29"/>
-    <mergeCell ref="M30:T30"/>
-    <mergeCell ref="U30:V30"/>
-    <mergeCell ref="W30:X30"/>
-    <mergeCell ref="Y30:AF30"/>
-    <mergeCell ref="AG30:AH30"/>
-    <mergeCell ref="AI30:AJ30"/>
-    <mergeCell ref="AK36:AR36"/>
-    <mergeCell ref="AS36:AT36"/>
-    <mergeCell ref="AK37:AR37"/>
-    <mergeCell ref="B40:H40"/>
-    <mergeCell ref="Y40:AF40"/>
-    <mergeCell ref="AG40:AH40"/>
-    <mergeCell ref="AK40:AR40"/>
-    <mergeCell ref="M36:T36"/>
-    <mergeCell ref="U36:V36"/>
-    <mergeCell ref="W36:X36"/>
-    <mergeCell ref="Y36:AF36"/>
-    <mergeCell ref="AG36:AH36"/>
-    <mergeCell ref="AI36:AJ36"/>
-    <mergeCell ref="L39:U40"/>
-    <mergeCell ref="AI41:AJ42"/>
-    <mergeCell ref="AL41:AO42"/>
-    <mergeCell ref="AS41:AT42"/>
-    <mergeCell ref="M44:T44"/>
-    <mergeCell ref="Y44:AF44"/>
-    <mergeCell ref="AG44:AH44"/>
-    <mergeCell ref="B41:H42"/>
-    <mergeCell ref="I41:J42"/>
-    <mergeCell ref="K41:L42"/>
-    <mergeCell ref="M41:T42"/>
-    <mergeCell ref="U41:V42"/>
-    <mergeCell ref="W41:X42"/>
-    <mergeCell ref="M46:T46"/>
-    <mergeCell ref="AK46:AR46"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="M47:T47"/>
-    <mergeCell ref="U47:V47"/>
-    <mergeCell ref="W47:X47"/>
-    <mergeCell ref="Y47:AF47"/>
-    <mergeCell ref="AG47:AH47"/>
-    <mergeCell ref="AI47:AJ47"/>
-    <mergeCell ref="X45:AG46"/>
-    <mergeCell ref="B61:AT61"/>
-    <mergeCell ref="B63:AT63"/>
-    <mergeCell ref="B64:AT64"/>
-    <mergeCell ref="AK47:AR47"/>
-    <mergeCell ref="AK48:AR48"/>
-    <mergeCell ref="AK50:AR50"/>
-    <mergeCell ref="B56:AT56"/>
-    <mergeCell ref="B57:AT57"/>
-    <mergeCell ref="B58:AT58"/>
-    <mergeCell ref="B59:AT60"/>
-    <mergeCell ref="B76:AT76"/>
-    <mergeCell ref="C79:O80"/>
-    <mergeCell ref="P79:T80"/>
-    <mergeCell ref="U79:AH79"/>
-    <mergeCell ref="AI79:AR80"/>
-    <mergeCell ref="U80:AA80"/>
-    <mergeCell ref="AB80:AH80"/>
-    <mergeCell ref="B66:AT66"/>
-    <mergeCell ref="B67:AT67"/>
-    <mergeCell ref="B68:AT68"/>
-    <mergeCell ref="B69:AT69"/>
-    <mergeCell ref="C81:O82"/>
-    <mergeCell ref="P81:T81"/>
-    <mergeCell ref="U81:AA81"/>
-    <mergeCell ref="AB81:AH84"/>
-    <mergeCell ref="AI81:AR86"/>
-    <mergeCell ref="P82:T82"/>
-    <mergeCell ref="U82:AA82"/>
-    <mergeCell ref="C83:O84"/>
-    <mergeCell ref="P83:T83"/>
-    <mergeCell ref="A88:AT88"/>
-    <mergeCell ref="U83:AA84"/>
-    <mergeCell ref="P84:T84"/>
-    <mergeCell ref="C85:O86"/>
-    <mergeCell ref="P85:T85"/>
-    <mergeCell ref="U85:AA85"/>
-    <mergeCell ref="AB85:AH86"/>
-    <mergeCell ref="P86:T86"/>
-    <mergeCell ref="U86:AA86"/>
+    <mergeCell ref="B7:I7"/>
+    <mergeCell ref="J7:U7"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="Y7:AF7"/>
+    <mergeCell ref="AG7:AR7"/>
+    <mergeCell ref="AS7:AT7"/>
+    <mergeCell ref="AH5:AI5"/>
+    <mergeCell ref="AK5:AT5"/>
+    <mergeCell ref="AV5:BC5"/>
+    <mergeCell ref="B6:I6"/>
+    <mergeCell ref="J6:W6"/>
+    <mergeCell ref="Y6:AF6"/>
+    <mergeCell ref="AG6:AT6"/>
+    <mergeCell ref="AW6:AX6"/>
+    <mergeCell ref="AZ6:BC6"/>
+    <mergeCell ref="AO1:AT1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="AO2:AT2"/>
+    <mergeCell ref="A3:AT3"/>
+    <mergeCell ref="BE4:BG4"/>
+    <mergeCell ref="B5:I5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="M5:U5"/>
+    <mergeCell ref="V5:W5"/>
+    <mergeCell ref="Y5:AG5"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="4">
@@ -12038,15 +12076,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="263dbbe5-076b-4606-a03b-9598f5f2f35a" xsi:nil="true"/>
@@ -12062,6 +12091,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12286,14 +12324,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31F2529B-DA47-47B2-9E29-6A6C8AE8452E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70DCB08F-36BD-4CC4-A1F7-88A1F6838D51}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -12306,6 +12336,14 @@
     <ds:schemaRef ds:uri="263dbbe5-076b-4606-a03b-9598f5f2f35a"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31F2529B-DA47-47B2-9E29-6A6C8AE8452E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
